--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$154</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$95</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$Q$99</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
@@ -501,7 +501,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129037221</v>
+        <v>129073665</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -516,10 +516,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45530</v>
+        <v>45531</v>
       </c>
       <c r="G2" s="1">
-        <v>45531</v>
+        <v>45533</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129041305</v>
+        <v>129076638</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -569,10 +569,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="G3" s="1">
-        <v>45530</v>
+        <v>45533</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129042376</v>
+        <v>129077394</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -622,10 +622,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="G4" s="1">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129044304</v>
+        <v>129078223</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,10 +675,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="G5" s="1">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>129046372</v>
+        <v>129090288</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -728,10 +728,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45530</v>
+        <v>45532</v>
       </c>
       <c r="G6" s="1">
-        <v>45530</v>
+        <v>45533</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>128749254</v>
+        <v>129090326</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -781,10 +781,10 @@
         <v>1211</v>
       </c>
       <c r="F7" s="1">
-        <v>45510</v>
+        <v>45532</v>
       </c>
       <c r="G7" s="1">
-        <v>45511</v>
+        <v>45532</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>129078587</v>
+        <v>129092580</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -837,7 +837,7 @@
         <v>45532</v>
       </c>
       <c r="G8" s="1">
-        <v>45533</v>
+        <v>45532</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -846,7 +846,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>129084428</v>
+        <v>129094904</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -887,10 +887,10 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G9" s="1">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -899,7 +899,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>129087682</v>
+        <v>129095400</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -940,7 +940,7 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G10" s="1">
         <v>45533</v>
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>125323047</v>
+        <v>129098829</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -990,13 +990,13 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G11" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1005,7 +1005,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>125336581</v>
+        <v>129100907</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1043,13 +1043,13 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F12" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G12" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1058,7 +1058,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125748458</v>
+        <v>129104872</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1099,10 +1099,10 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G13" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1111,7 +1111,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K13" t="s">
         <v>17</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>125788540</v>
+        <v>129104974</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,10 +1152,10 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G14" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1164,7 +1164,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>125795675</v>
+        <v>129110087</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1205,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G15" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1217,7 +1217,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>125939917</v>
+        <v>129111468</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1258,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G16" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1270,7 +1270,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K16" t="s">
         <v>17</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>125963226</v>
+        <v>129113921</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1308,13 +1308,13 @@
         <v>17</v>
       </c>
       <c r="E17">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F17" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G17" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1323,7 +1323,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K17" t="s">
         <v>17</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>126002915</v>
+        <v>129114173</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1364,10 +1364,10 @@
         <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G18" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1376,7 +1376,7 @@
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K18" t="s">
         <v>17</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>126005833</v>
+        <v>128749254</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1417,10 +1417,10 @@
         <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45532</v>
+        <v>45510</v>
       </c>
       <c r="G19" s="1">
-        <v>45532</v>
+        <v>45511</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1429,7 +1429,7 @@
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K19" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126046187</v>
+        <v>125190369</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1470,10 +1470,10 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G20" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>126105066</v>
+        <v>125306024</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1523,10 +1523,10 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G21" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>126105283</v>
+        <v>125348042</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1576,10 +1576,10 @@
         <v>1211</v>
       </c>
       <c r="F22" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G22" s="1">
-        <v>45532</v>
+        <v>45535</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>126225374</v>
+        <v>125383222</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1629,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G23" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>126267159</v>
+        <v>125404274</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1682,10 +1682,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G24" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>126484317</v>
+        <v>125417011</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,10 +1735,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G25" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>126511289</v>
+        <v>125509500</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1788,10 +1788,10 @@
         <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G26" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>126657404</v>
+        <v>125528046</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1841,7 +1841,7 @@
         <v>1211</v>
       </c>
       <c r="F27" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G27" s="1">
         <v>45533</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>126773768</v>
+        <v>125531574</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1894,7 +1894,7 @@
         <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45531</v>
+        <v>45533</v>
       </c>
       <c r="G28" s="1">
         <v>45533</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>126823459</v>
+        <v>125545369</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1947,10 +1947,10 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G29" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>126849610</v>
+        <v>125561893</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -1997,13 +1997,13 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G30" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127063602</v>
+        <v>125648343</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2053,10 +2053,10 @@
         <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G31" s="1">
-        <v>45532</v>
+        <v>45536</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>127141360</v>
+        <v>125763110</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2106,10 +2106,10 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G32" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127186176</v>
+        <v>125978049</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2159,10 +2159,10 @@
         <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G33" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127266757</v>
+        <v>125985496</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2212,10 +2212,10 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G34" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127283885</v>
+        <v>126045174</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2265,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G35" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127501603</v>
+        <v>126129410</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2318,10 +2318,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G36" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127568638</v>
+        <v>126131058</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2371,7 +2371,7 @@
         <v>1211</v>
       </c>
       <c r="F37" s="1">
-        <v>45531</v>
+        <v>45533</v>
       </c>
       <c r="G37" s="1">
         <v>45533</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127660045</v>
+        <v>126216502</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,10 +2424,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G38" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127730997</v>
+        <v>126218119</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2480,7 +2480,7 @@
         <v>45532</v>
       </c>
       <c r="G39" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>127733711</v>
+        <v>126290886</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2530,10 +2530,10 @@
         <v>1211</v>
       </c>
       <c r="F40" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G40" s="1">
-        <v>45532</v>
+        <v>45535</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>127746083</v>
+        <v>126405941</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2583,10 +2583,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G41" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>128136378</v>
+        <v>126470240</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2636,10 +2636,10 @@
         <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45531</v>
+        <v>45533</v>
       </c>
       <c r="G42" s="1">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>128169873</v>
+        <v>126527958</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,10 +2689,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G43" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>128172661</v>
+        <v>126631412</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2739,13 +2739,13 @@
         <v>17</v>
       </c>
       <c r="E44">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G44" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>128201960</v>
+        <v>126757605</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,10 +2795,10 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G45" s="1">
-        <v>45532</v>
+        <v>45535</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>128204245</v>
+        <v>126850646</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2848,10 +2848,10 @@
         <v>1211</v>
       </c>
       <c r="F46" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G46" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>128231160</v>
+        <v>126895799</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2901,10 +2901,10 @@
         <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G47" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>128376431</v>
+        <v>127094696</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2954,10 +2954,10 @@
         <v>1211</v>
       </c>
       <c r="F48" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G48" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>128398584</v>
+        <v>127156449</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3007,10 +3007,10 @@
         <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G49" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>128460155</v>
+        <v>127234900</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3060,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G50" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>128487134</v>
+        <v>127238211</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3113,10 +3113,10 @@
         <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G51" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>128541398</v>
+        <v>127273076</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3163,13 +3163,13 @@
         <v>17</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F52" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G52" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>128587732</v>
+        <v>127296354</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3219,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45532</v>
+        <v>45524</v>
       </c>
       <c r="G53" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>128732606</v>
+        <v>127299238</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3272,10 +3272,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G54" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>128941683</v>
+        <v>127441213</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3325,10 +3325,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G55" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>128980223</v>
+        <v>127495566</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3378,10 +3378,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G56" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>128986378</v>
+        <v>127587204</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3428,13 +3428,13 @@
         <v>17</v>
       </c>
       <c r="E57">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45525</v>
+        <v>45533</v>
       </c>
       <c r="G57" s="1">
-        <v>45525</v>
+        <v>45533</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>128986914</v>
+        <v>127613629</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3484,10 +3484,10 @@
         <v>1211</v>
       </c>
       <c r="F58" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="G58" s="1">
-        <v>45532</v>
+        <v>45535</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>129011512</v>
+        <v>127622355</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3537,10 +3537,10 @@
         <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G59" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129047465</v>
+        <v>127623395</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3590,10 +3590,10 @@
         <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G60" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>129049419</v>
+        <v>127645450</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3643,10 +3643,10 @@
         <v>1211</v>
       </c>
       <c r="F61" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="G61" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>129054678</v>
+        <v>127668769</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3696,10 +3696,10 @@
         <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G62" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129055159</v>
+        <v>127707875</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3749,10 +3749,10 @@
         <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G63" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129056537</v>
+        <v>127738579</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3802,10 +3802,10 @@
         <v>1211</v>
       </c>
       <c r="F64" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G64" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129058899</v>
+        <v>127846713</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3855,10 +3855,10 @@
         <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G65" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129077922</v>
+        <v>127917144</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3908,10 +3908,10 @@
         <v>1211</v>
       </c>
       <c r="F66" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="G66" s="1">
-        <v>45532</v>
+        <v>45536</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129078026</v>
+        <v>127987226</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3961,10 +3961,10 @@
         <v>1211</v>
       </c>
       <c r="F67" s="1">
-        <v>45532</v>
+        <v>45530</v>
       </c>
       <c r="G67" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129078074</v>
+        <v>128002204</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4014,10 +4014,10 @@
         <v>1211</v>
       </c>
       <c r="F68" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G68" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129078296</v>
+        <v>128137765</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4064,13 +4064,13 @@
         <v>17</v>
       </c>
       <c r="E69">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F69" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G69" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129081188</v>
+        <v>128269176</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4117,13 +4117,13 @@
         <v>17</v>
       </c>
       <c r="E70">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F70" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G70" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129083772</v>
+        <v>128385040</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4173,10 +4173,10 @@
         <v>1211</v>
       </c>
       <c r="F71" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G71" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129084335</v>
+        <v>128385207</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4223,13 +4223,13 @@
         <v>17</v>
       </c>
       <c r="E72">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F72" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G72" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129084413</v>
+        <v>128397444</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4279,10 +4279,10 @@
         <v>1211</v>
       </c>
       <c r="F73" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G73" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129084415</v>
+        <v>128437081</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4332,10 +4332,10 @@
         <v>1211</v>
       </c>
       <c r="F74" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="G74" s="1">
-        <v>45532</v>
+        <v>45535</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129084505</v>
+        <v>128591702</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4385,10 +4385,10 @@
         <v>1211</v>
       </c>
       <c r="F75" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="G75" s="1">
-        <v>45532</v>
+        <v>45535</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129084514</v>
+        <v>128791921</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4435,13 +4435,13 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="1">
         <v>45532</v>
       </c>
       <c r="G76" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129084731</v>
+        <v>128793491</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4488,13 +4488,13 @@
         <v>17</v>
       </c>
       <c r="E77">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F77" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G77" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129084848</v>
+        <v>128848462</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4544,10 +4544,10 @@
         <v>1211</v>
       </c>
       <c r="F78" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G78" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129085510</v>
+        <v>128855874</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4594,13 +4594,13 @@
         <v>17</v>
       </c>
       <c r="E79">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F79" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G79" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129085616</v>
+        <v>128870616</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4650,10 +4650,10 @@
         <v>1211</v>
       </c>
       <c r="F80" s="1">
-        <v>45532</v>
+        <v>45531</v>
       </c>
       <c r="G80" s="1">
-        <v>45532</v>
+        <v>45534</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129085655</v>
+        <v>128883435</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4703,10 +4703,10 @@
         <v>1211</v>
       </c>
       <c r="F81" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G81" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129085754</v>
+        <v>128956006</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4753,13 +4753,13 @@
         <v>17</v>
       </c>
       <c r="E82">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F82" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G82" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129085901</v>
+        <v>128986378</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4806,13 +4806,13 @@
         <v>17</v>
       </c>
       <c r="E83">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F83" s="1">
-        <v>45532</v>
+        <v>45525</v>
       </c>
       <c r="G83" s="1">
-        <v>45532</v>
+        <v>45525</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129086091</v>
+        <v>128989005</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4859,13 +4859,13 @@
         <v>17</v>
       </c>
       <c r="E84">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F84" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G84" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129086687</v>
+        <v>128993225</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4912,13 +4912,13 @@
         <v>17</v>
       </c>
       <c r="E85">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F85" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G85" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129086803</v>
+        <v>129000915</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4968,10 +4968,10 @@
         <v>1211</v>
       </c>
       <c r="F86" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G86" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129086982</v>
+        <v>129046466</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5018,13 +5018,13 @@
         <v>17</v>
       </c>
       <c r="E87">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F87" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G87" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -5059,7 +5059,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>128749254</v>
+        <v>129058643</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5074,10 +5074,10 @@
         <v>1211</v>
       </c>
       <c r="F88" s="1">
-        <v>45510</v>
+        <v>45533</v>
       </c>
       <c r="G88" s="1">
-        <v>45511</v>
+        <v>45533</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -5086,7 +5086,7 @@
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129039074</v>
+        <v>129067124</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5124,13 +5124,13 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F89" s="1">
-        <v>45530</v>
+        <v>45533</v>
       </c>
       <c r="G89" s="1">
-        <v>45531</v>
+        <v>45533</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -5139,7 +5139,7 @@
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129078587</v>
+        <v>129071243</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5180,7 +5180,7 @@
         <v>1211</v>
       </c>
       <c r="F90" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G90" s="1">
         <v>45533</v>
@@ -5192,7 +5192,7 @@
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129080488</v>
+        <v>129077136</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5230,10 +5230,10 @@
         <v>17</v>
       </c>
       <c r="E91">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F91" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G91" s="1">
         <v>45533</v>
@@ -5245,7 +5245,7 @@
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129084428</v>
+        <v>129078296</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5283,13 +5283,13 @@
         <v>17</v>
       </c>
       <c r="E92">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F92" s="1">
         <v>45532</v>
       </c>
       <c r="G92" s="1">
-        <v>45533</v>
+        <v>45532</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -5298,7 +5298,7 @@
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K92" t="s">
         <v>17</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129087682</v>
+        <v>129091959</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5339,7 +5339,7 @@
         <v>1211</v>
       </c>
       <c r="F93" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G93" s="1">
         <v>45533</v>
@@ -5351,7 +5351,7 @@
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K93" t="s">
         <v>17</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129087866</v>
+        <v>129092161</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5389,10 +5389,10 @@
         <v>17</v>
       </c>
       <c r="E94">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F94" s="1">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="G94" s="1">
         <v>45533</v>
@@ -5404,7 +5404,7 @@
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K94" t="s">
         <v>17</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>127839225</v>
+        <v>129092284</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5445,39 +5445,251 @@
         <v>1211</v>
       </c>
       <c r="F95" s="1">
+        <v>45533</v>
+      </c>
+      <c r="G95" s="1">
+        <v>45533</v>
+      </c>
+      <c r="H95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>129108332</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96">
+        <v>2013</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45533</v>
+      </c>
+      <c r="G96" s="1">
+        <v>45533</v>
+      </c>
+      <c r="H96" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8001</v>
+      </c>
+      <c r="K96" t="s">
+        <v>17</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>128749254</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97">
+        <v>1211</v>
+      </c>
+      <c r="F97" s="1">
+        <v>45510</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45511</v>
+      </c>
+      <c r="H97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8021</v>
+      </c>
+      <c r="K97" t="s">
+        <v>17</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>129039074</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98">
+        <v>2013</v>
+      </c>
+      <c r="F98" s="1">
         <v>45530</v>
       </c>
-      <c r="G95" s="1">
-        <v>45530</v>
-      </c>
-      <c r="H95" t="s">
-        <v>17</v>
-      </c>
-      <c r="I95">
-        <v>42</v>
-      </c>
-      <c r="J95">
-        <v>715</v>
-      </c>
-      <c r="K95" t="s">
-        <v>17</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
+      <c r="G98" s="1">
+        <v>45531</v>
+      </c>
+      <c r="H98" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8021</v>
+      </c>
+      <c r="K98" t="s">
+        <v>17</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>129110148</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99">
+        <v>2013</v>
+      </c>
+      <c r="F99" s="1">
+        <v>45533</v>
+      </c>
+      <c r="G99" s="1">
+        <v>45534</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8021</v>
+      </c>
+      <c r="K99" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$154</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$200</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$Q$134</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
@@ -501,7 +501,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129144369</v>
+        <v>129161310</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -516,10 +516,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45537</v>
+        <v>45538</v>
       </c>
       <c r="G2" s="1">
-        <v>45537</v>
+        <v>45538</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129146388</v>
+        <v>129174384</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -569,7 +569,7 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45537</v>
+        <v>45538</v>
       </c>
       <c r="G3" s="1">
         <v>45538</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129146680</v>
+        <v>129197378</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -619,13 +619,13 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="1">
-        <v>45537</v>
+        <v>45539</v>
       </c>
       <c r="G4" s="1">
-        <v>45537</v>
+        <v>45539</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129152234</v>
+        <v>129204849</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,10 +675,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45537</v>
+        <v>45540</v>
       </c>
       <c r="G5" s="1">
-        <v>45537</v>
+        <v>45541</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>129183457</v>
+        <v>129190578</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>129184178</v>
+        <v>125254042</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -834,7 +834,7 @@
         <v>1211</v>
       </c>
       <c r="F8" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G8" s="1">
         <v>45540</v>
@@ -846,7 +846,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>129190578</v>
+        <v>125533295</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -887,10 +887,10 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G9" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -899,7 +899,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>129197764</v>
+        <v>125596863</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -940,7 +940,7 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G10" s="1">
         <v>45540</v>
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>125260239</v>
+        <v>125634517</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -993,10 +993,10 @@
         <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G11" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>125313518</v>
+        <v>125768729</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1043,13 +1043,13 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G12" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125329502</v>
+        <v>125835456</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1099,7 +1099,7 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45538</v>
+        <v>45540</v>
       </c>
       <c r="G13" s="1">
         <v>45540</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>125436030</v>
+        <v>125886055</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,10 +1152,10 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G14" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>125478102</v>
+        <v>125955063</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1205,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G15" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>125529752</v>
+        <v>125987532</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1258,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G16" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>125573573</v>
+        <v>126046938</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1308,13 +1308,13 @@
         <v>17</v>
       </c>
       <c r="E17">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="1">
         <v>45539</v>
       </c>
       <c r="G17" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>125615219</v>
+        <v>126091843</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1364,10 +1364,10 @@
         <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G18" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>125630069</v>
+        <v>126109358</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1417,10 +1417,10 @@
         <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G19" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>125643998</v>
+        <v>126325895</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1470,10 +1470,10 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G20" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>125713635</v>
+        <v>126516782</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1523,10 +1523,10 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G21" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>125730549</v>
+        <v>126538522</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1576,10 +1576,10 @@
         <v>1211</v>
       </c>
       <c r="F22" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G22" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>125783604</v>
+        <v>126828631</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1629,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G23" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>125806957</v>
+        <v>126907961</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1682,10 +1682,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G24" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>125836682</v>
+        <v>126932850</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,10 +1735,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G25" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>125928099</v>
+        <v>127142518</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1788,10 +1788,10 @@
         <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="G26" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>125979271</v>
+        <v>127156313</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1841,10 +1841,10 @@
         <v>1211</v>
       </c>
       <c r="F27" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G27" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>126205330</v>
+        <v>127202712</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1894,10 +1894,10 @@
         <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G28" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>126236764</v>
+        <v>127228177</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1947,10 +1947,10 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G29" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>126248762</v>
+        <v>127382055</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -1997,10 +1997,10 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F30" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G30" s="1">
         <v>45540</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>126312726</v>
+        <v>127383497</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2053,7 +2053,7 @@
         <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45537</v>
+        <v>45540</v>
       </c>
       <c r="G31" s="1">
         <v>45540</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>126503756</v>
+        <v>127444797</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2106,10 +2106,10 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G32" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>126609356</v>
+        <v>127610835</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2159,10 +2159,10 @@
         <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G33" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>126645124</v>
+        <v>127688983</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2212,10 +2212,10 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G34" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>126799995</v>
+        <v>127725478</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2265,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G35" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>126867826</v>
+        <v>127725776</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2318,10 +2318,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G36" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>126935298</v>
+        <v>127737815</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2371,10 +2371,10 @@
         <v>1211</v>
       </c>
       <c r="F37" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G37" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>126972446</v>
+        <v>127747821</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,10 +2424,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G38" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127009436</v>
+        <v>127816501</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2477,10 +2477,10 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45539</v>
+        <v>45538</v>
       </c>
       <c r="G39" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>127073155</v>
+        <v>128042857</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2530,7 +2530,7 @@
         <v>1211</v>
       </c>
       <c r="F40" s="1">
-        <v>45537</v>
+        <v>45540</v>
       </c>
       <c r="G40" s="1">
         <v>45540</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>127096393</v>
+        <v>128067794</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2583,10 +2583,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G41" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>127151946</v>
+        <v>128209755</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2633,13 +2633,13 @@
         <v>17</v>
       </c>
       <c r="E42">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G42" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>127165724</v>
+        <v>128370345</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,7 +2689,7 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45537</v>
+        <v>45540</v>
       </c>
       <c r="G43" s="1">
         <v>45540</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>127168396</v>
+        <v>128474222</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2742,7 +2742,7 @@
         <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45538</v>
+        <v>45540</v>
       </c>
       <c r="G44" s="1">
         <v>45540</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>127286426</v>
+        <v>128479396</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,10 +2795,10 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G45" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>127293486</v>
+        <v>128543637</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2848,10 +2848,10 @@
         <v>1211</v>
       </c>
       <c r="F46" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G46" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>127374219</v>
+        <v>128616819</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2901,10 +2901,10 @@
         <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G47" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>127384841</v>
+        <v>128631722</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2954,10 +2954,10 @@
         <v>1211</v>
       </c>
       <c r="F48" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G48" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>127397837</v>
+        <v>128671509</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3010,7 +3010,7 @@
         <v>45539</v>
       </c>
       <c r="G49" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>127434514</v>
+        <v>128793088</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3060,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G50" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>127483685</v>
+        <v>128825377</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3113,7 +3113,7 @@
         <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G51" s="1">
         <v>45540</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>127543072</v>
+        <v>128838002</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3163,13 +3163,13 @@
         <v>17</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F52" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G52" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>127570475</v>
+        <v>128909042</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3219,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G53" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>127578524</v>
+        <v>128925561</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3272,10 +3272,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G54" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>127611022</v>
+        <v>128946421</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3328,7 +3328,7 @@
         <v>45539</v>
       </c>
       <c r="G55" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>127650683</v>
+        <v>128967377</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3378,10 +3378,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G56" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>127699086</v>
+        <v>128979031</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3428,13 +3428,13 @@
         <v>17</v>
       </c>
       <c r="E57">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G57" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>127731010</v>
+        <v>128982463</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3484,10 +3484,10 @@
         <v>1211</v>
       </c>
       <c r="F58" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G58" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>127836688</v>
+        <v>128992599</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3534,10 +3534,10 @@
         <v>17</v>
       </c>
       <c r="E59">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G59" s="1">
         <v>45540</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>127909751</v>
+        <v>129089119</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3590,10 +3590,10 @@
         <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G60" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>127914221</v>
+        <v>129095708</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3643,10 +3643,10 @@
         <v>1211</v>
       </c>
       <c r="F61" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G61" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>127930663</v>
+        <v>129103727</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3696,7 +3696,7 @@
         <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45538</v>
+        <v>45540</v>
       </c>
       <c r="G62" s="1">
         <v>45540</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>128224529</v>
+        <v>129115744</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3746,13 +3746,13 @@
         <v>17</v>
       </c>
       <c r="E63">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F63" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="G63" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>128227508</v>
+        <v>129132325</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3799,13 +3799,13 @@
         <v>17</v>
       </c>
       <c r="E64">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F64" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="G64" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>128271435</v>
+        <v>129146673</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3855,10 +3855,10 @@
         <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G65" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>128285838</v>
+        <v>129149508</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3908,10 +3908,10 @@
         <v>1211</v>
       </c>
       <c r="F66" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G66" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>128296657</v>
+        <v>129156811</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3961,7 +3961,7 @@
         <v>1211</v>
       </c>
       <c r="F67" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G67" s="1">
         <v>45540</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>128321458</v>
+        <v>129159884</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4014,7 +4014,7 @@
         <v>1211</v>
       </c>
       <c r="F68" s="1">
-        <v>45538</v>
+        <v>45540</v>
       </c>
       <c r="G68" s="1">
         <v>45540</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>128335245</v>
+        <v>129165865</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4067,7 +4067,7 @@
         <v>1211</v>
       </c>
       <c r="F69" s="1">
-        <v>45538</v>
+        <v>45540</v>
       </c>
       <c r="G69" s="1">
         <v>45540</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>128396610</v>
+        <v>129179833</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4120,10 +4120,10 @@
         <v>1211</v>
       </c>
       <c r="F70" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G70" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>128518629</v>
+        <v>129187945</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4170,13 +4170,13 @@
         <v>17</v>
       </c>
       <c r="E71">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F71" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="G71" s="1">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>128603291</v>
+        <v>129189044</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4226,10 +4226,10 @@
         <v>1211</v>
       </c>
       <c r="F72" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G72" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>128640847</v>
+        <v>129196697</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4279,10 +4279,10 @@
         <v>1211</v>
       </c>
       <c r="F73" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G73" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>128641975</v>
+        <v>128749254</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4332,10 +4332,10 @@
         <v>1211</v>
       </c>
       <c r="F74" s="1">
-        <v>45539</v>
+        <v>45510</v>
       </c>
       <c r="G74" s="1">
-        <v>45539</v>
+        <v>45511</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4344,7 +4344,7 @@
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K74" t="s">
         <v>17</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>128723827</v>
+        <v>129039074</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4382,13 +4382,13 @@
         <v>17</v>
       </c>
       <c r="E75">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F75" s="1">
-        <v>45539</v>
+        <v>45530</v>
       </c>
       <c r="G75" s="1">
-        <v>45539</v>
+        <v>45531</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -4397,7 +4397,7 @@
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K75" t="s">
         <v>17</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>128731066</v>
+        <v>129110148</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4435,13 +4435,13 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F76" s="1">
-        <v>45539</v>
+        <v>45533</v>
       </c>
       <c r="G76" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -4450,7 +4450,7 @@
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K76" t="s">
         <v>17</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>128792377</v>
+        <v>129190578</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4494,7 +4494,7 @@
         <v>45539</v>
       </c>
       <c r="G77" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4503,7 +4503,7 @@
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K77" t="s">
         <v>17</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>128811448</v>
+        <v>129179334</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4541,7 +4541,7 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F78" s="1">
         <v>45539</v>
@@ -4556,7 +4556,7 @@
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K78" t="s">
         <v>17</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>128849598</v>
+        <v>129179349</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4594,7 +4594,7 @@
         <v>17</v>
       </c>
       <c r="E79">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F79" s="1">
         <v>45539</v>
@@ -4609,7 +4609,7 @@
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K79" t="s">
         <v>17</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>128969191</v>
+        <v>129179397</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4647,13 +4647,13 @@
         <v>17</v>
       </c>
       <c r="E80">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F80" s="1">
-        <v>45538</v>
+        <v>45539</v>
       </c>
       <c r="G80" s="1">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4662,7 +4662,7 @@
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K80" t="s">
         <v>17</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>128979141</v>
+        <v>129179761</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4700,7 +4700,7 @@
         <v>17</v>
       </c>
       <c r="E81">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F81" s="1">
         <v>45539</v>
@@ -4715,7 +4715,7 @@
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K81" t="s">
         <v>17</v>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>128984444</v>
+        <v>129180333</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4753,7 +4753,7 @@
         <v>17</v>
       </c>
       <c r="E82">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F82" s="1">
         <v>45539</v>
@@ -4768,7 +4768,7 @@
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K82" t="s">
         <v>17</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129002649</v>
+        <v>129180387</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4806,13 +4806,13 @@
         <v>17</v>
       </c>
       <c r="E83">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F83" s="1">
         <v>45539</v>
       </c>
       <c r="G83" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -4821,7 +4821,7 @@
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K83" t="s">
         <v>17</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129031948</v>
+        <v>129183426</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4859,7 +4859,7 @@
         <v>17</v>
       </c>
       <c r="E84">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F84" s="1">
         <v>45539</v>
@@ -4874,7 +4874,7 @@
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K84" t="s">
         <v>17</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129032217</v>
+        <v>129183678</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4912,7 +4912,7 @@
         <v>17</v>
       </c>
       <c r="E85">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F85" s="1">
         <v>45539</v>
@@ -4927,7 +4927,7 @@
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K85" t="s">
         <v>17</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129063628</v>
+        <v>129184973</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4965,7 +4965,7 @@
         <v>17</v>
       </c>
       <c r="E86">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F86" s="1">
         <v>45539</v>
@@ -4980,7 +4980,7 @@
         <v>42</v>
       </c>
       <c r="J86">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K86" t="s">
         <v>17</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129078926</v>
+        <v>129185154</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5018,7 +5018,7 @@
         <v>17</v>
       </c>
       <c r="E87">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F87" s="1">
         <v>45539</v>
@@ -5033,7 +5033,7 @@
         <v>42</v>
       </c>
       <c r="J87">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K87" t="s">
         <v>17</v>
@@ -5059,7 +5059,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>129105243</v>
+        <v>129187787</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5071,7 +5071,7 @@
         <v>17</v>
       </c>
       <c r="E88">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F88" s="1">
         <v>45539</v>
@@ -5086,7 +5086,7 @@
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129106668</v>
+        <v>129189710</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5124,7 +5124,7 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F89" s="1">
         <v>45539</v>
@@ -5139,7 +5139,7 @@
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129115744</v>
+        <v>129189976</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5177,13 +5177,13 @@
         <v>17</v>
       </c>
       <c r="E90">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F90" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="G90" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -5192,7 +5192,7 @@
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129116466</v>
+        <v>129190253</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5230,13 +5230,13 @@
         <v>17</v>
       </c>
       <c r="E91">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F91" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="G91" s="1">
-        <v>45540</v>
+        <v>45539</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -5245,7 +5245,7 @@
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129126708</v>
+        <v>129190296</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5283,7 +5283,7 @@
         <v>17</v>
       </c>
       <c r="E92">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F92" s="1">
         <v>45539</v>
@@ -5298,7 +5298,7 @@
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K92" t="s">
         <v>17</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129131635</v>
+        <v>129190796</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5336,13 +5336,13 @@
         <v>17</v>
       </c>
       <c r="E93">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F93" s="1">
         <v>45539</v>
       </c>
       <c r="G93" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5351,7 +5351,7 @@
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K93" t="s">
         <v>17</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129132316</v>
+        <v>129190818</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5389,7 +5389,7 @@
         <v>17</v>
       </c>
       <c r="E94">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F94" s="1">
         <v>45539</v>
@@ -5404,7 +5404,7 @@
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K94" t="s">
         <v>17</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129132325</v>
+        <v>129190852</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5442,13 +5442,13 @@
         <v>17</v>
       </c>
       <c r="E95">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F95" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="G95" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -5457,7 +5457,7 @@
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K95" t="s">
         <v>17</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>129132376</v>
+        <v>129191186</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -5495,7 +5495,7 @@
         <v>17</v>
       </c>
       <c r="E96">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F96" s="1">
         <v>45539</v>
@@ -5510,7 +5510,7 @@
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K96" t="s">
         <v>17</v>
@@ -5536,7 +5536,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>129142820</v>
+        <v>129191714</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -5548,7 +5548,7 @@
         <v>17</v>
       </c>
       <c r="E97">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F97" s="1">
         <v>45539</v>
@@ -5563,7 +5563,7 @@
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K97" t="s">
         <v>17</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>129147186</v>
+        <v>129192057</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -5601,7 +5601,7 @@
         <v>17</v>
       </c>
       <c r="E98">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F98" s="1">
         <v>45539</v>
@@ -5616,7 +5616,7 @@
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K98" t="s">
         <v>17</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>129147552</v>
+        <v>129192063</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -5654,7 +5654,7 @@
         <v>17</v>
       </c>
       <c r="E99">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F99" s="1">
         <v>45539</v>
@@ -5669,7 +5669,7 @@
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K99" t="s">
         <v>17</v>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>129154389</v>
+        <v>129192064</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -5707,7 +5707,7 @@
         <v>17</v>
       </c>
       <c r="E100">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F100" s="1">
         <v>45539</v>
@@ -5722,7 +5722,7 @@
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K100" t="s">
         <v>17</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>129166497</v>
+        <v>129192164</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -5760,7 +5760,7 @@
         <v>17</v>
       </c>
       <c r="E101">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F101" s="1">
         <v>45539</v>
@@ -5775,7 +5775,7 @@
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K101" t="s">
         <v>17</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>129170582</v>
+        <v>129192233</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -5813,7 +5813,7 @@
         <v>17</v>
       </c>
       <c r="E102">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F102" s="1">
         <v>45539</v>
@@ -5828,7 +5828,7 @@
         <v>42</v>
       </c>
       <c r="J102">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K102" t="s">
         <v>17</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>129171496</v>
+        <v>129192772</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -5866,13 +5866,13 @@
         <v>17</v>
       </c>
       <c r="E103">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F103" s="1">
         <v>45539</v>
       </c>
       <c r="G103" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -5881,7 +5881,7 @@
         <v>42</v>
       </c>
       <c r="J103">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K103" t="s">
         <v>17</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>129172752</v>
+        <v>129193922</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -5919,7 +5919,7 @@
         <v>17</v>
       </c>
       <c r="E104">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F104" s="1">
         <v>45539</v>
@@ -5934,7 +5934,7 @@
         <v>42</v>
       </c>
       <c r="J104">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K104" t="s">
         <v>17</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>129176816</v>
+        <v>129193928</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -5972,7 +5972,7 @@
         <v>17</v>
       </c>
       <c r="E105">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F105" s="1">
         <v>45539</v>
@@ -5987,7 +5987,7 @@
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K105" t="s">
         <v>17</v>
@@ -6013,7 +6013,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>129180913</v>
+        <v>129194213</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -6025,7 +6025,7 @@
         <v>17</v>
       </c>
       <c r="E106">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F106" s="1">
         <v>45539</v>
@@ -6040,7 +6040,7 @@
         <v>42</v>
       </c>
       <c r="J106">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K106" t="s">
         <v>17</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>129181089</v>
+        <v>129194444</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -6078,7 +6078,7 @@
         <v>17</v>
       </c>
       <c r="E107">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F107" s="1">
         <v>45539</v>
@@ -6093,7 +6093,7 @@
         <v>42</v>
       </c>
       <c r="J107">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K107" t="s">
         <v>17</v>
@@ -6119,7 +6119,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>129181171</v>
+        <v>129194538</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -6131,7 +6131,7 @@
         <v>17</v>
       </c>
       <c r="E108">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F108" s="1">
         <v>45539</v>
@@ -6146,7 +6146,7 @@
         <v>42</v>
       </c>
       <c r="J108">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K108" t="s">
         <v>17</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>129181197</v>
+        <v>129194704</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -6184,13 +6184,13 @@
         <v>17</v>
       </c>
       <c r="E109">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F109" s="1">
         <v>45539</v>
       </c>
       <c r="G109" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -6199,7 +6199,7 @@
         <v>42</v>
       </c>
       <c r="J109">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K109" t="s">
         <v>17</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>129181240</v>
+        <v>129195637</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -6237,7 +6237,7 @@
         <v>17</v>
       </c>
       <c r="E110">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F110" s="1">
         <v>45539</v>
@@ -6252,7 +6252,7 @@
         <v>42</v>
       </c>
       <c r="J110">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K110" t="s">
         <v>17</v>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>129181325</v>
+        <v>129196396</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
@@ -6290,7 +6290,7 @@
         <v>17</v>
       </c>
       <c r="E111">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F111" s="1">
         <v>45539</v>
@@ -6305,7 +6305,7 @@
         <v>42</v>
       </c>
       <c r="J111">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K111" t="s">
         <v>17</v>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>129181767</v>
+        <v>129197616</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -6343,13 +6343,13 @@
         <v>17</v>
       </c>
       <c r="E112">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F112" s="1">
         <v>45539</v>
       </c>
       <c r="G112" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -6358,7 +6358,7 @@
         <v>42</v>
       </c>
       <c r="J112">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K112" t="s">
         <v>17</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>129182883</v>
+        <v>129197736</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -6396,13 +6396,13 @@
         <v>17</v>
       </c>
       <c r="E113">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F113" s="1">
         <v>45539</v>
       </c>
       <c r="G113" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -6411,7 +6411,7 @@
         <v>42</v>
       </c>
       <c r="J113">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K113" t="s">
         <v>17</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>129183563</v>
+        <v>129184712</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -6449,7 +6449,7 @@
         <v>17</v>
       </c>
       <c r="E114">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F114" s="1">
         <v>45539</v>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>129183573</v>
+        <v>129188459</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
@@ -6502,7 +6502,7 @@
         <v>17</v>
       </c>
       <c r="E115">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F115" s="1">
         <v>45539</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>129185171</v>
+        <v>129189014</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
@@ -6555,7 +6555,7 @@
         <v>17</v>
       </c>
       <c r="E116">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F116" s="1">
         <v>45539</v>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>129185875</v>
+        <v>129194716</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
@@ -6608,7 +6608,7 @@
         <v>17</v>
       </c>
       <c r="E117">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F117" s="1">
         <v>45539</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>129185884</v>
+        <v>129195399</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
@@ -6661,7 +6661,7 @@
         <v>17</v>
       </c>
       <c r="E118">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F118" s="1">
         <v>45539</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>129186514</v>
+        <v>129195730</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
@@ -6714,7 +6714,7 @@
         <v>17</v>
       </c>
       <c r="E119">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F119" s="1">
         <v>45539</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>129187345</v>
+        <v>129179574</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
@@ -6767,7 +6767,7 @@
         <v>17</v>
       </c>
       <c r="E120">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F120" s="1">
         <v>45539</v>
@@ -6782,7 +6782,7 @@
         <v>42</v>
       </c>
       <c r="J120">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K120" t="s">
         <v>17</v>
@@ -6808,7 +6808,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>129187945</v>
+        <v>129180407</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
@@ -6820,7 +6820,7 @@
         <v>17</v>
       </c>
       <c r="E121">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F121" s="1">
         <v>45539</v>
@@ -6835,7 +6835,7 @@
         <v>42</v>
       </c>
       <c r="J121">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K121" t="s">
         <v>17</v>
@@ -6861,7 +6861,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>129190908</v>
+        <v>129181177</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
@@ -6873,7 +6873,7 @@
         <v>17</v>
       </c>
       <c r="E122">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F122" s="1">
         <v>45539</v>
@@ -6888,7 +6888,7 @@
         <v>42</v>
       </c>
       <c r="J122">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K122" t="s">
         <v>17</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>129190927</v>
+        <v>129181429</v>
       </c>
       <c r="B123" t="s">
         <v>17</v>
@@ -6926,7 +6926,7 @@
         <v>17</v>
       </c>
       <c r="E123">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F123" s="1">
         <v>45539</v>
@@ -6941,7 +6941,7 @@
         <v>42</v>
       </c>
       <c r="J123">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K123" t="s">
         <v>17</v>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>129193597</v>
+        <v>129181437</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -6979,7 +6979,7 @@
         <v>17</v>
       </c>
       <c r="E124">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F124" s="1">
         <v>45539</v>
@@ -6994,7 +6994,7 @@
         <v>42</v>
       </c>
       <c r="J124">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K124" t="s">
         <v>17</v>
@@ -7020,7 +7020,7 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>129193836</v>
+        <v>129183636</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -7032,7 +7032,7 @@
         <v>17</v>
       </c>
       <c r="E125">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F125" s="1">
         <v>45539</v>
@@ -7047,7 +7047,7 @@
         <v>42</v>
       </c>
       <c r="J125">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K125" t="s">
         <v>17</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>129194346</v>
+        <v>129183728</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
@@ -7085,7 +7085,7 @@
         <v>17</v>
       </c>
       <c r="E126">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F126" s="1">
         <v>45539</v>
@@ -7100,7 +7100,7 @@
         <v>42</v>
       </c>
       <c r="J126">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K126" t="s">
         <v>17</v>
@@ -7126,7 +7126,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>129194818</v>
+        <v>129184232</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
@@ -7138,7 +7138,7 @@
         <v>17</v>
       </c>
       <c r="E127">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F127" s="1">
         <v>45539</v>
@@ -7153,7 +7153,7 @@
         <v>42</v>
       </c>
       <c r="J127">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K127" t="s">
         <v>17</v>
@@ -7179,7 +7179,7 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>129194857</v>
+        <v>129184999</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
@@ -7191,7 +7191,7 @@
         <v>17</v>
       </c>
       <c r="E128">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F128" s="1">
         <v>45539</v>
@@ -7206,7 +7206,7 @@
         <v>42</v>
       </c>
       <c r="J128">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K128" t="s">
         <v>17</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>129195873</v>
+        <v>129187748</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
@@ -7244,7 +7244,7 @@
         <v>17</v>
       </c>
       <c r="E129">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F129" s="1">
         <v>45539</v>
@@ -7259,7 +7259,7 @@
         <v>42</v>
       </c>
       <c r="J129">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K129" t="s">
         <v>17</v>
@@ -7285,7 +7285,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>129195908</v>
+        <v>129188795</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
@@ -7297,7 +7297,7 @@
         <v>17</v>
       </c>
       <c r="E130">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F130" s="1">
         <v>45539</v>
@@ -7312,7 +7312,7 @@
         <v>42</v>
       </c>
       <c r="J130">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K130" t="s">
         <v>17</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>129195938</v>
+        <v>129191947</v>
       </c>
       <c r="B131" t="s">
         <v>17</v>
@@ -7350,7 +7350,7 @@
         <v>17</v>
       </c>
       <c r="E131">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F131" s="1">
         <v>45539</v>
@@ -7365,7 +7365,7 @@
         <v>42</v>
       </c>
       <c r="J131">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K131" t="s">
         <v>17</v>
@@ -7391,7 +7391,7 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>129196117</v>
+        <v>129193649</v>
       </c>
       <c r="B132" t="s">
         <v>17</v>
@@ -7403,7 +7403,7 @@
         <v>17</v>
       </c>
       <c r="E132">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F132" s="1">
         <v>45539</v>
@@ -7418,7 +7418,7 @@
         <v>42</v>
       </c>
       <c r="J132">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K132" t="s">
         <v>17</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>129197631</v>
+        <v>129196347</v>
       </c>
       <c r="B133" t="s">
         <v>17</v>
@@ -7456,7 +7456,7 @@
         <v>17</v>
       </c>
       <c r="E133">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F133" s="1">
         <v>45539</v>
@@ -7471,7 +7471,7 @@
         <v>42</v>
       </c>
       <c r="J133">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K133" t="s">
         <v>17</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>129198404</v>
+        <v>129198198</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
@@ -7509,7 +7509,7 @@
         <v>17</v>
       </c>
       <c r="E134">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F134" s="1">
         <v>45539</v>
@@ -7524,7 +7524,7 @@
         <v>42</v>
       </c>
       <c r="J134">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K134" t="s">
         <v>17</v>
@@ -7545,3504 +7545,6 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>129198452</v>
-      </c>
-      <c r="B135" t="s">
-        <v>17</v>
-      </c>
-      <c r="C135" t="s">
-        <v>17</v>
-      </c>
-      <c r="D135" t="s">
-        <v>17</v>
-      </c>
-      <c r="E135">
-        <v>1211</v>
-      </c>
-      <c r="F135" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G135" s="1">
-        <v>45539</v>
-      </c>
-      <c r="H135" t="s">
-        <v>17</v>
-      </c>
-      <c r="I135">
-        <v>42</v>
-      </c>
-      <c r="J135">
-        <v>8001</v>
-      </c>
-      <c r="K135" t="s">
-        <v>17</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>128749254</v>
-      </c>
-      <c r="B136" t="s">
-        <v>17</v>
-      </c>
-      <c r="C136" t="s">
-        <v>17</v>
-      </c>
-      <c r="D136" t="s">
-        <v>17</v>
-      </c>
-      <c r="E136">
-        <v>1211</v>
-      </c>
-      <c r="F136" s="1">
-        <v>45510</v>
-      </c>
-      <c r="G136" s="1">
-        <v>45511</v>
-      </c>
-      <c r="H136" t="s">
-        <v>17</v>
-      </c>
-      <c r="I136">
-        <v>42</v>
-      </c>
-      <c r="J136">
-        <v>8021</v>
-      </c>
-      <c r="K136" t="s">
-        <v>17</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>129039074</v>
-      </c>
-      <c r="B137" t="s">
-        <v>17</v>
-      </c>
-      <c r="C137" t="s">
-        <v>17</v>
-      </c>
-      <c r="D137" t="s">
-        <v>17</v>
-      </c>
-      <c r="E137">
-        <v>2013</v>
-      </c>
-      <c r="F137" s="1">
-        <v>45530</v>
-      </c>
-      <c r="G137" s="1">
-        <v>45531</v>
-      </c>
-      <c r="H137" t="s">
-        <v>17</v>
-      </c>
-      <c r="I137">
-        <v>42</v>
-      </c>
-      <c r="J137">
-        <v>8021</v>
-      </c>
-      <c r="K137" t="s">
-        <v>17</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>129110148</v>
-      </c>
-      <c r="B138" t="s">
-        <v>17</v>
-      </c>
-      <c r="C138" t="s">
-        <v>17</v>
-      </c>
-      <c r="D138" t="s">
-        <v>17</v>
-      </c>
-      <c r="E138">
-        <v>2013</v>
-      </c>
-      <c r="F138" s="1">
-        <v>45533</v>
-      </c>
-      <c r="G138" s="1">
-        <v>45534</v>
-      </c>
-      <c r="H138" t="s">
-        <v>17</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
-        <v>8021</v>
-      </c>
-      <c r="K138" t="s">
-        <v>17</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>129183457</v>
-      </c>
-      <c r="B139" t="s">
-        <v>17</v>
-      </c>
-      <c r="C139" t="s">
-        <v>17</v>
-      </c>
-      <c r="D139" t="s">
-        <v>17</v>
-      </c>
-      <c r="E139">
-        <v>1211</v>
-      </c>
-      <c r="F139" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G139" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H139" t="s">
-        <v>17</v>
-      </c>
-      <c r="I139">
-        <v>42</v>
-      </c>
-      <c r="J139">
-        <v>8021</v>
-      </c>
-      <c r="K139" t="s">
-        <v>17</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>129184178</v>
-      </c>
-      <c r="B140" t="s">
-        <v>17</v>
-      </c>
-      <c r="C140" t="s">
-        <v>17</v>
-      </c>
-      <c r="D140" t="s">
-        <v>17</v>
-      </c>
-      <c r="E140">
-        <v>1211</v>
-      </c>
-      <c r="F140" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G140" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H140" t="s">
-        <v>17</v>
-      </c>
-      <c r="I140">
-        <v>42</v>
-      </c>
-      <c r="J140">
-        <v>8021</v>
-      </c>
-      <c r="K140" t="s">
-        <v>17</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>129184248</v>
-      </c>
-      <c r="B141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C141" t="s">
-        <v>17</v>
-      </c>
-      <c r="D141" t="s">
-        <v>17</v>
-      </c>
-      <c r="E141">
-        <v>2013</v>
-      </c>
-      <c r="F141" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G141" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H141" t="s">
-        <v>17</v>
-      </c>
-      <c r="I141">
-        <v>42</v>
-      </c>
-      <c r="J141">
-        <v>8021</v>
-      </c>
-      <c r="K141" t="s">
-        <v>17</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>129190578</v>
-      </c>
-      <c r="B142" t="s">
-        <v>17</v>
-      </c>
-      <c r="C142" t="s">
-        <v>17</v>
-      </c>
-      <c r="D142" t="s">
-        <v>17</v>
-      </c>
-      <c r="E142">
-        <v>1211</v>
-      </c>
-      <c r="F142" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G142" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H142" t="s">
-        <v>17</v>
-      </c>
-      <c r="I142">
-        <v>42</v>
-      </c>
-      <c r="J142">
-        <v>8021</v>
-      </c>
-      <c r="K142" t="s">
-        <v>17</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>129192911</v>
-      </c>
-      <c r="B143" t="s">
-        <v>17</v>
-      </c>
-      <c r="C143" t="s">
-        <v>17</v>
-      </c>
-      <c r="D143" t="s">
-        <v>17</v>
-      </c>
-      <c r="E143">
-        <v>2013</v>
-      </c>
-      <c r="F143" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G143" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H143" t="s">
-        <v>17</v>
-      </c>
-      <c r="I143">
-        <v>42</v>
-      </c>
-      <c r="J143">
-        <v>8021</v>
-      </c>
-      <c r="K143" t="s">
-        <v>17</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>129197764</v>
-      </c>
-      <c r="B144" t="s">
-        <v>17</v>
-      </c>
-      <c r="C144" t="s">
-        <v>17</v>
-      </c>
-      <c r="D144" t="s">
-        <v>17</v>
-      </c>
-      <c r="E144">
-        <v>1211</v>
-      </c>
-      <c r="F144" s="1">
-        <v>45539</v>
-      </c>
-      <c r="G144" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H144" t="s">
-        <v>17</v>
-      </c>
-      <c r="I144">
-        <v>42</v>
-      </c>
-      <c r="J144">
-        <v>8021</v>
-      </c>
-      <c r="K144" t="s">
-        <v>17</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>129158770</v>
-      </c>
-      <c r="B145" t="s">
-        <v>17</v>
-      </c>
-      <c r="C145" t="s">
-        <v>17</v>
-      </c>
-      <c r="D145" t="s">
-        <v>17</v>
-      </c>
-      <c r="E145">
-        <v>601</v>
-      </c>
-      <c r="F145" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G145" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H145" t="s">
-        <v>17</v>
-      </c>
-      <c r="I145">
-        <v>42</v>
-      </c>
-      <c r="J145">
-        <v>8013</v>
-      </c>
-      <c r="K145" t="s">
-        <v>17</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>129158773</v>
-      </c>
-      <c r="B146" t="s">
-        <v>17</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>17</v>
-      </c>
-      <c r="E146">
-        <v>601</v>
-      </c>
-      <c r="F146" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G146" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H146" t="s">
-        <v>17</v>
-      </c>
-      <c r="I146">
-        <v>42</v>
-      </c>
-      <c r="J146">
-        <v>8004</v>
-      </c>
-      <c r="K146" t="s">
-        <v>17</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>129158885</v>
-      </c>
-      <c r="B147" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" t="s">
-        <v>17</v>
-      </c>
-      <c r="D147" t="s">
-        <v>17</v>
-      </c>
-      <c r="E147">
-        <v>601</v>
-      </c>
-      <c r="F147" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G147" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H147" t="s">
-        <v>17</v>
-      </c>
-      <c r="I147">
-        <v>42</v>
-      </c>
-      <c r="J147">
-        <v>8013</v>
-      </c>
-      <c r="K147" t="s">
-        <v>17</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>129158929</v>
-      </c>
-      <c r="B148" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" t="s">
-        <v>17</v>
-      </c>
-      <c r="E148">
-        <v>601</v>
-      </c>
-      <c r="F148" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G148" s="1">
-        <v>45540</v>
-      </c>
-      <c r="H148" t="s">
-        <v>17</v>
-      </c>
-      <c r="I148">
-        <v>42</v>
-      </c>
-      <c r="J148">
-        <v>8013</v>
-      </c>
-      <c r="K148" t="s">
-        <v>17</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>129159038</v>
-      </c>
-      <c r="B149" t="s">
-        <v>17</v>
-      </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" t="s">
-        <v>17</v>
-      </c>
-      <c r="E149">
-        <v>601</v>
-      </c>
-      <c r="F149" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G149" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H149" t="s">
-        <v>17</v>
-      </c>
-      <c r="I149">
-        <v>42</v>
-      </c>
-      <c r="J149">
-        <v>8004</v>
-      </c>
-      <c r="K149" t="s">
-        <v>17</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>129159195</v>
-      </c>
-      <c r="B150" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" t="s">
-        <v>17</v>
-      </c>
-      <c r="E150">
-        <v>601</v>
-      </c>
-      <c r="F150" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G150" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H150" t="s">
-        <v>17</v>
-      </c>
-      <c r="I150">
-        <v>42</v>
-      </c>
-      <c r="J150">
-        <v>8004</v>
-      </c>
-      <c r="K150" t="s">
-        <v>17</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150">
-        <v>0</v>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A151">
-        <v>129159597</v>
-      </c>
-      <c r="B151" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" t="s">
-        <v>17</v>
-      </c>
-      <c r="E151">
-        <v>601</v>
-      </c>
-      <c r="F151" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G151" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H151" t="s">
-        <v>17</v>
-      </c>
-      <c r="I151">
-        <v>42</v>
-      </c>
-      <c r="J151">
-        <v>8004</v>
-      </c>
-      <c r="K151" t="s">
-        <v>17</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151">
-        <v>0</v>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A152">
-        <v>129159600</v>
-      </c>
-      <c r="B152" t="s">
-        <v>17</v>
-      </c>
-      <c r="C152" t="s">
-        <v>17</v>
-      </c>
-      <c r="D152" t="s">
-        <v>17</v>
-      </c>
-      <c r="E152">
-        <v>601</v>
-      </c>
-      <c r="F152" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G152" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H152" t="s">
-        <v>17</v>
-      </c>
-      <c r="I152">
-        <v>42</v>
-      </c>
-      <c r="J152">
-        <v>8013</v>
-      </c>
-      <c r="K152" t="s">
-        <v>17</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
-        <v>0</v>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A153">
-        <v>129159696</v>
-      </c>
-      <c r="B153" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" t="s">
-        <v>17</v>
-      </c>
-      <c r="D153" t="s">
-        <v>17</v>
-      </c>
-      <c r="E153">
-        <v>601</v>
-      </c>
-      <c r="F153" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G153" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H153" t="s">
-        <v>17</v>
-      </c>
-      <c r="I153">
-        <v>42</v>
-      </c>
-      <c r="J153">
-        <v>8004</v>
-      </c>
-      <c r="K153" t="s">
-        <v>17</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
-        <v>0</v>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A154">
-        <v>129159724</v>
-      </c>
-      <c r="B154" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" t="s">
-        <v>17</v>
-      </c>
-      <c r="E154">
-        <v>601</v>
-      </c>
-      <c r="F154" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G154" s="1">
-        <v>45539</v>
-      </c>
-      <c r="H154" t="s">
-        <v>17</v>
-      </c>
-      <c r="I154">
-        <v>42</v>
-      </c>
-      <c r="J154">
-        <v>8013</v>
-      </c>
-      <c r="K154" t="s">
-        <v>17</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154">
-        <v>0</v>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A155">
-        <v>129160523</v>
-      </c>
-      <c r="B155" t="s">
-        <v>17</v>
-      </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>17</v>
-      </c>
-      <c r="E155">
-        <v>601</v>
-      </c>
-      <c r="F155" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G155" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H155" t="s">
-        <v>17</v>
-      </c>
-      <c r="I155">
-        <v>42</v>
-      </c>
-      <c r="J155">
-        <v>8004</v>
-      </c>
-      <c r="K155" t="s">
-        <v>17</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
-        <v>0</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
-        <v>0</v>
-      </c>
-      <c r="Q155">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A156">
-        <v>129160955</v>
-      </c>
-      <c r="B156" t="s">
-        <v>17</v>
-      </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" t="s">
-        <v>17</v>
-      </c>
-      <c r="E156">
-        <v>601</v>
-      </c>
-      <c r="F156" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G156" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H156" t="s">
-        <v>17</v>
-      </c>
-      <c r="I156">
-        <v>42</v>
-      </c>
-      <c r="J156">
-        <v>8004</v>
-      </c>
-      <c r="K156" t="s">
-        <v>17</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
-        <v>0</v>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>0</v>
-      </c>
-      <c r="P156">
-        <v>0</v>
-      </c>
-      <c r="Q156">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A157">
-        <v>129161458</v>
-      </c>
-      <c r="B157" t="s">
-        <v>17</v>
-      </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
-      <c r="D157" t="s">
-        <v>17</v>
-      </c>
-      <c r="E157">
-        <v>601</v>
-      </c>
-      <c r="F157" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G157" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H157" t="s">
-        <v>17</v>
-      </c>
-      <c r="I157">
-        <v>42</v>
-      </c>
-      <c r="J157">
-        <v>8004</v>
-      </c>
-      <c r="K157" t="s">
-        <v>17</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157">
-        <v>0</v>
-      </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
-      <c r="O157">
-        <v>0</v>
-      </c>
-      <c r="P157">
-        <v>0</v>
-      </c>
-      <c r="Q157">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A158">
-        <v>129161654</v>
-      </c>
-      <c r="B158" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" t="s">
-        <v>17</v>
-      </c>
-      <c r="D158" t="s">
-        <v>17</v>
-      </c>
-      <c r="E158">
-        <v>601</v>
-      </c>
-      <c r="F158" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G158" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H158" t="s">
-        <v>17</v>
-      </c>
-      <c r="I158">
-        <v>42</v>
-      </c>
-      <c r="J158">
-        <v>8004</v>
-      </c>
-      <c r="K158" t="s">
-        <v>17</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
-        <v>0</v>
-      </c>
-      <c r="N158">
-        <v>0</v>
-      </c>
-      <c r="O158">
-        <v>0</v>
-      </c>
-      <c r="P158">
-        <v>0</v>
-      </c>
-      <c r="Q158">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159">
-        <v>129162344</v>
-      </c>
-      <c r="B159" t="s">
-        <v>17</v>
-      </c>
-      <c r="C159" t="s">
-        <v>17</v>
-      </c>
-      <c r="D159" t="s">
-        <v>17</v>
-      </c>
-      <c r="E159">
-        <v>601</v>
-      </c>
-      <c r="F159" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G159" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H159" t="s">
-        <v>17</v>
-      </c>
-      <c r="I159">
-        <v>42</v>
-      </c>
-      <c r="J159">
-        <v>8013</v>
-      </c>
-      <c r="K159" t="s">
-        <v>17</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="M159">
-        <v>0</v>
-      </c>
-      <c r="N159">
-        <v>0</v>
-      </c>
-      <c r="O159">
-        <v>0</v>
-      </c>
-      <c r="P159">
-        <v>0</v>
-      </c>
-      <c r="Q159">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160">
-        <v>129162356</v>
-      </c>
-      <c r="B160" t="s">
-        <v>17</v>
-      </c>
-      <c r="C160" t="s">
-        <v>17</v>
-      </c>
-      <c r="D160" t="s">
-        <v>17</v>
-      </c>
-      <c r="E160">
-        <v>601</v>
-      </c>
-      <c r="F160" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G160" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H160" t="s">
-        <v>17</v>
-      </c>
-      <c r="I160">
-        <v>42</v>
-      </c>
-      <c r="J160">
-        <v>8013</v>
-      </c>
-      <c r="K160" t="s">
-        <v>17</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160">
-        <v>0</v>
-      </c>
-      <c r="N160">
-        <v>0</v>
-      </c>
-      <c r="O160">
-        <v>0</v>
-      </c>
-      <c r="P160">
-        <v>0</v>
-      </c>
-      <c r="Q160">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A161">
-        <v>129162898</v>
-      </c>
-      <c r="B161" t="s">
-        <v>17</v>
-      </c>
-      <c r="C161" t="s">
-        <v>17</v>
-      </c>
-      <c r="D161" t="s">
-        <v>17</v>
-      </c>
-      <c r="E161">
-        <v>601</v>
-      </c>
-      <c r="F161" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G161" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H161" t="s">
-        <v>17</v>
-      </c>
-      <c r="I161">
-        <v>42</v>
-      </c>
-      <c r="J161">
-        <v>8004</v>
-      </c>
-      <c r="K161" t="s">
-        <v>17</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161">
-        <v>0</v>
-      </c>
-      <c r="N161">
-        <v>0</v>
-      </c>
-      <c r="O161">
-        <v>0</v>
-      </c>
-      <c r="P161">
-        <v>0</v>
-      </c>
-      <c r="Q161">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>129163899</v>
-      </c>
-      <c r="B162" t="s">
-        <v>17</v>
-      </c>
-      <c r="C162" t="s">
-        <v>17</v>
-      </c>
-      <c r="D162" t="s">
-        <v>17</v>
-      </c>
-      <c r="E162">
-        <v>601</v>
-      </c>
-      <c r="F162" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G162" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H162" t="s">
-        <v>17</v>
-      </c>
-      <c r="I162">
-        <v>42</v>
-      </c>
-      <c r="J162">
-        <v>8004</v>
-      </c>
-      <c r="K162" t="s">
-        <v>17</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162">
-        <v>0</v>
-      </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
-      <c r="O162">
-        <v>0</v>
-      </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A163">
-        <v>129166875</v>
-      </c>
-      <c r="B163" t="s">
-        <v>17</v>
-      </c>
-      <c r="C163" t="s">
-        <v>17</v>
-      </c>
-      <c r="D163" t="s">
-        <v>17</v>
-      </c>
-      <c r="E163">
-        <v>601</v>
-      </c>
-      <c r="F163" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G163" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H163" t="s">
-        <v>17</v>
-      </c>
-      <c r="I163">
-        <v>42</v>
-      </c>
-      <c r="J163">
-        <v>8004</v>
-      </c>
-      <c r="K163" t="s">
-        <v>17</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="M163">
-        <v>0</v>
-      </c>
-      <c r="N163">
-        <v>0</v>
-      </c>
-      <c r="O163">
-        <v>0</v>
-      </c>
-      <c r="P163">
-        <v>0</v>
-      </c>
-      <c r="Q163">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>129168182</v>
-      </c>
-      <c r="B164" t="s">
-        <v>17</v>
-      </c>
-      <c r="C164" t="s">
-        <v>17</v>
-      </c>
-      <c r="D164" t="s">
-        <v>17</v>
-      </c>
-      <c r="E164">
-        <v>601</v>
-      </c>
-      <c r="F164" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G164" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H164" t="s">
-        <v>17</v>
-      </c>
-      <c r="I164">
-        <v>42</v>
-      </c>
-      <c r="J164">
-        <v>8004</v>
-      </c>
-      <c r="K164" t="s">
-        <v>17</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164">
-        <v>0</v>
-      </c>
-      <c r="N164">
-        <v>0</v>
-      </c>
-      <c r="O164">
-        <v>0</v>
-      </c>
-      <c r="P164">
-        <v>0</v>
-      </c>
-      <c r="Q164">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>129168201</v>
-      </c>
-      <c r="B165" t="s">
-        <v>17</v>
-      </c>
-      <c r="C165" t="s">
-        <v>17</v>
-      </c>
-      <c r="D165" t="s">
-        <v>17</v>
-      </c>
-      <c r="E165">
-        <v>601</v>
-      </c>
-      <c r="F165" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G165" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H165" t="s">
-        <v>17</v>
-      </c>
-      <c r="I165">
-        <v>42</v>
-      </c>
-      <c r="J165">
-        <v>8004</v>
-      </c>
-      <c r="K165" t="s">
-        <v>17</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="M165">
-        <v>0</v>
-      </c>
-      <c r="N165">
-        <v>0</v>
-      </c>
-      <c r="O165">
-        <v>0</v>
-      </c>
-      <c r="P165">
-        <v>0</v>
-      </c>
-      <c r="Q165">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>129168217</v>
-      </c>
-      <c r="B166" t="s">
-        <v>17</v>
-      </c>
-      <c r="C166" t="s">
-        <v>17</v>
-      </c>
-      <c r="D166" t="s">
-        <v>17</v>
-      </c>
-      <c r="E166">
-        <v>601</v>
-      </c>
-      <c r="F166" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G166" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H166" t="s">
-        <v>17</v>
-      </c>
-      <c r="I166">
-        <v>42</v>
-      </c>
-      <c r="J166">
-        <v>8004</v>
-      </c>
-      <c r="K166" t="s">
-        <v>17</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166">
-        <v>0</v>
-      </c>
-      <c r="N166">
-        <v>0</v>
-      </c>
-      <c r="O166">
-        <v>0</v>
-      </c>
-      <c r="P166">
-        <v>0</v>
-      </c>
-      <c r="Q166">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>129169318</v>
-      </c>
-      <c r="B167" t="s">
-        <v>17</v>
-      </c>
-      <c r="C167" t="s">
-        <v>17</v>
-      </c>
-      <c r="D167" t="s">
-        <v>17</v>
-      </c>
-      <c r="E167">
-        <v>601</v>
-      </c>
-      <c r="F167" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G167" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H167" t="s">
-        <v>17</v>
-      </c>
-      <c r="I167">
-        <v>42</v>
-      </c>
-      <c r="J167">
-        <v>8004</v>
-      </c>
-      <c r="K167" t="s">
-        <v>17</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167">
-        <v>0</v>
-      </c>
-      <c r="N167">
-        <v>0</v>
-      </c>
-      <c r="O167">
-        <v>0</v>
-      </c>
-      <c r="P167">
-        <v>0</v>
-      </c>
-      <c r="Q167">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A168">
-        <v>129169351</v>
-      </c>
-      <c r="B168" t="s">
-        <v>17</v>
-      </c>
-      <c r="C168" t="s">
-        <v>17</v>
-      </c>
-      <c r="D168" t="s">
-        <v>17</v>
-      </c>
-      <c r="E168">
-        <v>601</v>
-      </c>
-      <c r="F168" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G168" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H168" t="s">
-        <v>17</v>
-      </c>
-      <c r="I168">
-        <v>42</v>
-      </c>
-      <c r="J168">
-        <v>8004</v>
-      </c>
-      <c r="K168" t="s">
-        <v>17</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="M168">
-        <v>0</v>
-      </c>
-      <c r="N168">
-        <v>0</v>
-      </c>
-      <c r="O168">
-        <v>0</v>
-      </c>
-      <c r="P168">
-        <v>0</v>
-      </c>
-      <c r="Q168">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>129169472</v>
-      </c>
-      <c r="B169" t="s">
-        <v>17</v>
-      </c>
-      <c r="C169" t="s">
-        <v>17</v>
-      </c>
-      <c r="D169" t="s">
-        <v>17</v>
-      </c>
-      <c r="E169">
-        <v>601</v>
-      </c>
-      <c r="F169" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G169" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H169" t="s">
-        <v>17</v>
-      </c>
-      <c r="I169">
-        <v>42</v>
-      </c>
-      <c r="J169">
-        <v>8013</v>
-      </c>
-      <c r="K169" t="s">
-        <v>17</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="M169">
-        <v>0</v>
-      </c>
-      <c r="N169">
-        <v>0</v>
-      </c>
-      <c r="O169">
-        <v>0</v>
-      </c>
-      <c r="P169">
-        <v>0</v>
-      </c>
-      <c r="Q169">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>129169476</v>
-      </c>
-      <c r="B170" t="s">
-        <v>17</v>
-      </c>
-      <c r="C170" t="s">
-        <v>17</v>
-      </c>
-      <c r="D170" t="s">
-        <v>17</v>
-      </c>
-      <c r="E170">
-        <v>601</v>
-      </c>
-      <c r="F170" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G170" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H170" t="s">
-        <v>17</v>
-      </c>
-      <c r="I170">
-        <v>42</v>
-      </c>
-      <c r="J170">
-        <v>8013</v>
-      </c>
-      <c r="K170" t="s">
-        <v>17</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="M170">
-        <v>0</v>
-      </c>
-      <c r="N170">
-        <v>0</v>
-      </c>
-      <c r="O170">
-        <v>0</v>
-      </c>
-      <c r="P170">
-        <v>0</v>
-      </c>
-      <c r="Q170">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A171">
-        <v>129169478</v>
-      </c>
-      <c r="B171" t="s">
-        <v>17</v>
-      </c>
-      <c r="C171" t="s">
-        <v>17</v>
-      </c>
-      <c r="D171" t="s">
-        <v>17</v>
-      </c>
-      <c r="E171">
-        <v>601</v>
-      </c>
-      <c r="F171" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G171" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H171" t="s">
-        <v>17</v>
-      </c>
-      <c r="I171">
-        <v>42</v>
-      </c>
-      <c r="J171">
-        <v>8013</v>
-      </c>
-      <c r="K171" t="s">
-        <v>17</v>
-      </c>
-      <c r="L171">
-        <v>0</v>
-      </c>
-      <c r="M171">
-        <v>0</v>
-      </c>
-      <c r="N171">
-        <v>0</v>
-      </c>
-      <c r="O171">
-        <v>0</v>
-      </c>
-      <c r="P171">
-        <v>0</v>
-      </c>
-      <c r="Q171">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A172">
-        <v>129171407</v>
-      </c>
-      <c r="B172" t="s">
-        <v>17</v>
-      </c>
-      <c r="C172" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" t="s">
-        <v>17</v>
-      </c>
-      <c r="E172">
-        <v>601</v>
-      </c>
-      <c r="F172" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G172" s="1">
-        <v>45539</v>
-      </c>
-      <c r="H172" t="s">
-        <v>17</v>
-      </c>
-      <c r="I172">
-        <v>42</v>
-      </c>
-      <c r="J172">
-        <v>8013</v>
-      </c>
-      <c r="K172" t="s">
-        <v>17</v>
-      </c>
-      <c r="L172">
-        <v>0</v>
-      </c>
-      <c r="M172">
-        <v>0</v>
-      </c>
-      <c r="N172">
-        <v>0</v>
-      </c>
-      <c r="O172">
-        <v>0</v>
-      </c>
-      <c r="P172">
-        <v>0</v>
-      </c>
-      <c r="Q172">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A173">
-        <v>129171439</v>
-      </c>
-      <c r="B173" t="s">
-        <v>17</v>
-      </c>
-      <c r="C173" t="s">
-        <v>17</v>
-      </c>
-      <c r="D173" t="s">
-        <v>17</v>
-      </c>
-      <c r="E173">
-        <v>601</v>
-      </c>
-      <c r="F173" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G173" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H173" t="s">
-        <v>17</v>
-      </c>
-      <c r="I173">
-        <v>42</v>
-      </c>
-      <c r="J173">
-        <v>8013</v>
-      </c>
-      <c r="K173" t="s">
-        <v>17</v>
-      </c>
-      <c r="L173">
-        <v>0</v>
-      </c>
-      <c r="M173">
-        <v>0</v>
-      </c>
-      <c r="N173">
-        <v>0</v>
-      </c>
-      <c r="O173">
-        <v>0</v>
-      </c>
-      <c r="P173">
-        <v>0</v>
-      </c>
-      <c r="Q173">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A174">
-        <v>129172529</v>
-      </c>
-      <c r="B174" t="s">
-        <v>17</v>
-      </c>
-      <c r="C174" t="s">
-        <v>17</v>
-      </c>
-      <c r="D174" t="s">
-        <v>17</v>
-      </c>
-      <c r="E174">
-        <v>601</v>
-      </c>
-      <c r="F174" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G174" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H174" t="s">
-        <v>17</v>
-      </c>
-      <c r="I174">
-        <v>42</v>
-      </c>
-      <c r="J174">
-        <v>8004</v>
-      </c>
-      <c r="K174" t="s">
-        <v>17</v>
-      </c>
-      <c r="L174">
-        <v>0</v>
-      </c>
-      <c r="M174">
-        <v>0</v>
-      </c>
-      <c r="N174">
-        <v>0</v>
-      </c>
-      <c r="O174">
-        <v>0</v>
-      </c>
-      <c r="P174">
-        <v>0</v>
-      </c>
-      <c r="Q174">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A175">
-        <v>129173042</v>
-      </c>
-      <c r="B175" t="s">
-        <v>17</v>
-      </c>
-      <c r="C175" t="s">
-        <v>17</v>
-      </c>
-      <c r="D175" t="s">
-        <v>17</v>
-      </c>
-      <c r="E175">
-        <v>601</v>
-      </c>
-      <c r="F175" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G175" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H175" t="s">
-        <v>17</v>
-      </c>
-      <c r="I175">
-        <v>42</v>
-      </c>
-      <c r="J175">
-        <v>8004</v>
-      </c>
-      <c r="K175" t="s">
-        <v>17</v>
-      </c>
-      <c r="L175">
-        <v>0</v>
-      </c>
-      <c r="M175">
-        <v>0</v>
-      </c>
-      <c r="N175">
-        <v>0</v>
-      </c>
-      <c r="O175">
-        <v>0</v>
-      </c>
-      <c r="P175">
-        <v>0</v>
-      </c>
-      <c r="Q175">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A176">
-        <v>129173252</v>
-      </c>
-      <c r="B176" t="s">
-        <v>17</v>
-      </c>
-      <c r="C176" t="s">
-        <v>17</v>
-      </c>
-      <c r="D176" t="s">
-        <v>17</v>
-      </c>
-      <c r="E176">
-        <v>601</v>
-      </c>
-      <c r="F176" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G176" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H176" t="s">
-        <v>17</v>
-      </c>
-      <c r="I176">
-        <v>42</v>
-      </c>
-      <c r="J176">
-        <v>8004</v>
-      </c>
-      <c r="K176" t="s">
-        <v>17</v>
-      </c>
-      <c r="L176">
-        <v>0</v>
-      </c>
-      <c r="M176">
-        <v>0</v>
-      </c>
-      <c r="N176">
-        <v>0</v>
-      </c>
-      <c r="O176">
-        <v>0</v>
-      </c>
-      <c r="P176">
-        <v>0</v>
-      </c>
-      <c r="Q176">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A177">
-        <v>129173695</v>
-      </c>
-      <c r="B177" t="s">
-        <v>17</v>
-      </c>
-      <c r="C177" t="s">
-        <v>17</v>
-      </c>
-      <c r="D177" t="s">
-        <v>17</v>
-      </c>
-      <c r="E177">
-        <v>601</v>
-      </c>
-      <c r="F177" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G177" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H177" t="s">
-        <v>17</v>
-      </c>
-      <c r="I177">
-        <v>42</v>
-      </c>
-      <c r="J177">
-        <v>8004</v>
-      </c>
-      <c r="K177" t="s">
-        <v>17</v>
-      </c>
-      <c r="L177">
-        <v>0</v>
-      </c>
-      <c r="M177">
-        <v>0</v>
-      </c>
-      <c r="N177">
-        <v>0</v>
-      </c>
-      <c r="O177">
-        <v>0</v>
-      </c>
-      <c r="P177">
-        <v>0</v>
-      </c>
-      <c r="Q177">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A178">
-        <v>129174306</v>
-      </c>
-      <c r="B178" t="s">
-        <v>17</v>
-      </c>
-      <c r="C178" t="s">
-        <v>17</v>
-      </c>
-      <c r="D178" t="s">
-        <v>17</v>
-      </c>
-      <c r="E178">
-        <v>601</v>
-      </c>
-      <c r="F178" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G178" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H178" t="s">
-        <v>17</v>
-      </c>
-      <c r="I178">
-        <v>42</v>
-      </c>
-      <c r="J178">
-        <v>8013</v>
-      </c>
-      <c r="K178" t="s">
-        <v>17</v>
-      </c>
-      <c r="L178">
-        <v>0</v>
-      </c>
-      <c r="M178">
-        <v>0</v>
-      </c>
-      <c r="N178">
-        <v>0</v>
-      </c>
-      <c r="O178">
-        <v>0</v>
-      </c>
-      <c r="P178">
-        <v>0</v>
-      </c>
-      <c r="Q178">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A179">
-        <v>129174386</v>
-      </c>
-      <c r="B179" t="s">
-        <v>17</v>
-      </c>
-      <c r="C179" t="s">
-        <v>17</v>
-      </c>
-      <c r="D179" t="s">
-        <v>17</v>
-      </c>
-      <c r="E179">
-        <v>601</v>
-      </c>
-      <c r="F179" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G179" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H179" t="s">
-        <v>17</v>
-      </c>
-      <c r="I179">
-        <v>42</v>
-      </c>
-      <c r="J179">
-        <v>8004</v>
-      </c>
-      <c r="K179" t="s">
-        <v>17</v>
-      </c>
-      <c r="L179">
-        <v>0</v>
-      </c>
-      <c r="M179">
-        <v>0</v>
-      </c>
-      <c r="N179">
-        <v>0</v>
-      </c>
-      <c r="O179">
-        <v>0</v>
-      </c>
-      <c r="P179">
-        <v>0</v>
-      </c>
-      <c r="Q179">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A180">
-        <v>129174780</v>
-      </c>
-      <c r="B180" t="s">
-        <v>17</v>
-      </c>
-      <c r="C180" t="s">
-        <v>17</v>
-      </c>
-      <c r="D180" t="s">
-        <v>17</v>
-      </c>
-      <c r="E180">
-        <v>601</v>
-      </c>
-      <c r="F180" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G180" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H180" t="s">
-        <v>17</v>
-      </c>
-      <c r="I180">
-        <v>42</v>
-      </c>
-      <c r="J180">
-        <v>8004</v>
-      </c>
-      <c r="K180" t="s">
-        <v>17</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
-      <c r="M180">
-        <v>0</v>
-      </c>
-      <c r="N180">
-        <v>0</v>
-      </c>
-      <c r="O180">
-        <v>0</v>
-      </c>
-      <c r="P180">
-        <v>0</v>
-      </c>
-      <c r="Q180">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A181">
-        <v>129162488</v>
-      </c>
-      <c r="B181" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" t="s">
-        <v>17</v>
-      </c>
-      <c r="D181" t="s">
-        <v>17</v>
-      </c>
-      <c r="E181">
-        <v>601</v>
-      </c>
-      <c r="F181" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G181" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H181" t="s">
-        <v>17</v>
-      </c>
-      <c r="I181">
-        <v>42</v>
-      </c>
-      <c r="J181">
-        <v>8001</v>
-      </c>
-      <c r="K181" t="s">
-        <v>17</v>
-      </c>
-      <c r="L181">
-        <v>0</v>
-      </c>
-      <c r="M181">
-        <v>0</v>
-      </c>
-      <c r="N181">
-        <v>0</v>
-      </c>
-      <c r="O181">
-        <v>0</v>
-      </c>
-      <c r="P181">
-        <v>0</v>
-      </c>
-      <c r="Q181">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A182">
-        <v>129166204</v>
-      </c>
-      <c r="B182" t="s">
-        <v>17</v>
-      </c>
-      <c r="C182" t="s">
-        <v>17</v>
-      </c>
-      <c r="D182" t="s">
-        <v>17</v>
-      </c>
-      <c r="E182">
-        <v>601</v>
-      </c>
-      <c r="F182" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G182" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H182" t="s">
-        <v>17</v>
-      </c>
-      <c r="I182">
-        <v>42</v>
-      </c>
-      <c r="J182">
-        <v>8001</v>
-      </c>
-      <c r="K182" t="s">
-        <v>17</v>
-      </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-      <c r="M182">
-        <v>0</v>
-      </c>
-      <c r="N182">
-        <v>0</v>
-      </c>
-      <c r="O182">
-        <v>0</v>
-      </c>
-      <c r="P182">
-        <v>0</v>
-      </c>
-      <c r="Q182">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A183">
-        <v>129169251</v>
-      </c>
-      <c r="B183" t="s">
-        <v>17</v>
-      </c>
-      <c r="C183" t="s">
-        <v>17</v>
-      </c>
-      <c r="D183" t="s">
-        <v>17</v>
-      </c>
-      <c r="E183">
-        <v>601</v>
-      </c>
-      <c r="F183" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G183" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H183" t="s">
-        <v>17</v>
-      </c>
-      <c r="I183">
-        <v>42</v>
-      </c>
-      <c r="J183">
-        <v>8001</v>
-      </c>
-      <c r="K183" t="s">
-        <v>17</v>
-      </c>
-      <c r="L183">
-        <v>0</v>
-      </c>
-      <c r="M183">
-        <v>0</v>
-      </c>
-      <c r="N183">
-        <v>0</v>
-      </c>
-      <c r="O183">
-        <v>0</v>
-      </c>
-      <c r="P183">
-        <v>0</v>
-      </c>
-      <c r="Q183">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A184">
-        <v>129028097</v>
-      </c>
-      <c r="B184" t="s">
-        <v>17</v>
-      </c>
-      <c r="C184" t="s">
-        <v>17</v>
-      </c>
-      <c r="D184" t="s">
-        <v>17</v>
-      </c>
-      <c r="E184">
-        <v>601</v>
-      </c>
-      <c r="F184" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G184" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H184" t="s">
-        <v>17</v>
-      </c>
-      <c r="I184">
-        <v>42</v>
-      </c>
-      <c r="J184">
-        <v>8004</v>
-      </c>
-      <c r="K184" t="s">
-        <v>17</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
-      <c r="M184">
-        <v>0</v>
-      </c>
-      <c r="N184">
-        <v>0</v>
-      </c>
-      <c r="O184">
-        <v>0</v>
-      </c>
-      <c r="P184">
-        <v>0</v>
-      </c>
-      <c r="Q184">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A185">
-        <v>129159280</v>
-      </c>
-      <c r="B185" t="s">
-        <v>17</v>
-      </c>
-      <c r="C185" t="s">
-        <v>17</v>
-      </c>
-      <c r="D185" t="s">
-        <v>17</v>
-      </c>
-      <c r="E185">
-        <v>601</v>
-      </c>
-      <c r="F185" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G185" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H185" t="s">
-        <v>17</v>
-      </c>
-      <c r="I185">
-        <v>42</v>
-      </c>
-      <c r="J185">
-        <v>8004</v>
-      </c>
-      <c r="K185" t="s">
-        <v>17</v>
-      </c>
-      <c r="L185">
-        <v>0</v>
-      </c>
-      <c r="M185">
-        <v>0</v>
-      </c>
-      <c r="N185">
-        <v>0</v>
-      </c>
-      <c r="O185">
-        <v>0</v>
-      </c>
-      <c r="P185">
-        <v>0</v>
-      </c>
-      <c r="Q185">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A186">
-        <v>129159583</v>
-      </c>
-      <c r="B186" t="s">
-        <v>17</v>
-      </c>
-      <c r="C186" t="s">
-        <v>17</v>
-      </c>
-      <c r="D186" t="s">
-        <v>17</v>
-      </c>
-      <c r="E186">
-        <v>601</v>
-      </c>
-      <c r="F186" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G186" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H186" t="s">
-        <v>17</v>
-      </c>
-      <c r="I186">
-        <v>42</v>
-      </c>
-      <c r="J186">
-        <v>8004</v>
-      </c>
-      <c r="K186" t="s">
-        <v>17</v>
-      </c>
-      <c r="L186">
-        <v>0</v>
-      </c>
-      <c r="M186">
-        <v>0</v>
-      </c>
-      <c r="N186">
-        <v>0</v>
-      </c>
-      <c r="O186">
-        <v>0</v>
-      </c>
-      <c r="P186">
-        <v>0</v>
-      </c>
-      <c r="Q186">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A187">
-        <v>129160032</v>
-      </c>
-      <c r="B187" t="s">
-        <v>17</v>
-      </c>
-      <c r="C187" t="s">
-        <v>17</v>
-      </c>
-      <c r="D187" t="s">
-        <v>17</v>
-      </c>
-      <c r="E187">
-        <v>601</v>
-      </c>
-      <c r="F187" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G187" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H187" t="s">
-        <v>17</v>
-      </c>
-      <c r="I187">
-        <v>42</v>
-      </c>
-      <c r="J187">
-        <v>1117</v>
-      </c>
-      <c r="K187" t="s">
-        <v>17</v>
-      </c>
-      <c r="L187">
-        <v>0</v>
-      </c>
-      <c r="M187">
-        <v>0</v>
-      </c>
-      <c r="N187">
-        <v>0</v>
-      </c>
-      <c r="O187">
-        <v>0</v>
-      </c>
-      <c r="P187">
-        <v>0</v>
-      </c>
-      <c r="Q187">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A188">
-        <v>129160531</v>
-      </c>
-      <c r="B188" t="s">
-        <v>17</v>
-      </c>
-      <c r="C188" t="s">
-        <v>17</v>
-      </c>
-      <c r="D188" t="s">
-        <v>17</v>
-      </c>
-      <c r="E188">
-        <v>601</v>
-      </c>
-      <c r="F188" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G188" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H188" t="s">
-        <v>17</v>
-      </c>
-      <c r="I188">
-        <v>42</v>
-      </c>
-      <c r="J188">
-        <v>8004</v>
-      </c>
-      <c r="K188" t="s">
-        <v>17</v>
-      </c>
-      <c r="L188">
-        <v>0</v>
-      </c>
-      <c r="M188">
-        <v>0</v>
-      </c>
-      <c r="N188">
-        <v>0</v>
-      </c>
-      <c r="O188">
-        <v>0</v>
-      </c>
-      <c r="P188">
-        <v>0</v>
-      </c>
-      <c r="Q188">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A189">
-        <v>129160800</v>
-      </c>
-      <c r="B189" t="s">
-        <v>17</v>
-      </c>
-      <c r="C189" t="s">
-        <v>17</v>
-      </c>
-      <c r="D189" t="s">
-        <v>17</v>
-      </c>
-      <c r="E189">
-        <v>601</v>
-      </c>
-      <c r="F189" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G189" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H189" t="s">
-        <v>17</v>
-      </c>
-      <c r="I189">
-        <v>42</v>
-      </c>
-      <c r="J189">
-        <v>8004</v>
-      </c>
-      <c r="K189" t="s">
-        <v>17</v>
-      </c>
-      <c r="L189">
-        <v>0</v>
-      </c>
-      <c r="M189">
-        <v>0</v>
-      </c>
-      <c r="N189">
-        <v>0</v>
-      </c>
-      <c r="O189">
-        <v>0</v>
-      </c>
-      <c r="P189">
-        <v>0</v>
-      </c>
-      <c r="Q189">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A190">
-        <v>129161910</v>
-      </c>
-      <c r="B190" t="s">
-        <v>17</v>
-      </c>
-      <c r="C190" t="s">
-        <v>17</v>
-      </c>
-      <c r="D190" t="s">
-        <v>17</v>
-      </c>
-      <c r="E190">
-        <v>601</v>
-      </c>
-      <c r="F190" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G190" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H190" t="s">
-        <v>17</v>
-      </c>
-      <c r="I190">
-        <v>42</v>
-      </c>
-      <c r="J190">
-        <v>8004</v>
-      </c>
-      <c r="K190" t="s">
-        <v>17</v>
-      </c>
-      <c r="L190">
-        <v>0</v>
-      </c>
-      <c r="M190">
-        <v>0</v>
-      </c>
-      <c r="N190">
-        <v>0</v>
-      </c>
-      <c r="O190">
-        <v>0</v>
-      </c>
-      <c r="P190">
-        <v>0</v>
-      </c>
-      <c r="Q190">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A191">
-        <v>129165627</v>
-      </c>
-      <c r="B191" t="s">
-        <v>17</v>
-      </c>
-      <c r="C191" t="s">
-        <v>17</v>
-      </c>
-      <c r="D191" t="s">
-        <v>17</v>
-      </c>
-      <c r="E191">
-        <v>601</v>
-      </c>
-      <c r="F191" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G191" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H191" t="s">
-        <v>17</v>
-      </c>
-      <c r="I191">
-        <v>42</v>
-      </c>
-      <c r="J191">
-        <v>8004</v>
-      </c>
-      <c r="K191" t="s">
-        <v>17</v>
-      </c>
-      <c r="L191">
-        <v>0</v>
-      </c>
-      <c r="M191">
-        <v>0</v>
-      </c>
-      <c r="N191">
-        <v>0</v>
-      </c>
-      <c r="O191">
-        <v>0</v>
-      </c>
-      <c r="P191">
-        <v>0</v>
-      </c>
-      <c r="Q191">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A192">
-        <v>129166348</v>
-      </c>
-      <c r="B192" t="s">
-        <v>17</v>
-      </c>
-      <c r="C192" t="s">
-        <v>17</v>
-      </c>
-      <c r="D192" t="s">
-        <v>17</v>
-      </c>
-      <c r="E192">
-        <v>601</v>
-      </c>
-      <c r="F192" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G192" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H192" t="s">
-        <v>17</v>
-      </c>
-      <c r="I192">
-        <v>42</v>
-      </c>
-      <c r="J192">
-        <v>8004</v>
-      </c>
-      <c r="K192" t="s">
-        <v>17</v>
-      </c>
-      <c r="L192">
-        <v>0</v>
-      </c>
-      <c r="M192">
-        <v>0</v>
-      </c>
-      <c r="N192">
-        <v>0</v>
-      </c>
-      <c r="O192">
-        <v>0</v>
-      </c>
-      <c r="P192">
-        <v>0</v>
-      </c>
-      <c r="Q192">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A193">
-        <v>129168851</v>
-      </c>
-      <c r="B193" t="s">
-        <v>17</v>
-      </c>
-      <c r="C193" t="s">
-        <v>17</v>
-      </c>
-      <c r="D193" t="s">
-        <v>17</v>
-      </c>
-      <c r="E193">
-        <v>601</v>
-      </c>
-      <c r="F193" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G193" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H193" t="s">
-        <v>17</v>
-      </c>
-      <c r="I193">
-        <v>42</v>
-      </c>
-      <c r="J193">
-        <v>8004</v>
-      </c>
-      <c r="K193" t="s">
-        <v>17</v>
-      </c>
-      <c r="L193">
-        <v>0</v>
-      </c>
-      <c r="M193">
-        <v>0</v>
-      </c>
-      <c r="N193">
-        <v>0</v>
-      </c>
-      <c r="O193">
-        <v>0</v>
-      </c>
-      <c r="P193">
-        <v>0</v>
-      </c>
-      <c r="Q193">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>129169088</v>
-      </c>
-      <c r="B194" t="s">
-        <v>17</v>
-      </c>
-      <c r="C194" t="s">
-        <v>17</v>
-      </c>
-      <c r="D194" t="s">
-        <v>17</v>
-      </c>
-      <c r="E194">
-        <v>601</v>
-      </c>
-      <c r="F194" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G194" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H194" t="s">
-        <v>17</v>
-      </c>
-      <c r="I194">
-        <v>42</v>
-      </c>
-      <c r="J194">
-        <v>8004</v>
-      </c>
-      <c r="K194" t="s">
-        <v>17</v>
-      </c>
-      <c r="L194">
-        <v>0</v>
-      </c>
-      <c r="M194">
-        <v>0</v>
-      </c>
-      <c r="N194">
-        <v>0</v>
-      </c>
-      <c r="O194">
-        <v>0</v>
-      </c>
-      <c r="P194">
-        <v>0</v>
-      </c>
-      <c r="Q194">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A195">
-        <v>129169648</v>
-      </c>
-      <c r="B195" t="s">
-        <v>17</v>
-      </c>
-      <c r="C195" t="s">
-        <v>17</v>
-      </c>
-      <c r="D195" t="s">
-        <v>17</v>
-      </c>
-      <c r="E195">
-        <v>601</v>
-      </c>
-      <c r="F195" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G195" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H195" t="s">
-        <v>17</v>
-      </c>
-      <c r="I195">
-        <v>42</v>
-      </c>
-      <c r="J195">
-        <v>8004</v>
-      </c>
-      <c r="K195" t="s">
-        <v>17</v>
-      </c>
-      <c r="L195">
-        <v>0</v>
-      </c>
-      <c r="M195">
-        <v>0</v>
-      </c>
-      <c r="N195">
-        <v>0</v>
-      </c>
-      <c r="O195">
-        <v>0</v>
-      </c>
-      <c r="P195">
-        <v>0</v>
-      </c>
-      <c r="Q195">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>129170216</v>
-      </c>
-      <c r="B196" t="s">
-        <v>17</v>
-      </c>
-      <c r="C196" t="s">
-        <v>17</v>
-      </c>
-      <c r="D196" t="s">
-        <v>17</v>
-      </c>
-      <c r="E196">
-        <v>601</v>
-      </c>
-      <c r="F196" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G196" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H196" t="s">
-        <v>17</v>
-      </c>
-      <c r="I196">
-        <v>42</v>
-      </c>
-      <c r="J196">
-        <v>8004</v>
-      </c>
-      <c r="K196" t="s">
-        <v>17</v>
-      </c>
-      <c r="L196">
-        <v>0</v>
-      </c>
-      <c r="M196">
-        <v>0</v>
-      </c>
-      <c r="N196">
-        <v>0</v>
-      </c>
-      <c r="O196">
-        <v>0</v>
-      </c>
-      <c r="P196">
-        <v>0</v>
-      </c>
-      <c r="Q196">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>129171006</v>
-      </c>
-      <c r="B197" t="s">
-        <v>17</v>
-      </c>
-      <c r="C197" t="s">
-        <v>17</v>
-      </c>
-      <c r="D197" t="s">
-        <v>17</v>
-      </c>
-      <c r="E197">
-        <v>601</v>
-      </c>
-      <c r="F197" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G197" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H197" t="s">
-        <v>17</v>
-      </c>
-      <c r="I197">
-        <v>42</v>
-      </c>
-      <c r="J197">
-        <v>8004</v>
-      </c>
-      <c r="K197" t="s">
-        <v>17</v>
-      </c>
-      <c r="L197">
-        <v>0</v>
-      </c>
-      <c r="M197">
-        <v>0</v>
-      </c>
-      <c r="N197">
-        <v>0</v>
-      </c>
-      <c r="O197">
-        <v>0</v>
-      </c>
-      <c r="P197">
-        <v>0</v>
-      </c>
-      <c r="Q197">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A198">
-        <v>129171080</v>
-      </c>
-      <c r="B198" t="s">
-        <v>17</v>
-      </c>
-      <c r="C198" t="s">
-        <v>17</v>
-      </c>
-      <c r="D198" t="s">
-        <v>17</v>
-      </c>
-      <c r="E198">
-        <v>601</v>
-      </c>
-      <c r="F198" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G198" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H198" t="s">
-        <v>17</v>
-      </c>
-      <c r="I198">
-        <v>42</v>
-      </c>
-      <c r="J198">
-        <v>8004</v>
-      </c>
-      <c r="K198" t="s">
-        <v>17</v>
-      </c>
-      <c r="L198">
-        <v>0</v>
-      </c>
-      <c r="M198">
-        <v>0</v>
-      </c>
-      <c r="N198">
-        <v>0</v>
-      </c>
-      <c r="O198">
-        <v>0</v>
-      </c>
-      <c r="P198">
-        <v>0</v>
-      </c>
-      <c r="Q198">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A199">
-        <v>129172826</v>
-      </c>
-      <c r="B199" t="s">
-        <v>17</v>
-      </c>
-      <c r="C199" t="s">
-        <v>17</v>
-      </c>
-      <c r="D199" t="s">
-        <v>17</v>
-      </c>
-      <c r="E199">
-        <v>601</v>
-      </c>
-      <c r="F199" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G199" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H199" t="s">
-        <v>17</v>
-      </c>
-      <c r="I199">
-        <v>42</v>
-      </c>
-      <c r="J199">
-        <v>8004</v>
-      </c>
-      <c r="K199" t="s">
-        <v>17</v>
-      </c>
-      <c r="L199">
-        <v>0</v>
-      </c>
-      <c r="M199">
-        <v>0</v>
-      </c>
-      <c r="N199">
-        <v>0</v>
-      </c>
-      <c r="O199">
-        <v>0</v>
-      </c>
-      <c r="P199">
-        <v>0</v>
-      </c>
-      <c r="Q199">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A200">
-        <v>129174105</v>
-      </c>
-      <c r="B200" t="s">
-        <v>17</v>
-      </c>
-      <c r="C200" t="s">
-        <v>17</v>
-      </c>
-      <c r="D200" t="s">
-        <v>17</v>
-      </c>
-      <c r="E200">
-        <v>601</v>
-      </c>
-      <c r="F200" s="1">
-        <v>45538</v>
-      </c>
-      <c r="G200" s="1">
-        <v>45538</v>
-      </c>
-      <c r="H200" t="s">
-        <v>17</v>
-      </c>
-      <c r="I200">
-        <v>42</v>
-      </c>
-      <c r="J200">
-        <v>8004</v>
-      </c>
-      <c r="K200" t="s">
-        <v>17</v>
-      </c>
-      <c r="L200">
-        <v>0</v>
-      </c>
-      <c r="M200">
-        <v>0</v>
-      </c>
-      <c r="N200">
-        <v>0</v>
-      </c>
-      <c r="O200">
-        <v>0</v>
-      </c>
-      <c r="P200">
-        <v>0</v>
-      </c>
-      <c r="Q200">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Bloqueios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80B94CC-1F95-47F4-9325-D4014B7F49CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C92DDF-8B25-4655-A786-8B1F6BA2602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$154</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$169</definedName>
+    <definedName name="Fiel">Fiel!$A$1:$Q$169</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="18">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -423,27 +423,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1048576"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q275"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="16" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -501,7 +498,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129161310</v>
+        <v>129218023</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -516,10 +513,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45538</v>
+        <v>45541</v>
       </c>
       <c r="G2" s="1">
-        <v>45538</v>
+        <v>45542</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -554,7 +551,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129174384</v>
+        <v>129227329</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -569,10 +566,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45538</v>
+        <v>45541</v>
       </c>
       <c r="G3" s="1">
-        <v>45538</v>
+        <v>45544</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -607,7 +604,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129197378</v>
+        <v>129231852</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -619,13 +616,13 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G4" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -660,7 +657,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129204849</v>
+        <v>129236362</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,7 +672,7 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G5" s="1">
         <v>45541</v>
@@ -819,7 +816,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>125254042</v>
+        <v>125263823</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -834,10 +831,10 @@
         <v>1211</v>
       </c>
       <c r="F8" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G8" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -872,7 +869,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>125533295</v>
+        <v>125289206</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -887,7 +884,7 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G9" s="1">
         <v>45541</v>
@@ -925,7 +922,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>125596863</v>
+        <v>125399699</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -940,10 +937,10 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G10" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -978,7 +975,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>125634517</v>
+        <v>125410463</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -993,10 +990,10 @@
         <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G11" s="1">
-        <v>45541</v>
+        <v>45543</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1031,7 +1028,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>125768729</v>
+        <v>125418686</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1046,10 +1043,10 @@
         <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G12" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1084,7 +1081,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125835456</v>
+        <v>125465569</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1099,10 +1096,10 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45540</v>
+        <v>45542</v>
       </c>
       <c r="G13" s="1">
-        <v>45540</v>
+        <v>45542</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1137,7 +1134,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>125886055</v>
+        <v>125486415</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,10 +1149,10 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G14" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1190,7 +1187,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>125955063</v>
+        <v>125531460</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1202,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G15" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1243,7 +1240,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>125987532</v>
+        <v>125608449</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1255,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G16" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1296,7 +1293,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>126046938</v>
+        <v>125712273</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1311,7 +1308,7 @@
         <v>1211</v>
       </c>
       <c r="F17" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G17" s="1">
         <v>45541</v>
@@ -1349,7 +1346,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>126091843</v>
+        <v>125763506</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1364,7 +1361,7 @@
         <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G18" s="1">
         <v>45541</v>
@@ -1402,7 +1399,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>126109358</v>
+        <v>125782218</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1417,10 +1414,10 @@
         <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G19" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126325895</v>
+        <v>125797017</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1470,10 +1467,10 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G20" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1508,7 +1505,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>126516782</v>
+        <v>125800703</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1523,7 +1520,7 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G21" s="1">
         <v>45541</v>
@@ -1561,7 +1558,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>126538522</v>
+        <v>125847282</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1576,10 +1573,10 @@
         <v>1211</v>
       </c>
       <c r="F22" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G22" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1611,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>126828631</v>
+        <v>125964104</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1626,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G23" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1664,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>126907961</v>
+        <v>125969270</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1682,10 +1679,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G24" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1717,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>126932850</v>
+        <v>126090102</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,10 +1732,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45540</v>
+        <v>45542</v>
       </c>
       <c r="G25" s="1">
-        <v>45540</v>
+        <v>45542</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1773,7 +1770,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>127142518</v>
+        <v>126098795</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1788,7 +1785,7 @@
         <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="G26" s="1">
         <v>45541</v>
@@ -1826,7 +1823,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>127156313</v>
+        <v>126104825</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1841,10 +1838,10 @@
         <v>1211</v>
       </c>
       <c r="F27" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G27" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1879,7 +1876,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>127202712</v>
+        <v>126127404</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1894,10 +1891,10 @@
         <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G28" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1932,7 +1929,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>127228177</v>
+        <v>126245338</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1947,10 +1944,10 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G29" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1985,7 +1982,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>127382055</v>
+        <v>126373809</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -1997,13 +1994,13 @@
         <v>17</v>
       </c>
       <c r="E30">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G30" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2038,7 +2035,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127383497</v>
+        <v>126458210</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2050,13 +2047,13 @@
         <v>17</v>
       </c>
       <c r="E31">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F31" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G31" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2091,7 +2088,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>127444797</v>
+        <v>126475521</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2106,10 +2103,10 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45540</v>
+        <v>45538</v>
       </c>
       <c r="G32" s="1">
-        <v>45540</v>
+        <v>45544</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -2144,7 +2141,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127610835</v>
+        <v>126500432</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2159,10 +2156,10 @@
         <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G33" s="1">
-        <v>45540</v>
+        <v>45544</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2197,7 +2194,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127688983</v>
+        <v>126553035</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2212,10 +2209,10 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G34" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2250,7 +2247,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127725478</v>
+        <v>126602549</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2262,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G35" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2300,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127725776</v>
+        <v>126612057</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2318,10 +2315,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G36" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2356,7 +2353,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127737815</v>
+        <v>126623408</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2371,10 +2368,10 @@
         <v>1211</v>
       </c>
       <c r="F37" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G37" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2409,7 +2406,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127747821</v>
+        <v>126632282</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,10 +2421,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G38" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2462,7 +2459,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127816501</v>
+        <v>126665332</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2477,7 +2474,7 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45538</v>
+        <v>45541</v>
       </c>
       <c r="G39" s="1">
         <v>45541</v>
@@ -2515,7 +2512,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>128042857</v>
+        <v>126690569</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2530,10 +2527,10 @@
         <v>1211</v>
       </c>
       <c r="F40" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G40" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2568,7 +2565,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>128067794</v>
+        <v>126693444</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2583,10 +2580,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G41" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2621,7 +2618,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>128209755</v>
+        <v>126718369</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2636,10 +2633,10 @@
         <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G42" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2671,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>128370345</v>
+        <v>126783060</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,10 +2686,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G43" s="1">
-        <v>45540</v>
+        <v>45543</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2727,7 +2724,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>128474222</v>
+        <v>126810590</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2742,10 +2739,10 @@
         <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G44" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2780,7 +2777,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>128479396</v>
+        <v>126903711</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,10 +2792,10 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G45" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2833,7 +2830,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>128543637</v>
+        <v>126979137</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2848,10 +2845,10 @@
         <v>1211</v>
       </c>
       <c r="F46" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G46" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2886,7 +2883,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>128616819</v>
+        <v>127092469</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2901,10 +2898,10 @@
         <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G47" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2939,7 +2936,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>128631722</v>
+        <v>127137339</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2954,7 +2951,7 @@
         <v>1211</v>
       </c>
       <c r="F48" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G48" s="1">
         <v>45541</v>
@@ -2992,7 +2989,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>128671509</v>
+        <v>127164814</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3007,7 +3004,7 @@
         <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G49" s="1">
         <v>45541</v>
@@ -3045,7 +3042,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>128793088</v>
+        <v>127196178</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3057,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G50" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3095,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>128825377</v>
+        <v>127277467</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3110,13 +3107,13 @@
         <v>17</v>
       </c>
       <c r="E51">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F51" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G51" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3151,7 +3148,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>128838002</v>
+        <v>127297087</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3163,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="E52">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G52" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3201,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>128909042</v>
+        <v>127332502</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3216,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G53" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3254,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>128925561</v>
+        <v>127335112</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3272,10 +3269,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G54" s="1">
-        <v>45540</v>
+        <v>45544</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3307,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>128946421</v>
+        <v>127468191</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3325,7 +3322,7 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G55" s="1">
         <v>45541</v>
@@ -3363,7 +3360,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>128967377</v>
+        <v>127511890</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3378,10 +3375,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G56" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3413,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>128979031</v>
+        <v>127587596</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3431,10 +3428,10 @@
         <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G57" s="1">
-        <v>45540</v>
+        <v>45544</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3469,7 +3466,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>128982463</v>
+        <v>127666366</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3484,10 +3481,10 @@
         <v>1211</v>
       </c>
       <c r="F58" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G58" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3522,7 +3519,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>128992599</v>
+        <v>127757708</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3537,10 +3534,10 @@
         <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G59" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3575,7 +3572,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129089119</v>
+        <v>127786910</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3590,10 +3587,10 @@
         <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G60" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3628,7 +3625,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>129095708</v>
+        <v>127788396</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3643,10 +3640,10 @@
         <v>1211</v>
       </c>
       <c r="F61" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G61" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3681,7 +3678,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>129103727</v>
+        <v>127817938</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3696,10 +3693,10 @@
         <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G62" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3734,7 +3731,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129115744</v>
+        <v>127822362</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3746,13 +3743,13 @@
         <v>17</v>
       </c>
       <c r="E63">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="G63" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3787,7 +3784,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129132325</v>
+        <v>127880293</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3799,13 +3796,13 @@
         <v>17</v>
       </c>
       <c r="E64">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="G64" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3840,7 +3837,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129146673</v>
+        <v>127952431</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3855,10 +3852,10 @@
         <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G65" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3893,7 +3890,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129149508</v>
+        <v>128001523</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3908,10 +3905,10 @@
         <v>1211</v>
       </c>
       <c r="F66" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G66" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3946,7 +3943,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129156811</v>
+        <v>128038856</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3961,10 +3958,10 @@
         <v>1211</v>
       </c>
       <c r="F67" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G67" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3999,7 +3996,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129159884</v>
+        <v>128087208</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4011,13 +4008,13 @@
         <v>17</v>
       </c>
       <c r="E68">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F68" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G68" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -4052,7 +4049,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129165865</v>
+        <v>128088230</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4064,13 +4061,13 @@
         <v>17</v>
       </c>
       <c r="E69">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F69" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G69" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -4105,7 +4102,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129179833</v>
+        <v>128155328</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4120,10 +4117,10 @@
         <v>1211</v>
       </c>
       <c r="F70" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G70" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4158,7 +4155,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129187945</v>
+        <v>128167862</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4170,13 +4167,13 @@
         <v>17</v>
       </c>
       <c r="E71">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G71" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4211,7 +4208,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129189044</v>
+        <v>128230297</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4226,10 +4223,10 @@
         <v>1211</v>
       </c>
       <c r="F72" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G72" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4264,7 +4261,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129196697</v>
+        <v>128232608</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4279,10 +4276,10 @@
         <v>1211</v>
       </c>
       <c r="F73" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="G73" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4317,7 +4314,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>128749254</v>
+        <v>128240199</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4332,10 +4329,10 @@
         <v>1211</v>
       </c>
       <c r="F74" s="1">
-        <v>45510</v>
+        <v>45541</v>
       </c>
       <c r="G74" s="1">
-        <v>45511</v>
+        <v>45541</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4344,7 +4341,7 @@
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K74" t="s">
         <v>17</v>
@@ -4370,7 +4367,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129039074</v>
+        <v>128252504</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4382,13 +4379,13 @@
         <v>17</v>
       </c>
       <c r="E75">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F75" s="1">
-        <v>45530</v>
+        <v>45541</v>
       </c>
       <c r="G75" s="1">
-        <v>45531</v>
+        <v>45544</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -4397,7 +4394,7 @@
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K75" t="s">
         <v>17</v>
@@ -4423,7 +4420,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129110148</v>
+        <v>128417640</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4435,13 +4432,13 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="1">
-        <v>45533</v>
+        <v>45541</v>
       </c>
       <c r="G76" s="1">
-        <v>45534</v>
+        <v>45541</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -4450,7 +4447,7 @@
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K76" t="s">
         <v>17</v>
@@ -4476,7 +4473,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129190578</v>
+        <v>128428529</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4491,10 +4488,10 @@
         <v>1211</v>
       </c>
       <c r="F77" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G77" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4503,7 +4500,7 @@
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K77" t="s">
         <v>17</v>
@@ -4529,7 +4526,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129179334</v>
+        <v>128479591</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4541,13 +4538,13 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F78" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G78" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4556,7 +4553,7 @@
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K78" t="s">
         <v>17</v>
@@ -4582,7 +4579,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129179349</v>
+        <v>128489779</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4594,13 +4591,13 @@
         <v>17</v>
       </c>
       <c r="E79">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F79" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G79" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4609,7 +4606,7 @@
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K79" t="s">
         <v>17</v>
@@ -4635,7 +4632,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129179397</v>
+        <v>128551229</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4647,13 +4644,13 @@
         <v>17</v>
       </c>
       <c r="E80">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F80" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G80" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4662,7 +4659,7 @@
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K80" t="s">
         <v>17</v>
@@ -4688,7 +4685,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129179761</v>
+        <v>128574903</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4700,13 +4697,13 @@
         <v>17</v>
       </c>
       <c r="E81">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F81" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G81" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -4715,7 +4712,7 @@
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K81" t="s">
         <v>17</v>
@@ -4741,7 +4738,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129180333</v>
+        <v>128581782</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4753,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="E82">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F82" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G82" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -4768,7 +4765,7 @@
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K82" t="s">
         <v>17</v>
@@ -4794,7 +4791,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129180387</v>
+        <v>128584588</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4806,13 +4803,13 @@
         <v>17</v>
       </c>
       <c r="E83">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F83" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G83" s="1">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -4821,7 +4818,7 @@
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K83" t="s">
         <v>17</v>
@@ -4847,7 +4844,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129183426</v>
+        <v>128651112</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4859,13 +4856,13 @@
         <v>17</v>
       </c>
       <c r="E84">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F84" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G84" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -4874,7 +4871,7 @@
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K84" t="s">
         <v>17</v>
@@ -4900,7 +4897,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129183678</v>
+        <v>128653522</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4912,13 +4909,13 @@
         <v>17</v>
       </c>
       <c r="E85">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F85" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G85" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -4927,7 +4924,7 @@
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K85" t="s">
         <v>17</v>
@@ -4953,7 +4950,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129184973</v>
+        <v>128724114</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4965,13 +4962,13 @@
         <v>17</v>
       </c>
       <c r="E86">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F86" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="G86" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -4980,7 +4977,7 @@
         <v>42</v>
       </c>
       <c r="J86">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K86" t="s">
         <v>17</v>
@@ -5006,7 +5003,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129185154</v>
+        <v>128803318</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5018,13 +5015,13 @@
         <v>17</v>
       </c>
       <c r="E87">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F87" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G87" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -5033,7 +5030,7 @@
         <v>42</v>
       </c>
       <c r="J87">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K87" t="s">
         <v>17</v>
@@ -5059,7 +5056,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>129187787</v>
+        <v>128820718</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5071,13 +5068,13 @@
         <v>17</v>
       </c>
       <c r="E88">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F88" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G88" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -5086,7 +5083,7 @@
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -5112,7 +5109,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129189710</v>
+        <v>128824764</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5124,13 +5121,13 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F89" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G89" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -5139,7 +5136,7 @@
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -5165,7 +5162,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129189976</v>
+        <v>128903730</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5177,13 +5174,13 @@
         <v>17</v>
       </c>
       <c r="E90">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F90" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G90" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -5192,7 +5189,7 @@
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -5218,7 +5215,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129190253</v>
+        <v>128906338</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5230,13 +5227,13 @@
         <v>17</v>
       </c>
       <c r="E91">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F91" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G91" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -5245,7 +5242,7 @@
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
@@ -5271,7 +5268,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129190296</v>
+        <v>128907967</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5283,13 +5280,13 @@
         <v>17</v>
       </c>
       <c r="E92">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F92" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G92" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -5298,7 +5295,7 @@
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K92" t="s">
         <v>17</v>
@@ -5324,7 +5321,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129190796</v>
+        <v>128940629</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5336,13 +5333,13 @@
         <v>17</v>
       </c>
       <c r="E93">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F93" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G93" s="1">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5351,7 +5348,7 @@
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K93" t="s">
         <v>17</v>
@@ -5377,7 +5374,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129190818</v>
+        <v>128967127</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5389,13 +5386,13 @@
         <v>17</v>
       </c>
       <c r="E94">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F94" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G94" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -5404,7 +5401,7 @@
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K94" t="s">
         <v>17</v>
@@ -5430,7 +5427,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129190852</v>
+        <v>128984867</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5442,13 +5439,13 @@
         <v>17</v>
       </c>
       <c r="E95">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F95" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G95" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -5457,7 +5454,7 @@
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K95" t="s">
         <v>17</v>
@@ -5483,7 +5480,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>129191186</v>
+        <v>128999789</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -5495,13 +5492,13 @@
         <v>17</v>
       </c>
       <c r="E96">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F96" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G96" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -5510,7 +5507,7 @@
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K96" t="s">
         <v>17</v>
@@ -5536,7 +5533,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>129191714</v>
+        <v>129015345</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -5548,13 +5545,13 @@
         <v>17</v>
       </c>
       <c r="E97">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F97" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G97" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -5563,7 +5560,7 @@
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K97" t="s">
         <v>17</v>
@@ -5589,7 +5586,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>129192057</v>
+        <v>129016518</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -5601,13 +5598,13 @@
         <v>17</v>
       </c>
       <c r="E98">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F98" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G98" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -5616,7 +5613,7 @@
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K98" t="s">
         <v>17</v>
@@ -5642,7 +5639,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>129192063</v>
+        <v>129050558</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -5654,13 +5651,13 @@
         <v>17</v>
       </c>
       <c r="E99">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F99" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G99" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -5669,7 +5666,7 @@
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K99" t="s">
         <v>17</v>
@@ -5695,7 +5692,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>129192064</v>
+        <v>129093064</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -5707,13 +5704,13 @@
         <v>17</v>
       </c>
       <c r="E100">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F100" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G100" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -5722,7 +5719,7 @@
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K100" t="s">
         <v>17</v>
@@ -5748,7 +5745,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>129192164</v>
+        <v>129099939</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -5760,13 +5757,13 @@
         <v>17</v>
       </c>
       <c r="E101">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F101" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G101" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5775,7 +5772,7 @@
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K101" t="s">
         <v>17</v>
@@ -5801,7 +5798,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>129192233</v>
+        <v>129107269</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -5813,13 +5810,13 @@
         <v>17</v>
       </c>
       <c r="E102">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F102" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G102" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -5828,7 +5825,7 @@
         <v>42</v>
       </c>
       <c r="J102">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K102" t="s">
         <v>17</v>
@@ -5854,7 +5851,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>129192772</v>
+        <v>129111894</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -5866,13 +5863,13 @@
         <v>17</v>
       </c>
       <c r="E103">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F103" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G103" s="1">
-        <v>45542</v>
+        <v>45541</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -5881,7 +5878,7 @@
         <v>42</v>
       </c>
       <c r="J103">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K103" t="s">
         <v>17</v>
@@ -5907,7 +5904,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>129193922</v>
+        <v>129115744</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -5919,13 +5916,13 @@
         <v>17</v>
       </c>
       <c r="E104">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F104" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="G104" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -5934,7 +5931,7 @@
         <v>42</v>
       </c>
       <c r="J104">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K104" t="s">
         <v>17</v>
@@ -5960,7 +5957,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>129193928</v>
+        <v>129132325</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -5972,13 +5969,13 @@
         <v>17</v>
       </c>
       <c r="E105">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F105" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="G105" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -5987,7 +5984,7 @@
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K105" t="s">
         <v>17</v>
@@ -6013,7 +6010,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>129194213</v>
+        <v>129139313</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -6025,13 +6022,13 @@
         <v>17</v>
       </c>
       <c r="E106">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F106" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G106" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -6040,7 +6037,7 @@
         <v>42</v>
       </c>
       <c r="J106">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K106" t="s">
         <v>17</v>
@@ -6066,7 +6063,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>129194444</v>
+        <v>129151950</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -6078,13 +6075,13 @@
         <v>17</v>
       </c>
       <c r="E107">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F107" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G107" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -6093,7 +6090,7 @@
         <v>42</v>
       </c>
       <c r="J107">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K107" t="s">
         <v>17</v>
@@ -6119,7 +6116,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>129194538</v>
+        <v>129152475</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -6131,13 +6128,13 @@
         <v>17</v>
       </c>
       <c r="E108">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F108" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G108" s="1">
-        <v>45539</v>
+        <v>45544</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -6146,7 +6143,7 @@
         <v>42</v>
       </c>
       <c r="J108">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K108" t="s">
         <v>17</v>
@@ -6172,7 +6169,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>129194704</v>
+        <v>129166899</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -6184,10 +6181,10 @@
         <v>17</v>
       </c>
       <c r="E109">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F109" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G109" s="1">
         <v>45541</v>
@@ -6199,7 +6196,7 @@
         <v>42</v>
       </c>
       <c r="J109">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K109" t="s">
         <v>17</v>
@@ -6225,7 +6222,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>129195637</v>
+        <v>129180191</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -6237,13 +6234,13 @@
         <v>17</v>
       </c>
       <c r="E110">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F110" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G110" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -6252,7 +6249,7 @@
         <v>42</v>
       </c>
       <c r="J110">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K110" t="s">
         <v>17</v>
@@ -6278,7 +6275,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>129196396</v>
+        <v>129187945</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
@@ -6290,7 +6287,7 @@
         <v>17</v>
       </c>
       <c r="E111">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F111" s="1">
         <v>45539</v>
@@ -6305,7 +6302,7 @@
         <v>42</v>
       </c>
       <c r="J111">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K111" t="s">
         <v>17</v>
@@ -6331,7 +6328,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>129197616</v>
+        <v>129189311</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -6343,13 +6340,13 @@
         <v>17</v>
       </c>
       <c r="E112">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F112" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G112" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -6358,7 +6355,7 @@
         <v>42</v>
       </c>
       <c r="J112">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K112" t="s">
         <v>17</v>
@@ -6384,7 +6381,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>129197736</v>
+        <v>129191077</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -6396,13 +6393,13 @@
         <v>17</v>
       </c>
       <c r="E113">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F113" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G113" s="1">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -6411,7 +6408,7 @@
         <v>42</v>
       </c>
       <c r="J113">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K113" t="s">
         <v>17</v>
@@ -6437,7 +6434,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>129184712</v>
+        <v>129196032</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -6449,13 +6446,13 @@
         <v>17</v>
       </c>
       <c r="E114">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F114" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G114" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -6490,7 +6487,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>129188459</v>
+        <v>129200410</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
@@ -6502,13 +6499,13 @@
         <v>17</v>
       </c>
       <c r="E115">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F115" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G115" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -6543,7 +6540,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>129189014</v>
+        <v>129209076</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
@@ -6555,13 +6552,13 @@
         <v>17</v>
       </c>
       <c r="E116">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F116" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G116" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -6596,7 +6593,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>129194716</v>
+        <v>129212470</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
@@ -6608,13 +6605,13 @@
         <v>17</v>
       </c>
       <c r="E117">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F117" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G117" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -6649,7 +6646,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>129195399</v>
+        <v>129225196</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
@@ -6661,13 +6658,13 @@
         <v>17</v>
       </c>
       <c r="E118">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F118" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="G118" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -6702,7 +6699,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>129195730</v>
+        <v>128749254</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
@@ -6714,13 +6711,13 @@
         <v>17</v>
       </c>
       <c r="E119">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F119" s="1">
-        <v>45539</v>
+        <v>45510</v>
       </c>
       <c r="G119" s="1">
-        <v>45539</v>
+        <v>45511</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -6729,7 +6726,7 @@
         <v>42</v>
       </c>
       <c r="J119">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K119" t="s">
         <v>17</v>
@@ -6755,7 +6752,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>129179574</v>
+        <v>129039074</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
@@ -6767,13 +6764,13 @@
         <v>17</v>
       </c>
       <c r="E120">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F120" s="1">
-        <v>45539</v>
+        <v>45530</v>
       </c>
       <c r="G120" s="1">
-        <v>45539</v>
+        <v>45531</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -6782,7 +6779,7 @@
         <v>42</v>
       </c>
       <c r="J120">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K120" t="s">
         <v>17</v>
@@ -6808,7 +6805,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>129180407</v>
+        <v>129110148</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
@@ -6820,13 +6817,13 @@
         <v>17</v>
       </c>
       <c r="E121">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F121" s="1">
-        <v>45539</v>
+        <v>45533</v>
       </c>
       <c r="G121" s="1">
-        <v>45539</v>
+        <v>45534</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -6835,7 +6832,7 @@
         <v>42</v>
       </c>
       <c r="J121">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K121" t="s">
         <v>17</v>
@@ -6861,7 +6858,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>129181177</v>
+        <v>129190578</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
@@ -6873,13 +6870,13 @@
         <v>17</v>
       </c>
       <c r="E122">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F122" s="1">
         <v>45539</v>
       </c>
       <c r="G122" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -6888,7 +6885,7 @@
         <v>42</v>
       </c>
       <c r="J122">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K122" t="s">
         <v>17</v>
@@ -6914,7 +6911,7 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>129181429</v>
+        <v>129199299</v>
       </c>
       <c r="B123" t="s">
         <v>17</v>
@@ -6929,10 +6926,10 @@
         <v>601</v>
       </c>
       <c r="F123" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G123" s="1">
-        <v>45539</v>
+        <v>45542</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -6941,7 +6938,7 @@
         <v>42</v>
       </c>
       <c r="J123">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K123" t="s">
         <v>17</v>
@@ -6967,7 +6964,7 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>129181437</v>
+        <v>129199303</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -6982,10 +6979,10 @@
         <v>601</v>
       </c>
       <c r="F124" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G124" s="1">
-        <v>45539</v>
+        <v>45541</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -6994,7 +6991,7 @@
         <v>42</v>
       </c>
       <c r="J124">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K124" t="s">
         <v>17</v>
@@ -7020,7 +7017,7 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>129183636</v>
+        <v>129199737</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -7035,10 +7032,10 @@
         <v>601</v>
       </c>
       <c r="F125" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G125" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -7073,7 +7070,7 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>129183728</v>
+        <v>129199955</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
@@ -7088,10 +7085,10 @@
         <v>601</v>
       </c>
       <c r="F126" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G126" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -7126,7 +7123,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>129184232</v>
+        <v>129201204</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
@@ -7141,10 +7138,10 @@
         <v>601</v>
       </c>
       <c r="F127" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G127" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -7179,7 +7176,7 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>129184999</v>
+        <v>129201216</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
@@ -7194,10 +7191,10 @@
         <v>601</v>
       </c>
       <c r="F128" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G128" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -7232,7 +7229,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>129187748</v>
+        <v>129202457</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
@@ -7247,10 +7244,10 @@
         <v>601</v>
       </c>
       <c r="F129" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G129" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -7259,7 +7256,7 @@
         <v>42</v>
       </c>
       <c r="J129">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K129" t="s">
         <v>17</v>
@@ -7285,7 +7282,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>129188795</v>
+        <v>129202468</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
@@ -7300,10 +7297,10 @@
         <v>601</v>
       </c>
       <c r="F130" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G130" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -7312,7 +7309,7 @@
         <v>42</v>
       </c>
       <c r="J130">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K130" t="s">
         <v>17</v>
@@ -7338,7 +7335,7 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>129191947</v>
+        <v>129202522</v>
       </c>
       <c r="B131" t="s">
         <v>17</v>
@@ -7353,10 +7350,10 @@
         <v>601</v>
       </c>
       <c r="F131" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G131" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -7391,7 +7388,7 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>129193649</v>
+        <v>129202811</v>
       </c>
       <c r="B132" t="s">
         <v>17</v>
@@ -7406,10 +7403,10 @@
         <v>601</v>
       </c>
       <c r="F132" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G132" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -7418,7 +7415,7 @@
         <v>42</v>
       </c>
       <c r="J132">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K132" t="s">
         <v>17</v>
@@ -7444,7 +7441,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>129196347</v>
+        <v>129203083</v>
       </c>
       <c r="B133" t="s">
         <v>17</v>
@@ -7459,10 +7456,10 @@
         <v>601</v>
       </c>
       <c r="F133" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G133" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -7497,7 +7494,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>129198198</v>
+        <v>129206579</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
@@ -7512,10 +7509,10 @@
         <v>601</v>
       </c>
       <c r="F134" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="G134" s="1">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -7545,6 +7542,5889 @@
         <v>0</v>
       </c>
       <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>129206948</v>
+      </c>
+      <c r="B135" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G135" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8004</v>
+      </c>
+      <c r="K135" t="s">
+        <v>17</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>129207427</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G136" s="1">
+        <v>45541</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8013</v>
+      </c>
+      <c r="K136" t="s">
+        <v>17</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>129208086</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G137" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8004</v>
+      </c>
+      <c r="K137" t="s">
+        <v>17</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>129208508</v>
+      </c>
+      <c r="B138" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G138" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8004</v>
+      </c>
+      <c r="K138" t="s">
+        <v>17</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>129208673</v>
+      </c>
+      <c r="B139" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G139" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="K139" t="s">
+        <v>17</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>129208990</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140">
+        <v>601</v>
+      </c>
+      <c r="F140" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G140" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8004</v>
+      </c>
+      <c r="K140" t="s">
+        <v>17</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>129210986</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141">
+        <v>601</v>
+      </c>
+      <c r="F141" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G141" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8004</v>
+      </c>
+      <c r="K141" t="s">
+        <v>17</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>129211279</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142">
+        <v>601</v>
+      </c>
+      <c r="F142" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G142" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8004</v>
+      </c>
+      <c r="K142" t="s">
+        <v>17</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>129211435</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143">
+        <v>601</v>
+      </c>
+      <c r="F143" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G143" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8004</v>
+      </c>
+      <c r="K143" t="s">
+        <v>17</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>129212247</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144">
+        <v>601</v>
+      </c>
+      <c r="F144" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G144" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8004</v>
+      </c>
+      <c r="K144" t="s">
+        <v>17</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>129212832</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145">
+        <v>601</v>
+      </c>
+      <c r="F145" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G145" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8004</v>
+      </c>
+      <c r="K145" t="s">
+        <v>17</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>129213326</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146">
+        <v>601</v>
+      </c>
+      <c r="F146" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G146" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8004</v>
+      </c>
+      <c r="K146" t="s">
+        <v>17</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>129214146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147">
+        <v>601</v>
+      </c>
+      <c r="F147" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G147" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>8004</v>
+      </c>
+      <c r="K147" t="s">
+        <v>17</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>129214359</v>
+      </c>
+      <c r="B148" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148">
+        <v>601</v>
+      </c>
+      <c r="F148" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G148" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>8004</v>
+      </c>
+      <c r="K148" t="s">
+        <v>17</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>129214474</v>
+      </c>
+      <c r="B149" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149">
+        <v>601</v>
+      </c>
+      <c r="F149" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G149" s="1">
+        <v>45542</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
+        <v>8013</v>
+      </c>
+      <c r="K149" t="s">
+        <v>17</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>129214544</v>
+      </c>
+      <c r="B150" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150">
+        <v>601</v>
+      </c>
+      <c r="F150" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G150" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>8013</v>
+      </c>
+      <c r="K150" t="s">
+        <v>17</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>129214651</v>
+      </c>
+      <c r="B151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151">
+        <v>601</v>
+      </c>
+      <c r="F151" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G151" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151">
+        <v>42</v>
+      </c>
+      <c r="J151">
+        <v>8013</v>
+      </c>
+      <c r="K151" t="s">
+        <v>17</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>129214851</v>
+      </c>
+      <c r="B152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152">
+        <v>601</v>
+      </c>
+      <c r="F152" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G152" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152">
+        <v>42</v>
+      </c>
+      <c r="J152">
+        <v>8004</v>
+      </c>
+      <c r="K152" t="s">
+        <v>17</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>129214942</v>
+      </c>
+      <c r="B153" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153">
+        <v>601</v>
+      </c>
+      <c r="F153" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G153" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153">
+        <v>42</v>
+      </c>
+      <c r="J153">
+        <v>8004</v>
+      </c>
+      <c r="K153" t="s">
+        <v>17</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>129215279</v>
+      </c>
+      <c r="B154" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154">
+        <v>601</v>
+      </c>
+      <c r="F154" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G154" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154">
+        <v>42</v>
+      </c>
+      <c r="J154">
+        <v>8004</v>
+      </c>
+      <c r="K154" t="s">
+        <v>17</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>129215627</v>
+      </c>
+      <c r="B155" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155">
+        <v>601</v>
+      </c>
+      <c r="F155" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G155" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155">
+        <v>42</v>
+      </c>
+      <c r="J155">
+        <v>8004</v>
+      </c>
+      <c r="K155" t="s">
+        <v>17</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>129199466</v>
+      </c>
+      <c r="B156" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156">
+        <v>601</v>
+      </c>
+      <c r="F156" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G156" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156">
+        <v>42</v>
+      </c>
+      <c r="J156">
+        <v>8001</v>
+      </c>
+      <c r="K156" t="s">
+        <v>17</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>129214240</v>
+      </c>
+      <c r="B157" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157">
+        <v>601</v>
+      </c>
+      <c r="F157" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G157" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157">
+        <v>42</v>
+      </c>
+      <c r="J157">
+        <v>8001</v>
+      </c>
+      <c r="K157" t="s">
+        <v>17</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+      <c r="Q157">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>129214729</v>
+      </c>
+      <c r="B158" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>17</v>
+      </c>
+      <c r="E158">
+        <v>601</v>
+      </c>
+      <c r="F158" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G158" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158">
+        <v>42</v>
+      </c>
+      <c r="J158">
+        <v>8001</v>
+      </c>
+      <c r="K158" t="s">
+        <v>17</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>0</v>
+      </c>
+      <c r="Q158">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>128374994</v>
+      </c>
+      <c r="B159" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159">
+        <v>601</v>
+      </c>
+      <c r="F159" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G159" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159">
+        <v>42</v>
+      </c>
+      <c r="J159">
+        <v>8004</v>
+      </c>
+      <c r="K159" t="s">
+        <v>17</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+      <c r="Q159">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>129199352</v>
+      </c>
+      <c r="B160" t="s">
+        <v>17</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160">
+        <v>601</v>
+      </c>
+      <c r="F160" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G160" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160">
+        <v>42</v>
+      </c>
+      <c r="J160">
+        <v>8004</v>
+      </c>
+      <c r="K160" t="s">
+        <v>17</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>0</v>
+      </c>
+      <c r="Q160">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>129206983</v>
+      </c>
+      <c r="B161" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161">
+        <v>601</v>
+      </c>
+      <c r="F161" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G161" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161">
+        <v>42</v>
+      </c>
+      <c r="J161">
+        <v>8004</v>
+      </c>
+      <c r="K161" t="s">
+        <v>17</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>0</v>
+      </c>
+      <c r="Q161">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>129207857</v>
+      </c>
+      <c r="B162" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162">
+        <v>601</v>
+      </c>
+      <c r="F162" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G162" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162">
+        <v>42</v>
+      </c>
+      <c r="J162">
+        <v>8004</v>
+      </c>
+      <c r="K162" t="s">
+        <v>17</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>129208610</v>
+      </c>
+      <c r="B163" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163">
+        <v>601</v>
+      </c>
+      <c r="F163" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G163" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163">
+        <v>42</v>
+      </c>
+      <c r="J163">
+        <v>8004</v>
+      </c>
+      <c r="K163" t="s">
+        <v>17</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="Q163">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>129209296</v>
+      </c>
+      <c r="B164" t="s">
+        <v>17</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164">
+        <v>601</v>
+      </c>
+      <c r="F164" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G164" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164">
+        <v>42</v>
+      </c>
+      <c r="J164">
+        <v>8004</v>
+      </c>
+      <c r="K164" t="s">
+        <v>17</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="Q164">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>129211659</v>
+      </c>
+      <c r="B165" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165">
+        <v>601</v>
+      </c>
+      <c r="F165" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G165" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165">
+        <v>42</v>
+      </c>
+      <c r="J165">
+        <v>8004</v>
+      </c>
+      <c r="K165" t="s">
+        <v>17</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>129211727</v>
+      </c>
+      <c r="B166" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166">
+        <v>601</v>
+      </c>
+      <c r="F166" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G166" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166">
+        <v>42</v>
+      </c>
+      <c r="J166">
+        <v>8004</v>
+      </c>
+      <c r="K166" t="s">
+        <v>17</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="Q166">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>129212781</v>
+      </c>
+      <c r="B167" t="s">
+        <v>17</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167">
+        <v>601</v>
+      </c>
+      <c r="F167" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G167" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167">
+        <v>42</v>
+      </c>
+      <c r="J167">
+        <v>8004</v>
+      </c>
+      <c r="K167" t="s">
+        <v>17</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="Q167">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>129213146</v>
+      </c>
+      <c r="B168" t="s">
+        <v>17</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168">
+        <v>601</v>
+      </c>
+      <c r="F168" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G168" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168">
+        <v>42</v>
+      </c>
+      <c r="J168">
+        <v>8004</v>
+      </c>
+      <c r="K168" t="s">
+        <v>17</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <v>0</v>
+      </c>
+      <c r="Q168">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>129213999</v>
+      </c>
+      <c r="B169" t="s">
+        <v>17</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169">
+        <v>601</v>
+      </c>
+      <c r="F169" s="1">
+        <v>45540</v>
+      </c>
+      <c r="G169" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169">
+        <v>42</v>
+      </c>
+      <c r="J169">
+        <v>8004</v>
+      </c>
+      <c r="K169" t="s">
+        <v>17</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+      <c r="Q169">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>128374994</v>
+      </c>
+      <c r="E170">
+        <v>601</v>
+      </c>
+      <c r="F170" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G170" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I170">
+        <v>42</v>
+      </c>
+      <c r="J170">
+        <v>8004</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="Q170">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>129199299</v>
+      </c>
+      <c r="E171">
+        <v>601</v>
+      </c>
+      <c r="F171" s="2">
+        <v>45542</v>
+      </c>
+      <c r="G171" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I171">
+        <v>42</v>
+      </c>
+      <c r="J171">
+        <v>8013</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="Q171">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>129199303</v>
+      </c>
+      <c r="E172">
+        <v>601</v>
+      </c>
+      <c r="F172" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G172" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I172">
+        <v>42</v>
+      </c>
+      <c r="J172">
+        <v>8013</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>0</v>
+      </c>
+      <c r="Q172">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>129199352</v>
+      </c>
+      <c r="E173">
+        <v>601</v>
+      </c>
+      <c r="F173" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G173" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I173">
+        <v>42</v>
+      </c>
+      <c r="J173">
+        <v>8004</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>129199466</v>
+      </c>
+      <c r="E174">
+        <v>601</v>
+      </c>
+      <c r="F174" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G174" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I174">
+        <v>42</v>
+      </c>
+      <c r="J174">
+        <v>8001</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>0</v>
+      </c>
+      <c r="Q174">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>129199737</v>
+      </c>
+      <c r="E175">
+        <v>601</v>
+      </c>
+      <c r="F175" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G175" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I175">
+        <v>42</v>
+      </c>
+      <c r="J175">
+        <v>8004</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>0</v>
+      </c>
+      <c r="Q175">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>129199955</v>
+      </c>
+      <c r="E176">
+        <v>601</v>
+      </c>
+      <c r="F176" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G176" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I176">
+        <v>42</v>
+      </c>
+      <c r="J176">
+        <v>8004</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176">
+        <v>0</v>
+      </c>
+      <c r="P176">
+        <v>0</v>
+      </c>
+      <c r="Q176">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>129201204</v>
+      </c>
+      <c r="E177">
+        <v>601</v>
+      </c>
+      <c r="F177" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G177" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I177">
+        <v>42</v>
+      </c>
+      <c r="J177">
+        <v>8004</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <v>0</v>
+      </c>
+      <c r="Q177">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>129201216</v>
+      </c>
+      <c r="E178">
+        <v>601</v>
+      </c>
+      <c r="F178" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G178" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I178">
+        <v>42</v>
+      </c>
+      <c r="J178">
+        <v>8004</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+      <c r="Q178">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>129202451</v>
+      </c>
+      <c r="E179">
+        <v>601</v>
+      </c>
+      <c r="F179" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G179" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I179">
+        <v>42</v>
+      </c>
+      <c r="J179">
+        <v>8003</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+      <c r="Q179">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>129202457</v>
+      </c>
+      <c r="E180">
+        <v>601</v>
+      </c>
+      <c r="F180" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G180" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I180">
+        <v>42</v>
+      </c>
+      <c r="J180">
+        <v>8013</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180">
+        <v>0</v>
+      </c>
+      <c r="P180">
+        <v>0</v>
+      </c>
+      <c r="Q180">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>129202468</v>
+      </c>
+      <c r="E181">
+        <v>601</v>
+      </c>
+      <c r="F181" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G181" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I181">
+        <v>42</v>
+      </c>
+      <c r="J181">
+        <v>8013</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>0</v>
+      </c>
+      <c r="O181">
+        <v>0</v>
+      </c>
+      <c r="P181">
+        <v>0</v>
+      </c>
+      <c r="Q181">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>129202522</v>
+      </c>
+      <c r="E182">
+        <v>601</v>
+      </c>
+      <c r="F182" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G182" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I182">
+        <v>42</v>
+      </c>
+      <c r="J182">
+        <v>8004</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+      <c r="P182">
+        <v>0</v>
+      </c>
+      <c r="Q182">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>129202811</v>
+      </c>
+      <c r="E183">
+        <v>601</v>
+      </c>
+      <c r="F183" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G183" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I183">
+        <v>42</v>
+      </c>
+      <c r="J183">
+        <v>8013</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183">
+        <v>0</v>
+      </c>
+      <c r="P183">
+        <v>0</v>
+      </c>
+      <c r="Q183">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>129203083</v>
+      </c>
+      <c r="E184">
+        <v>601</v>
+      </c>
+      <c r="F184" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G184" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I184">
+        <v>42</v>
+      </c>
+      <c r="J184">
+        <v>8004</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>0</v>
+      </c>
+      <c r="Q184">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>129203943</v>
+      </c>
+      <c r="E185">
+        <v>601</v>
+      </c>
+      <c r="F185" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G185" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I185">
+        <v>42</v>
+      </c>
+      <c r="J185">
+        <v>8001</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>0</v>
+      </c>
+      <c r="Q185">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>129204544</v>
+      </c>
+      <c r="E186">
+        <v>601</v>
+      </c>
+      <c r="F186" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G186" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I186">
+        <v>42</v>
+      </c>
+      <c r="J186">
+        <v>8001</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+      <c r="P186">
+        <v>0</v>
+      </c>
+      <c r="Q186">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>129206579</v>
+      </c>
+      <c r="E187">
+        <v>601</v>
+      </c>
+      <c r="F187" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G187" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I187">
+        <v>42</v>
+      </c>
+      <c r="J187">
+        <v>8004</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187">
+        <v>0</v>
+      </c>
+      <c r="P187">
+        <v>0</v>
+      </c>
+      <c r="Q187">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>129206948</v>
+      </c>
+      <c r="E188">
+        <v>601</v>
+      </c>
+      <c r="F188" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G188" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I188">
+        <v>42</v>
+      </c>
+      <c r="J188">
+        <v>8004</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188">
+        <v>0</v>
+      </c>
+      <c r="P188">
+        <v>0</v>
+      </c>
+      <c r="Q188">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>129206983</v>
+      </c>
+      <c r="E189">
+        <v>601</v>
+      </c>
+      <c r="F189" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G189" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I189">
+        <v>42</v>
+      </c>
+      <c r="J189">
+        <v>8004</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189">
+        <v>0</v>
+      </c>
+      <c r="P189">
+        <v>0</v>
+      </c>
+      <c r="Q189">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>129207857</v>
+      </c>
+      <c r="E190">
+        <v>601</v>
+      </c>
+      <c r="F190" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G190" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I190">
+        <v>42</v>
+      </c>
+      <c r="J190">
+        <v>8004</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>0</v>
+      </c>
+      <c r="O190">
+        <v>0</v>
+      </c>
+      <c r="P190">
+        <v>0</v>
+      </c>
+      <c r="Q190">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>129208086</v>
+      </c>
+      <c r="E191">
+        <v>601</v>
+      </c>
+      <c r="F191" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G191" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I191">
+        <v>42</v>
+      </c>
+      <c r="J191">
+        <v>8004</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>0</v>
+      </c>
+      <c r="O191">
+        <v>0</v>
+      </c>
+      <c r="P191">
+        <v>0</v>
+      </c>
+      <c r="Q191">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>129208508</v>
+      </c>
+      <c r="E192">
+        <v>601</v>
+      </c>
+      <c r="F192" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G192" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I192">
+        <v>42</v>
+      </c>
+      <c r="J192">
+        <v>8004</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>0</v>
+      </c>
+      <c r="O192">
+        <v>0</v>
+      </c>
+      <c r="P192">
+        <v>0</v>
+      </c>
+      <c r="Q192">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>129208610</v>
+      </c>
+      <c r="E193">
+        <v>601</v>
+      </c>
+      <c r="F193" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G193" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I193">
+        <v>42</v>
+      </c>
+      <c r="J193">
+        <v>8004</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193">
+        <v>0</v>
+      </c>
+      <c r="P193">
+        <v>0</v>
+      </c>
+      <c r="Q193">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>129208673</v>
+      </c>
+      <c r="E194">
+        <v>601</v>
+      </c>
+      <c r="F194" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G194" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I194">
+        <v>42</v>
+      </c>
+      <c r="J194">
+        <v>8004</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+      <c r="P194">
+        <v>0</v>
+      </c>
+      <c r="Q194">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>129208990</v>
+      </c>
+      <c r="E195">
+        <v>601</v>
+      </c>
+      <c r="F195" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G195" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I195">
+        <v>42</v>
+      </c>
+      <c r="J195">
+        <v>8004</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195">
+        <v>0</v>
+      </c>
+      <c r="P195">
+        <v>0</v>
+      </c>
+      <c r="Q195">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>129209296</v>
+      </c>
+      <c r="E196">
+        <v>601</v>
+      </c>
+      <c r="F196" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G196" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I196">
+        <v>42</v>
+      </c>
+      <c r="J196">
+        <v>8004</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196">
+        <v>0</v>
+      </c>
+      <c r="P196">
+        <v>0</v>
+      </c>
+      <c r="Q196">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>129210986</v>
+      </c>
+      <c r="E197">
+        <v>601</v>
+      </c>
+      <c r="F197" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G197" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I197">
+        <v>42</v>
+      </c>
+      <c r="J197">
+        <v>8004</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197">
+        <v>0</v>
+      </c>
+      <c r="P197">
+        <v>0</v>
+      </c>
+      <c r="Q197">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>129211279</v>
+      </c>
+      <c r="E198">
+        <v>601</v>
+      </c>
+      <c r="F198" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G198" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I198">
+        <v>42</v>
+      </c>
+      <c r="J198">
+        <v>8004</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <v>0</v>
+      </c>
+      <c r="P198">
+        <v>0</v>
+      </c>
+      <c r="Q198">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>129211435</v>
+      </c>
+      <c r="E199">
+        <v>601</v>
+      </c>
+      <c r="F199" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G199" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I199">
+        <v>42</v>
+      </c>
+      <c r="J199">
+        <v>8004</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199">
+        <v>0</v>
+      </c>
+      <c r="P199">
+        <v>0</v>
+      </c>
+      <c r="Q199">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>129211659</v>
+      </c>
+      <c r="E200">
+        <v>601</v>
+      </c>
+      <c r="F200" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G200" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I200">
+        <v>42</v>
+      </c>
+      <c r="J200">
+        <v>8004</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+      <c r="P200">
+        <v>0</v>
+      </c>
+      <c r="Q200">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>129211727</v>
+      </c>
+      <c r="E201">
+        <v>601</v>
+      </c>
+      <c r="F201" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G201" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I201">
+        <v>42</v>
+      </c>
+      <c r="J201">
+        <v>8004</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201">
+        <v>0</v>
+      </c>
+      <c r="P201">
+        <v>0</v>
+      </c>
+      <c r="Q201">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>129212247</v>
+      </c>
+      <c r="E202">
+        <v>601</v>
+      </c>
+      <c r="F202" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G202" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I202">
+        <v>42</v>
+      </c>
+      <c r="J202">
+        <v>8004</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>0</v>
+      </c>
+      <c r="O202">
+        <v>0</v>
+      </c>
+      <c r="P202">
+        <v>0</v>
+      </c>
+      <c r="Q202">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>129212781</v>
+      </c>
+      <c r="E203">
+        <v>601</v>
+      </c>
+      <c r="F203" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G203" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I203">
+        <v>42</v>
+      </c>
+      <c r="J203">
+        <v>8004</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203">
+        <v>0</v>
+      </c>
+      <c r="P203">
+        <v>0</v>
+      </c>
+      <c r="Q203">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>129212832</v>
+      </c>
+      <c r="E204">
+        <v>601</v>
+      </c>
+      <c r="F204" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G204" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I204">
+        <v>42</v>
+      </c>
+      <c r="J204">
+        <v>8004</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204">
+        <v>0</v>
+      </c>
+      <c r="P204">
+        <v>0</v>
+      </c>
+      <c r="Q204">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>129213146</v>
+      </c>
+      <c r="E205">
+        <v>601</v>
+      </c>
+      <c r="F205" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G205" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I205">
+        <v>42</v>
+      </c>
+      <c r="J205">
+        <v>8004</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205">
+        <v>0</v>
+      </c>
+      <c r="P205">
+        <v>0</v>
+      </c>
+      <c r="Q205">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>129213326</v>
+      </c>
+      <c r="E206">
+        <v>601</v>
+      </c>
+      <c r="F206" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G206" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I206">
+        <v>42</v>
+      </c>
+      <c r="J206">
+        <v>8004</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>0</v>
+      </c>
+      <c r="O206">
+        <v>0</v>
+      </c>
+      <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>129213999</v>
+      </c>
+      <c r="E207">
+        <v>601</v>
+      </c>
+      <c r="F207" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G207" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I207">
+        <v>42</v>
+      </c>
+      <c r="J207">
+        <v>8004</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>0</v>
+      </c>
+      <c r="O207">
+        <v>0</v>
+      </c>
+      <c r="P207">
+        <v>0</v>
+      </c>
+      <c r="Q207">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>129214146</v>
+      </c>
+      <c r="E208">
+        <v>601</v>
+      </c>
+      <c r="F208" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G208" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I208">
+        <v>42</v>
+      </c>
+      <c r="J208">
+        <v>8004</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>0</v>
+      </c>
+      <c r="O208">
+        <v>0</v>
+      </c>
+      <c r="P208">
+        <v>0</v>
+      </c>
+      <c r="Q208">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>129214240</v>
+      </c>
+      <c r="E209">
+        <v>601</v>
+      </c>
+      <c r="F209" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G209" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I209">
+        <v>42</v>
+      </c>
+      <c r="J209">
+        <v>8001</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+      <c r="N209">
+        <v>0</v>
+      </c>
+      <c r="O209">
+        <v>0</v>
+      </c>
+      <c r="P209">
+        <v>0</v>
+      </c>
+      <c r="Q209">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>129214359</v>
+      </c>
+      <c r="E210">
+        <v>601</v>
+      </c>
+      <c r="F210" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G210" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I210">
+        <v>42</v>
+      </c>
+      <c r="J210">
+        <v>8004</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210">
+        <v>0</v>
+      </c>
+      <c r="P210">
+        <v>0</v>
+      </c>
+      <c r="Q210">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>129214474</v>
+      </c>
+      <c r="E211">
+        <v>601</v>
+      </c>
+      <c r="F211" s="2">
+        <v>45542</v>
+      </c>
+      <c r="G211" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I211">
+        <v>42</v>
+      </c>
+      <c r="J211">
+        <v>8013</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>0</v>
+      </c>
+      <c r="O211">
+        <v>0</v>
+      </c>
+      <c r="P211">
+        <v>0</v>
+      </c>
+      <c r="Q211">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>129214544</v>
+      </c>
+      <c r="E212">
+        <v>601</v>
+      </c>
+      <c r="F212" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G212" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I212">
+        <v>42</v>
+      </c>
+      <c r="J212">
+        <v>8013</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>0</v>
+      </c>
+      <c r="O212">
+        <v>0</v>
+      </c>
+      <c r="P212">
+        <v>0</v>
+      </c>
+      <c r="Q212">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>129214651</v>
+      </c>
+      <c r="E213">
+        <v>601</v>
+      </c>
+      <c r="F213" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G213" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I213">
+        <v>42</v>
+      </c>
+      <c r="J213">
+        <v>8013</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213">
+        <v>0</v>
+      </c>
+      <c r="P213">
+        <v>0</v>
+      </c>
+      <c r="Q213">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>129214729</v>
+      </c>
+      <c r="E214">
+        <v>601</v>
+      </c>
+      <c r="F214" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G214" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I214">
+        <v>42</v>
+      </c>
+      <c r="J214">
+        <v>8001</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>0</v>
+      </c>
+      <c r="O214">
+        <v>0</v>
+      </c>
+      <c r="P214">
+        <v>0</v>
+      </c>
+      <c r="Q214">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>129214851</v>
+      </c>
+      <c r="E215">
+        <v>601</v>
+      </c>
+      <c r="F215" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G215" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I215">
+        <v>42</v>
+      </c>
+      <c r="J215">
+        <v>8004</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>0</v>
+      </c>
+      <c r="O215">
+        <v>0</v>
+      </c>
+      <c r="P215">
+        <v>0</v>
+      </c>
+      <c r="Q215">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>129214942</v>
+      </c>
+      <c r="E216">
+        <v>601</v>
+      </c>
+      <c r="F216" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G216" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I216">
+        <v>42</v>
+      </c>
+      <c r="J216">
+        <v>8004</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>0</v>
+      </c>
+      <c r="O216">
+        <v>0</v>
+      </c>
+      <c r="P216">
+        <v>0</v>
+      </c>
+      <c r="Q216">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>129215279</v>
+      </c>
+      <c r="E217">
+        <v>601</v>
+      </c>
+      <c r="F217" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G217" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I217">
+        <v>42</v>
+      </c>
+      <c r="J217">
+        <v>8004</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217">
+        <v>0</v>
+      </c>
+      <c r="P217">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>129215627</v>
+      </c>
+      <c r="E218">
+        <v>601</v>
+      </c>
+      <c r="F218" s="2">
+        <v>45540</v>
+      </c>
+      <c r="G218" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I218">
+        <v>42</v>
+      </c>
+      <c r="J218">
+        <v>8004</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>0</v>
+      </c>
+      <c r="O218">
+        <v>0</v>
+      </c>
+      <c r="P218">
+        <v>0</v>
+      </c>
+      <c r="Q218">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>129217895</v>
+      </c>
+      <c r="E219">
+        <v>601</v>
+      </c>
+      <c r="F219" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G219" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I219">
+        <v>42</v>
+      </c>
+      <c r="J219">
+        <v>8004</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>0</v>
+      </c>
+      <c r="O219">
+        <v>0</v>
+      </c>
+      <c r="P219">
+        <v>0</v>
+      </c>
+      <c r="Q219">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>129218125</v>
+      </c>
+      <c r="E220">
+        <v>601</v>
+      </c>
+      <c r="F220" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G220" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I220">
+        <v>42</v>
+      </c>
+      <c r="J220">
+        <v>8004</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>0</v>
+      </c>
+      <c r="O220">
+        <v>0</v>
+      </c>
+      <c r="P220">
+        <v>0</v>
+      </c>
+      <c r="Q220">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>129218364</v>
+      </c>
+      <c r="E221">
+        <v>601</v>
+      </c>
+      <c r="F221" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G221" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I221">
+        <v>42</v>
+      </c>
+      <c r="J221">
+        <v>8004</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>0</v>
+      </c>
+      <c r="O221">
+        <v>0</v>
+      </c>
+      <c r="P221">
+        <v>0</v>
+      </c>
+      <c r="Q221">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>129218440</v>
+      </c>
+      <c r="E222">
+        <v>601</v>
+      </c>
+      <c r="F222" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G222" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I222">
+        <v>42</v>
+      </c>
+      <c r="J222">
+        <v>1118</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>0</v>
+      </c>
+      <c r="O222">
+        <v>0</v>
+      </c>
+      <c r="P222">
+        <v>0</v>
+      </c>
+      <c r="Q222">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>129218597</v>
+      </c>
+      <c r="E223">
+        <v>601</v>
+      </c>
+      <c r="F223" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G223" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I223">
+        <v>42</v>
+      </c>
+      <c r="J223">
+        <v>8004</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>0</v>
+      </c>
+      <c r="O223">
+        <v>0</v>
+      </c>
+      <c r="P223">
+        <v>0</v>
+      </c>
+      <c r="Q223">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>129218655</v>
+      </c>
+      <c r="E224">
+        <v>601</v>
+      </c>
+      <c r="F224" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G224" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I224">
+        <v>42</v>
+      </c>
+      <c r="J224">
+        <v>8004</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>0</v>
+      </c>
+      <c r="O224">
+        <v>0</v>
+      </c>
+      <c r="P224">
+        <v>0</v>
+      </c>
+      <c r="Q224">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>129218691</v>
+      </c>
+      <c r="E225">
+        <v>601</v>
+      </c>
+      <c r="F225" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G225" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I225">
+        <v>42</v>
+      </c>
+      <c r="J225">
+        <v>8004</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>0</v>
+      </c>
+      <c r="O225">
+        <v>0</v>
+      </c>
+      <c r="P225">
+        <v>0</v>
+      </c>
+      <c r="Q225">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>129218805</v>
+      </c>
+      <c r="E226">
+        <v>601</v>
+      </c>
+      <c r="F226" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G226" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I226">
+        <v>42</v>
+      </c>
+      <c r="J226">
+        <v>8004</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226">
+        <v>0</v>
+      </c>
+      <c r="P226">
+        <v>0</v>
+      </c>
+      <c r="Q226">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>129218941</v>
+      </c>
+      <c r="E227">
+        <v>601</v>
+      </c>
+      <c r="F227" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G227" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I227">
+        <v>42</v>
+      </c>
+      <c r="J227">
+        <v>8004</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>0</v>
+      </c>
+      <c r="O227">
+        <v>0</v>
+      </c>
+      <c r="P227">
+        <v>0</v>
+      </c>
+      <c r="Q227">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>129219501</v>
+      </c>
+      <c r="E228">
+        <v>601</v>
+      </c>
+      <c r="F228" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G228" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I228">
+        <v>42</v>
+      </c>
+      <c r="J228">
+        <v>1118</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228">
+        <v>0</v>
+      </c>
+      <c r="P228">
+        <v>0</v>
+      </c>
+      <c r="Q228">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>129219759</v>
+      </c>
+      <c r="E229">
+        <v>601</v>
+      </c>
+      <c r="F229" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G229" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I229">
+        <v>42</v>
+      </c>
+      <c r="J229">
+        <v>8003</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>0</v>
+      </c>
+      <c r="O229">
+        <v>0</v>
+      </c>
+      <c r="P229">
+        <v>0</v>
+      </c>
+      <c r="Q229">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>129219793</v>
+      </c>
+      <c r="E230">
+        <v>601</v>
+      </c>
+      <c r="F230" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G230" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I230">
+        <v>42</v>
+      </c>
+      <c r="J230">
+        <v>8013</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>0</v>
+      </c>
+      <c r="O230">
+        <v>0</v>
+      </c>
+      <c r="P230">
+        <v>0</v>
+      </c>
+      <c r="Q230">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>129221142</v>
+      </c>
+      <c r="E231">
+        <v>601</v>
+      </c>
+      <c r="F231" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G231" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I231">
+        <v>42</v>
+      </c>
+      <c r="J231">
+        <v>8013</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>0</v>
+      </c>
+      <c r="O231">
+        <v>0</v>
+      </c>
+      <c r="P231">
+        <v>0</v>
+      </c>
+      <c r="Q231">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>129222096</v>
+      </c>
+      <c r="E232">
+        <v>601</v>
+      </c>
+      <c r="F232" s="2">
+        <v>45542</v>
+      </c>
+      <c r="G232" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I232">
+        <v>42</v>
+      </c>
+      <c r="J232">
+        <v>8013</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232">
+        <v>0</v>
+      </c>
+      <c r="P232">
+        <v>0</v>
+      </c>
+      <c r="Q232">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>129222344</v>
+      </c>
+      <c r="E233">
+        <v>601</v>
+      </c>
+      <c r="F233" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G233" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I233">
+        <v>42</v>
+      </c>
+      <c r="J233">
+        <v>8001</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>0</v>
+      </c>
+      <c r="O233">
+        <v>0</v>
+      </c>
+      <c r="P233">
+        <v>0</v>
+      </c>
+      <c r="Q233">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>129222507</v>
+      </c>
+      <c r="E234">
+        <v>601</v>
+      </c>
+      <c r="F234" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G234" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I234">
+        <v>42</v>
+      </c>
+      <c r="J234">
+        <v>8004</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234">
+        <v>0</v>
+      </c>
+      <c r="P234">
+        <v>0</v>
+      </c>
+      <c r="Q234">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>129222666</v>
+      </c>
+      <c r="E235">
+        <v>601</v>
+      </c>
+      <c r="F235" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G235" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I235">
+        <v>42</v>
+      </c>
+      <c r="J235">
+        <v>8004</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235">
+        <v>0</v>
+      </c>
+      <c r="P235">
+        <v>0</v>
+      </c>
+      <c r="Q235">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>129223343</v>
+      </c>
+      <c r="E236">
+        <v>601</v>
+      </c>
+      <c r="F236" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G236" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I236">
+        <v>42</v>
+      </c>
+      <c r="J236">
+        <v>8004</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236">
+        <v>0</v>
+      </c>
+      <c r="P236">
+        <v>0</v>
+      </c>
+      <c r="Q236">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>129223449</v>
+      </c>
+      <c r="E237">
+        <v>601</v>
+      </c>
+      <c r="F237" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G237" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I237">
+        <v>42</v>
+      </c>
+      <c r="J237">
+        <v>8004</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>0</v>
+      </c>
+      <c r="N237">
+        <v>0</v>
+      </c>
+      <c r="O237">
+        <v>0</v>
+      </c>
+      <c r="P237">
+        <v>0</v>
+      </c>
+      <c r="Q237">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>129223850</v>
+      </c>
+      <c r="E238">
+        <v>601</v>
+      </c>
+      <c r="F238" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G238" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I238">
+        <v>42</v>
+      </c>
+      <c r="J238">
+        <v>8004</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <v>0</v>
+      </c>
+      <c r="P238">
+        <v>0</v>
+      </c>
+      <c r="Q238">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>129224263</v>
+      </c>
+      <c r="E239">
+        <v>601</v>
+      </c>
+      <c r="F239" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G239" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I239">
+        <v>42</v>
+      </c>
+      <c r="J239">
+        <v>8004</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239">
+        <v>0</v>
+      </c>
+      <c r="N239">
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <v>0</v>
+      </c>
+      <c r="P239">
+        <v>0</v>
+      </c>
+      <c r="Q239">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>129225476</v>
+      </c>
+      <c r="E240">
+        <v>601</v>
+      </c>
+      <c r="F240" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G240" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I240">
+        <v>42</v>
+      </c>
+      <c r="J240">
+        <v>8004</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>0</v>
+      </c>
+      <c r="O240">
+        <v>0</v>
+      </c>
+      <c r="P240">
+        <v>0</v>
+      </c>
+      <c r="Q240">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>129225680</v>
+      </c>
+      <c r="E241">
+        <v>601</v>
+      </c>
+      <c r="F241" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G241" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I241">
+        <v>42</v>
+      </c>
+      <c r="J241">
+        <v>8004</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>0</v>
+      </c>
+      <c r="O241">
+        <v>0</v>
+      </c>
+      <c r="P241">
+        <v>0</v>
+      </c>
+      <c r="Q241">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>129225721</v>
+      </c>
+      <c r="E242">
+        <v>601</v>
+      </c>
+      <c r="F242" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G242" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I242">
+        <v>42</v>
+      </c>
+      <c r="J242">
+        <v>8004</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>0</v>
+      </c>
+      <c r="P242">
+        <v>0</v>
+      </c>
+      <c r="Q242">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>129225802</v>
+      </c>
+      <c r="E243">
+        <v>601</v>
+      </c>
+      <c r="F243" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G243" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I243">
+        <v>42</v>
+      </c>
+      <c r="J243">
+        <v>8004</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>0</v>
+      </c>
+      <c r="O243">
+        <v>0</v>
+      </c>
+      <c r="P243">
+        <v>0</v>
+      </c>
+      <c r="Q243">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>129225892</v>
+      </c>
+      <c r="E244">
+        <v>601</v>
+      </c>
+      <c r="F244" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G244" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I244">
+        <v>42</v>
+      </c>
+      <c r="J244">
+        <v>8004</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>0</v>
+      </c>
+      <c r="O244">
+        <v>0</v>
+      </c>
+      <c r="P244">
+        <v>0</v>
+      </c>
+      <c r="Q244">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>129225916</v>
+      </c>
+      <c r="E245">
+        <v>601</v>
+      </c>
+      <c r="F245" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G245" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I245">
+        <v>42</v>
+      </c>
+      <c r="J245">
+        <v>8004</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245">
+        <v>0</v>
+      </c>
+      <c r="P245">
+        <v>0</v>
+      </c>
+      <c r="Q245">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>129226045</v>
+      </c>
+      <c r="E246">
+        <v>601</v>
+      </c>
+      <c r="F246" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G246" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I246">
+        <v>42</v>
+      </c>
+      <c r="J246">
+        <v>8004</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246">
+        <v>0</v>
+      </c>
+      <c r="P246">
+        <v>0</v>
+      </c>
+      <c r="Q246">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>129226582</v>
+      </c>
+      <c r="E247">
+        <v>601</v>
+      </c>
+      <c r="F247" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G247" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I247">
+        <v>42</v>
+      </c>
+      <c r="J247">
+        <v>8013</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>0</v>
+      </c>
+      <c r="O247">
+        <v>0</v>
+      </c>
+      <c r="P247">
+        <v>0</v>
+      </c>
+      <c r="Q247">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>129226804</v>
+      </c>
+      <c r="E248">
+        <v>601</v>
+      </c>
+      <c r="F248" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G248" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I248">
+        <v>42</v>
+      </c>
+      <c r="J248">
+        <v>8013</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>0</v>
+      </c>
+      <c r="O248">
+        <v>0</v>
+      </c>
+      <c r="P248">
+        <v>0</v>
+      </c>
+      <c r="Q248">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>129226842</v>
+      </c>
+      <c r="E249">
+        <v>601</v>
+      </c>
+      <c r="F249" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G249" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I249">
+        <v>42</v>
+      </c>
+      <c r="J249">
+        <v>8013</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>0</v>
+      </c>
+      <c r="O249">
+        <v>0</v>
+      </c>
+      <c r="P249">
+        <v>0</v>
+      </c>
+      <c r="Q249">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>129227347</v>
+      </c>
+      <c r="E250">
+        <v>601</v>
+      </c>
+      <c r="F250" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G250" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I250">
+        <v>42</v>
+      </c>
+      <c r="J250">
+        <v>8004</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>0</v>
+      </c>
+      <c r="O250">
+        <v>0</v>
+      </c>
+      <c r="P250">
+        <v>0</v>
+      </c>
+      <c r="Q250">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>129227854</v>
+      </c>
+      <c r="E251">
+        <v>601</v>
+      </c>
+      <c r="F251" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G251" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I251">
+        <v>42</v>
+      </c>
+      <c r="J251">
+        <v>8004</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
+        <v>0</v>
+      </c>
+      <c r="O251">
+        <v>0</v>
+      </c>
+      <c r="P251">
+        <v>0</v>
+      </c>
+      <c r="Q251">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>129227855</v>
+      </c>
+      <c r="E252">
+        <v>601</v>
+      </c>
+      <c r="F252" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G252" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I252">
+        <v>42</v>
+      </c>
+      <c r="J252">
+        <v>8004</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>0</v>
+      </c>
+      <c r="P252">
+        <v>0</v>
+      </c>
+      <c r="Q252">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>129227856</v>
+      </c>
+      <c r="E253">
+        <v>601</v>
+      </c>
+      <c r="F253" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G253" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I253">
+        <v>42</v>
+      </c>
+      <c r="J253">
+        <v>8004</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>0</v>
+      </c>
+      <c r="P253">
+        <v>0</v>
+      </c>
+      <c r="Q253">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>129227898</v>
+      </c>
+      <c r="E254">
+        <v>601</v>
+      </c>
+      <c r="F254" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G254" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I254">
+        <v>42</v>
+      </c>
+      <c r="J254">
+        <v>8013</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>0</v>
+      </c>
+      <c r="O254">
+        <v>0</v>
+      </c>
+      <c r="P254">
+        <v>0</v>
+      </c>
+      <c r="Q254">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>129228279</v>
+      </c>
+      <c r="E255">
+        <v>601</v>
+      </c>
+      <c r="F255" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G255" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I255">
+        <v>42</v>
+      </c>
+      <c r="J255">
+        <v>8004</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>0</v>
+      </c>
+      <c r="O255">
+        <v>0</v>
+      </c>
+      <c r="P255">
+        <v>0</v>
+      </c>
+      <c r="Q255">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>129228642</v>
+      </c>
+      <c r="E256">
+        <v>601</v>
+      </c>
+      <c r="F256" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G256" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I256">
+        <v>42</v>
+      </c>
+      <c r="J256">
+        <v>8013</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>0</v>
+      </c>
+      <c r="O256">
+        <v>0</v>
+      </c>
+      <c r="P256">
+        <v>0</v>
+      </c>
+      <c r="Q256">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>129228672</v>
+      </c>
+      <c r="E257">
+        <v>601</v>
+      </c>
+      <c r="F257" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G257" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I257">
+        <v>42</v>
+      </c>
+      <c r="J257">
+        <v>8013</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>0</v>
+      </c>
+      <c r="O257">
+        <v>0</v>
+      </c>
+      <c r="P257">
+        <v>0</v>
+      </c>
+      <c r="Q257">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>129228678</v>
+      </c>
+      <c r="E258">
+        <v>601</v>
+      </c>
+      <c r="F258" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G258" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I258">
+        <v>42</v>
+      </c>
+      <c r="J258">
+        <v>8013</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>0</v>
+      </c>
+      <c r="P258">
+        <v>0</v>
+      </c>
+      <c r="Q258">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>129229037</v>
+      </c>
+      <c r="E259">
+        <v>601</v>
+      </c>
+      <c r="F259" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G259" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I259">
+        <v>42</v>
+      </c>
+      <c r="J259">
+        <v>8004</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>0</v>
+      </c>
+      <c r="O259">
+        <v>0</v>
+      </c>
+      <c r="P259">
+        <v>0</v>
+      </c>
+      <c r="Q259">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>129229102</v>
+      </c>
+      <c r="E260">
+        <v>601</v>
+      </c>
+      <c r="F260" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G260" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I260">
+        <v>42</v>
+      </c>
+      <c r="J260">
+        <v>8004</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>0</v>
+      </c>
+      <c r="Q260">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>129229321</v>
+      </c>
+      <c r="E261">
+        <v>601</v>
+      </c>
+      <c r="F261" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G261" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I261">
+        <v>42</v>
+      </c>
+      <c r="J261">
+        <v>8004</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
+      </c>
+      <c r="N261">
+        <v>0</v>
+      </c>
+      <c r="O261">
+        <v>0</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>129229907</v>
+      </c>
+      <c r="E262">
+        <v>601</v>
+      </c>
+      <c r="F262" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G262" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I262">
+        <v>42</v>
+      </c>
+      <c r="J262">
+        <v>8013</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0</v>
+      </c>
+      <c r="Q262">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>129230337</v>
+      </c>
+      <c r="E263">
+        <v>601</v>
+      </c>
+      <c r="F263" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G263" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I263">
+        <v>42</v>
+      </c>
+      <c r="J263">
+        <v>8013</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
+      </c>
+      <c r="N263">
+        <v>0</v>
+      </c>
+      <c r="O263">
+        <v>0</v>
+      </c>
+      <c r="P263">
+        <v>0</v>
+      </c>
+      <c r="Q263">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>129230459</v>
+      </c>
+      <c r="E264">
+        <v>601</v>
+      </c>
+      <c r="F264" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G264" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I264">
+        <v>42</v>
+      </c>
+      <c r="J264">
+        <v>8013</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264">
+        <v>0</v>
+      </c>
+      <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0</v>
+      </c>
+      <c r="Q264">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>129230864</v>
+      </c>
+      <c r="E265">
+        <v>601</v>
+      </c>
+      <c r="F265" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G265" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I265">
+        <v>42</v>
+      </c>
+      <c r="J265">
+        <v>8013</v>
+      </c>
+      <c r="L265">
+        <v>0</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
+      </c>
+      <c r="N265">
+        <v>0</v>
+      </c>
+      <c r="O265">
+        <v>0</v>
+      </c>
+      <c r="P265">
+        <v>0</v>
+      </c>
+      <c r="Q265">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>129230979</v>
+      </c>
+      <c r="E266">
+        <v>601</v>
+      </c>
+      <c r="F266" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G266" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I266">
+        <v>42</v>
+      </c>
+      <c r="J266">
+        <v>8004</v>
+      </c>
+      <c r="L266">
+        <v>0</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>0</v>
+      </c>
+      <c r="O266">
+        <v>0</v>
+      </c>
+      <c r="P266">
+        <v>0</v>
+      </c>
+      <c r="Q266">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>129232353</v>
+      </c>
+      <c r="E267">
+        <v>601</v>
+      </c>
+      <c r="F267" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G267" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I267">
+        <v>42</v>
+      </c>
+      <c r="J267">
+        <v>8004</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+      <c r="M267">
+        <v>0</v>
+      </c>
+      <c r="N267">
+        <v>0</v>
+      </c>
+      <c r="O267">
+        <v>0</v>
+      </c>
+      <c r="P267">
+        <v>0</v>
+      </c>
+      <c r="Q267">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>129232846</v>
+      </c>
+      <c r="E268">
+        <v>601</v>
+      </c>
+      <c r="F268" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G268" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I268">
+        <v>42</v>
+      </c>
+      <c r="J268">
+        <v>8013</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+      <c r="M268">
+        <v>0</v>
+      </c>
+      <c r="N268">
+        <v>0</v>
+      </c>
+      <c r="O268">
+        <v>0</v>
+      </c>
+      <c r="P268">
+        <v>0</v>
+      </c>
+      <c r="Q268">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>129233403</v>
+      </c>
+      <c r="E269">
+        <v>601</v>
+      </c>
+      <c r="F269" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G269" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I269">
+        <v>42</v>
+      </c>
+      <c r="J269">
+        <v>8013</v>
+      </c>
+      <c r="L269">
+        <v>0</v>
+      </c>
+      <c r="M269">
+        <v>0</v>
+      </c>
+      <c r="N269">
+        <v>0</v>
+      </c>
+      <c r="O269">
+        <v>0</v>
+      </c>
+      <c r="P269">
+        <v>0</v>
+      </c>
+      <c r="Q269">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>129233449</v>
+      </c>
+      <c r="E270">
+        <v>601</v>
+      </c>
+      <c r="F270" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G270" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I270">
+        <v>42</v>
+      </c>
+      <c r="J270">
+        <v>8004</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+      <c r="M270">
+        <v>0</v>
+      </c>
+      <c r="N270">
+        <v>0</v>
+      </c>
+      <c r="O270">
+        <v>0</v>
+      </c>
+      <c r="P270">
+        <v>0</v>
+      </c>
+      <c r="Q270">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>129233980</v>
+      </c>
+      <c r="E271">
+        <v>601</v>
+      </c>
+      <c r="F271" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G271" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I271">
+        <v>42</v>
+      </c>
+      <c r="J271">
+        <v>8004</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+      <c r="M271">
+        <v>0</v>
+      </c>
+      <c r="N271">
+        <v>0</v>
+      </c>
+      <c r="O271">
+        <v>0</v>
+      </c>
+      <c r="P271">
+        <v>0</v>
+      </c>
+      <c r="Q271">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>129234006</v>
+      </c>
+      <c r="E272">
+        <v>601</v>
+      </c>
+      <c r="F272" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G272" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I272">
+        <v>42</v>
+      </c>
+      <c r="J272">
+        <v>8013</v>
+      </c>
+      <c r="L272">
+        <v>0</v>
+      </c>
+      <c r="M272">
+        <v>0</v>
+      </c>
+      <c r="N272">
+        <v>0</v>
+      </c>
+      <c r="O272">
+        <v>0</v>
+      </c>
+      <c r="P272">
+        <v>0</v>
+      </c>
+      <c r="Q272">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>129234081</v>
+      </c>
+      <c r="E273">
+        <v>601</v>
+      </c>
+      <c r="F273" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G273" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I273">
+        <v>42</v>
+      </c>
+      <c r="J273">
+        <v>8004</v>
+      </c>
+      <c r="L273">
+        <v>0</v>
+      </c>
+      <c r="M273">
+        <v>0</v>
+      </c>
+      <c r="N273">
+        <v>0</v>
+      </c>
+      <c r="O273">
+        <v>0</v>
+      </c>
+      <c r="P273">
+        <v>0</v>
+      </c>
+      <c r="Q273">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>129234086</v>
+      </c>
+      <c r="E274">
+        <v>601</v>
+      </c>
+      <c r="F274" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G274" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I274">
+        <v>42</v>
+      </c>
+      <c r="J274">
+        <v>8004</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+      <c r="M274">
+        <v>0</v>
+      </c>
+      <c r="N274">
+        <v>0</v>
+      </c>
+      <c r="O274">
+        <v>0</v>
+      </c>
+      <c r="P274">
+        <v>0</v>
+      </c>
+      <c r="Q274">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>129235161</v>
+      </c>
+      <c r="E275">
+        <v>601</v>
+      </c>
+      <c r="F275" s="2">
+        <v>45541</v>
+      </c>
+      <c r="G275" s="2">
+        <v>45541</v>
+      </c>
+      <c r="I275">
+        <v>42</v>
+      </c>
+      <c r="J275">
+        <v>8004</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
+      </c>
+      <c r="N275">
+        <v>0</v>
+      </c>
+      <c r="O275">
+        <v>0</v>
+      </c>
+      <c r="P275">
+        <v>0</v>
+      </c>
+      <c r="Q275">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$169</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$80</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$Q$158</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
@@ -607,7 +607,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>125300411</v>
+        <v>129258249</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -622,10 +622,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G4" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -634,7 +634,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>125333015</v>
+        <v>129258946</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,10 +675,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="G5" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -687,7 +687,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>125359003</v>
+        <v>129267204</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -728,10 +728,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G6" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -740,7 +740,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>125442413</v>
+        <v>129268021</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -781,10 +781,10 @@
         <v>1211</v>
       </c>
       <c r="F7" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G7" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>125583356</v>
+        <v>129268076</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -834,10 +834,10 @@
         <v>1211</v>
       </c>
       <c r="F8" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G8" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -846,7 +846,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>125586889</v>
+        <v>129268797</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -887,10 +887,10 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G9" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -899,7 +899,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>125654857</v>
+        <v>129269192</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -937,13 +937,13 @@
         <v>17</v>
       </c>
       <c r="E10">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G10" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>125699019</v>
+        <v>125371391</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -993,7 +993,7 @@
         <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G11" s="1">
         <v>45545</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>125700493</v>
+        <v>125579863</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1043,10 +1043,10 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F12" s="1">
-        <v>45542</v>
+        <v>45545</v>
       </c>
       <c r="G12" s="1">
         <v>45545</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125984256</v>
+        <v>125766342</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1099,7 +1099,7 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G13" s="1">
         <v>45545</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>126169434</v>
+        <v>125834327</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,10 +1152,10 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45544</v>
+        <v>45539</v>
       </c>
       <c r="G14" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>126350088</v>
+        <v>125973674</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1205,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G15" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>126427702</v>
+        <v>126011689</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1258,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G16" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>126427803</v>
+        <v>126064870</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1311,10 +1311,10 @@
         <v>1211</v>
       </c>
       <c r="F17" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G17" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>126454971</v>
+        <v>126079805</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1361,13 +1361,13 @@
         <v>17</v>
       </c>
       <c r="E18">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F18" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G18" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>126493896</v>
+        <v>126165673</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1417,10 +1417,10 @@
         <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G19" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126663942</v>
+        <v>126186459</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1473,7 +1473,7 @@
         <v>45544</v>
       </c>
       <c r="G20" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>126792261</v>
+        <v>126254887</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1523,10 +1523,10 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G21" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>127025678</v>
+        <v>126255796</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1573,13 +1573,13 @@
         <v>17</v>
       </c>
       <c r="E22">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F22" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G22" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>127038451</v>
+        <v>126311203</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1629,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G23" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>127059953</v>
+        <v>126564456</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1679,13 +1679,13 @@
         <v>17</v>
       </c>
       <c r="E24">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G24" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>127061856</v>
+        <v>126629834</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,7 +1735,7 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G25" s="1">
         <v>45545</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>127067686</v>
+        <v>126828458</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1788,10 +1788,10 @@
         <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G26" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>127156690</v>
+        <v>127067241</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1841,10 +1841,10 @@
         <v>1211</v>
       </c>
       <c r="F27" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G27" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>127234320</v>
+        <v>127111265</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1891,13 +1891,13 @@
         <v>17</v>
       </c>
       <c r="E28">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G28" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>127272836</v>
+        <v>127127223</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1947,10 +1947,10 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G29" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>127476034</v>
+        <v>127134867</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -2000,10 +2000,10 @@
         <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G30" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127526200</v>
+        <v>127228055</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2053,10 +2053,10 @@
         <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G31" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>127546789</v>
+        <v>127305630</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2106,7 +2106,7 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="G32" s="1">
         <v>45545</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127636408</v>
+        <v>127563636</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2159,10 +2159,10 @@
         <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G33" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127661612</v>
+        <v>127576562</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2209,13 +2209,13 @@
         <v>17</v>
       </c>
       <c r="E34">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G34" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127684492</v>
+        <v>127606262</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2265,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G35" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127706462</v>
+        <v>127635050</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2318,10 +2318,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G36" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127708717</v>
+        <v>127831038</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2371,10 +2371,10 @@
         <v>1211</v>
       </c>
       <c r="F37" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G37" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127817666</v>
+        <v>127847709</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,10 +2424,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G38" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127934450</v>
+        <v>127947974</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2477,10 +2477,10 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45544</v>
+        <v>45541</v>
       </c>
       <c r="G39" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>128081134</v>
+        <v>128083490</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2527,13 +2527,13 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F40" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G40" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>128100590</v>
+        <v>128085519</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2583,10 +2583,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G41" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>128140148</v>
+        <v>128204367</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2636,10 +2636,10 @@
         <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G42" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>128228221</v>
+        <v>128220589</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,10 +2689,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G43" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>128291167</v>
+        <v>128268252</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2739,13 +2739,13 @@
         <v>17</v>
       </c>
       <c r="E44">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F44" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G44" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>128406882</v>
+        <v>128291804</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,7 +2795,7 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G45" s="1">
         <v>45545</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>128435465</v>
+        <v>128456931</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2848,7 +2848,7 @@
         <v>1211</v>
       </c>
       <c r="F46" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="G46" s="1">
         <v>45545</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>128441496</v>
+        <v>128632296</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2898,13 +2898,13 @@
         <v>17</v>
       </c>
       <c r="E47">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G47" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>128470367</v>
+        <v>128763123</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2951,13 +2951,13 @@
         <v>17</v>
       </c>
       <c r="E48">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F48" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G48" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>128493556</v>
+        <v>128782394</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3007,7 +3007,7 @@
         <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="G49" s="1">
         <v>45545</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>128525041</v>
+        <v>128793066</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3060,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G50" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>128581523</v>
+        <v>128798903</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3113,10 +3113,10 @@
         <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G51" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>128607619</v>
+        <v>128820712</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3166,10 +3166,10 @@
         <v>1211</v>
       </c>
       <c r="F52" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G52" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>128715711</v>
+        <v>128862015</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3219,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G53" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>128782422</v>
+        <v>128917387</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3272,10 +3272,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G54" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>128809037</v>
+        <v>128945240</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3325,10 +3325,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G55" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>128828053</v>
+        <v>128987686</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3378,10 +3378,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G56" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>128901619</v>
+        <v>129092682</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3431,10 +3431,10 @@
         <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G57" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>128994969</v>
+        <v>129095690</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3481,13 +3481,13 @@
         <v>17</v>
       </c>
       <c r="E58">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F58" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G58" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>129115744</v>
+        <v>129110151</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3534,13 +3534,13 @@
         <v>17</v>
       </c>
       <c r="E59">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45534</v>
+        <v>45545</v>
       </c>
       <c r="G59" s="1">
-        <v>45534</v>
+        <v>45545</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129129958</v>
+        <v>129115744</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3587,13 +3587,13 @@
         <v>17</v>
       </c>
       <c r="E60">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F60" s="1">
-        <v>45544</v>
+        <v>45534</v>
       </c>
       <c r="G60" s="1">
-        <v>45544</v>
+        <v>45534</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>129155094</v>
+        <v>129149024</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3696,10 +3696,10 @@
         <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G62" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129166957</v>
+        <v>129175013</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3749,10 +3749,10 @@
         <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G63" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129180851</v>
+        <v>129187945</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3799,13 +3799,13 @@
         <v>17</v>
       </c>
       <c r="E64">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F64" s="1">
-        <v>45544</v>
+        <v>45539</v>
       </c>
       <c r="G64" s="1">
-        <v>45544</v>
+        <v>45539</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129187945</v>
+        <v>129191152</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3852,13 +3852,13 @@
         <v>17</v>
       </c>
       <c r="E65">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45539</v>
+        <v>45544</v>
       </c>
       <c r="G65" s="1">
-        <v>45539</v>
+        <v>45546</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129196235</v>
+        <v>129198879</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3905,13 +3905,13 @@
         <v>17</v>
       </c>
       <c r="E66">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F66" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G66" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129202043</v>
+        <v>129205733</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3961,10 +3961,10 @@
         <v>1211</v>
       </c>
       <c r="F67" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G67" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129206313</v>
+        <v>129206141</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4011,13 +4011,13 @@
         <v>17</v>
       </c>
       <c r="E68">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F68" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G68" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129225196</v>
+        <v>129209489</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4064,13 +4064,13 @@
         <v>17</v>
       </c>
       <c r="E69">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F69" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="G69" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129226577</v>
+        <v>129213290</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4117,13 +4117,13 @@
         <v>17</v>
       </c>
       <c r="E70">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F70" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G70" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129227825</v>
+        <v>129214299</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4173,10 +4173,10 @@
         <v>1211</v>
       </c>
       <c r="F71" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G71" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129228737</v>
+        <v>129215344</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4226,10 +4226,10 @@
         <v>1211</v>
       </c>
       <c r="F72" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G72" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129241833</v>
+        <v>129221810</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4276,13 +4276,13 @@
         <v>17</v>
       </c>
       <c r="E73">
-        <v>2013</v>
+        <v>1213</v>
       </c>
       <c r="F73" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G73" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129252899</v>
+        <v>129221921</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4329,13 +4329,13 @@
         <v>17</v>
       </c>
       <c r="E74">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F74" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G74" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>128749254</v>
+        <v>129224319</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4385,10 +4385,10 @@
         <v>1211</v>
       </c>
       <c r="F75" s="1">
-        <v>45510</v>
+        <v>45545</v>
       </c>
       <c r="G75" s="1">
-        <v>45511</v>
+        <v>45545</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -4397,7 +4397,7 @@
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K75" t="s">
         <v>17</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129039074</v>
+        <v>129236255</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4435,13 +4435,13 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="1">
-        <v>45530</v>
+        <v>45545</v>
       </c>
       <c r="G76" s="1">
-        <v>45531</v>
+        <v>45545</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -4450,7 +4450,7 @@
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K76" t="s">
         <v>17</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129110148</v>
+        <v>129237646</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4488,13 +4488,13 @@
         <v>17</v>
       </c>
       <c r="E77">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F77" s="1">
-        <v>45533</v>
+        <v>45545</v>
       </c>
       <c r="G77" s="1">
-        <v>45534</v>
+        <v>45545</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4503,7 +4503,7 @@
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K77" t="s">
         <v>17</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129190578</v>
+        <v>129241386</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4544,10 +4544,10 @@
         <v>1211</v>
       </c>
       <c r="F78" s="1">
-        <v>45539</v>
+        <v>45545</v>
       </c>
       <c r="G78" s="1">
-        <v>45540</v>
+        <v>45545</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4556,7 +4556,7 @@
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K78" t="s">
         <v>17</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129205888</v>
+        <v>129251692</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4594,13 +4594,13 @@
         <v>17</v>
       </c>
       <c r="E79">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F79" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="G79" s="1">
-        <v>45541</v>
+        <v>45545</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4609,7 +4609,7 @@
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K79" t="s">
         <v>17</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129205969</v>
+        <v>129252899</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4647,42 +4647,4176 @@
         <v>17</v>
       </c>
       <c r="E80">
+        <v>2013</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8001</v>
+      </c>
+      <c r="K80" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>129258438</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81">
+        <v>1211</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G81" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8001</v>
+      </c>
+      <c r="K81" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>129262971</v>
+      </c>
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H82" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>17</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>129263151</v>
+      </c>
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83">
+        <v>2002</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G83" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H83" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8001</v>
+      </c>
+      <c r="K83" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>129264118</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G84" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H84" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8001</v>
+      </c>
+      <c r="K84" t="s">
+        <v>17</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>129264828</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85">
+        <v>1211</v>
+      </c>
+      <c r="F85" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H85" t="s">
+        <v>17</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8001</v>
+      </c>
+      <c r="K85" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>129268191</v>
+      </c>
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G86" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H86" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8001</v>
+      </c>
+      <c r="K86" t="s">
+        <v>17</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>129268195</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87">
+        <v>2013</v>
+      </c>
+      <c r="F87" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H87" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8001</v>
+      </c>
+      <c r="K87" t="s">
+        <v>17</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>129268527</v>
+      </c>
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8001</v>
+      </c>
+      <c r="K88" t="s">
+        <v>17</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>129268536</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89">
+        <v>2013</v>
+      </c>
+      <c r="F89" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H89" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8001</v>
+      </c>
+      <c r="K89" t="s">
+        <v>17</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>129268557</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G90" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H90" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8001</v>
+      </c>
+      <c r="K90" t="s">
+        <v>17</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>129269328</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91">
+        <v>2013</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G91" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H91" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8001</v>
+      </c>
+      <c r="K91" t="s">
+        <v>17</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>129270289</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G92" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H92" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8001</v>
+      </c>
+      <c r="K92" t="s">
+        <v>17</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>129271164</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G93" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H93" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8001</v>
+      </c>
+      <c r="K93" t="s">
+        <v>17</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>129272475</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G94" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H94" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8001</v>
+      </c>
+      <c r="K94" t="s">
+        <v>17</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>129273628</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G95" s="1">
+        <v>45545</v>
+      </c>
+      <c r="H95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>128749254</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96">
+        <v>1211</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45510</v>
+      </c>
+      <c r="G96" s="1">
+        <v>45511</v>
+      </c>
+      <c r="H96" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8021</v>
+      </c>
+      <c r="K96" t="s">
+        <v>17</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>129039074</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97">
+        <v>2013</v>
+      </c>
+      <c r="F97" s="1">
+        <v>45530</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45531</v>
+      </c>
+      <c r="H97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8021</v>
+      </c>
+      <c r="K97" t="s">
+        <v>17</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>129110148</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98">
+        <v>2013</v>
+      </c>
+      <c r="F98" s="1">
+        <v>45533</v>
+      </c>
+      <c r="G98" s="1">
+        <v>45534</v>
+      </c>
+      <c r="H98" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8021</v>
+      </c>
+      <c r="K98" t="s">
+        <v>17</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>129190578</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99">
+        <v>1211</v>
+      </c>
+      <c r="F99" s="1">
+        <v>45539</v>
+      </c>
+      <c r="G99" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8021</v>
+      </c>
+      <c r="K99" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>129258174</v>
+      </c>
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100">
+        <v>2002</v>
+      </c>
+      <c r="F100" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G100" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H100" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8021</v>
+      </c>
+      <c r="K100" t="s">
+        <v>17</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>129258249</v>
+      </c>
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101">
+        <v>1211</v>
+      </c>
+      <c r="F101" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G101" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H101" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8021</v>
+      </c>
+      <c r="K101" t="s">
+        <v>17</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>129258946</v>
+      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102">
+        <v>1211</v>
+      </c>
+      <c r="F102" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G102" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H102" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8021</v>
+      </c>
+      <c r="K102" t="s">
+        <v>17</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>129260372</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103">
+        <v>1211</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G103" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H103" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8021</v>
+      </c>
+      <c r="K103" t="s">
+        <v>17</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>129262213</v>
+      </c>
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104">
+        <v>2013</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G104" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H104" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8021</v>
+      </c>
+      <c r="K104" t="s">
+        <v>17</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>129266700</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105">
+        <v>2013</v>
+      </c>
+      <c r="F105" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G105" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H105" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8021</v>
+      </c>
+      <c r="K105" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>129267204</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106">
+        <v>1211</v>
+      </c>
+      <c r="F106" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G106" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8021</v>
+      </c>
+      <c r="K106" t="s">
+        <v>17</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>129268021</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107">
+        <v>1211</v>
+      </c>
+      <c r="F107" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G107" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H107" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8021</v>
+      </c>
+      <c r="K107" t="s">
+        <v>17</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>129268076</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108">
+        <v>1211</v>
+      </c>
+      <c r="F108" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G108" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H108" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8021</v>
+      </c>
+      <c r="K108" t="s">
+        <v>17</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>129268797</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109">
+        <v>1211</v>
+      </c>
+      <c r="F109" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G109" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8021</v>
+      </c>
+      <c r="K109" t="s">
+        <v>17</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>129269192</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110">
+        <v>1211</v>
+      </c>
+      <c r="F110" s="1">
+        <v>45545</v>
+      </c>
+      <c r="G110" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8021</v>
+      </c>
+      <c r="K110" t="s">
+        <v>17</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>129220638</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111">
         <v>601</v>
       </c>
-      <c r="F80" s="1">
-        <v>45541</v>
-      </c>
-      <c r="G80" s="1">
-        <v>45541</v>
-      </c>
-      <c r="H80" t="s">
-        <v>17</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
+      <c r="F111" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G111" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
         <v>8004</v>
       </c>
-      <c r="K80" t="s">
-        <v>17</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
+      <c r="K111" t="s">
+        <v>17</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>129240278</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G112" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8004</v>
+      </c>
+      <c r="K112" t="s">
+        <v>17</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>129241275</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G113" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8004</v>
+      </c>
+      <c r="K113" t="s">
+        <v>17</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>129241539</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G114" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8004</v>
+      </c>
+      <c r="K114" t="s">
+        <v>17</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>129241604</v>
+      </c>
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G115" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8004</v>
+      </c>
+      <c r="K115" t="s">
+        <v>17</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>129241983</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G116" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8004</v>
+      </c>
+      <c r="K116" t="s">
+        <v>17</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>129242802</v>
+      </c>
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G117" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8004</v>
+      </c>
+      <c r="K117" t="s">
+        <v>17</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>129243599</v>
+      </c>
+      <c r="B118" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G118" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8004</v>
+      </c>
+      <c r="K118" t="s">
+        <v>17</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>129243783</v>
+      </c>
+      <c r="B119" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G119" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8004</v>
+      </c>
+      <c r="K119" t="s">
+        <v>17</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>129243881</v>
+      </c>
+      <c r="B120" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G120" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8004</v>
+      </c>
+      <c r="K120" t="s">
+        <v>17</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>129244078</v>
+      </c>
+      <c r="B121" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G121" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8004</v>
+      </c>
+      <c r="K121" t="s">
+        <v>17</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>129244148</v>
+      </c>
+      <c r="B122" t="s">
+        <v>17</v>
+      </c>
+      <c r="C122" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G122" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8004</v>
+      </c>
+      <c r="K122" t="s">
+        <v>17</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>129246781</v>
+      </c>
+      <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G123" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8004</v>
+      </c>
+      <c r="K123" t="s">
+        <v>17</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>129247185</v>
+      </c>
+      <c r="B124" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G124" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8004</v>
+      </c>
+      <c r="K124" t="s">
+        <v>17</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>129247308</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G125" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8004</v>
+      </c>
+      <c r="K125" t="s">
+        <v>17</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>129247455</v>
+      </c>
+      <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126">
+        <v>601</v>
+      </c>
+      <c r="F126" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G126" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8013</v>
+      </c>
+      <c r="K126" t="s">
+        <v>17</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>129247609</v>
+      </c>
+      <c r="B127" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127">
+        <v>601</v>
+      </c>
+      <c r="F127" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G127" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8004</v>
+      </c>
+      <c r="K127" t="s">
+        <v>17</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>129247620</v>
+      </c>
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128">
+        <v>601</v>
+      </c>
+      <c r="F128" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G128" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8004</v>
+      </c>
+      <c r="K128" t="s">
+        <v>17</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>129247871</v>
+      </c>
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129">
+        <v>601</v>
+      </c>
+      <c r="F129" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G129" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8004</v>
+      </c>
+      <c r="K129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129248327</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130">
+        <v>601</v>
+      </c>
+      <c r="F130" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G130" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8004</v>
+      </c>
+      <c r="K130" t="s">
+        <v>17</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>129248718</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131">
+        <v>601</v>
+      </c>
+      <c r="F131" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G131" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8013</v>
+      </c>
+      <c r="K131" t="s">
+        <v>17</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>129249252</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132">
+        <v>601</v>
+      </c>
+      <c r="F132" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G132" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8004</v>
+      </c>
+      <c r="K132" t="s">
+        <v>17</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>129249615</v>
+      </c>
+      <c r="B133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133">
+        <v>601</v>
+      </c>
+      <c r="F133" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G133" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8004</v>
+      </c>
+      <c r="K133" t="s">
+        <v>17</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>129249978</v>
+      </c>
+      <c r="B134" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134">
+        <v>601</v>
+      </c>
+      <c r="F134" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G134" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8004</v>
+      </c>
+      <c r="K134" t="s">
+        <v>17</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>129250532</v>
+      </c>
+      <c r="B135" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G135" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8004</v>
+      </c>
+      <c r="K135" t="s">
+        <v>17</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>129250695</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G136" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8004</v>
+      </c>
+      <c r="K136" t="s">
+        <v>17</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>129252787</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G137" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8013</v>
+      </c>
+      <c r="K137" t="s">
+        <v>17</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>129253748</v>
+      </c>
+      <c r="B138" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G138" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>1118</v>
+      </c>
+      <c r="K138" t="s">
+        <v>17</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>129254046</v>
+      </c>
+      <c r="B139" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G139" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="K139" t="s">
+        <v>17</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>129254186</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140">
+        <v>601</v>
+      </c>
+      <c r="F140" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G140" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8004</v>
+      </c>
+      <c r="K140" t="s">
+        <v>17</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>129254437</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141">
+        <v>601</v>
+      </c>
+      <c r="F141" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G141" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8004</v>
+      </c>
+      <c r="K141" t="s">
+        <v>17</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>129254466</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142">
+        <v>601</v>
+      </c>
+      <c r="F142" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G142" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8004</v>
+      </c>
+      <c r="K142" t="s">
+        <v>17</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>129254824</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143">
+        <v>601</v>
+      </c>
+      <c r="F143" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G143" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>1118</v>
+      </c>
+      <c r="K143" t="s">
+        <v>17</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>129254882</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144">
+        <v>601</v>
+      </c>
+      <c r="F144" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G144" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8004</v>
+      </c>
+      <c r="K144" t="s">
+        <v>17</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>129255469</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145">
+        <v>601</v>
+      </c>
+      <c r="F145" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G145" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8004</v>
+      </c>
+      <c r="K145" t="s">
+        <v>17</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>129255983</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146">
+        <v>601</v>
+      </c>
+      <c r="F146" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G146" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8004</v>
+      </c>
+      <c r="K146" t="s">
+        <v>17</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>129248327</v>
+      </c>
+      <c r="B147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147">
+        <v>601</v>
+      </c>
+      <c r="F147" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G147" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>8004</v>
+      </c>
+      <c r="K147" t="s">
+        <v>17</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>129241671</v>
+      </c>
+      <c r="B148" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148">
+        <v>601</v>
+      </c>
+      <c r="F148" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G148" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>8004</v>
+      </c>
+      <c r="K148" t="s">
+        <v>17</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>129243689</v>
+      </c>
+      <c r="B149" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149">
+        <v>601</v>
+      </c>
+      <c r="F149" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G149" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
+        <v>8004</v>
+      </c>
+      <c r="K149" t="s">
+        <v>17</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>129245312</v>
+      </c>
+      <c r="B150" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150">
+        <v>601</v>
+      </c>
+      <c r="F150" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G150" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>8004</v>
+      </c>
+      <c r="K150" t="s">
+        <v>17</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>129245622</v>
+      </c>
+      <c r="B151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151">
+        <v>601</v>
+      </c>
+      <c r="F151" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G151" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151">
+        <v>42</v>
+      </c>
+      <c r="J151">
+        <v>8004</v>
+      </c>
+      <c r="K151" t="s">
+        <v>17</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>129246423</v>
+      </c>
+      <c r="B152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152">
+        <v>601</v>
+      </c>
+      <c r="F152" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G152" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152">
+        <v>42</v>
+      </c>
+      <c r="J152">
+        <v>8004</v>
+      </c>
+      <c r="K152" t="s">
+        <v>17</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>129247017</v>
+      </c>
+      <c r="B153" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153">
+        <v>601</v>
+      </c>
+      <c r="F153" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G153" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153">
+        <v>42</v>
+      </c>
+      <c r="J153">
+        <v>8004</v>
+      </c>
+      <c r="K153" t="s">
+        <v>17</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>129248040</v>
+      </c>
+      <c r="B154" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154">
+        <v>601</v>
+      </c>
+      <c r="F154" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G154" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154">
+        <v>42</v>
+      </c>
+      <c r="J154">
+        <v>8004</v>
+      </c>
+      <c r="K154" t="s">
+        <v>17</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>129248418</v>
+      </c>
+      <c r="B155" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155">
+        <v>601</v>
+      </c>
+      <c r="F155" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G155" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155">
+        <v>42</v>
+      </c>
+      <c r="J155">
+        <v>8004</v>
+      </c>
+      <c r="K155" t="s">
+        <v>17</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>129249085</v>
+      </c>
+      <c r="B156" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156">
+        <v>601</v>
+      </c>
+      <c r="F156" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G156" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156">
+        <v>42</v>
+      </c>
+      <c r="J156">
+        <v>8004</v>
+      </c>
+      <c r="K156" t="s">
+        <v>17</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>129253589</v>
+      </c>
+      <c r="B157" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157">
+        <v>601</v>
+      </c>
+      <c r="F157" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G157" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157">
+        <v>42</v>
+      </c>
+      <c r="J157">
+        <v>8004</v>
+      </c>
+      <c r="K157" t="s">
+        <v>17</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+      <c r="Q157">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>129253794</v>
+      </c>
+      <c r="B158" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>17</v>
+      </c>
+      <c r="E158">
+        <v>601</v>
+      </c>
+      <c r="F158" s="1">
+        <v>45544</v>
+      </c>
+      <c r="G158" s="1">
+        <v>45544</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158">
+        <v>42</v>
+      </c>
+      <c r="J158">
+        <v>8004</v>
+      </c>
+      <c r="K158" t="s">
+        <v>17</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>0</v>
+      </c>
+      <c r="Q158">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$169</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$158</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$Q$110</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
@@ -501,7 +501,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>128749254</v>
+        <v>129240989</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -516,10 +516,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45510</v>
+        <v>45544</v>
       </c>
       <c r="G2" s="1">
-        <v>45511</v>
+        <v>45544</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -528,7 +528,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129190578</v>
+        <v>129241496</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -569,10 +569,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45539</v>
+        <v>45544</v>
       </c>
       <c r="G3" s="1">
-        <v>45540</v>
+        <v>45544</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -581,7 +581,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K3" t="s">
         <v>17</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129258249</v>
+        <v>129244978</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -622,10 +622,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="G4" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -634,7 +634,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129258946</v>
+        <v>128749254</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,10 +675,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45545</v>
+        <v>45510</v>
       </c>
       <c r="G5" s="1">
-        <v>45546</v>
+        <v>45511</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>129267204</v>
+        <v>129190578</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -728,10 +728,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="G6" s="1">
-        <v>45546</v>
+        <v>45540</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>129268021</v>
+        <v>125381852</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -781,10 +781,10 @@
         <v>1211</v>
       </c>
       <c r="F7" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G7" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>129268076</v>
+        <v>125697897</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -834,7 +834,7 @@
         <v>1211</v>
       </c>
       <c r="F8" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G8" s="1">
         <v>45546</v>
@@ -846,7 +846,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>129268797</v>
+        <v>125707425</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -887,7 +887,7 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G9" s="1">
         <v>45546</v>
@@ -899,7 +899,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>129269192</v>
+        <v>125926152</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -940,7 +940,7 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G10" s="1">
         <v>45546</v>
@@ -952,7 +952,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>125371391</v>
+        <v>125935971</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -993,10 +993,10 @@
         <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G11" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>125579863</v>
+        <v>125941029</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1043,13 +1043,13 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G12" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125766342</v>
+        <v>125943257</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1099,10 +1099,10 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G13" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>125834327</v>
+        <v>125974195</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,7 +1152,7 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45539</v>
+        <v>45546</v>
       </c>
       <c r="G14" s="1">
         <v>45546</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>125973674</v>
+        <v>126032582</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1205,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G15" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>126011689</v>
+        <v>126138307</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1258,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G16" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>126064870</v>
+        <v>126429015</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1311,10 +1311,10 @@
         <v>1211</v>
       </c>
       <c r="F17" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G17" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>126079805</v>
+        <v>126504851</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1361,13 +1361,13 @@
         <v>17</v>
       </c>
       <c r="E18">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G18" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>126165673</v>
+        <v>126527576</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1414,13 +1414,13 @@
         <v>17</v>
       </c>
       <c r="E19">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F19" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G19" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126186459</v>
+        <v>126748614</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1470,7 +1470,7 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="G20" s="1">
         <v>45546</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>126254887</v>
+        <v>127006310</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1523,10 +1523,10 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G21" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>126255796</v>
+        <v>127023581</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1573,13 +1573,13 @@
         <v>17</v>
       </c>
       <c r="E22">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G22" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>126311203</v>
+        <v>127029736</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1629,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G23" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>126564456</v>
+        <v>127109037</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1682,10 +1682,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G24" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>126629834</v>
+        <v>127213554</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,10 +1735,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G25" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>126828458</v>
+        <v>127254296</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1785,13 +1785,13 @@
         <v>17</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F26" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G26" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>127067241</v>
+        <v>127416253</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1841,10 +1841,10 @@
         <v>1211</v>
       </c>
       <c r="F27" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G27" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>127111265</v>
+        <v>127484798</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1894,10 +1894,10 @@
         <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G28" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>127127223</v>
+        <v>127522427</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1947,7 +1947,7 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G29" s="1">
         <v>45546</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>127134867</v>
+        <v>127533501</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -2000,10 +2000,10 @@
         <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G30" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127228055</v>
+        <v>127549522</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2053,10 +2053,10 @@
         <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G31" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>127305630</v>
+        <v>127609361</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2106,10 +2106,10 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G32" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127563636</v>
+        <v>127701671</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2159,10 +2159,10 @@
         <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G33" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127576562</v>
+        <v>127740733</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2212,10 +2212,10 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45545</v>
+        <v>45541</v>
       </c>
       <c r="G34" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127606262</v>
+        <v>128173658</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2265,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G35" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127635050</v>
+        <v>128221377</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2318,10 +2318,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G36" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127831038</v>
+        <v>128235553</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2368,13 +2368,13 @@
         <v>17</v>
       </c>
       <c r="E37">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F37" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G37" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127847709</v>
+        <v>128421372</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,7 +2424,7 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G38" s="1">
         <v>45546</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127947974</v>
+        <v>128474273</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2477,7 +2477,7 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45541</v>
+        <v>45546</v>
       </c>
       <c r="G39" s="1">
         <v>45546</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>128083490</v>
+        <v>128685998</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2527,13 +2527,13 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G40" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>128085519</v>
+        <v>128732885</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2583,10 +2583,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G41" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>128204367</v>
+        <v>128780631</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2633,13 +2633,13 @@
         <v>17</v>
       </c>
       <c r="E42">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F42" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G42" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>128220589</v>
+        <v>128829885</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,10 +2689,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G43" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>128268252</v>
+        <v>128881736</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2739,13 +2739,13 @@
         <v>17</v>
       </c>
       <c r="E44">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G44" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>128291804</v>
+        <v>129080014</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,10 +2795,10 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G45" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>128456931</v>
+        <v>129132325</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2845,13 +2845,13 @@
         <v>17</v>
       </c>
       <c r="E46">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F46" s="1">
-        <v>45545</v>
+        <v>45534</v>
       </c>
       <c r="G46" s="1">
-        <v>45545</v>
+        <v>45534</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>128632296</v>
+        <v>129161649</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2901,10 +2901,10 @@
         <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G47" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>128763123</v>
+        <v>129187945</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2951,13 +2951,13 @@
         <v>17</v>
       </c>
       <c r="E48">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F48" s="1">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="G48" s="1">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>128782394</v>
+        <v>129204177</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3007,10 +3007,10 @@
         <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G49" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>128793066</v>
+        <v>129235920</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3060,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G50" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>128798903</v>
+        <v>129239379</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3113,10 +3113,10 @@
         <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G51" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>128820712</v>
+        <v>129252899</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3163,13 +3163,13 @@
         <v>17</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F52" s="1">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="G52" s="1">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>128862015</v>
+        <v>129255586</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3219,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G53" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>128917387</v>
+        <v>129266911</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3272,10 +3272,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G54" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>128945240</v>
+        <v>129271465</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3325,10 +3325,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G55" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>128987686</v>
+        <v>129290559</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3375,13 +3375,13 @@
         <v>17</v>
       </c>
       <c r="E56">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F56" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G56" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>129092682</v>
+        <v>128749254</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3431,10 +3431,10 @@
         <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45545</v>
+        <v>45510</v>
       </c>
       <c r="G57" s="1">
-        <v>45545</v>
+        <v>45511</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3443,7 +3443,7 @@
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K57" t="s">
         <v>17</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>129095690</v>
+        <v>129039074</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3481,13 +3481,13 @@
         <v>17</v>
       </c>
       <c r="E58">
-        <v>1212</v>
+        <v>2013</v>
       </c>
       <c r="F58" s="1">
-        <v>45545</v>
+        <v>45530</v>
       </c>
       <c r="G58" s="1">
-        <v>45545</v>
+        <v>45531</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3496,7 +3496,7 @@
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K58" t="s">
         <v>17</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>129110151</v>
+        <v>129110148</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3534,13 +3534,13 @@
         <v>17</v>
       </c>
       <c r="E59">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F59" s="1">
-        <v>45545</v>
+        <v>45533</v>
       </c>
       <c r="G59" s="1">
-        <v>45545</v>
+        <v>45534</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3549,7 +3549,7 @@
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K59" t="s">
         <v>17</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129115744</v>
+        <v>129190578</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3587,13 +3587,13 @@
         <v>17</v>
       </c>
       <c r="E60">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>45534</v>
+        <v>45539</v>
       </c>
       <c r="G60" s="1">
-        <v>45534</v>
+        <v>45540</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3602,7 +3602,7 @@
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K60" t="s">
         <v>17</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>129132325</v>
+        <v>129262213</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3643,10 +3643,10 @@
         <v>2013</v>
       </c>
       <c r="F61" s="1">
-        <v>45534</v>
+        <v>45545</v>
       </c>
       <c r="G61" s="1">
-        <v>45534</v>
+        <v>45546</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3655,7 +3655,7 @@
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K61" t="s">
         <v>17</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>129149024</v>
+        <v>129258265</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3693,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="E62">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F62" s="1">
         <v>45545</v>
@@ -3708,7 +3708,7 @@
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K62" t="s">
         <v>17</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129175013</v>
+        <v>129258361</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3746,7 +3746,7 @@
         <v>17</v>
       </c>
       <c r="E63">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F63" s="1">
         <v>45545</v>
@@ -3761,7 +3761,7 @@
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K63" t="s">
         <v>17</v>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129187945</v>
+        <v>129258889</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3799,13 +3799,13 @@
         <v>17</v>
       </c>
       <c r="E64">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F64" s="1">
-        <v>45539</v>
+        <v>45545</v>
       </c>
       <c r="G64" s="1">
-        <v>45539</v>
+        <v>45545</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3814,7 +3814,7 @@
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K64" t="s">
         <v>17</v>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129191152</v>
+        <v>129259171</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3852,13 +3852,13 @@
         <v>17</v>
       </c>
       <c r="E65">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F65" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G65" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3867,7 +3867,7 @@
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K65" t="s">
         <v>17</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129198879</v>
+        <v>129261391</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3905,7 +3905,7 @@
         <v>17</v>
       </c>
       <c r="E66">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F66" s="1">
         <v>45545</v>
@@ -3920,7 +3920,7 @@
         <v>42</v>
       </c>
       <c r="J66">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K66" t="s">
         <v>17</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129205733</v>
+        <v>129261401</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3958,7 +3958,7 @@
         <v>17</v>
       </c>
       <c r="E67">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F67" s="1">
         <v>45545</v>
@@ -3973,7 +3973,7 @@
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K67" t="s">
         <v>17</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129206141</v>
+        <v>129261403</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4011,7 +4011,7 @@
         <v>17</v>
       </c>
       <c r="E68">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F68" s="1">
         <v>45545</v>
@@ -4026,7 +4026,7 @@
         <v>42</v>
       </c>
       <c r="J68">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K68" t="s">
         <v>17</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129209489</v>
+        <v>129261408</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4064,7 +4064,7 @@
         <v>17</v>
       </c>
       <c r="E69">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F69" s="1">
         <v>45545</v>
@@ -4079,7 +4079,7 @@
         <v>42</v>
       </c>
       <c r="J69">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K69" t="s">
         <v>17</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129213290</v>
+        <v>129261409</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4117,7 +4117,7 @@
         <v>17</v>
       </c>
       <c r="E70">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F70" s="1">
         <v>45545</v>
@@ -4132,7 +4132,7 @@
         <v>42</v>
       </c>
       <c r="J70">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K70" t="s">
         <v>17</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129214299</v>
+        <v>129261795</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4170,13 +4170,13 @@
         <v>17</v>
       </c>
       <c r="E71">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F71" s="1">
         <v>45545</v>
       </c>
       <c r="G71" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4185,7 +4185,7 @@
         <v>42</v>
       </c>
       <c r="J71">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K71" t="s">
         <v>17</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129215344</v>
+        <v>129262133</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4223,7 +4223,7 @@
         <v>17</v>
       </c>
       <c r="E72">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F72" s="1">
         <v>45545</v>
@@ -4238,7 +4238,7 @@
         <v>42</v>
       </c>
       <c r="J72">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K72" t="s">
         <v>17</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129221810</v>
+        <v>129262659</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4276,7 +4276,7 @@
         <v>17</v>
       </c>
       <c r="E73">
-        <v>1213</v>
+        <v>601</v>
       </c>
       <c r="F73" s="1">
         <v>45545</v>
@@ -4291,7 +4291,7 @@
         <v>42</v>
       </c>
       <c r="J73">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K73" t="s">
         <v>17</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129221921</v>
+        <v>129262830</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4329,7 +4329,7 @@
         <v>17</v>
       </c>
       <c r="E74">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F74" s="1">
         <v>45545</v>
@@ -4344,7 +4344,7 @@
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K74" t="s">
         <v>17</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129224319</v>
+        <v>129264205</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4382,7 +4382,7 @@
         <v>17</v>
       </c>
       <c r="E75">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F75" s="1">
         <v>45545</v>
@@ -4397,7 +4397,7 @@
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K75" t="s">
         <v>17</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129236255</v>
+        <v>129266368</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4435,7 +4435,7 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F76" s="1">
         <v>45545</v>
@@ -4450,7 +4450,7 @@
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K76" t="s">
         <v>17</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129237646</v>
+        <v>129266710</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4488,7 +4488,7 @@
         <v>17</v>
       </c>
       <c r="E77">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F77" s="1">
         <v>45545</v>
@@ -4503,7 +4503,7 @@
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K77" t="s">
         <v>17</v>
@@ -4529,7 +4529,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129241386</v>
+        <v>129266764</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4541,7 +4541,7 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F78" s="1">
         <v>45545</v>
@@ -4556,7 +4556,7 @@
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K78" t="s">
         <v>17</v>
@@ -4582,7 +4582,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129251692</v>
+        <v>129267670</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4594,13 +4594,13 @@
         <v>17</v>
       </c>
       <c r="E79">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F79" s="1">
         <v>45545</v>
       </c>
       <c r="G79" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4609,7 +4609,7 @@
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K79" t="s">
         <v>17</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129252899</v>
+        <v>129268413</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4647,13 +4647,13 @@
         <v>17</v>
       </c>
       <c r="E80">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F80" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G80" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4662,7 +4662,7 @@
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K80" t="s">
         <v>17</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129258438</v>
+        <v>129268418</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4700,7 +4700,7 @@
         <v>17</v>
       </c>
       <c r="E81">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F81" s="1">
         <v>45545</v>
@@ -4715,7 +4715,7 @@
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K81" t="s">
         <v>17</v>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129262971</v>
+        <v>129268420</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4753,7 +4753,7 @@
         <v>17</v>
       </c>
       <c r="E82">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F82" s="1">
         <v>45545</v>
@@ -4768,7 +4768,7 @@
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K82" t="s">
         <v>17</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129263151</v>
+        <v>129268426</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4806,7 +4806,7 @@
         <v>17</v>
       </c>
       <c r="E83">
-        <v>2002</v>
+        <v>601</v>
       </c>
       <c r="F83" s="1">
         <v>45545</v>
@@ -4821,7 +4821,7 @@
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K83" t="s">
         <v>17</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129264118</v>
+        <v>129268589</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4859,7 +4859,7 @@
         <v>17</v>
       </c>
       <c r="E84">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F84" s="1">
         <v>45545</v>
@@ -4874,7 +4874,7 @@
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K84" t="s">
         <v>17</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129264828</v>
+        <v>129268926</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4912,7 +4912,7 @@
         <v>17</v>
       </c>
       <c r="E85">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F85" s="1">
         <v>45545</v>
@@ -4927,7 +4927,7 @@
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K85" t="s">
         <v>17</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129268191</v>
+        <v>129268934</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4965,7 +4965,7 @@
         <v>17</v>
       </c>
       <c r="E86">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F86" s="1">
         <v>45545</v>
@@ -4980,7 +4980,7 @@
         <v>42</v>
       </c>
       <c r="J86">
-        <v>8001</v>
+        <v>1118</v>
       </c>
       <c r="K86" t="s">
         <v>17</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129268195</v>
+        <v>129269441</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5018,7 +5018,7 @@
         <v>17</v>
       </c>
       <c r="E87">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F87" s="1">
         <v>45545</v>
@@ -5033,7 +5033,7 @@
         <v>42</v>
       </c>
       <c r="J87">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K87" t="s">
         <v>17</v>
@@ -5059,7 +5059,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>129268527</v>
+        <v>129269798</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5071,7 +5071,7 @@
         <v>17</v>
       </c>
       <c r="E88">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F88" s="1">
         <v>45545</v>
@@ -5086,7 +5086,7 @@
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129268536</v>
+        <v>129272390</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5124,13 +5124,13 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F89" s="1">
         <v>45545</v>
       </c>
       <c r="G89" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -5139,7 +5139,7 @@
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129268557</v>
+        <v>129272799</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5177,7 +5177,7 @@
         <v>17</v>
       </c>
       <c r="E90">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F90" s="1">
         <v>45545</v>
@@ -5192,7 +5192,7 @@
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129269328</v>
+        <v>129266892</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5230,7 +5230,7 @@
         <v>17</v>
       </c>
       <c r="E91">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F91" s="1">
         <v>45545</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129270289</v>
+        <v>129268398</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5283,7 +5283,7 @@
         <v>17</v>
       </c>
       <c r="E92">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F92" s="1">
         <v>45545</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129271164</v>
+        <v>129270728</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5336,7 +5336,7 @@
         <v>17</v>
       </c>
       <c r="E93">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F93" s="1">
         <v>45545</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129272475</v>
+        <v>129271160</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5389,7 +5389,7 @@
         <v>17</v>
       </c>
       <c r="E94">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F94" s="1">
         <v>45545</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129273628</v>
+        <v>129260017</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5442,7 +5442,7 @@
         <v>17</v>
       </c>
       <c r="E95">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F95" s="1">
         <v>45545</v>
@@ -5457,7 +5457,7 @@
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K95" t="s">
         <v>17</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>128749254</v>
+        <v>129263374</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -5495,13 +5495,13 @@
         <v>17</v>
       </c>
       <c r="E96">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F96" s="1">
-        <v>45510</v>
+        <v>45545</v>
       </c>
       <c r="G96" s="1">
-        <v>45511</v>
+        <v>45545</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -5510,7 +5510,7 @@
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K96" t="s">
         <v>17</v>
@@ -5536,7 +5536,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>129039074</v>
+        <v>129263822</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -5548,13 +5548,13 @@
         <v>17</v>
       </c>
       <c r="E97">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F97" s="1">
-        <v>45530</v>
+        <v>45545</v>
       </c>
       <c r="G97" s="1">
-        <v>45531</v>
+        <v>45545</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -5563,7 +5563,7 @@
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K97" t="s">
         <v>17</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>129110148</v>
+        <v>129264196</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -5601,13 +5601,13 @@
         <v>17</v>
       </c>
       <c r="E98">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F98" s="1">
-        <v>45533</v>
+        <v>45545</v>
       </c>
       <c r="G98" s="1">
-        <v>45534</v>
+        <v>45545</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -5616,7 +5616,7 @@
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K98" t="s">
         <v>17</v>
@@ -5642,7 +5642,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>129190578</v>
+        <v>129265755</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -5654,13 +5654,13 @@
         <v>17</v>
       </c>
       <c r="E99">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F99" s="1">
-        <v>45539</v>
+        <v>45545</v>
       </c>
       <c r="G99" s="1">
-        <v>45540</v>
+        <v>45545</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -5669,7 +5669,7 @@
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K99" t="s">
         <v>17</v>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>129258174</v>
+        <v>129266752</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -5707,13 +5707,13 @@
         <v>17</v>
       </c>
       <c r="E100">
-        <v>2002</v>
+        <v>601</v>
       </c>
       <c r="F100" s="1">
         <v>45545</v>
       </c>
       <c r="G100" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -5722,7 +5722,7 @@
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K100" t="s">
         <v>17</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>129258249</v>
+        <v>129267737</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -5760,13 +5760,13 @@
         <v>17</v>
       </c>
       <c r="E101">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F101" s="1">
         <v>45545</v>
       </c>
       <c r="G101" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5775,7 +5775,7 @@
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K101" t="s">
         <v>17</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>129258946</v>
+        <v>129268433</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -5813,13 +5813,13 @@
         <v>17</v>
       </c>
       <c r="E102">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F102" s="1">
         <v>45545</v>
       </c>
       <c r="G102" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -5828,7 +5828,7 @@
         <v>42</v>
       </c>
       <c r="J102">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K102" t="s">
         <v>17</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>129260372</v>
+        <v>129269106</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -5866,13 +5866,13 @@
         <v>17</v>
       </c>
       <c r="E103">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F103" s="1">
         <v>45545</v>
       </c>
       <c r="G103" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -5881,7 +5881,7 @@
         <v>42</v>
       </c>
       <c r="J103">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K103" t="s">
         <v>17</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>129262213</v>
+        <v>129269160</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -5919,13 +5919,13 @@
         <v>17</v>
       </c>
       <c r="E104">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F104" s="1">
         <v>45545</v>
       </c>
       <c r="G104" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -5934,7 +5934,7 @@
         <v>42</v>
       </c>
       <c r="J104">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K104" t="s">
         <v>17</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>129266700</v>
+        <v>129271168</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -5972,13 +5972,13 @@
         <v>17</v>
       </c>
       <c r="E105">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F105" s="1">
         <v>45545</v>
       </c>
       <c r="G105" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -5987,7 +5987,7 @@
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K105" t="s">
         <v>17</v>
@@ -6013,7 +6013,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>129267204</v>
+        <v>129271387</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -6025,13 +6025,13 @@
         <v>17</v>
       </c>
       <c r="E106">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F106" s="1">
         <v>45545</v>
       </c>
       <c r="G106" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -6040,7 +6040,7 @@
         <v>42</v>
       </c>
       <c r="J106">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K106" t="s">
         <v>17</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>129268021</v>
+        <v>129271975</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -6078,13 +6078,13 @@
         <v>17</v>
       </c>
       <c r="E107">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F107" s="1">
         <v>45545</v>
       </c>
       <c r="G107" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -6093,7 +6093,7 @@
         <v>42</v>
       </c>
       <c r="J107">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K107" t="s">
         <v>17</v>
@@ -6119,7 +6119,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>129268076</v>
+        <v>129272017</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -6131,13 +6131,13 @@
         <v>17</v>
       </c>
       <c r="E108">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F108" s="1">
         <v>45545</v>
       </c>
       <c r="G108" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -6146,7 +6146,7 @@
         <v>42</v>
       </c>
       <c r="J108">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K108" t="s">
         <v>17</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>129268797</v>
+        <v>129272516</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -6184,13 +6184,13 @@
         <v>17</v>
       </c>
       <c r="E109">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F109" s="1">
         <v>45545</v>
       </c>
       <c r="G109" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -6199,7 +6199,7 @@
         <v>42</v>
       </c>
       <c r="J109">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K109" t="s">
         <v>17</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>129269192</v>
+        <v>129273481</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -6237,13 +6237,13 @@
         <v>17</v>
       </c>
       <c r="E110">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F110" s="1">
         <v>45545</v>
       </c>
       <c r="G110" s="1">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -6252,7 +6252,7 @@
         <v>42</v>
       </c>
       <c r="J110">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K110" t="s">
         <v>17</v>
@@ -6273,2550 +6273,6 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>129220638</v>
-      </c>
-      <c r="B111" t="s">
-        <v>17</v>
-      </c>
-      <c r="C111" t="s">
-        <v>17</v>
-      </c>
-      <c r="D111" t="s">
-        <v>17</v>
-      </c>
-      <c r="E111">
-        <v>601</v>
-      </c>
-      <c r="F111" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G111" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H111" t="s">
-        <v>17</v>
-      </c>
-      <c r="I111">
-        <v>42</v>
-      </c>
-      <c r="J111">
-        <v>8004</v>
-      </c>
-      <c r="K111" t="s">
-        <v>17</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>129240278</v>
-      </c>
-      <c r="B112" t="s">
-        <v>17</v>
-      </c>
-      <c r="C112" t="s">
-        <v>17</v>
-      </c>
-      <c r="D112" t="s">
-        <v>17</v>
-      </c>
-      <c r="E112">
-        <v>601</v>
-      </c>
-      <c r="F112" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G112" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H112" t="s">
-        <v>17</v>
-      </c>
-      <c r="I112">
-        <v>42</v>
-      </c>
-      <c r="J112">
-        <v>8004</v>
-      </c>
-      <c r="K112" t="s">
-        <v>17</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>129241275</v>
-      </c>
-      <c r="B113" t="s">
-        <v>17</v>
-      </c>
-      <c r="C113" t="s">
-        <v>17</v>
-      </c>
-      <c r="D113" t="s">
-        <v>17</v>
-      </c>
-      <c r="E113">
-        <v>601</v>
-      </c>
-      <c r="F113" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G113" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H113" t="s">
-        <v>17</v>
-      </c>
-      <c r="I113">
-        <v>42</v>
-      </c>
-      <c r="J113">
-        <v>8004</v>
-      </c>
-      <c r="K113" t="s">
-        <v>17</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113">
-        <v>0</v>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>129241539</v>
-      </c>
-      <c r="B114" t="s">
-        <v>17</v>
-      </c>
-      <c r="C114" t="s">
-        <v>17</v>
-      </c>
-      <c r="D114" t="s">
-        <v>17</v>
-      </c>
-      <c r="E114">
-        <v>601</v>
-      </c>
-      <c r="F114" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G114" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H114" t="s">
-        <v>17</v>
-      </c>
-      <c r="I114">
-        <v>42</v>
-      </c>
-      <c r="J114">
-        <v>8004</v>
-      </c>
-      <c r="K114" t="s">
-        <v>17</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>129241604</v>
-      </c>
-      <c r="B115" t="s">
-        <v>17</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
-      </c>
-      <c r="D115" t="s">
-        <v>17</v>
-      </c>
-      <c r="E115">
-        <v>601</v>
-      </c>
-      <c r="F115" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G115" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H115" t="s">
-        <v>17</v>
-      </c>
-      <c r="I115">
-        <v>42</v>
-      </c>
-      <c r="J115">
-        <v>8004</v>
-      </c>
-      <c r="K115" t="s">
-        <v>17</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>129241983</v>
-      </c>
-      <c r="B116" t="s">
-        <v>17</v>
-      </c>
-      <c r="C116" t="s">
-        <v>17</v>
-      </c>
-      <c r="D116" t="s">
-        <v>17</v>
-      </c>
-      <c r="E116">
-        <v>601</v>
-      </c>
-      <c r="F116" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G116" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H116" t="s">
-        <v>17</v>
-      </c>
-      <c r="I116">
-        <v>42</v>
-      </c>
-      <c r="J116">
-        <v>8004</v>
-      </c>
-      <c r="K116" t="s">
-        <v>17</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>129242802</v>
-      </c>
-      <c r="B117" t="s">
-        <v>17</v>
-      </c>
-      <c r="C117" t="s">
-        <v>17</v>
-      </c>
-      <c r="D117" t="s">
-        <v>17</v>
-      </c>
-      <c r="E117">
-        <v>601</v>
-      </c>
-      <c r="F117" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G117" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H117" t="s">
-        <v>17</v>
-      </c>
-      <c r="I117">
-        <v>42</v>
-      </c>
-      <c r="J117">
-        <v>8004</v>
-      </c>
-      <c r="K117" t="s">
-        <v>17</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>129243599</v>
-      </c>
-      <c r="B118" t="s">
-        <v>17</v>
-      </c>
-      <c r="C118" t="s">
-        <v>17</v>
-      </c>
-      <c r="D118" t="s">
-        <v>17</v>
-      </c>
-      <c r="E118">
-        <v>601</v>
-      </c>
-      <c r="F118" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G118" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H118" t="s">
-        <v>17</v>
-      </c>
-      <c r="I118">
-        <v>42</v>
-      </c>
-      <c r="J118">
-        <v>8004</v>
-      </c>
-      <c r="K118" t="s">
-        <v>17</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>129243783</v>
-      </c>
-      <c r="B119" t="s">
-        <v>17</v>
-      </c>
-      <c r="C119" t="s">
-        <v>17</v>
-      </c>
-      <c r="D119" t="s">
-        <v>17</v>
-      </c>
-      <c r="E119">
-        <v>601</v>
-      </c>
-      <c r="F119" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G119" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H119" t="s">
-        <v>17</v>
-      </c>
-      <c r="I119">
-        <v>42</v>
-      </c>
-      <c r="J119">
-        <v>8004</v>
-      </c>
-      <c r="K119" t="s">
-        <v>17</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>129243881</v>
-      </c>
-      <c r="B120" t="s">
-        <v>17</v>
-      </c>
-      <c r="C120" t="s">
-        <v>17</v>
-      </c>
-      <c r="D120" t="s">
-        <v>17</v>
-      </c>
-      <c r="E120">
-        <v>601</v>
-      </c>
-      <c r="F120" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G120" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H120" t="s">
-        <v>17</v>
-      </c>
-      <c r="I120">
-        <v>42</v>
-      </c>
-      <c r="J120">
-        <v>8004</v>
-      </c>
-      <c r="K120" t="s">
-        <v>17</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>129244078</v>
-      </c>
-      <c r="B121" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" t="s">
-        <v>17</v>
-      </c>
-      <c r="D121" t="s">
-        <v>17</v>
-      </c>
-      <c r="E121">
-        <v>601</v>
-      </c>
-      <c r="F121" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G121" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H121" t="s">
-        <v>17</v>
-      </c>
-      <c r="I121">
-        <v>42</v>
-      </c>
-      <c r="J121">
-        <v>8004</v>
-      </c>
-      <c r="K121" t="s">
-        <v>17</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>129244148</v>
-      </c>
-      <c r="B122" t="s">
-        <v>17</v>
-      </c>
-      <c r="C122" t="s">
-        <v>17</v>
-      </c>
-      <c r="D122" t="s">
-        <v>17</v>
-      </c>
-      <c r="E122">
-        <v>601</v>
-      </c>
-      <c r="F122" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G122" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H122" t="s">
-        <v>17</v>
-      </c>
-      <c r="I122">
-        <v>42</v>
-      </c>
-      <c r="J122">
-        <v>8004</v>
-      </c>
-      <c r="K122" t="s">
-        <v>17</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>129246781</v>
-      </c>
-      <c r="B123" t="s">
-        <v>17</v>
-      </c>
-      <c r="C123" t="s">
-        <v>17</v>
-      </c>
-      <c r="D123" t="s">
-        <v>17</v>
-      </c>
-      <c r="E123">
-        <v>601</v>
-      </c>
-      <c r="F123" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G123" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H123" t="s">
-        <v>17</v>
-      </c>
-      <c r="I123">
-        <v>42</v>
-      </c>
-      <c r="J123">
-        <v>8004</v>
-      </c>
-      <c r="K123" t="s">
-        <v>17</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>129247185</v>
-      </c>
-      <c r="B124" t="s">
-        <v>17</v>
-      </c>
-      <c r="C124" t="s">
-        <v>17</v>
-      </c>
-      <c r="D124" t="s">
-        <v>17</v>
-      </c>
-      <c r="E124">
-        <v>601</v>
-      </c>
-      <c r="F124" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G124" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H124" t="s">
-        <v>17</v>
-      </c>
-      <c r="I124">
-        <v>42</v>
-      </c>
-      <c r="J124">
-        <v>8004</v>
-      </c>
-      <c r="K124" t="s">
-        <v>17</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>129247308</v>
-      </c>
-      <c r="B125" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" t="s">
-        <v>17</v>
-      </c>
-      <c r="D125" t="s">
-        <v>17</v>
-      </c>
-      <c r="E125">
-        <v>601</v>
-      </c>
-      <c r="F125" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G125" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H125" t="s">
-        <v>17</v>
-      </c>
-      <c r="I125">
-        <v>42</v>
-      </c>
-      <c r="J125">
-        <v>8004</v>
-      </c>
-      <c r="K125" t="s">
-        <v>17</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>129247455</v>
-      </c>
-      <c r="B126" t="s">
-        <v>17</v>
-      </c>
-      <c r="C126" t="s">
-        <v>17</v>
-      </c>
-      <c r="D126" t="s">
-        <v>17</v>
-      </c>
-      <c r="E126">
-        <v>601</v>
-      </c>
-      <c r="F126" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G126" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H126" t="s">
-        <v>17</v>
-      </c>
-      <c r="I126">
-        <v>42</v>
-      </c>
-      <c r="J126">
-        <v>8013</v>
-      </c>
-      <c r="K126" t="s">
-        <v>17</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>129247609</v>
-      </c>
-      <c r="B127" t="s">
-        <v>17</v>
-      </c>
-      <c r="C127" t="s">
-        <v>17</v>
-      </c>
-      <c r="D127" t="s">
-        <v>17</v>
-      </c>
-      <c r="E127">
-        <v>601</v>
-      </c>
-      <c r="F127" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G127" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H127" t="s">
-        <v>17</v>
-      </c>
-      <c r="I127">
-        <v>42</v>
-      </c>
-      <c r="J127">
-        <v>8004</v>
-      </c>
-      <c r="K127" t="s">
-        <v>17</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
-        <v>0</v>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>129247620</v>
-      </c>
-      <c r="B128" t="s">
-        <v>17</v>
-      </c>
-      <c r="C128" t="s">
-        <v>17</v>
-      </c>
-      <c r="D128" t="s">
-        <v>17</v>
-      </c>
-      <c r="E128">
-        <v>601</v>
-      </c>
-      <c r="F128" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G128" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H128" t="s">
-        <v>17</v>
-      </c>
-      <c r="I128">
-        <v>42</v>
-      </c>
-      <c r="J128">
-        <v>8004</v>
-      </c>
-      <c r="K128" t="s">
-        <v>17</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
-        <v>0</v>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>129247871</v>
-      </c>
-      <c r="B129" t="s">
-        <v>17</v>
-      </c>
-      <c r="C129" t="s">
-        <v>17</v>
-      </c>
-      <c r="D129" t="s">
-        <v>17</v>
-      </c>
-      <c r="E129">
-        <v>601</v>
-      </c>
-      <c r="F129" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G129" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H129" t="s">
-        <v>17</v>
-      </c>
-      <c r="I129">
-        <v>42</v>
-      </c>
-      <c r="J129">
-        <v>8004</v>
-      </c>
-      <c r="K129" t="s">
-        <v>17</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
-        <v>0</v>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>129248327</v>
-      </c>
-      <c r="B130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C130" t="s">
-        <v>17</v>
-      </c>
-      <c r="D130" t="s">
-        <v>17</v>
-      </c>
-      <c r="E130">
-        <v>601</v>
-      </c>
-      <c r="F130" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G130" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H130" t="s">
-        <v>17</v>
-      </c>
-      <c r="I130">
-        <v>42</v>
-      </c>
-      <c r="J130">
-        <v>8004</v>
-      </c>
-      <c r="K130" t="s">
-        <v>17</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>129248718</v>
-      </c>
-      <c r="B131" t="s">
-        <v>17</v>
-      </c>
-      <c r="C131" t="s">
-        <v>17</v>
-      </c>
-      <c r="D131" t="s">
-        <v>17</v>
-      </c>
-      <c r="E131">
-        <v>601</v>
-      </c>
-      <c r="F131" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G131" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H131" t="s">
-        <v>17</v>
-      </c>
-      <c r="I131">
-        <v>42</v>
-      </c>
-      <c r="J131">
-        <v>8013</v>
-      </c>
-      <c r="K131" t="s">
-        <v>17</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>129249252</v>
-      </c>
-      <c r="B132" t="s">
-        <v>17</v>
-      </c>
-      <c r="C132" t="s">
-        <v>17</v>
-      </c>
-      <c r="D132" t="s">
-        <v>17</v>
-      </c>
-      <c r="E132">
-        <v>601</v>
-      </c>
-      <c r="F132" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G132" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H132" t="s">
-        <v>17</v>
-      </c>
-      <c r="I132">
-        <v>42</v>
-      </c>
-      <c r="J132">
-        <v>8004</v>
-      </c>
-      <c r="K132" t="s">
-        <v>17</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>129249615</v>
-      </c>
-      <c r="B133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C133" t="s">
-        <v>17</v>
-      </c>
-      <c r="D133" t="s">
-        <v>17</v>
-      </c>
-      <c r="E133">
-        <v>601</v>
-      </c>
-      <c r="F133" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G133" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H133" t="s">
-        <v>17</v>
-      </c>
-      <c r="I133">
-        <v>42</v>
-      </c>
-      <c r="J133">
-        <v>8004</v>
-      </c>
-      <c r="K133" t="s">
-        <v>17</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>129249978</v>
-      </c>
-      <c r="B134" t="s">
-        <v>17</v>
-      </c>
-      <c r="C134" t="s">
-        <v>17</v>
-      </c>
-      <c r="D134" t="s">
-        <v>17</v>
-      </c>
-      <c r="E134">
-        <v>601</v>
-      </c>
-      <c r="F134" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G134" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H134" t="s">
-        <v>17</v>
-      </c>
-      <c r="I134">
-        <v>42</v>
-      </c>
-      <c r="J134">
-        <v>8004</v>
-      </c>
-      <c r="K134" t="s">
-        <v>17</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>0</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>129250532</v>
-      </c>
-      <c r="B135" t="s">
-        <v>17</v>
-      </c>
-      <c r="C135" t="s">
-        <v>17</v>
-      </c>
-      <c r="D135" t="s">
-        <v>17</v>
-      </c>
-      <c r="E135">
-        <v>601</v>
-      </c>
-      <c r="F135" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G135" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H135" t="s">
-        <v>17</v>
-      </c>
-      <c r="I135">
-        <v>42</v>
-      </c>
-      <c r="J135">
-        <v>8004</v>
-      </c>
-      <c r="K135" t="s">
-        <v>17</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>129250695</v>
-      </c>
-      <c r="B136" t="s">
-        <v>17</v>
-      </c>
-      <c r="C136" t="s">
-        <v>17</v>
-      </c>
-      <c r="D136" t="s">
-        <v>17</v>
-      </c>
-      <c r="E136">
-        <v>601</v>
-      </c>
-      <c r="F136" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G136" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H136" t="s">
-        <v>17</v>
-      </c>
-      <c r="I136">
-        <v>42</v>
-      </c>
-      <c r="J136">
-        <v>8004</v>
-      </c>
-      <c r="K136" t="s">
-        <v>17</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>129252787</v>
-      </c>
-      <c r="B137" t="s">
-        <v>17</v>
-      </c>
-      <c r="C137" t="s">
-        <v>17</v>
-      </c>
-      <c r="D137" t="s">
-        <v>17</v>
-      </c>
-      <c r="E137">
-        <v>601</v>
-      </c>
-      <c r="F137" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G137" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H137" t="s">
-        <v>17</v>
-      </c>
-      <c r="I137">
-        <v>42</v>
-      </c>
-      <c r="J137">
-        <v>8013</v>
-      </c>
-      <c r="K137" t="s">
-        <v>17</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>129253748</v>
-      </c>
-      <c r="B138" t="s">
-        <v>17</v>
-      </c>
-      <c r="C138" t="s">
-        <v>17</v>
-      </c>
-      <c r="D138" t="s">
-        <v>17</v>
-      </c>
-      <c r="E138">
-        <v>601</v>
-      </c>
-      <c r="F138" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G138" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H138" t="s">
-        <v>17</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
-        <v>1118</v>
-      </c>
-      <c r="K138" t="s">
-        <v>17</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>129254046</v>
-      </c>
-      <c r="B139" t="s">
-        <v>17</v>
-      </c>
-      <c r="C139" t="s">
-        <v>17</v>
-      </c>
-      <c r="D139" t="s">
-        <v>17</v>
-      </c>
-      <c r="E139">
-        <v>601</v>
-      </c>
-      <c r="F139" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G139" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H139" t="s">
-        <v>17</v>
-      </c>
-      <c r="I139">
-        <v>42</v>
-      </c>
-      <c r="J139">
-        <v>8004</v>
-      </c>
-      <c r="K139" t="s">
-        <v>17</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>129254186</v>
-      </c>
-      <c r="B140" t="s">
-        <v>17</v>
-      </c>
-      <c r="C140" t="s">
-        <v>17</v>
-      </c>
-      <c r="D140" t="s">
-        <v>17</v>
-      </c>
-      <c r="E140">
-        <v>601</v>
-      </c>
-      <c r="F140" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G140" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H140" t="s">
-        <v>17</v>
-      </c>
-      <c r="I140">
-        <v>42</v>
-      </c>
-      <c r="J140">
-        <v>8004</v>
-      </c>
-      <c r="K140" t="s">
-        <v>17</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>129254437</v>
-      </c>
-      <c r="B141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C141" t="s">
-        <v>17</v>
-      </c>
-      <c r="D141" t="s">
-        <v>17</v>
-      </c>
-      <c r="E141">
-        <v>601</v>
-      </c>
-      <c r="F141" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G141" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H141" t="s">
-        <v>17</v>
-      </c>
-      <c r="I141">
-        <v>42</v>
-      </c>
-      <c r="J141">
-        <v>8004</v>
-      </c>
-      <c r="K141" t="s">
-        <v>17</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>129254466</v>
-      </c>
-      <c r="B142" t="s">
-        <v>17</v>
-      </c>
-      <c r="C142" t="s">
-        <v>17</v>
-      </c>
-      <c r="D142" t="s">
-        <v>17</v>
-      </c>
-      <c r="E142">
-        <v>601</v>
-      </c>
-      <c r="F142" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G142" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H142" t="s">
-        <v>17</v>
-      </c>
-      <c r="I142">
-        <v>42</v>
-      </c>
-      <c r="J142">
-        <v>8004</v>
-      </c>
-      <c r="K142" t="s">
-        <v>17</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>129254824</v>
-      </c>
-      <c r="B143" t="s">
-        <v>17</v>
-      </c>
-      <c r="C143" t="s">
-        <v>17</v>
-      </c>
-      <c r="D143" t="s">
-        <v>17</v>
-      </c>
-      <c r="E143">
-        <v>601</v>
-      </c>
-      <c r="F143" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G143" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H143" t="s">
-        <v>17</v>
-      </c>
-      <c r="I143">
-        <v>42</v>
-      </c>
-      <c r="J143">
-        <v>1118</v>
-      </c>
-      <c r="K143" t="s">
-        <v>17</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>129254882</v>
-      </c>
-      <c r="B144" t="s">
-        <v>17</v>
-      </c>
-      <c r="C144" t="s">
-        <v>17</v>
-      </c>
-      <c r="D144" t="s">
-        <v>17</v>
-      </c>
-      <c r="E144">
-        <v>601</v>
-      </c>
-      <c r="F144" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G144" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H144" t="s">
-        <v>17</v>
-      </c>
-      <c r="I144">
-        <v>42</v>
-      </c>
-      <c r="J144">
-        <v>8004</v>
-      </c>
-      <c r="K144" t="s">
-        <v>17</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>129255469</v>
-      </c>
-      <c r="B145" t="s">
-        <v>17</v>
-      </c>
-      <c r="C145" t="s">
-        <v>17</v>
-      </c>
-      <c r="D145" t="s">
-        <v>17</v>
-      </c>
-      <c r="E145">
-        <v>601</v>
-      </c>
-      <c r="F145" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G145" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H145" t="s">
-        <v>17</v>
-      </c>
-      <c r="I145">
-        <v>42</v>
-      </c>
-      <c r="J145">
-        <v>8004</v>
-      </c>
-      <c r="K145" t="s">
-        <v>17</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>129255983</v>
-      </c>
-      <c r="B146" t="s">
-        <v>17</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>17</v>
-      </c>
-      <c r="E146">
-        <v>601</v>
-      </c>
-      <c r="F146" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G146" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H146" t="s">
-        <v>17</v>
-      </c>
-      <c r="I146">
-        <v>42</v>
-      </c>
-      <c r="J146">
-        <v>8004</v>
-      </c>
-      <c r="K146" t="s">
-        <v>17</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>129248327</v>
-      </c>
-      <c r="B147" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" t="s">
-        <v>17</v>
-      </c>
-      <c r="D147" t="s">
-        <v>17</v>
-      </c>
-      <c r="E147">
-        <v>601</v>
-      </c>
-      <c r="F147" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G147" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H147" t="s">
-        <v>17</v>
-      </c>
-      <c r="I147">
-        <v>42</v>
-      </c>
-      <c r="J147">
-        <v>8004</v>
-      </c>
-      <c r="K147" t="s">
-        <v>17</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>129241671</v>
-      </c>
-      <c r="B148" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" t="s">
-        <v>17</v>
-      </c>
-      <c r="E148">
-        <v>601</v>
-      </c>
-      <c r="F148" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G148" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H148" t="s">
-        <v>17</v>
-      </c>
-      <c r="I148">
-        <v>42</v>
-      </c>
-      <c r="J148">
-        <v>8004</v>
-      </c>
-      <c r="K148" t="s">
-        <v>17</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>129243689</v>
-      </c>
-      <c r="B149" t="s">
-        <v>17</v>
-      </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" t="s">
-        <v>17</v>
-      </c>
-      <c r="E149">
-        <v>601</v>
-      </c>
-      <c r="F149" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G149" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H149" t="s">
-        <v>17</v>
-      </c>
-      <c r="I149">
-        <v>42</v>
-      </c>
-      <c r="J149">
-        <v>8004</v>
-      </c>
-      <c r="K149" t="s">
-        <v>17</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>129245312</v>
-      </c>
-      <c r="B150" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" t="s">
-        <v>17</v>
-      </c>
-      <c r="E150">
-        <v>601</v>
-      </c>
-      <c r="F150" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G150" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H150" t="s">
-        <v>17</v>
-      </c>
-      <c r="I150">
-        <v>42</v>
-      </c>
-      <c r="J150">
-        <v>8004</v>
-      </c>
-      <c r="K150" t="s">
-        <v>17</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150">
-        <v>0</v>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A151">
-        <v>129245622</v>
-      </c>
-      <c r="B151" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" t="s">
-        <v>17</v>
-      </c>
-      <c r="E151">
-        <v>601</v>
-      </c>
-      <c r="F151" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G151" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H151" t="s">
-        <v>17</v>
-      </c>
-      <c r="I151">
-        <v>42</v>
-      </c>
-      <c r="J151">
-        <v>8004</v>
-      </c>
-      <c r="K151" t="s">
-        <v>17</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151">
-        <v>0</v>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A152">
-        <v>129246423</v>
-      </c>
-      <c r="B152" t="s">
-        <v>17</v>
-      </c>
-      <c r="C152" t="s">
-        <v>17</v>
-      </c>
-      <c r="D152" t="s">
-        <v>17</v>
-      </c>
-      <c r="E152">
-        <v>601</v>
-      </c>
-      <c r="F152" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G152" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H152" t="s">
-        <v>17</v>
-      </c>
-      <c r="I152">
-        <v>42</v>
-      </c>
-      <c r="J152">
-        <v>8004</v>
-      </c>
-      <c r="K152" t="s">
-        <v>17</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
-        <v>0</v>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A153">
-        <v>129247017</v>
-      </c>
-      <c r="B153" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" t="s">
-        <v>17</v>
-      </c>
-      <c r="D153" t="s">
-        <v>17</v>
-      </c>
-      <c r="E153">
-        <v>601</v>
-      </c>
-      <c r="F153" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G153" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H153" t="s">
-        <v>17</v>
-      </c>
-      <c r="I153">
-        <v>42</v>
-      </c>
-      <c r="J153">
-        <v>8004</v>
-      </c>
-      <c r="K153" t="s">
-        <v>17</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
-        <v>0</v>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A154">
-        <v>129248040</v>
-      </c>
-      <c r="B154" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" t="s">
-        <v>17</v>
-      </c>
-      <c r="E154">
-        <v>601</v>
-      </c>
-      <c r="F154" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G154" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H154" t="s">
-        <v>17</v>
-      </c>
-      <c r="I154">
-        <v>42</v>
-      </c>
-      <c r="J154">
-        <v>8004</v>
-      </c>
-      <c r="K154" t="s">
-        <v>17</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154">
-        <v>0</v>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A155">
-        <v>129248418</v>
-      </c>
-      <c r="B155" t="s">
-        <v>17</v>
-      </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>17</v>
-      </c>
-      <c r="E155">
-        <v>601</v>
-      </c>
-      <c r="F155" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G155" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H155" t="s">
-        <v>17</v>
-      </c>
-      <c r="I155">
-        <v>42</v>
-      </c>
-      <c r="J155">
-        <v>8004</v>
-      </c>
-      <c r="K155" t="s">
-        <v>17</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
-        <v>0</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
-        <v>0</v>
-      </c>
-      <c r="Q155">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A156">
-        <v>129249085</v>
-      </c>
-      <c r="B156" t="s">
-        <v>17</v>
-      </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" t="s">
-        <v>17</v>
-      </c>
-      <c r="E156">
-        <v>601</v>
-      </c>
-      <c r="F156" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G156" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H156" t="s">
-        <v>17</v>
-      </c>
-      <c r="I156">
-        <v>42</v>
-      </c>
-      <c r="J156">
-        <v>8004</v>
-      </c>
-      <c r="K156" t="s">
-        <v>17</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
-        <v>0</v>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>0</v>
-      </c>
-      <c r="P156">
-        <v>0</v>
-      </c>
-      <c r="Q156">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A157">
-        <v>129253589</v>
-      </c>
-      <c r="B157" t="s">
-        <v>17</v>
-      </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
-      <c r="D157" t="s">
-        <v>17</v>
-      </c>
-      <c r="E157">
-        <v>601</v>
-      </c>
-      <c r="F157" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G157" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H157" t="s">
-        <v>17</v>
-      </c>
-      <c r="I157">
-        <v>42</v>
-      </c>
-      <c r="J157">
-        <v>8004</v>
-      </c>
-      <c r="K157" t="s">
-        <v>17</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157">
-        <v>0</v>
-      </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
-      <c r="O157">
-        <v>0</v>
-      </c>
-      <c r="P157">
-        <v>0</v>
-      </c>
-      <c r="Q157">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A158">
-        <v>129253794</v>
-      </c>
-      <c r="B158" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" t="s">
-        <v>17</v>
-      </c>
-      <c r="D158" t="s">
-        <v>17</v>
-      </c>
-      <c r="E158">
-        <v>601</v>
-      </c>
-      <c r="F158" s="1">
-        <v>45544</v>
-      </c>
-      <c r="G158" s="1">
-        <v>45544</v>
-      </c>
-      <c r="H158" t="s">
-        <v>17</v>
-      </c>
-      <c r="I158">
-        <v>42</v>
-      </c>
-      <c r="J158">
-        <v>8004</v>
-      </c>
-      <c r="K158" t="s">
-        <v>17</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
-        <v>0</v>
-      </c>
-      <c r="N158">
-        <v>0</v>
-      </c>
-      <c r="O158">
-        <v>0</v>
-      </c>
-      <c r="P158">
-        <v>0</v>
-      </c>
-      <c r="Q158">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Bloqueios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C92DDF-8B25-4655-A786-8B1F6BA2602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341F865F-18F1-406D-BCE8-C229E75144D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$169</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$146</definedName>
+    <definedName name="Fiel">Fiel!$A$1:$Q$146</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="18">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -116,10 +116,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,27 +422,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1048576"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="16" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -501,7 +497,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129240989</v>
+        <v>129260317</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -516,10 +512,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G2" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -554,7 +550,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129241496</v>
+        <v>129261886</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -569,10 +565,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G3" s="1">
-        <v>45544</v>
+        <v>45546</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -607,7 +603,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129244978</v>
+        <v>129270813</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -622,7 +618,7 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="G4" s="1">
         <v>45545</v>
@@ -660,7 +656,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>128749254</v>
+        <v>129274546</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -675,10 +671,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45510</v>
+        <v>45545</v>
       </c>
       <c r="G5" s="1">
-        <v>45511</v>
+        <v>45545</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -687,7 +683,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -713,7 +709,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>129190578</v>
+        <v>129277037</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -728,10 +724,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45539</v>
+        <v>45546</v>
       </c>
       <c r="G6" s="1">
-        <v>45540</v>
+        <v>45546</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -740,7 +736,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -766,7 +762,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>125381852</v>
+        <v>129277615</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -778,13 +774,13 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F7" s="1">
         <v>45546</v>
       </c>
       <c r="G7" s="1">
-        <v>45547</v>
+        <v>45546</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -793,7 +789,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -819,7 +815,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>125697897</v>
+        <v>129287396</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -846,7 +842,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -872,7 +868,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>125707425</v>
+        <v>129293946</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -899,7 +895,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -925,7 +921,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>125926152</v>
+        <v>129298922</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -940,10 +936,10 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G10" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -952,7 +948,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -978,7 +974,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>125935971</v>
+        <v>129305431</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -993,10 +989,10 @@
         <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G11" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1005,7 +1001,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
@@ -1031,7 +1027,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>125941029</v>
+        <v>129307000</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1046,7 +1042,7 @@
         <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G12" s="1">
         <v>45547</v>
@@ -1058,7 +1054,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
@@ -1084,7 +1080,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125943257</v>
+        <v>129307684</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1099,10 +1095,10 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G13" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1111,7 +1107,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K13" t="s">
         <v>17</v>
@@ -1137,7 +1133,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>125974195</v>
+        <v>129307991</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1152,10 +1148,10 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G14" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1164,7 +1160,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -1190,7 +1186,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>126032582</v>
+        <v>129313918</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1205,10 +1201,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G15" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1217,7 +1213,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -1243,7 +1239,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>126138307</v>
+        <v>129190578</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1258,10 +1254,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45546</v>
+        <v>45539</v>
       </c>
       <c r="G16" s="1">
-        <v>45546</v>
+        <v>45540</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1270,7 +1266,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K16" t="s">
         <v>17</v>
@@ -1296,7 +1292,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>126429015</v>
+        <v>129311887</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1311,10 +1307,10 @@
         <v>1211</v>
       </c>
       <c r="F17" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G17" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1323,7 +1319,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K17" t="s">
         <v>17</v>
@@ -1349,7 +1345,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>126504851</v>
+        <v>125557861</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1364,10 +1360,10 @@
         <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G18" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1402,7 +1398,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>126527576</v>
+        <v>125602176</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1414,13 +1410,13 @@
         <v>17</v>
       </c>
       <c r="E19">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G19" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1455,7 +1451,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126748614</v>
+        <v>125608625</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1470,10 +1466,10 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G20" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1508,7 +1504,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>127006310</v>
+        <v>125684554</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1523,10 +1519,10 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G21" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1561,7 +1557,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>127023581</v>
+        <v>125819749</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1573,13 +1569,13 @@
         <v>17</v>
       </c>
       <c r="E22">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F22" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G22" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1614,7 +1610,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>127029736</v>
+        <v>125825809</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1629,10 +1625,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G23" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1667,7 +1663,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>127109037</v>
+        <v>126023815</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1682,10 +1678,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G24" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1720,7 +1716,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>127213554</v>
+        <v>126085660</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1735,10 +1731,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G25" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1773,7 +1769,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>127254296</v>
+        <v>126106576</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1785,13 +1781,13 @@
         <v>17</v>
       </c>
       <c r="E26">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G26" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1826,7 +1822,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>127416253</v>
+        <v>126197398</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1844,7 +1840,7 @@
         <v>45546</v>
       </c>
       <c r="G27" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1879,7 +1875,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>127484798</v>
+        <v>126338229</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1894,10 +1890,10 @@
         <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G28" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1932,7 +1928,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>127522427</v>
+        <v>126360865</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1950,7 +1946,7 @@
         <v>45546</v>
       </c>
       <c r="G29" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1985,7 +1981,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>127533501</v>
+        <v>126366489</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -2000,10 +1996,10 @@
         <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G30" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2038,7 +2034,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127549522</v>
+        <v>126553784</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2053,10 +2049,10 @@
         <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G31" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2091,7 +2087,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>127609361</v>
+        <v>126576573</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2106,10 +2102,10 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G32" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -2144,7 +2140,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127701671</v>
+        <v>126641034</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2159,7 +2155,7 @@
         <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G33" s="1">
         <v>45547</v>
@@ -2197,7 +2193,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127740733</v>
+        <v>126670643</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2212,7 +2208,7 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45541</v>
+        <v>45547</v>
       </c>
       <c r="G34" s="1">
         <v>45547</v>
@@ -2250,7 +2246,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>128173658</v>
+        <v>126798230</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2265,10 +2261,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G35" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2303,7 +2299,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>128221377</v>
+        <v>126831827</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2318,10 +2314,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G36" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2356,7 +2352,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>128235553</v>
+        <v>126864052</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2368,13 +2364,13 @@
         <v>17</v>
       </c>
       <c r="E37">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="1">
         <v>45546</v>
       </c>
       <c r="G37" s="1">
-        <v>45547</v>
+        <v>45550</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2409,7 +2405,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>128421372</v>
+        <v>126894266</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2424,10 +2420,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G38" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2462,7 +2458,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>128474273</v>
+        <v>126915845</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2477,10 +2473,10 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G39" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2515,7 +2511,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>128685998</v>
+        <v>126935468</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2527,13 +2523,13 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F40" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G40" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2568,7 +2564,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>128732885</v>
+        <v>126947839</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2583,10 +2579,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G41" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2621,7 +2617,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>128780631</v>
+        <v>126956472</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2633,13 +2629,13 @@
         <v>17</v>
       </c>
       <c r="E42">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G42" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2674,7 +2670,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>128829885</v>
+        <v>127009581</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2689,10 +2685,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G43" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2727,7 +2723,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>128881736</v>
+        <v>127108250</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2742,10 +2738,10 @@
         <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G44" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2780,7 +2776,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>129080014</v>
+        <v>127166267</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2795,10 +2791,10 @@
         <v>1211</v>
       </c>
       <c r="F45" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G45" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2833,7 +2829,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>129132325</v>
+        <v>127204045</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2845,13 +2841,13 @@
         <v>17</v>
       </c>
       <c r="E46">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="1">
-        <v>45534</v>
+        <v>45547</v>
       </c>
       <c r="G46" s="1">
-        <v>45534</v>
+        <v>45547</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2886,7 +2882,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>129161649</v>
+        <v>127427404</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2901,10 +2897,10 @@
         <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G47" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2939,7 +2935,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>129187945</v>
+        <v>127449756</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2951,13 +2947,13 @@
         <v>17</v>
       </c>
       <c r="E48">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="1">
-        <v>45539</v>
+        <v>45547</v>
       </c>
       <c r="G48" s="1">
-        <v>45539</v>
+        <v>45547</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2992,7 +2988,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>129204177</v>
+        <v>127574005</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3004,13 +3000,13 @@
         <v>17</v>
       </c>
       <c r="E49">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F49" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G49" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -3045,7 +3041,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>129235920</v>
+        <v>127671254</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3060,10 +3056,10 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45546</v>
+        <v>45541</v>
       </c>
       <c r="G50" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -3098,7 +3094,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>129239379</v>
+        <v>127682155</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3113,10 +3109,10 @@
         <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G51" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3151,7 +3147,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>129252899</v>
+        <v>127766216</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3163,13 +3159,13 @@
         <v>17</v>
       </c>
       <c r="E52">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F52" s="1">
-        <v>45544</v>
+        <v>45547</v>
       </c>
       <c r="G52" s="1">
-        <v>45544</v>
+        <v>45547</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3204,7 +3200,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>129255586</v>
+        <v>127828417</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3219,10 +3215,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G53" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3257,7 +3253,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>129266911</v>
+        <v>127848051</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3275,7 +3271,7 @@
         <v>45546</v>
       </c>
       <c r="G54" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3310,7 +3306,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>129271465</v>
+        <v>127866577</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3325,10 +3321,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G55" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3363,7 +3359,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>129290559</v>
+        <v>127911021</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3375,13 +3371,13 @@
         <v>17</v>
       </c>
       <c r="E56">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G56" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3416,7 +3412,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>128749254</v>
+        <v>128231240</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3431,10 +3427,10 @@
         <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45510</v>
+        <v>45544</v>
       </c>
       <c r="G57" s="1">
-        <v>45511</v>
+        <v>45548</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3443,7 +3439,7 @@
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K57" t="s">
         <v>17</v>
@@ -3469,7 +3465,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>129039074</v>
+        <v>128249260</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3481,13 +3477,13 @@
         <v>17</v>
       </c>
       <c r="E58">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="1">
-        <v>45530</v>
+        <v>45547</v>
       </c>
       <c r="G58" s="1">
-        <v>45531</v>
+        <v>45547</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3496,7 +3492,7 @@
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K58" t="s">
         <v>17</v>
@@ -3522,7 +3518,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>129110148</v>
+        <v>128288278</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3534,13 +3530,13 @@
         <v>17</v>
       </c>
       <c r="E59">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45533</v>
+        <v>45547</v>
       </c>
       <c r="G59" s="1">
-        <v>45534</v>
+        <v>45547</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3549,7 +3545,7 @@
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K59" t="s">
         <v>17</v>
@@ -3575,7 +3571,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129190578</v>
+        <v>128336336</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3587,13 +3583,13 @@
         <v>17</v>
       </c>
       <c r="E60">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F60" s="1">
-        <v>45539</v>
+        <v>45547</v>
       </c>
       <c r="G60" s="1">
-        <v>45540</v>
+        <v>45547</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3602,7 +3598,7 @@
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K60" t="s">
         <v>17</v>
@@ -3628,7 +3624,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>129262213</v>
+        <v>128460091</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3640,13 +3636,13 @@
         <v>17</v>
       </c>
       <c r="E61">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F61" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G61" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3655,7 +3651,7 @@
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K61" t="s">
         <v>17</v>
@@ -3681,7 +3677,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>129258265</v>
+        <v>128474576</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3693,13 +3689,13 @@
         <v>17</v>
       </c>
       <c r="E62">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G62" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3708,7 +3704,7 @@
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K62" t="s">
         <v>17</v>
@@ -3734,7 +3730,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129258361</v>
+        <v>128495144</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3746,13 +3742,13 @@
         <v>17</v>
       </c>
       <c r="E63">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G63" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3761,7 +3757,7 @@
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K63" t="s">
         <v>17</v>
@@ -3787,7 +3783,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129258889</v>
+        <v>128571286</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3799,13 +3795,13 @@
         <v>17</v>
       </c>
       <c r="E64">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G64" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3814,7 +3810,7 @@
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K64" t="s">
         <v>17</v>
@@ -3840,7 +3836,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129259171</v>
+        <v>128595065</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3852,13 +3848,13 @@
         <v>17</v>
       </c>
       <c r="E65">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G65" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3867,7 +3863,7 @@
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K65" t="s">
         <v>17</v>
@@ -3893,7 +3889,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129261391</v>
+        <v>128652742</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3905,13 +3901,13 @@
         <v>17</v>
       </c>
       <c r="E66">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F66" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G66" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3920,7 +3916,7 @@
         <v>42</v>
       </c>
       <c r="J66">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K66" t="s">
         <v>17</v>
@@ -3946,7 +3942,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129261401</v>
+        <v>128785157</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3958,13 +3954,13 @@
         <v>17</v>
       </c>
       <c r="E67">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F67" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G67" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3973,7 +3969,7 @@
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K67" t="s">
         <v>17</v>
@@ -3999,7 +3995,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129261403</v>
+        <v>128837370</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4011,13 +4007,13 @@
         <v>17</v>
       </c>
       <c r="E68">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G68" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -4026,7 +4022,7 @@
         <v>42</v>
       </c>
       <c r="J68">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K68" t="s">
         <v>17</v>
@@ -4052,7 +4048,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129261408</v>
+        <v>128879968</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4064,13 +4060,13 @@
         <v>17</v>
       </c>
       <c r="E69">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F69" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G69" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -4079,7 +4075,7 @@
         <v>42</v>
       </c>
       <c r="J69">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K69" t="s">
         <v>17</v>
@@ -4105,7 +4101,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129261409</v>
+        <v>128898555</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4117,13 +4113,13 @@
         <v>17</v>
       </c>
       <c r="E70">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F70" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G70" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4132,7 +4128,7 @@
         <v>42</v>
       </c>
       <c r="J70">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K70" t="s">
         <v>17</v>
@@ -4158,7 +4154,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129261795</v>
+        <v>129079623</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4170,13 +4166,13 @@
         <v>17</v>
       </c>
       <c r="E71">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G71" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4185,7 +4181,7 @@
         <v>42</v>
       </c>
       <c r="J71">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K71" t="s">
         <v>17</v>
@@ -4211,7 +4207,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129262133</v>
+        <v>129103911</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4223,13 +4219,13 @@
         <v>17</v>
       </c>
       <c r="E72">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F72" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G72" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4238,7 +4234,7 @@
         <v>42</v>
       </c>
       <c r="J72">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K72" t="s">
         <v>17</v>
@@ -4264,7 +4260,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129262659</v>
+        <v>129135499</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4276,13 +4272,13 @@
         <v>17</v>
       </c>
       <c r="E73">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G73" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4291,7 +4287,7 @@
         <v>42</v>
       </c>
       <c r="J73">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K73" t="s">
         <v>17</v>
@@ -4317,7 +4313,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129262830</v>
+        <v>129180445</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4329,13 +4325,13 @@
         <v>17</v>
       </c>
       <c r="E74">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G74" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4344,7 +4340,7 @@
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K74" t="s">
         <v>17</v>
@@ -4370,7 +4366,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129264205</v>
+        <v>129187945</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4382,13 +4378,13 @@
         <v>17</v>
       </c>
       <c r="E75">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F75" s="1">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="G75" s="1">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -4397,7 +4393,7 @@
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K75" t="s">
         <v>17</v>
@@ -4423,7 +4419,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129266368</v>
+        <v>129201008</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4435,13 +4431,13 @@
         <v>17</v>
       </c>
       <c r="E76">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G76" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -4450,7 +4446,7 @@
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K76" t="s">
         <v>17</v>
@@ -4476,7 +4472,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129266710</v>
+        <v>129215560</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4488,13 +4484,13 @@
         <v>17</v>
       </c>
       <c r="E77">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F77" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G77" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4503,7 +4499,7 @@
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K77" t="s">
         <v>17</v>
@@ -4529,7 +4525,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129266764</v>
+        <v>129227991</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4541,13 +4537,13 @@
         <v>17</v>
       </c>
       <c r="E78">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F78" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G78" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4556,7 +4552,7 @@
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K78" t="s">
         <v>17</v>
@@ -4582,7 +4578,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129267670</v>
+        <v>129248695</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4594,13 +4590,13 @@
         <v>17</v>
       </c>
       <c r="E79">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F79" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G79" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4609,7 +4605,7 @@
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K79" t="s">
         <v>17</v>
@@ -4635,7 +4631,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129268413</v>
+        <v>129248839</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4647,13 +4643,13 @@
         <v>17</v>
       </c>
       <c r="E80">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F80" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G80" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4662,7 +4658,7 @@
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K80" t="s">
         <v>17</v>
@@ -4688,7 +4684,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129268418</v>
+        <v>129252899</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4700,13 +4696,13 @@
         <v>17</v>
       </c>
       <c r="E81">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F81" s="1">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="G81" s="1">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -4715,7 +4711,7 @@
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K81" t="s">
         <v>17</v>
@@ -4741,7 +4737,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129268420</v>
+        <v>129253147</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4753,13 +4749,13 @@
         <v>17</v>
       </c>
       <c r="E82">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F82" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G82" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -4768,7 +4764,7 @@
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K82" t="s">
         <v>17</v>
@@ -4794,7 +4790,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129268426</v>
+        <v>129256716</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4806,13 +4802,13 @@
         <v>17</v>
       </c>
       <c r="E83">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F83" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G83" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -4821,7 +4817,7 @@
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K83" t="s">
         <v>17</v>
@@ -4847,7 +4843,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129268589</v>
+        <v>129283400</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4859,13 +4855,13 @@
         <v>17</v>
       </c>
       <c r="E84">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F84" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G84" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -4874,7 +4870,7 @@
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K84" t="s">
         <v>17</v>
@@ -4900,7 +4896,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129268926</v>
+        <v>129284917</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4912,13 +4908,13 @@
         <v>17</v>
       </c>
       <c r="E85">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F85" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G85" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -4927,7 +4923,7 @@
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K85" t="s">
         <v>17</v>
@@ -4953,7 +4949,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129268934</v>
+        <v>129294744</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4965,13 +4961,13 @@
         <v>17</v>
       </c>
       <c r="E86">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F86" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G86" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -4980,7 +4976,7 @@
         <v>42</v>
       </c>
       <c r="J86">
-        <v>1118</v>
+        <v>8001</v>
       </c>
       <c r="K86" t="s">
         <v>17</v>
@@ -5006,7 +5002,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129269441</v>
+        <v>129307778</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5018,13 +5014,13 @@
         <v>17</v>
       </c>
       <c r="E87">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F87" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G87" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -5033,7 +5029,7 @@
         <v>42</v>
       </c>
       <c r="J87">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K87" t="s">
         <v>17</v>
@@ -5059,7 +5055,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>129269798</v>
+        <v>129039074</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5071,13 +5067,13 @@
         <v>17</v>
       </c>
       <c r="E88">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F88" s="1">
-        <v>45545</v>
+        <v>45530</v>
       </c>
       <c r="G88" s="1">
-        <v>45545</v>
+        <v>45531</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -5086,7 +5082,7 @@
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -5112,7 +5108,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129272390</v>
+        <v>129110148</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5124,13 +5120,13 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F89" s="1">
-        <v>45545</v>
+        <v>45533</v>
       </c>
       <c r="G89" s="1">
-        <v>45547</v>
+        <v>45534</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -5139,7 +5135,7 @@
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8013</v>
+        <v>8021</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -5165,7 +5161,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129272799</v>
+        <v>129190578</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5177,13 +5173,13 @@
         <v>17</v>
       </c>
       <c r="E90">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F90" s="1">
-        <v>45545</v>
+        <v>45539</v>
       </c>
       <c r="G90" s="1">
-        <v>45545</v>
+        <v>45540</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -5192,7 +5188,7 @@
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -5218,7 +5214,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129266892</v>
+        <v>129262213</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5230,13 +5226,13 @@
         <v>17</v>
       </c>
       <c r="E91">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F91" s="1">
         <v>45545</v>
       </c>
       <c r="G91" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -5245,7 +5241,7 @@
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
@@ -5271,7 +5267,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129268398</v>
+        <v>129302902</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5283,13 +5279,13 @@
         <v>17</v>
       </c>
       <c r="E92">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F92" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G92" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -5298,7 +5294,7 @@
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K92" t="s">
         <v>17</v>
@@ -5324,7 +5320,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129270728</v>
+        <v>129311887</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5336,13 +5332,13 @@
         <v>17</v>
       </c>
       <c r="E93">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F93" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="G93" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5351,7 +5347,7 @@
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="K93" t="s">
         <v>17</v>
@@ -5377,7 +5373,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129271160</v>
+        <v>129277367</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5392,10 +5388,10 @@
         <v>601</v>
       </c>
       <c r="F94" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G94" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -5404,7 +5400,7 @@
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K94" t="s">
         <v>17</v>
@@ -5430,7 +5426,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129260017</v>
+        <v>129277833</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5445,10 +5441,10 @@
         <v>601</v>
       </c>
       <c r="F95" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G95" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -5483,7 +5479,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>129263374</v>
+        <v>129278069</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -5498,10 +5494,10 @@
         <v>601</v>
       </c>
       <c r="F96" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G96" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -5536,7 +5532,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>129263822</v>
+        <v>129278072</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -5551,10 +5547,10 @@
         <v>601</v>
       </c>
       <c r="F97" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G97" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -5563,7 +5559,7 @@
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K97" t="s">
         <v>17</v>
@@ -5589,7 +5585,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>129264196</v>
+        <v>129278810</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -5604,10 +5600,10 @@
         <v>601</v>
       </c>
       <c r="F98" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G98" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -5616,7 +5612,7 @@
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K98" t="s">
         <v>17</v>
@@ -5642,7 +5638,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>129265755</v>
+        <v>129279786</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -5657,10 +5653,10 @@
         <v>601</v>
       </c>
       <c r="F99" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G99" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -5695,7 +5691,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>129266752</v>
+        <v>129280530</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -5710,10 +5706,10 @@
         <v>601</v>
       </c>
       <c r="F100" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G100" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -5748,7 +5744,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>129267737</v>
+        <v>129280835</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -5763,10 +5759,10 @@
         <v>601</v>
       </c>
       <c r="F101" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G101" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5801,7 +5797,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>129268433</v>
+        <v>129281127</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -5816,10 +5812,10 @@
         <v>601</v>
       </c>
       <c r="F102" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G102" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -5854,7 +5850,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>129269106</v>
+        <v>129281389</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -5869,10 +5865,10 @@
         <v>601</v>
       </c>
       <c r="F103" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G103" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -5907,7 +5903,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>129269160</v>
+        <v>129282364</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -5922,10 +5918,10 @@
         <v>601</v>
       </c>
       <c r="F104" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G104" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -5960,7 +5956,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>129271168</v>
+        <v>129285188</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -5975,10 +5971,10 @@
         <v>601</v>
       </c>
       <c r="F105" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G105" s="1">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -5987,7 +5983,7 @@
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K105" t="s">
         <v>17</v>
@@ -6013,7 +6009,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>129271387</v>
+        <v>129285910</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -6028,10 +6024,10 @@
         <v>601</v>
       </c>
       <c r="F106" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G106" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -6066,7 +6062,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>129271975</v>
+        <v>129286578</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -6081,10 +6077,10 @@
         <v>601</v>
       </c>
       <c r="F107" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G107" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -6119,7 +6115,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>129272017</v>
+        <v>129286639</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -6134,10 +6130,10 @@
         <v>601</v>
       </c>
       <c r="F108" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G108" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -6172,7 +6168,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>129272516</v>
+        <v>129286778</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -6187,10 +6183,10 @@
         <v>601</v>
       </c>
       <c r="F109" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G109" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -6225,7 +6221,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>129273481</v>
+        <v>129287219</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -6240,10 +6236,10 @@
         <v>601</v>
       </c>
       <c r="F110" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="G110" s="1">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -6276,7 +6272,1916 @@
         <v>61</v>
       </c>
     </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>129287842</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111">
+        <v>601</v>
+      </c>
+      <c r="F111" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G111" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8004</v>
+      </c>
+      <c r="K111" t="s">
+        <v>17</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>129289063</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G112" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8004</v>
+      </c>
+      <c r="K112" t="s">
+        <v>17</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>129290063</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G113" s="1">
+        <v>45548</v>
+      </c>
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8013</v>
+      </c>
+      <c r="K113" t="s">
+        <v>17</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>129290358</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G114" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8004</v>
+      </c>
+      <c r="K114" t="s">
+        <v>17</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>129291046</v>
+      </c>
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G115" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8004</v>
+      </c>
+      <c r="K115" t="s">
+        <v>17</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>129291818</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G116" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8004</v>
+      </c>
+      <c r="K116" t="s">
+        <v>17</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>129292228</v>
+      </c>
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G117" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8004</v>
+      </c>
+      <c r="K117" t="s">
+        <v>17</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>129293096</v>
+      </c>
+      <c r="B118" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G118" s="1">
+        <v>45548</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8013</v>
+      </c>
+      <c r="K118" t="s">
+        <v>17</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>129293525</v>
+      </c>
+      <c r="B119" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G119" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>1117</v>
+      </c>
+      <c r="K119" t="s">
+        <v>17</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>129293691</v>
+      </c>
+      <c r="B120" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G120" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>1117</v>
+      </c>
+      <c r="K120" t="s">
+        <v>17</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>129293714</v>
+      </c>
+      <c r="B121" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G121" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>1117</v>
+      </c>
+      <c r="K121" t="s">
+        <v>17</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>129281452</v>
+      </c>
+      <c r="B122" t="s">
+        <v>17</v>
+      </c>
+      <c r="C122" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G122" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8001</v>
+      </c>
+      <c r="K122" t="s">
+        <v>17</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>129281981</v>
+      </c>
+      <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G123" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8001</v>
+      </c>
+      <c r="K123" t="s">
+        <v>17</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>129284427</v>
+      </c>
+      <c r="B124" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G124" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8001</v>
+      </c>
+      <c r="K124" t="s">
+        <v>17</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>129284857</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G125" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8001</v>
+      </c>
+      <c r="K125" t="s">
+        <v>17</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>129280237</v>
+      </c>
+      <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126">
+        <v>609</v>
+      </c>
+      <c r="F126" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G126" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8004</v>
+      </c>
+      <c r="K126" t="s">
+        <v>17</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>129042009</v>
+      </c>
+      <c r="B127" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127">
+        <v>601</v>
+      </c>
+      <c r="F127" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G127" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8004</v>
+      </c>
+      <c r="K127" t="s">
+        <v>17</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>129277501</v>
+      </c>
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128">
+        <v>601</v>
+      </c>
+      <c r="F128" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G128" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8004</v>
+      </c>
+      <c r="K128" t="s">
+        <v>17</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>129277982</v>
+      </c>
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129">
+        <v>601</v>
+      </c>
+      <c r="F129" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G129" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8004</v>
+      </c>
+      <c r="K129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129280154</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130">
+        <v>601</v>
+      </c>
+      <c r="F130" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G130" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8004</v>
+      </c>
+      <c r="K130" t="s">
+        <v>17</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>129280657</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131">
+        <v>601</v>
+      </c>
+      <c r="F131" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G131" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8004</v>
+      </c>
+      <c r="K131" t="s">
+        <v>17</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>129280753</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132">
+        <v>601</v>
+      </c>
+      <c r="F132" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G132" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8004</v>
+      </c>
+      <c r="K132" t="s">
+        <v>17</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>129280869</v>
+      </c>
+      <c r="B133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133">
+        <v>601</v>
+      </c>
+      <c r="F133" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G133" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8004</v>
+      </c>
+      <c r="K133" t="s">
+        <v>17</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>129281066</v>
+      </c>
+      <c r="B134" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134">
+        <v>601</v>
+      </c>
+      <c r="F134" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G134" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8004</v>
+      </c>
+      <c r="K134" t="s">
+        <v>17</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>129282859</v>
+      </c>
+      <c r="B135" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G135" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8004</v>
+      </c>
+      <c r="K135" t="s">
+        <v>17</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>129283456</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G136" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8004</v>
+      </c>
+      <c r="K136" t="s">
+        <v>17</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>129283829</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G137" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8004</v>
+      </c>
+      <c r="K137" t="s">
+        <v>17</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>129284579</v>
+      </c>
+      <c r="B138" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G138" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8004</v>
+      </c>
+      <c r="K138" t="s">
+        <v>17</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>129285003</v>
+      </c>
+      <c r="B139" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G139" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="K139" t="s">
+        <v>17</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>129286449</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140">
+        <v>601</v>
+      </c>
+      <c r="F140" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G140" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8004</v>
+      </c>
+      <c r="K140" t="s">
+        <v>17</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>129287329</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141">
+        <v>601</v>
+      </c>
+      <c r="F141" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G141" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8004</v>
+      </c>
+      <c r="K141" t="s">
+        <v>17</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>129288313</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142">
+        <v>601</v>
+      </c>
+      <c r="F142" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G142" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8004</v>
+      </c>
+      <c r="K142" t="s">
+        <v>17</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>129289504</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143">
+        <v>601</v>
+      </c>
+      <c r="F143" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G143" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8004</v>
+      </c>
+      <c r="K143" t="s">
+        <v>17</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>129290514</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144">
+        <v>601</v>
+      </c>
+      <c r="F144" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G144" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8004</v>
+      </c>
+      <c r="K144" t="s">
+        <v>17</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>129292545</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145">
+        <v>601</v>
+      </c>
+      <c r="F145" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G145" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8004</v>
+      </c>
+      <c r="K145" t="s">
+        <v>17</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>129292705</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146">
+        <v>601</v>
+      </c>
+      <c r="F146" s="1">
+        <v>45546</v>
+      </c>
+      <c r="G146" s="1">
+        <v>45546</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8004</v>
+      </c>
+      <c r="K146" t="s">
+        <v>17</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:Q146" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341F865F-18F1-406D-BCE8-C229E75144D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14746FA5-4339-44F6-9A61-EBF0422F8A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$146</definedName>
-    <definedName name="Fiel">Fiel!$A$1:$Q$146</definedName>
+    <definedName name="Fiel">Fiel!$A$1:$Q$142</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="18">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -116,9 +116,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q146"/>
+  <dimension ref="A1:Q236"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -497,7 +498,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129260317</v>
+        <v>129322989</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -512,10 +513,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="G2" s="1">
-        <v>45545</v>
+        <v>45549</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -550,7 +551,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129261886</v>
+        <v>129324166</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -565,10 +566,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="G3" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -603,7 +604,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129270813</v>
+        <v>129324629</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -618,10 +619,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="G4" s="1">
-        <v>45545</v>
+        <v>45549</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -656,7 +657,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129274546</v>
+        <v>129326820</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -671,10 +672,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="G5" s="1">
-        <v>45545</v>
+        <v>45548</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -709,7 +710,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>129277037</v>
+        <v>129326911</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -724,10 +725,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G6" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -762,7 +763,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>129277615</v>
+        <v>129331649</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -774,13 +775,13 @@
         <v>17</v>
       </c>
       <c r="E7">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G7" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
@@ -815,7 +816,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>129287396</v>
+        <v>129190578</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -830,10 +831,10 @@
         <v>1211</v>
       </c>
       <c r="F8" s="1">
-        <v>45546</v>
+        <v>45539</v>
       </c>
       <c r="G8" s="1">
-        <v>45546</v>
+        <v>45540</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -842,7 +843,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -868,7 +869,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>129293946</v>
+        <v>129311887</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -883,10 +884,10 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G9" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -895,7 +896,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -921,7 +922,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>129298922</v>
+        <v>125354253</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -936,10 +937,10 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G10" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -948,7 +949,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -974,7 +975,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>129305431</v>
+        <v>125401081</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -989,10 +990,10 @@
         <v>1211</v>
       </c>
       <c r="F11" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G11" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1001,7 +1002,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
@@ -1027,7 +1028,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>129307000</v>
+        <v>125503398</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1042,10 +1043,10 @@
         <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G12" s="1">
-        <v>45547</v>
+        <v>45550</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1054,7 +1055,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
@@ -1080,7 +1081,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>129307684</v>
+        <v>125552059</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1095,10 +1096,10 @@
         <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G13" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1107,7 +1108,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K13" t="s">
         <v>17</v>
@@ -1133,7 +1134,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>129307991</v>
+        <v>125594653</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1148,10 +1149,10 @@
         <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G14" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1160,7 +1161,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -1186,7 +1187,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>129313918</v>
+        <v>125663597</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1201,10 +1202,10 @@
         <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G15" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1213,7 +1214,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -1239,7 +1240,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>129190578</v>
+        <v>125672689</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1254,10 +1255,10 @@
         <v>1211</v>
       </c>
       <c r="F16" s="1">
-        <v>45539</v>
+        <v>45549</v>
       </c>
       <c r="G16" s="1">
-        <v>45540</v>
+        <v>45549</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1266,7 +1267,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K16" t="s">
         <v>17</v>
@@ -1292,7 +1293,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>129311887</v>
+        <v>125715996</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -1307,7 +1308,7 @@
         <v>1211</v>
       </c>
       <c r="F17" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G17" s="1">
         <v>45548</v>
@@ -1319,7 +1320,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K17" t="s">
         <v>17</v>
@@ -1345,7 +1346,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>125557861</v>
+        <v>125826931</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -1360,10 +1361,10 @@
         <v>1211</v>
       </c>
       <c r="F18" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G18" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1398,7 +1399,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>125602176</v>
+        <v>125944560</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -1413,7 +1414,7 @@
         <v>1211</v>
       </c>
       <c r="F19" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G19" s="1">
         <v>45548</v>
@@ -1451,7 +1452,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>125608625</v>
+        <v>126054587</v>
       </c>
       <c r="B20" t="s">
         <v>17</v>
@@ -1466,10 +1467,10 @@
         <v>1211</v>
       </c>
       <c r="F20" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G20" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1504,7 +1505,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>125684554</v>
+        <v>126087658</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -1519,10 +1520,10 @@
         <v>1211</v>
       </c>
       <c r="F21" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G21" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1557,7 +1558,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>125819749</v>
+        <v>126094908</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1569,13 +1570,13 @@
         <v>17</v>
       </c>
       <c r="E22">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G22" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1610,7 +1611,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>125825809</v>
+        <v>126114823</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1625,10 +1626,10 @@
         <v>1211</v>
       </c>
       <c r="F23" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G23" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1663,7 +1664,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>126023815</v>
+        <v>126121158</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -1678,10 +1679,10 @@
         <v>1211</v>
       </c>
       <c r="F24" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G24" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1716,7 +1717,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>126085660</v>
+        <v>126154826</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -1731,10 +1732,10 @@
         <v>1211</v>
       </c>
       <c r="F25" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G25" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1769,7 +1770,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>126106576</v>
+        <v>126156070</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -1784,10 +1785,10 @@
         <v>1211</v>
       </c>
       <c r="F26" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G26" s="1">
-        <v>45548</v>
+        <v>45550</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1822,7 +1823,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>126197398</v>
+        <v>126160048</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -1837,7 +1838,7 @@
         <v>1211</v>
       </c>
       <c r="F27" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G27" s="1">
         <v>45548</v>
@@ -1875,7 +1876,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>126338229</v>
+        <v>126230562</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1890,10 +1891,10 @@
         <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G28" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1928,7 +1929,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>126360865</v>
+        <v>126303706</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1943,7 +1944,7 @@
         <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G29" s="1">
         <v>45548</v>
@@ -1981,7 +1982,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>126366489</v>
+        <v>126504932</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -1996,10 +1997,10 @@
         <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G30" s="1">
-        <v>45548</v>
+        <v>45549</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2034,7 +2035,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>126553784</v>
+        <v>126577868</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2049,10 +2050,10 @@
         <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G31" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2087,7 +2088,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>126576573</v>
+        <v>126699050</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2102,10 +2103,10 @@
         <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G32" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -2140,7 +2141,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>126641034</v>
+        <v>126807132</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2152,13 +2153,13 @@
         <v>17</v>
       </c>
       <c r="E33">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F33" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G33" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2193,7 +2194,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>126670643</v>
+        <v>126824467</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2208,10 +2209,10 @@
         <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G34" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2246,7 +2247,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>126798230</v>
+        <v>126826392</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -2261,10 +2262,10 @@
         <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G35" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2299,7 +2300,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>126831827</v>
+        <v>126915968</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
@@ -2314,10 +2315,10 @@
         <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G36" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2352,7 +2353,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>126864052</v>
+        <v>126934335</v>
       </c>
       <c r="B37" t="s">
         <v>17</v>
@@ -2367,10 +2368,10 @@
         <v>1211</v>
       </c>
       <c r="F37" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G37" s="1">
-        <v>45550</v>
+        <v>45548</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2405,7 +2406,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>126894266</v>
+        <v>126954310</v>
       </c>
       <c r="B38" t="s">
         <v>17</v>
@@ -2420,10 +2421,10 @@
         <v>1211</v>
       </c>
       <c r="F38" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G38" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2458,7 +2459,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>126915845</v>
+        <v>127028133</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2473,10 +2474,10 @@
         <v>1211</v>
       </c>
       <c r="F39" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G39" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2511,7 +2512,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>126935468</v>
+        <v>127061744</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2523,13 +2524,13 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G40" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2564,7 +2565,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>126947839</v>
+        <v>127078228</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2579,10 +2580,10 @@
         <v>1211</v>
       </c>
       <c r="F41" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G41" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2617,7 +2618,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>126956472</v>
+        <v>127163144</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
@@ -2632,10 +2633,10 @@
         <v>1211</v>
       </c>
       <c r="F42" s="1">
-        <v>45547</v>
+        <v>45546</v>
       </c>
       <c r="G42" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2670,7 +2671,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>127009581</v>
+        <v>127278233</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2685,10 +2686,10 @@
         <v>1211</v>
       </c>
       <c r="F43" s="1">
-        <v>45547</v>
+        <v>45550</v>
       </c>
       <c r="G43" s="1">
-        <v>45547</v>
+        <v>45550</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2723,7 +2724,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>127108250</v>
+        <v>127352636</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -2738,7 +2739,7 @@
         <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G44" s="1">
         <v>45548</v>
@@ -2776,7 +2777,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>127166267</v>
+        <v>127491764</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
@@ -2788,13 +2789,13 @@
         <v>17</v>
       </c>
       <c r="E45">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F45" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G45" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2829,7 +2830,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>127204045</v>
+        <v>127580325</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
@@ -2844,10 +2845,10 @@
         <v>1211</v>
       </c>
       <c r="F46" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G46" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2882,7 +2883,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>127427404</v>
+        <v>127586731</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
@@ -2897,10 +2898,10 @@
         <v>1211</v>
       </c>
       <c r="F47" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G47" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2935,7 +2936,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>127449756</v>
+        <v>127626302</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -2950,10 +2951,10 @@
         <v>1211</v>
       </c>
       <c r="F48" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G48" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2988,7 +2989,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>127574005</v>
+        <v>127676152</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
@@ -3000,13 +3001,13 @@
         <v>17</v>
       </c>
       <c r="E49">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G49" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -3041,7 +3042,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>127671254</v>
+        <v>127739596</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
@@ -3056,7 +3057,7 @@
         <v>1211</v>
       </c>
       <c r="F50" s="1">
-        <v>45541</v>
+        <v>45548</v>
       </c>
       <c r="G50" s="1">
         <v>45548</v>
@@ -3094,7 +3095,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>127682155</v>
+        <v>127750707</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -3106,13 +3107,13 @@
         <v>17</v>
       </c>
       <c r="E51">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F51" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G51" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -3147,7 +3148,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>127766216</v>
+        <v>127765702</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -3159,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="E52">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G52" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -3200,7 +3201,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>127828417</v>
+        <v>127813083</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -3215,10 +3216,10 @@
         <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G53" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -3253,7 +3254,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>127848051</v>
+        <v>127918670</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -3268,7 +3269,7 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G54" s="1">
         <v>45548</v>
@@ -3306,7 +3307,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>127866577</v>
+        <v>127929519</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -3321,10 +3322,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G55" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -3359,7 +3360,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>127911021</v>
+        <v>127940380</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -3374,10 +3375,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G56" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -3412,7 +3413,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>128231240</v>
+        <v>127968058</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -3427,7 +3428,7 @@
         <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45544</v>
+        <v>45548</v>
       </c>
       <c r="G57" s="1">
         <v>45548</v>
@@ -3465,7 +3466,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>128249260</v>
+        <v>128011447</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
@@ -3480,10 +3481,10 @@
         <v>1211</v>
       </c>
       <c r="F58" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G58" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3518,7 +3519,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>128288278</v>
+        <v>128120979</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -3533,10 +3534,10 @@
         <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G59" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3571,7 +3572,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>128336336</v>
+        <v>128123797</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -3586,10 +3587,10 @@
         <v>1212</v>
       </c>
       <c r="F60" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G60" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3624,7 +3625,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>128460091</v>
+        <v>128242694</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -3636,10 +3637,10 @@
         <v>17</v>
       </c>
       <c r="E61">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F61" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G61" s="1">
         <v>45548</v>
@@ -3677,7 +3678,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>128474576</v>
+        <v>128271283</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -3692,10 +3693,10 @@
         <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G62" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3730,7 +3731,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>128495144</v>
+        <v>128330507</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -3745,10 +3746,10 @@
         <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G63" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3783,7 +3784,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>128571286</v>
+        <v>128360364</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -3798,10 +3799,10 @@
         <v>1211</v>
       </c>
       <c r="F64" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G64" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3836,7 +3837,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>128595065</v>
+        <v>128403551</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -3851,10 +3852,10 @@
         <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G65" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3889,7 +3890,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>128652742</v>
+        <v>128435834</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
@@ -3901,13 +3902,13 @@
         <v>17</v>
       </c>
       <c r="E66">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G66" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3942,7 +3943,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>128785157</v>
+        <v>128459600</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -3954,13 +3955,13 @@
         <v>17</v>
       </c>
       <c r="E67">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G67" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3995,7 +3996,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>128837370</v>
+        <v>128483376</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -4010,7 +4011,7 @@
         <v>1211</v>
       </c>
       <c r="F68" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G68" s="1">
         <v>45548</v>
@@ -4048,7 +4049,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>128879968</v>
+        <v>128516763</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -4063,10 +4064,10 @@
         <v>1211</v>
       </c>
       <c r="F69" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G69" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -4101,7 +4102,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>128898555</v>
+        <v>128562630</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -4113,13 +4114,13 @@
         <v>17</v>
       </c>
       <c r="E70">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F70" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G70" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -4154,7 +4155,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129079623</v>
+        <v>128650353</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -4169,10 +4170,10 @@
         <v>1211</v>
       </c>
       <c r="F71" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G71" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -4207,7 +4208,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129103911</v>
+        <v>128670156</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -4222,10 +4223,10 @@
         <v>1211</v>
       </c>
       <c r="F72" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G72" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -4260,7 +4261,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129135499</v>
+        <v>128715201</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -4278,7 +4279,7 @@
         <v>45547</v>
       </c>
       <c r="G73" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -4313,7 +4314,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129180445</v>
+        <v>128728035</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -4328,10 +4329,10 @@
         <v>1211</v>
       </c>
       <c r="F74" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G74" s="1">
-        <v>45547</v>
+        <v>45551</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -4366,7 +4367,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129187945</v>
+        <v>128756486</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -4378,13 +4379,13 @@
         <v>17</v>
       </c>
       <c r="E75">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F75" s="1">
-        <v>45539</v>
+        <v>45548</v>
       </c>
       <c r="G75" s="1">
-        <v>45539</v>
+        <v>45548</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -4419,7 +4420,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129201008</v>
+        <v>128766279</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
@@ -4434,10 +4435,10 @@
         <v>1211</v>
       </c>
       <c r="F76" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G76" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -4472,7 +4473,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129215560</v>
+        <v>128800403</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -4487,10 +4488,10 @@
         <v>1211</v>
       </c>
       <c r="F77" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G77" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -4525,7 +4526,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129227991</v>
+        <v>128867691</v>
       </c>
       <c r="B78" t="s">
         <v>17</v>
@@ -4540,10 +4541,10 @@
         <v>1211</v>
       </c>
       <c r="F78" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="G78" s="1">
-        <v>45547</v>
+        <v>45549</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4578,7 +4579,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129248695</v>
+        <v>128929302</v>
       </c>
       <c r="B79" t="s">
         <v>17</v>
@@ -4593,10 +4594,10 @@
         <v>1211</v>
       </c>
       <c r="F79" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G79" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -4631,7 +4632,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129248839</v>
+        <v>128949123</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -4646,10 +4647,10 @@
         <v>1211</v>
       </c>
       <c r="F80" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G80" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -4684,7 +4685,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129252899</v>
+        <v>128966512</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -4696,13 +4697,13 @@
         <v>17</v>
       </c>
       <c r="E81">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F81" s="1">
-        <v>45544</v>
+        <v>45548</v>
       </c>
       <c r="G81" s="1">
-        <v>45544</v>
+        <v>45548</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -4737,7 +4738,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129253147</v>
+        <v>129051392</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -4752,10 +4753,10 @@
         <v>1211</v>
       </c>
       <c r="F82" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G82" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -4790,7 +4791,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129256716</v>
+        <v>129099682</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -4802,13 +4803,13 @@
         <v>17</v>
       </c>
       <c r="E83">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F83" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G83" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -4843,7 +4844,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129283400</v>
+        <v>129125719</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
@@ -4858,10 +4859,10 @@
         <v>1211</v>
       </c>
       <c r="F84" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G84" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -4896,7 +4897,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129284917</v>
+        <v>129154595</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
@@ -4911,10 +4912,10 @@
         <v>1211</v>
       </c>
       <c r="F85" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G85" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -4949,7 +4950,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129294744</v>
+        <v>129187945</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
@@ -4961,13 +4962,13 @@
         <v>17</v>
       </c>
       <c r="E86">
-        <v>1213</v>
+        <v>2013</v>
       </c>
       <c r="F86" s="1">
-        <v>45547</v>
+        <v>45539</v>
       </c>
       <c r="G86" s="1">
-        <v>45547</v>
+        <v>45539</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -5002,7 +5003,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129307778</v>
+        <v>129199086</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
@@ -5014,13 +5015,13 @@
         <v>17</v>
       </c>
       <c r="E87">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F87" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G87" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -5055,7 +5056,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>129039074</v>
+        <v>129210414</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
@@ -5067,13 +5068,13 @@
         <v>17</v>
       </c>
       <c r="E88">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F88" s="1">
-        <v>45530</v>
+        <v>45548</v>
       </c>
       <c r="G88" s="1">
-        <v>45531</v>
+        <v>45548</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -5082,7 +5083,7 @@
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -5108,7 +5109,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129110148</v>
+        <v>129248055</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -5120,13 +5121,13 @@
         <v>17</v>
       </c>
       <c r="E89">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F89" s="1">
-        <v>45533</v>
+        <v>45548</v>
       </c>
       <c r="G89" s="1">
-        <v>45534</v>
+        <v>45548</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -5135,7 +5136,7 @@
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -5161,7 +5162,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129190578</v>
+        <v>129250978</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -5176,10 +5177,10 @@
         <v>1211</v>
       </c>
       <c r="F90" s="1">
-        <v>45539</v>
+        <v>45548</v>
       </c>
       <c r="G90" s="1">
-        <v>45540</v>
+        <v>45548</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -5188,7 +5189,7 @@
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -5214,7 +5215,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129262213</v>
+        <v>129252899</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
@@ -5229,10 +5230,10 @@
         <v>2013</v>
       </c>
       <c r="F91" s="1">
-        <v>45545</v>
+        <v>45544</v>
       </c>
       <c r="G91" s="1">
-        <v>45546</v>
+        <v>45544</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -5241,7 +5242,7 @@
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
@@ -5267,7 +5268,7 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129302902</v>
+        <v>129268773</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
@@ -5279,10 +5280,10 @@
         <v>17</v>
       </c>
       <c r="E92">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F92" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G92" s="1">
         <v>45548</v>
@@ -5294,7 +5295,7 @@
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K92" t="s">
         <v>17</v>
@@ -5320,7 +5321,7 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129311887</v>
+        <v>129272218</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
@@ -5335,7 +5336,7 @@
         <v>1211</v>
       </c>
       <c r="F93" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="G93" s="1">
         <v>45548</v>
@@ -5347,7 +5348,7 @@
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K93" t="s">
         <v>17</v>
@@ -5373,7 +5374,7 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129277367</v>
+        <v>129275113</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
@@ -5385,13 +5386,13 @@
         <v>17</v>
       </c>
       <c r="E94">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F94" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G94" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -5400,7 +5401,7 @@
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K94" t="s">
         <v>17</v>
@@ -5426,7 +5427,7 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129277833</v>
+        <v>129284494</v>
       </c>
       <c r="B95" t="s">
         <v>17</v>
@@ -5438,13 +5439,13 @@
         <v>17</v>
       </c>
       <c r="E95">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F95" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G95" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -5453,7 +5454,7 @@
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K95" t="s">
         <v>17</v>
@@ -5479,7 +5480,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>129278069</v>
+        <v>129293565</v>
       </c>
       <c r="B96" t="s">
         <v>17</v>
@@ -5491,13 +5492,13 @@
         <v>17</v>
       </c>
       <c r="E96">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F96" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G96" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -5506,7 +5507,7 @@
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K96" t="s">
         <v>17</v>
@@ -5532,7 +5533,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>129278072</v>
+        <v>129307778</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
@@ -5544,13 +5545,13 @@
         <v>17</v>
       </c>
       <c r="E97">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F97" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G97" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -5559,7 +5560,7 @@
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K97" t="s">
         <v>17</v>
@@ -5585,7 +5586,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>129278810</v>
+        <v>129328708</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
@@ -5597,13 +5598,13 @@
         <v>17</v>
       </c>
       <c r="E98">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F98" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="G98" s="1">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -5612,7 +5613,7 @@
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="K98" t="s">
         <v>17</v>
@@ -5638,7 +5639,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>129279786</v>
+        <v>129039074</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
@@ -5650,13 +5651,13 @@
         <v>17</v>
       </c>
       <c r="E99">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F99" s="1">
-        <v>45546</v>
+        <v>45530</v>
       </c>
       <c r="G99" s="1">
-        <v>45546</v>
+        <v>45531</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -5665,7 +5666,7 @@
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K99" t="s">
         <v>17</v>
@@ -5691,7 +5692,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>129280530</v>
+        <v>129110148</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
@@ -5703,13 +5704,13 @@
         <v>17</v>
       </c>
       <c r="E100">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F100" s="1">
-        <v>45546</v>
+        <v>45533</v>
       </c>
       <c r="G100" s="1">
-        <v>45546</v>
+        <v>45534</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -5718,7 +5719,7 @@
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K100" t="s">
         <v>17</v>
@@ -5744,7 +5745,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>129280835</v>
+        <v>129302902</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
@@ -5756,13 +5757,13 @@
         <v>17</v>
       </c>
       <c r="E101">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F101" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G101" s="1">
-        <v>45546</v>
+        <v>45548</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5771,7 +5772,7 @@
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K101" t="s">
         <v>17</v>
@@ -5797,7 +5798,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>129281127</v>
+        <v>129297740</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
@@ -5812,10 +5813,10 @@
         <v>601</v>
       </c>
       <c r="F102" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G102" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -5850,7 +5851,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>129281389</v>
+        <v>129297885</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
@@ -5865,10 +5866,10 @@
         <v>601</v>
       </c>
       <c r="F103" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G103" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -5903,7 +5904,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>129282364</v>
+        <v>129298729</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -5918,10 +5919,10 @@
         <v>601</v>
       </c>
       <c r="F104" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G104" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -5956,7 +5957,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>129285188</v>
+        <v>129299334</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -5971,7 +5972,7 @@
         <v>601</v>
       </c>
       <c r="F105" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G105" s="1">
         <v>45547</v>
@@ -5983,7 +5984,7 @@
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K105" t="s">
         <v>17</v>
@@ -6009,7 +6010,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>129285910</v>
+        <v>129299612</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -6024,10 +6025,10 @@
         <v>601</v>
       </c>
       <c r="F106" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G106" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -6062,7 +6063,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>129286578</v>
+        <v>129300929</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -6077,10 +6078,10 @@
         <v>601</v>
       </c>
       <c r="F107" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G107" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -6115,7 +6116,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>129286639</v>
+        <v>129301943</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -6130,10 +6131,10 @@
         <v>601</v>
       </c>
       <c r="F108" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G108" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -6168,7 +6169,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>129286778</v>
+        <v>129304525</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -6183,10 +6184,10 @@
         <v>601</v>
       </c>
       <c r="F109" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G109" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -6221,7 +6222,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>129287219</v>
+        <v>129306342</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -6236,10 +6237,10 @@
         <v>601</v>
       </c>
       <c r="F110" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G110" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -6274,7 +6275,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>129287842</v>
+        <v>129307931</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
@@ -6289,10 +6290,10 @@
         <v>601</v>
       </c>
       <c r="F111" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G111" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -6327,7 +6328,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>129289063</v>
+        <v>129308396</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -6342,10 +6343,10 @@
         <v>601</v>
       </c>
       <c r="F112" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G112" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -6380,7 +6381,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>129290063</v>
+        <v>129308616</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -6395,10 +6396,10 @@
         <v>601</v>
       </c>
       <c r="F113" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G113" s="1">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -6433,7 +6434,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>129290358</v>
+        <v>129308800</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -6448,10 +6449,10 @@
         <v>601</v>
       </c>
       <c r="F114" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G114" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -6486,7 +6487,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>129291046</v>
+        <v>129308886</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
@@ -6501,10 +6502,10 @@
         <v>601</v>
       </c>
       <c r="F115" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G115" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -6539,7 +6540,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>129291818</v>
+        <v>129311890</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
@@ -6554,10 +6555,10 @@
         <v>601</v>
       </c>
       <c r="F116" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G116" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -6566,7 +6567,7 @@
         <v>42</v>
       </c>
       <c r="J116">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K116" t="s">
         <v>17</v>
@@ -6592,7 +6593,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>129292228</v>
+        <v>129311926</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
@@ -6607,10 +6608,10 @@
         <v>601</v>
       </c>
       <c r="F117" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G117" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -6619,7 +6620,7 @@
         <v>42</v>
       </c>
       <c r="J117">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K117" t="s">
         <v>17</v>
@@ -6645,7 +6646,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>129293096</v>
+        <v>129312043</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
@@ -6660,10 +6661,10 @@
         <v>601</v>
       </c>
       <c r="F118" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G118" s="1">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -6672,7 +6673,7 @@
         <v>42</v>
       </c>
       <c r="J118">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K118" t="s">
         <v>17</v>
@@ -6698,7 +6699,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>129293525</v>
+        <v>129312345</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
@@ -6713,10 +6714,10 @@
         <v>601</v>
       </c>
       <c r="F119" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G119" s="1">
-        <v>45546</v>
+        <v>45549</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -6725,7 +6726,7 @@
         <v>42</v>
       </c>
       <c r="J119">
-        <v>1117</v>
+        <v>8013</v>
       </c>
       <c r="K119" t="s">
         <v>17</v>
@@ -6751,7 +6752,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>129293691</v>
+        <v>129312921</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
@@ -6766,10 +6767,10 @@
         <v>601</v>
       </c>
       <c r="F120" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G120" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -6778,7 +6779,7 @@
         <v>42</v>
       </c>
       <c r="J120">
-        <v>1117</v>
+        <v>8013</v>
       </c>
       <c r="K120" t="s">
         <v>17</v>
@@ -6804,7 +6805,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>129293714</v>
+        <v>129313613</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
@@ -6819,10 +6820,10 @@
         <v>601</v>
       </c>
       <c r="F121" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G121" s="1">
-        <v>45546</v>
+        <v>45549</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -6831,7 +6832,7 @@
         <v>42</v>
       </c>
       <c r="J121">
-        <v>1117</v>
+        <v>8013</v>
       </c>
       <c r="K121" t="s">
         <v>17</v>
@@ -6857,7 +6858,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>129281452</v>
+        <v>129314111</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
@@ -6872,10 +6873,10 @@
         <v>601</v>
       </c>
       <c r="F122" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G122" s="1">
-        <v>45546</v>
+        <v>45549</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -6884,7 +6885,7 @@
         <v>42</v>
       </c>
       <c r="J122">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K122" t="s">
         <v>17</v>
@@ -6910,7 +6911,7 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>129281981</v>
+        <v>129304397</v>
       </c>
       <c r="B123" t="s">
         <v>17</v>
@@ -6925,10 +6926,10 @@
         <v>601</v>
       </c>
       <c r="F123" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G123" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -6963,7 +6964,7 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>129284427</v>
+        <v>129304889</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -6978,10 +6979,10 @@
         <v>601</v>
       </c>
       <c r="F124" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G124" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -7016,7 +7017,7 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>129284857</v>
+        <v>129305619</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -7031,10 +7032,10 @@
         <v>601</v>
       </c>
       <c r="F125" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G125" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -7069,7 +7070,7 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>129280237</v>
+        <v>128037205</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
@@ -7081,13 +7082,13 @@
         <v>17</v>
       </c>
       <c r="E126">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F126" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G126" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -7122,7 +7123,7 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>129042009</v>
+        <v>129296122</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
@@ -7137,10 +7138,10 @@
         <v>601</v>
       </c>
       <c r="F127" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G127" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -7175,7 +7176,7 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>129277501</v>
+        <v>129298087</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
@@ -7190,10 +7191,10 @@
         <v>601</v>
       </c>
       <c r="F128" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G128" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -7228,7 +7229,7 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>129277982</v>
+        <v>129300078</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
@@ -7243,10 +7244,10 @@
         <v>601</v>
       </c>
       <c r="F129" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G129" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -7281,7 +7282,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>129280154</v>
+        <v>129300449</v>
       </c>
       <c r="B130" t="s">
         <v>17</v>
@@ -7296,10 +7297,10 @@
         <v>601</v>
       </c>
       <c r="F130" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G130" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -7334,7 +7335,7 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>129280657</v>
+        <v>129300790</v>
       </c>
       <c r="B131" t="s">
         <v>17</v>
@@ -7349,10 +7350,10 @@
         <v>601</v>
       </c>
       <c r="F131" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G131" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -7387,7 +7388,7 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>129280753</v>
+        <v>129301195</v>
       </c>
       <c r="B132" t="s">
         <v>17</v>
@@ -7402,10 +7403,10 @@
         <v>601</v>
       </c>
       <c r="F132" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G132" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -7440,7 +7441,7 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>129280869</v>
+        <v>129301679</v>
       </c>
       <c r="B133" t="s">
         <v>17</v>
@@ -7455,10 +7456,10 @@
         <v>601</v>
       </c>
       <c r="F133" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G133" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -7493,7 +7494,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>129281066</v>
+        <v>129301804</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
@@ -7508,10 +7509,10 @@
         <v>601</v>
       </c>
       <c r="F134" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G134" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -7546,7 +7547,7 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>129282859</v>
+        <v>129302267</v>
       </c>
       <c r="B135" t="s">
         <v>17</v>
@@ -7561,10 +7562,10 @@
         <v>601</v>
       </c>
       <c r="F135" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G135" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -7599,7 +7600,7 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>129283456</v>
+        <v>129303522</v>
       </c>
       <c r="B136" t="s">
         <v>17</v>
@@ -7614,10 +7615,10 @@
         <v>601</v>
       </c>
       <c r="F136" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G136" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -7652,7 +7653,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>129283829</v>
+        <v>129303721</v>
       </c>
       <c r="B137" t="s">
         <v>17</v>
@@ -7667,10 +7668,10 @@
         <v>601</v>
       </c>
       <c r="F137" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G137" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -7705,7 +7706,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>129284579</v>
+        <v>129306165</v>
       </c>
       <c r="B138" t="s">
         <v>17</v>
@@ -7720,10 +7721,10 @@
         <v>601</v>
       </c>
       <c r="F138" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G138" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -7758,7 +7759,7 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>129285003</v>
+        <v>129310665</v>
       </c>
       <c r="B139" t="s">
         <v>17</v>
@@ -7773,10 +7774,10 @@
         <v>601</v>
       </c>
       <c r="F139" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G139" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -7811,7 +7812,7 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>129286449</v>
+        <v>129312163</v>
       </c>
       <c r="B140" t="s">
         <v>17</v>
@@ -7826,10 +7827,10 @@
         <v>601</v>
       </c>
       <c r="F140" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="G140" s="1">
-        <v>45546</v>
+        <v>45547</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -7864,37 +7865,22 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>129287329</v>
-      </c>
-      <c r="B141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C141" t="s">
-        <v>17</v>
-      </c>
-      <c r="D141" t="s">
-        <v>17</v>
+        <v>129243586</v>
       </c>
       <c r="E141">
         <v>601</v>
       </c>
-      <c r="F141" s="1">
-        <v>45546</v>
-      </c>
-      <c r="G141" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H141" t="s">
-        <v>17</v>
+      <c r="F141" s="2">
+        <v>45544</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45544</v>
       </c>
       <c r="I141">
         <v>42</v>
       </c>
       <c r="J141">
-        <v>8004</v>
-      </c>
-      <c r="K141" t="s">
-        <v>17</v>
+        <v>8003</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -7917,37 +7903,22 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>129288313</v>
-      </c>
-      <c r="B142" t="s">
-        <v>17</v>
-      </c>
-      <c r="C142" t="s">
-        <v>17</v>
-      </c>
-      <c r="D142" t="s">
-        <v>17</v>
+        <v>129266683</v>
       </c>
       <c r="E142">
         <v>601</v>
       </c>
-      <c r="F142" s="1">
-        <v>45546</v>
-      </c>
-      <c r="G142" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H142" t="s">
-        <v>17</v>
+      <c r="F142" s="2">
+        <v>45545</v>
+      </c>
+      <c r="G142" s="2">
+        <v>45545</v>
       </c>
       <c r="I142">
         <v>42</v>
       </c>
       <c r="J142">
-        <v>8004</v>
-      </c>
-      <c r="K142" t="s">
-        <v>17</v>
+        <v>8003</v>
       </c>
       <c r="L142">
         <v>0</v>
@@ -7970,37 +7941,22 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>129289504</v>
-      </c>
-      <c r="B143" t="s">
-        <v>17</v>
-      </c>
-      <c r="C143" t="s">
-        <v>17</v>
-      </c>
-      <c r="D143" t="s">
-        <v>17</v>
+        <v>129268722</v>
       </c>
       <c r="E143">
         <v>601</v>
       </c>
-      <c r="F143" s="1">
-        <v>45546</v>
-      </c>
-      <c r="G143" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H143" t="s">
-        <v>17</v>
+      <c r="F143" s="2">
+        <v>45545</v>
+      </c>
+      <c r="G143" s="2">
+        <v>45545</v>
       </c>
       <c r="I143">
         <v>42</v>
       </c>
       <c r="J143">
-        <v>8004</v>
-      </c>
-      <c r="K143" t="s">
-        <v>17</v>
+        <v>8003</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -8023,37 +7979,22 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>129290514</v>
-      </c>
-      <c r="B144" t="s">
-        <v>17</v>
-      </c>
-      <c r="C144" t="s">
-        <v>17</v>
-      </c>
-      <c r="D144" t="s">
-        <v>17</v>
+        <v>129273914</v>
       </c>
       <c r="E144">
         <v>601</v>
       </c>
-      <c r="F144" s="1">
-        <v>45546</v>
-      </c>
-      <c r="G144" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H144" t="s">
-        <v>17</v>
+      <c r="F144" s="2">
+        <v>45545</v>
+      </c>
+      <c r="G144" s="2">
+        <v>45545</v>
       </c>
       <c r="I144">
         <v>42</v>
       </c>
       <c r="J144">
-        <v>8004</v>
-      </c>
-      <c r="K144" t="s">
-        <v>17</v>
+        <v>1118</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -8076,28 +8017,16 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>129292545</v>
-      </c>
-      <c r="B145" t="s">
-        <v>17</v>
-      </c>
-      <c r="C145" t="s">
-        <v>17</v>
-      </c>
-      <c r="D145" t="s">
-        <v>17</v>
+        <v>129296122</v>
       </c>
       <c r="E145">
         <v>601</v>
       </c>
-      <c r="F145" s="1">
-        <v>45546</v>
-      </c>
-      <c r="G145" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H145" t="s">
-        <v>17</v>
+      <c r="F145" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G145" s="2">
+        <v>45547</v>
       </c>
       <c r="I145">
         <v>42</v>
@@ -8105,9 +8034,6 @@
       <c r="J145">
         <v>8004</v>
       </c>
-      <c r="K145" t="s">
-        <v>17</v>
-      </c>
       <c r="L145">
         <v>0</v>
       </c>
@@ -8129,28 +8055,16 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>129292705</v>
-      </c>
-      <c r="B146" t="s">
-        <v>17</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>17</v>
+        <v>129297740</v>
       </c>
       <c r="E146">
         <v>601</v>
       </c>
-      <c r="F146" s="1">
-        <v>45546</v>
-      </c>
-      <c r="G146" s="1">
-        <v>45546</v>
-      </c>
-      <c r="H146" t="s">
-        <v>17</v>
+      <c r="F146" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G146" s="2">
+        <v>45547</v>
       </c>
       <c r="I146">
         <v>42</v>
@@ -8158,9 +8072,6 @@
       <c r="J146">
         <v>8004</v>
       </c>
-      <c r="K146" t="s">
-        <v>17</v>
-      </c>
       <c r="L146">
         <v>0</v>
       </c>
@@ -8180,8 +8091,3427 @@
         <v>61</v>
       </c>
     </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>129297885</v>
+      </c>
+      <c r="E147">
+        <v>601</v>
+      </c>
+      <c r="F147" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G147" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>8004</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>129298087</v>
+      </c>
+      <c r="E148">
+        <v>601</v>
+      </c>
+      <c r="F148" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G148" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>8004</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>129298729</v>
+      </c>
+      <c r="E149">
+        <v>601</v>
+      </c>
+      <c r="F149" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G149" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
+        <v>8004</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>129299334</v>
+      </c>
+      <c r="E150">
+        <v>601</v>
+      </c>
+      <c r="F150" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G150" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>8004</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>129299612</v>
+      </c>
+      <c r="E151">
+        <v>601</v>
+      </c>
+      <c r="F151" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G151" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I151">
+        <v>42</v>
+      </c>
+      <c r="J151">
+        <v>8004</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>129300078</v>
+      </c>
+      <c r="E152">
+        <v>601</v>
+      </c>
+      <c r="F152" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G152" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I152">
+        <v>42</v>
+      </c>
+      <c r="J152">
+        <v>8004</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>129300449</v>
+      </c>
+      <c r="E153">
+        <v>601</v>
+      </c>
+      <c r="F153" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G153" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I153">
+        <v>42</v>
+      </c>
+      <c r="J153">
+        <v>8004</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>129300790</v>
+      </c>
+      <c r="E154">
+        <v>601</v>
+      </c>
+      <c r="F154" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G154" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I154">
+        <v>42</v>
+      </c>
+      <c r="J154">
+        <v>8004</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>129300929</v>
+      </c>
+      <c r="E155">
+        <v>601</v>
+      </c>
+      <c r="F155" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G155" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I155">
+        <v>42</v>
+      </c>
+      <c r="J155">
+        <v>8004</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>129301195</v>
+      </c>
+      <c r="E156">
+        <v>601</v>
+      </c>
+      <c r="F156" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G156" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I156">
+        <v>42</v>
+      </c>
+      <c r="J156">
+        <v>8004</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>129301679</v>
+      </c>
+      <c r="E157">
+        <v>601</v>
+      </c>
+      <c r="F157" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G157" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I157">
+        <v>42</v>
+      </c>
+      <c r="J157">
+        <v>8004</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+      <c r="Q157">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>129301804</v>
+      </c>
+      <c r="E158">
+        <v>601</v>
+      </c>
+      <c r="F158" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G158" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I158">
+        <v>42</v>
+      </c>
+      <c r="J158">
+        <v>8004</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>0</v>
+      </c>
+      <c r="Q158">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>129301943</v>
+      </c>
+      <c r="E159">
+        <v>601</v>
+      </c>
+      <c r="F159" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G159" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I159">
+        <v>42</v>
+      </c>
+      <c r="J159">
+        <v>8004</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+      <c r="Q159">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>129302267</v>
+      </c>
+      <c r="E160">
+        <v>601</v>
+      </c>
+      <c r="F160" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G160" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I160">
+        <v>42</v>
+      </c>
+      <c r="J160">
+        <v>8004</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>0</v>
+      </c>
+      <c r="Q160">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>129303522</v>
+      </c>
+      <c r="E161">
+        <v>601</v>
+      </c>
+      <c r="F161" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G161" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I161">
+        <v>42</v>
+      </c>
+      <c r="J161">
+        <v>8004</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>0</v>
+      </c>
+      <c r="Q161">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>129303721</v>
+      </c>
+      <c r="E162">
+        <v>601</v>
+      </c>
+      <c r="F162" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G162" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I162">
+        <v>42</v>
+      </c>
+      <c r="J162">
+        <v>8004</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>129304397</v>
+      </c>
+      <c r="E163">
+        <v>601</v>
+      </c>
+      <c r="F163" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G163" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I163">
+        <v>42</v>
+      </c>
+      <c r="J163">
+        <v>8001</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="Q163">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>129304525</v>
+      </c>
+      <c r="E164">
+        <v>601</v>
+      </c>
+      <c r="F164" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G164" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I164">
+        <v>42</v>
+      </c>
+      <c r="J164">
+        <v>8004</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="Q164">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>129304889</v>
+      </c>
+      <c r="E165">
+        <v>601</v>
+      </c>
+      <c r="F165" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G165" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I165">
+        <v>42</v>
+      </c>
+      <c r="J165">
+        <v>8001</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>129305619</v>
+      </c>
+      <c r="E166">
+        <v>601</v>
+      </c>
+      <c r="F166" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G166" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I166">
+        <v>42</v>
+      </c>
+      <c r="J166">
+        <v>8001</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="Q166">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>129306165</v>
+      </c>
+      <c r="E167">
+        <v>601</v>
+      </c>
+      <c r="F167" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G167" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I167">
+        <v>42</v>
+      </c>
+      <c r="J167">
+        <v>8004</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="Q167">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>129306342</v>
+      </c>
+      <c r="E168">
+        <v>601</v>
+      </c>
+      <c r="F168" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G168" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I168">
+        <v>42</v>
+      </c>
+      <c r="J168">
+        <v>8004</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <v>0</v>
+      </c>
+      <c r="Q168">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>129307931</v>
+      </c>
+      <c r="E169">
+        <v>601</v>
+      </c>
+      <c r="F169" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G169" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I169">
+        <v>42</v>
+      </c>
+      <c r="J169">
+        <v>8004</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+      <c r="Q169">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>129308396</v>
+      </c>
+      <c r="E170">
+        <v>601</v>
+      </c>
+      <c r="F170" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G170" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I170">
+        <v>42</v>
+      </c>
+      <c r="J170">
+        <v>8004</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="Q170">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>129308616</v>
+      </c>
+      <c r="E171">
+        <v>601</v>
+      </c>
+      <c r="F171" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G171" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I171">
+        <v>42</v>
+      </c>
+      <c r="J171">
+        <v>8013</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="Q171">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>129308800</v>
+      </c>
+      <c r="E172">
+        <v>601</v>
+      </c>
+      <c r="F172" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G172" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I172">
+        <v>42</v>
+      </c>
+      <c r="J172">
+        <v>8004</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>0</v>
+      </c>
+      <c r="Q172">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>129308886</v>
+      </c>
+      <c r="E173">
+        <v>601</v>
+      </c>
+      <c r="F173" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G173" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I173">
+        <v>42</v>
+      </c>
+      <c r="J173">
+        <v>8004</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>129310628</v>
+      </c>
+      <c r="E174">
+        <v>601</v>
+      </c>
+      <c r="F174" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G174" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I174">
+        <v>42</v>
+      </c>
+      <c r="J174">
+        <v>8003</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>0</v>
+      </c>
+      <c r="Q174">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>129310665</v>
+      </c>
+      <c r="E175">
+        <v>601</v>
+      </c>
+      <c r="F175" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G175" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I175">
+        <v>42</v>
+      </c>
+      <c r="J175">
+        <v>8004</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>0</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>0</v>
+      </c>
+      <c r="Q175">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>129311890</v>
+      </c>
+      <c r="E176">
+        <v>601</v>
+      </c>
+      <c r="F176" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G176" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I176">
+        <v>42</v>
+      </c>
+      <c r="J176">
+        <v>8013</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176">
+        <v>0</v>
+      </c>
+      <c r="P176">
+        <v>0</v>
+      </c>
+      <c r="Q176">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>129311926</v>
+      </c>
+      <c r="E177">
+        <v>601</v>
+      </c>
+      <c r="F177" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G177" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I177">
+        <v>42</v>
+      </c>
+      <c r="J177">
+        <v>8013</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <v>0</v>
+      </c>
+      <c r="Q177">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>129312043</v>
+      </c>
+      <c r="E178">
+        <v>601</v>
+      </c>
+      <c r="F178" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G178" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I178">
+        <v>42</v>
+      </c>
+      <c r="J178">
+        <v>8004</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+      <c r="Q178">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>129312163</v>
+      </c>
+      <c r="E179">
+        <v>601</v>
+      </c>
+      <c r="F179" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G179" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I179">
+        <v>42</v>
+      </c>
+      <c r="J179">
+        <v>8004</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+      <c r="Q179">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>129312345</v>
+      </c>
+      <c r="E180">
+        <v>601</v>
+      </c>
+      <c r="F180" s="2">
+        <v>45549</v>
+      </c>
+      <c r="G180" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I180">
+        <v>42</v>
+      </c>
+      <c r="J180">
+        <v>8013</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180">
+        <v>0</v>
+      </c>
+      <c r="P180">
+        <v>0</v>
+      </c>
+      <c r="Q180">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>129312921</v>
+      </c>
+      <c r="E181">
+        <v>601</v>
+      </c>
+      <c r="F181" s="2">
+        <v>45547</v>
+      </c>
+      <c r="G181" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I181">
+        <v>42</v>
+      </c>
+      <c r="J181">
+        <v>8013</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>0</v>
+      </c>
+      <c r="O181">
+        <v>0</v>
+      </c>
+      <c r="P181">
+        <v>0</v>
+      </c>
+      <c r="Q181">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>129313613</v>
+      </c>
+      <c r="E182">
+        <v>601</v>
+      </c>
+      <c r="F182" s="2">
+        <v>45549</v>
+      </c>
+      <c r="G182" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I182">
+        <v>42</v>
+      </c>
+      <c r="J182">
+        <v>8013</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+      <c r="P182">
+        <v>0</v>
+      </c>
+      <c r="Q182">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>129314111</v>
+      </c>
+      <c r="E183">
+        <v>601</v>
+      </c>
+      <c r="F183" s="2">
+        <v>45549</v>
+      </c>
+      <c r="G183" s="2">
+        <v>45547</v>
+      </c>
+      <c r="I183">
+        <v>42</v>
+      </c>
+      <c r="J183">
+        <v>8013</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183">
+        <v>0</v>
+      </c>
+      <c r="P183">
+        <v>0</v>
+      </c>
+      <c r="Q183">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>129314903</v>
+      </c>
+      <c r="E184">
+        <v>601</v>
+      </c>
+      <c r="F184" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G184" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I184">
+        <v>42</v>
+      </c>
+      <c r="J184">
+        <v>8013</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>0</v>
+      </c>
+      <c r="Q184">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>129314905</v>
+      </c>
+      <c r="E185">
+        <v>601</v>
+      </c>
+      <c r="F185" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G185" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I185">
+        <v>42</v>
+      </c>
+      <c r="J185">
+        <v>8013</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>0</v>
+      </c>
+      <c r="Q185">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>129314908</v>
+      </c>
+      <c r="E186">
+        <v>601</v>
+      </c>
+      <c r="F186" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G186" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I186">
+        <v>42</v>
+      </c>
+      <c r="J186">
+        <v>8013</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+      <c r="P186">
+        <v>0</v>
+      </c>
+      <c r="Q186">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>129315005</v>
+      </c>
+      <c r="E187">
+        <v>601</v>
+      </c>
+      <c r="F187" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G187" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I187">
+        <v>42</v>
+      </c>
+      <c r="J187">
+        <v>8013</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187">
+        <v>0</v>
+      </c>
+      <c r="P187">
+        <v>0</v>
+      </c>
+      <c r="Q187">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>129315010</v>
+      </c>
+      <c r="E188">
+        <v>601</v>
+      </c>
+      <c r="F188" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G188" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I188">
+        <v>42</v>
+      </c>
+      <c r="J188">
+        <v>8003</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>0</v>
+      </c>
+      <c r="O188">
+        <v>0</v>
+      </c>
+      <c r="P188">
+        <v>0</v>
+      </c>
+      <c r="Q188">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>129315026</v>
+      </c>
+      <c r="E189">
+        <v>601</v>
+      </c>
+      <c r="F189" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G189" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I189">
+        <v>42</v>
+      </c>
+      <c r="J189">
+        <v>8003</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189">
+        <v>0</v>
+      </c>
+      <c r="P189">
+        <v>0</v>
+      </c>
+      <c r="Q189">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>129315362</v>
+      </c>
+      <c r="E190">
+        <v>601</v>
+      </c>
+      <c r="F190" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G190" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I190">
+        <v>42</v>
+      </c>
+      <c r="J190">
+        <v>8013</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>0</v>
+      </c>
+      <c r="N190">
+        <v>0</v>
+      </c>
+      <c r="O190">
+        <v>0</v>
+      </c>
+      <c r="P190">
+        <v>0</v>
+      </c>
+      <c r="Q190">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>129315363</v>
+      </c>
+      <c r="E191">
+        <v>601</v>
+      </c>
+      <c r="F191" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G191" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I191">
+        <v>42</v>
+      </c>
+      <c r="J191">
+        <v>8013</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>0</v>
+      </c>
+      <c r="O191">
+        <v>0</v>
+      </c>
+      <c r="P191">
+        <v>0</v>
+      </c>
+      <c r="Q191">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>129315365</v>
+      </c>
+      <c r="E192">
+        <v>601</v>
+      </c>
+      <c r="F192" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G192" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I192">
+        <v>42</v>
+      </c>
+      <c r="J192">
+        <v>8013</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>0</v>
+      </c>
+      <c r="O192">
+        <v>0</v>
+      </c>
+      <c r="P192">
+        <v>0</v>
+      </c>
+      <c r="Q192">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>129315366</v>
+      </c>
+      <c r="E193">
+        <v>601</v>
+      </c>
+      <c r="F193" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G193" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I193">
+        <v>42</v>
+      </c>
+      <c r="J193">
+        <v>8013</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>0</v>
+      </c>
+      <c r="O193">
+        <v>0</v>
+      </c>
+      <c r="P193">
+        <v>0</v>
+      </c>
+      <c r="Q193">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>129315367</v>
+      </c>
+      <c r="E194">
+        <v>601</v>
+      </c>
+      <c r="F194" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G194" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I194">
+        <v>42</v>
+      </c>
+      <c r="J194">
+        <v>8013</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="N194">
+        <v>0</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+      <c r="P194">
+        <v>0</v>
+      </c>
+      <c r="Q194">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>129315368</v>
+      </c>
+      <c r="E195">
+        <v>601</v>
+      </c>
+      <c r="F195" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G195" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I195">
+        <v>42</v>
+      </c>
+      <c r="J195">
+        <v>8013</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195">
+        <v>0</v>
+      </c>
+      <c r="P195">
+        <v>0</v>
+      </c>
+      <c r="Q195">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>129317237</v>
+      </c>
+      <c r="E196">
+        <v>601</v>
+      </c>
+      <c r="F196" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G196" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I196">
+        <v>42</v>
+      </c>
+      <c r="J196">
+        <v>8004</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="N196">
+        <v>0</v>
+      </c>
+      <c r="O196">
+        <v>0</v>
+      </c>
+      <c r="P196">
+        <v>0</v>
+      </c>
+      <c r="Q196">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>129317254</v>
+      </c>
+      <c r="E197">
+        <v>601</v>
+      </c>
+      <c r="F197" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G197" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I197">
+        <v>42</v>
+      </c>
+      <c r="J197">
+        <v>8013</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197">
+        <v>0</v>
+      </c>
+      <c r="P197">
+        <v>0</v>
+      </c>
+      <c r="Q197">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>129317349</v>
+      </c>
+      <c r="E198">
+        <v>601</v>
+      </c>
+      <c r="F198" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G198" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I198">
+        <v>42</v>
+      </c>
+      <c r="J198">
+        <v>8004</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <v>0</v>
+      </c>
+      <c r="P198">
+        <v>0</v>
+      </c>
+      <c r="Q198">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>129317461</v>
+      </c>
+      <c r="E199">
+        <v>601</v>
+      </c>
+      <c r="F199" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G199" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I199">
+        <v>42</v>
+      </c>
+      <c r="J199">
+        <v>8004</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="N199">
+        <v>0</v>
+      </c>
+      <c r="O199">
+        <v>0</v>
+      </c>
+      <c r="P199">
+        <v>0</v>
+      </c>
+      <c r="Q199">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>129317712</v>
+      </c>
+      <c r="E200">
+        <v>601</v>
+      </c>
+      <c r="F200" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G200" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I200">
+        <v>42</v>
+      </c>
+      <c r="J200">
+        <v>8004</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+      <c r="P200">
+        <v>0</v>
+      </c>
+      <c r="Q200">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>129318356</v>
+      </c>
+      <c r="E201">
+        <v>601</v>
+      </c>
+      <c r="F201" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G201" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I201">
+        <v>42</v>
+      </c>
+      <c r="J201">
+        <v>8004</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>0</v>
+      </c>
+      <c r="O201">
+        <v>0</v>
+      </c>
+      <c r="P201">
+        <v>0</v>
+      </c>
+      <c r="Q201">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>129318584</v>
+      </c>
+      <c r="E202">
+        <v>601</v>
+      </c>
+      <c r="F202" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G202" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I202">
+        <v>42</v>
+      </c>
+      <c r="J202">
+        <v>8001</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="N202">
+        <v>0</v>
+      </c>
+      <c r="O202">
+        <v>0</v>
+      </c>
+      <c r="P202">
+        <v>0</v>
+      </c>
+      <c r="Q202">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>129318710</v>
+      </c>
+      <c r="E203">
+        <v>601</v>
+      </c>
+      <c r="F203" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G203" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I203">
+        <v>42</v>
+      </c>
+      <c r="J203">
+        <v>8004</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203">
+        <v>0</v>
+      </c>
+      <c r="P203">
+        <v>0</v>
+      </c>
+      <c r="Q203">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>129320130</v>
+      </c>
+      <c r="E204">
+        <v>601</v>
+      </c>
+      <c r="F204" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G204" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I204">
+        <v>42</v>
+      </c>
+      <c r="J204">
+        <v>8003</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="N204">
+        <v>0</v>
+      </c>
+      <c r="O204">
+        <v>0</v>
+      </c>
+      <c r="P204">
+        <v>0</v>
+      </c>
+      <c r="Q204">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>129320172</v>
+      </c>
+      <c r="E205">
+        <v>601</v>
+      </c>
+      <c r="F205" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G205" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I205">
+        <v>42</v>
+      </c>
+      <c r="J205">
+        <v>8004</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="N205">
+        <v>0</v>
+      </c>
+      <c r="O205">
+        <v>0</v>
+      </c>
+      <c r="P205">
+        <v>0</v>
+      </c>
+      <c r="Q205">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>129320836</v>
+      </c>
+      <c r="E206">
+        <v>601</v>
+      </c>
+      <c r="F206" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G206" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I206">
+        <v>42</v>
+      </c>
+      <c r="J206">
+        <v>1118</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="N206">
+        <v>0</v>
+      </c>
+      <c r="O206">
+        <v>0</v>
+      </c>
+      <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>129320936</v>
+      </c>
+      <c r="E207">
+        <v>601</v>
+      </c>
+      <c r="F207" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G207" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I207">
+        <v>42</v>
+      </c>
+      <c r="J207">
+        <v>8001</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="N207">
+        <v>0</v>
+      </c>
+      <c r="O207">
+        <v>0</v>
+      </c>
+      <c r="P207">
+        <v>0</v>
+      </c>
+      <c r="Q207">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>129321286</v>
+      </c>
+      <c r="E208">
+        <v>601</v>
+      </c>
+      <c r="F208" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G208" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I208">
+        <v>42</v>
+      </c>
+      <c r="J208">
+        <v>8004</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="N208">
+        <v>0</v>
+      </c>
+      <c r="O208">
+        <v>0</v>
+      </c>
+      <c r="P208">
+        <v>0</v>
+      </c>
+      <c r="Q208">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>129322113</v>
+      </c>
+      <c r="E209">
+        <v>601</v>
+      </c>
+      <c r="F209" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G209" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I209">
+        <v>42</v>
+      </c>
+      <c r="J209">
+        <v>8001</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209">
+        <v>0</v>
+      </c>
+      <c r="N209">
+        <v>0</v>
+      </c>
+      <c r="O209">
+        <v>0</v>
+      </c>
+      <c r="P209">
+        <v>0</v>
+      </c>
+      <c r="Q209">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>129322145</v>
+      </c>
+      <c r="E210">
+        <v>601</v>
+      </c>
+      <c r="F210" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G210" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I210">
+        <v>42</v>
+      </c>
+      <c r="J210">
+        <v>8004</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210">
+        <v>0</v>
+      </c>
+      <c r="P210">
+        <v>0</v>
+      </c>
+      <c r="Q210">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>129322353</v>
+      </c>
+      <c r="E211">
+        <v>601</v>
+      </c>
+      <c r="F211" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G211" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I211">
+        <v>42</v>
+      </c>
+      <c r="J211">
+        <v>8004</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>0</v>
+      </c>
+      <c r="O211">
+        <v>0</v>
+      </c>
+      <c r="P211">
+        <v>0</v>
+      </c>
+      <c r="Q211">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>129322533</v>
+      </c>
+      <c r="E212">
+        <v>601</v>
+      </c>
+      <c r="F212" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G212" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I212">
+        <v>42</v>
+      </c>
+      <c r="J212">
+        <v>8004</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+      <c r="M212">
+        <v>0</v>
+      </c>
+      <c r="N212">
+        <v>0</v>
+      </c>
+      <c r="O212">
+        <v>0</v>
+      </c>
+      <c r="P212">
+        <v>0</v>
+      </c>
+      <c r="Q212">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>129322571</v>
+      </c>
+      <c r="E213">
+        <v>601</v>
+      </c>
+      <c r="F213" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G213" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I213">
+        <v>42</v>
+      </c>
+      <c r="J213">
+        <v>8013</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213">
+        <v>0</v>
+      </c>
+      <c r="P213">
+        <v>0</v>
+      </c>
+      <c r="Q213">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>129323228</v>
+      </c>
+      <c r="E214">
+        <v>601</v>
+      </c>
+      <c r="F214" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G214" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I214">
+        <v>42</v>
+      </c>
+      <c r="J214">
+        <v>8004</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>0</v>
+      </c>
+      <c r="N214">
+        <v>0</v>
+      </c>
+      <c r="O214">
+        <v>0</v>
+      </c>
+      <c r="P214">
+        <v>0</v>
+      </c>
+      <c r="Q214">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>129323289</v>
+      </c>
+      <c r="E215">
+        <v>601</v>
+      </c>
+      <c r="F215" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G215" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I215">
+        <v>42</v>
+      </c>
+      <c r="J215">
+        <v>1118</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>0</v>
+      </c>
+      <c r="O215">
+        <v>0</v>
+      </c>
+      <c r="P215">
+        <v>0</v>
+      </c>
+      <c r="Q215">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>129323631</v>
+      </c>
+      <c r="E216">
+        <v>601</v>
+      </c>
+      <c r="F216" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G216" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I216">
+        <v>42</v>
+      </c>
+      <c r="J216">
+        <v>8004</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>0</v>
+      </c>
+      <c r="O216">
+        <v>0</v>
+      </c>
+      <c r="P216">
+        <v>0</v>
+      </c>
+      <c r="Q216">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>129324237</v>
+      </c>
+      <c r="E217">
+        <v>601</v>
+      </c>
+      <c r="F217" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G217" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I217">
+        <v>42</v>
+      </c>
+      <c r="J217">
+        <v>8004</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217">
+        <v>0</v>
+      </c>
+      <c r="P217">
+        <v>0</v>
+      </c>
+      <c r="Q217">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>129324632</v>
+      </c>
+      <c r="E218">
+        <v>601</v>
+      </c>
+      <c r="F218" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G218" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I218">
+        <v>42</v>
+      </c>
+      <c r="J218">
+        <v>8004</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>0</v>
+      </c>
+      <c r="O218">
+        <v>0</v>
+      </c>
+      <c r="P218">
+        <v>0</v>
+      </c>
+      <c r="Q218">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>129325434</v>
+      </c>
+      <c r="E219">
+        <v>601</v>
+      </c>
+      <c r="F219" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G219" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I219">
+        <v>42</v>
+      </c>
+      <c r="J219">
+        <v>8004</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+      <c r="M219">
+        <v>0</v>
+      </c>
+      <c r="N219">
+        <v>0</v>
+      </c>
+      <c r="O219">
+        <v>0</v>
+      </c>
+      <c r="P219">
+        <v>0</v>
+      </c>
+      <c r="Q219">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>129325510</v>
+      </c>
+      <c r="E220">
+        <v>601</v>
+      </c>
+      <c r="F220" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G220" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I220">
+        <v>42</v>
+      </c>
+      <c r="J220">
+        <v>8004</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>0</v>
+      </c>
+      <c r="O220">
+        <v>0</v>
+      </c>
+      <c r="P220">
+        <v>0</v>
+      </c>
+      <c r="Q220">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>129326088</v>
+      </c>
+      <c r="E221">
+        <v>601</v>
+      </c>
+      <c r="F221" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G221" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I221">
+        <v>42</v>
+      </c>
+      <c r="J221">
+        <v>8004</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>0</v>
+      </c>
+      <c r="O221">
+        <v>0</v>
+      </c>
+      <c r="P221">
+        <v>0</v>
+      </c>
+      <c r="Q221">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>129326814</v>
+      </c>
+      <c r="E222">
+        <v>601</v>
+      </c>
+      <c r="F222" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G222" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I222">
+        <v>42</v>
+      </c>
+      <c r="J222">
+        <v>8004</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>0</v>
+      </c>
+      <c r="O222">
+        <v>0</v>
+      </c>
+      <c r="P222">
+        <v>0</v>
+      </c>
+      <c r="Q222">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>129327095</v>
+      </c>
+      <c r="E223">
+        <v>601</v>
+      </c>
+      <c r="F223" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G223" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I223">
+        <v>42</v>
+      </c>
+      <c r="J223">
+        <v>8004</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>0</v>
+      </c>
+      <c r="O223">
+        <v>0</v>
+      </c>
+      <c r="P223">
+        <v>0</v>
+      </c>
+      <c r="Q223">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>129328074</v>
+      </c>
+      <c r="E224">
+        <v>601</v>
+      </c>
+      <c r="F224" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G224" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I224">
+        <v>42</v>
+      </c>
+      <c r="J224">
+        <v>8004</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>0</v>
+      </c>
+      <c r="N224">
+        <v>0</v>
+      </c>
+      <c r="O224">
+        <v>0</v>
+      </c>
+      <c r="P224">
+        <v>0</v>
+      </c>
+      <c r="Q224">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>129328259</v>
+      </c>
+      <c r="E225">
+        <v>601</v>
+      </c>
+      <c r="F225" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G225" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I225">
+        <v>42</v>
+      </c>
+      <c r="J225">
+        <v>8004</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>0</v>
+      </c>
+      <c r="O225">
+        <v>0</v>
+      </c>
+      <c r="P225">
+        <v>0</v>
+      </c>
+      <c r="Q225">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>129328734</v>
+      </c>
+      <c r="E226">
+        <v>601</v>
+      </c>
+      <c r="F226" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G226" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I226">
+        <v>42</v>
+      </c>
+      <c r="J226">
+        <v>8004</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>0</v>
+      </c>
+      <c r="O226">
+        <v>0</v>
+      </c>
+      <c r="P226">
+        <v>0</v>
+      </c>
+      <c r="Q226">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>129328842</v>
+      </c>
+      <c r="E227">
+        <v>601</v>
+      </c>
+      <c r="F227" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G227" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I227">
+        <v>42</v>
+      </c>
+      <c r="J227">
+        <v>8004</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>0</v>
+      </c>
+      <c r="O227">
+        <v>0</v>
+      </c>
+      <c r="P227">
+        <v>0</v>
+      </c>
+      <c r="Q227">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>129329291</v>
+      </c>
+      <c r="E228">
+        <v>601</v>
+      </c>
+      <c r="F228" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G228" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I228">
+        <v>42</v>
+      </c>
+      <c r="J228">
+        <v>8004</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228">
+        <v>0</v>
+      </c>
+      <c r="P228">
+        <v>0</v>
+      </c>
+      <c r="Q228">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>129330462</v>
+      </c>
+      <c r="E229">
+        <v>601</v>
+      </c>
+      <c r="F229" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G229" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I229">
+        <v>42</v>
+      </c>
+      <c r="J229">
+        <v>8004</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>0</v>
+      </c>
+      <c r="O229">
+        <v>0</v>
+      </c>
+      <c r="P229">
+        <v>0</v>
+      </c>
+      <c r="Q229">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>129331460</v>
+      </c>
+      <c r="E230">
+        <v>601</v>
+      </c>
+      <c r="F230" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G230" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I230">
+        <v>42</v>
+      </c>
+      <c r="J230">
+        <v>8004</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>0</v>
+      </c>
+      <c r="O230">
+        <v>0</v>
+      </c>
+      <c r="P230">
+        <v>0</v>
+      </c>
+      <c r="Q230">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>129332246</v>
+      </c>
+      <c r="E231">
+        <v>601</v>
+      </c>
+      <c r="F231" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G231" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I231">
+        <v>42</v>
+      </c>
+      <c r="J231">
+        <v>8004</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>0</v>
+      </c>
+      <c r="O231">
+        <v>0</v>
+      </c>
+      <c r="P231">
+        <v>0</v>
+      </c>
+      <c r="Q231">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>129332309</v>
+      </c>
+      <c r="E232">
+        <v>601</v>
+      </c>
+      <c r="F232" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G232" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I232">
+        <v>42</v>
+      </c>
+      <c r="J232">
+        <v>8004</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232">
+        <v>0</v>
+      </c>
+      <c r="P232">
+        <v>0</v>
+      </c>
+      <c r="Q232">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>129332613</v>
+      </c>
+      <c r="E233">
+        <v>601</v>
+      </c>
+      <c r="F233" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G233" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I233">
+        <v>42</v>
+      </c>
+      <c r="J233">
+        <v>8004</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>0</v>
+      </c>
+      <c r="O233">
+        <v>0</v>
+      </c>
+      <c r="P233">
+        <v>0</v>
+      </c>
+      <c r="Q233">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>129332619</v>
+      </c>
+      <c r="E234">
+        <v>601</v>
+      </c>
+      <c r="F234" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G234" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I234">
+        <v>42</v>
+      </c>
+      <c r="J234">
+        <v>8004</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234">
+        <v>0</v>
+      </c>
+      <c r="P234">
+        <v>0</v>
+      </c>
+      <c r="Q234">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>129335768</v>
+      </c>
+      <c r="E235">
+        <v>601</v>
+      </c>
+      <c r="F235" s="2">
+        <v>45548</v>
+      </c>
+      <c r="G235" s="2">
+        <v>45548</v>
+      </c>
+      <c r="I235">
+        <v>42</v>
+      </c>
+      <c r="J235">
+        <v>8004</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>0</v>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235">
+        <v>0</v>
+      </c>
+      <c r="P235">
+        <v>0</v>
+      </c>
+      <c r="Q235">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>129338486</v>
+      </c>
+      <c r="E236">
+        <v>601</v>
+      </c>
+      <c r="F236" s="2">
+        <v>45549</v>
+      </c>
+      <c r="G236" s="2">
+        <v>45549</v>
+      </c>
+      <c r="I236">
+        <v>42</v>
+      </c>
+      <c r="J236">
+        <v>8004</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>0</v>
+      </c>
+      <c r="O236">
+        <v>0</v>
+      </c>
+      <c r="P236">
+        <v>0</v>
+      </c>
+      <c r="Q236">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q146" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443D7211-97F4-406D-8FA4-92ED526E6D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BA153F-3D32-49A6-9D0F-0BEE4B28911D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$1490</definedName>
-    <definedName name="Fiel">Fiel!$A$1:$Q$18</definedName>
+    <definedName name="Fiel">Fiel!$A$1:$Q$38</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="18">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -498,7 +498,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129349778</v>
+        <v>129360906</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -513,10 +513,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45551</v>
+        <v>45552</v>
       </c>
       <c r="G2" s="1">
-        <v>45551</v>
+        <v>45552</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -551,7 +551,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129352917</v>
+        <v>129370464</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -566,7 +566,7 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45551</v>
+        <v>45552</v>
       </c>
       <c r="G3" s="1">
         <v>45552</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129353746</v>
+        <v>129375296</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -619,10 +619,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45551</v>
+        <v>45552</v>
       </c>
       <c r="G4" s="1">
-        <v>45551</v>
+        <v>45552</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
@@ -657,7 +657,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129190578</v>
+        <v>129381591</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -672,10 +672,10 @@
         <v>1211</v>
       </c>
       <c r="F5" s="1">
-        <v>45539</v>
+        <v>45553</v>
       </c>
       <c r="G5" s="1">
-        <v>45540</v>
+        <v>45554</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
@@ -684,7 +684,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -710,7 +710,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>129311887</v>
+        <v>129383791</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -725,10 +725,10 @@
         <v>1211</v>
       </c>
       <c r="F6" s="1">
-        <v>45547</v>
+        <v>45553</v>
       </c>
       <c r="G6" s="1">
-        <v>45548</v>
+        <v>45553</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -737,7 +737,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>129379286</v>
+        <v>129389743</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -790,7 +790,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>125423225</v>
+        <v>129393501</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -828,10 +828,10 @@
         <v>17</v>
       </c>
       <c r="E8">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F8" s="1">
-        <v>45551</v>
+        <v>45553</v>
       </c>
       <c r="G8" s="1">
         <v>45554</v>
@@ -843,7 +843,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>126760968</v>
+        <v>129397349</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -884,7 +884,7 @@
         <v>1211</v>
       </c>
       <c r="F9" s="1">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="G9" s="1">
         <v>45554</v>
@@ -896,7 +896,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>127072625</v>
+        <v>129399116</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -937,10 +937,10 @@
         <v>1211</v>
       </c>
       <c r="F10" s="1">
-        <v>45551</v>
+        <v>45554</v>
       </c>
       <c r="G10" s="1">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H10" t="s">
         <v>17</v>
@@ -949,7 +949,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>127283696</v>
+        <v>129399493</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -987,10 +987,10 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F11" s="1">
-        <v>45548</v>
+        <v>45554</v>
       </c>
       <c r="G11" s="1">
         <v>45554</v>
@@ -1002,7 +1002,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>127349785</v>
+        <v>129408045</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1043,7 +1043,7 @@
         <v>1211</v>
       </c>
       <c r="F12" s="1">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="G12" s="1">
         <v>45554</v>
@@ -1055,7 +1055,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>129039074</v>
+        <v>129410081</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1093,13 +1093,13 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="1">
-        <v>45530</v>
+        <v>45554</v>
       </c>
       <c r="G13" s="1">
-        <v>45531</v>
+        <v>45554</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1108,7 +1108,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K13" t="s">
         <v>17</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>129110148</v>
+        <v>129412347</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1146,13 +1146,13 @@
         <v>17</v>
       </c>
       <c r="E14">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="1">
-        <v>45533</v>
+        <v>45554</v>
       </c>
       <c r="G14" s="1">
-        <v>45534</v>
+        <v>45555</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1161,7 +1161,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>129374503</v>
+        <v>129413924</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1199,13 +1199,13 @@
         <v>17</v>
       </c>
       <c r="E15">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="1">
-        <v>45552</v>
+        <v>45554</v>
       </c>
       <c r="G15" s="1">
-        <v>45553</v>
+        <v>45555</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1214,7 +1214,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -1240,22 +1240,37 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>128656503</v>
+        <v>129190578</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>601</v>
-      </c>
-      <c r="F16" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G16" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45539</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45540</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
       </c>
       <c r="I16">
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8004</v>
+        <v>8021</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1278,22 +1293,37 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>128657515</v>
+        <v>129311887</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
       </c>
       <c r="E17">
-        <v>601</v>
-      </c>
-      <c r="F17" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G17" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45547</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45548</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
       </c>
       <c r="I17">
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8004</v>
+        <v>8021</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1316,22 +1346,37 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>129341380</v>
+        <v>129379286</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>601</v>
-      </c>
-      <c r="F18" s="2">
+        <v>1211</v>
+      </c>
+      <c r="F18" s="1">
         <v>45553</v>
       </c>
-      <c r="G18" s="2">
-        <v>45551</v>
+      <c r="G18" s="1">
+        <v>45554</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
       </c>
       <c r="I18">
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8013</v>
+        <v>8021</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1354,22 +1399,37 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>129341610</v>
+        <v>125459584</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
       </c>
       <c r="E19">
-        <v>601</v>
-      </c>
-      <c r="F19" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G19" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45554</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
       </c>
       <c r="I19">
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1392,22 +1452,37 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>129341717</v>
+        <v>127133185</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
       </c>
       <c r="E20">
-        <v>601</v>
-      </c>
-      <c r="F20" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G20" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45553</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1430,22 +1505,37 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>129341844</v>
+        <v>127168672</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
       </c>
       <c r="E21">
-        <v>601</v>
-      </c>
-      <c r="F21" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G21" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45548</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45556</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1468,22 +1558,37 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>129341883</v>
+        <v>127172160</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
       </c>
       <c r="E22">
-        <v>601</v>
-      </c>
-      <c r="F22" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G22" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45554</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1506,22 +1611,37 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>129342561</v>
+        <v>127356658</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>601</v>
-      </c>
-      <c r="F23" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G23" s="2">
-        <v>45551</v>
+        <v>1212</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45553</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1544,22 +1664,37 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>129343062</v>
+        <v>127872524</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>601</v>
-      </c>
-      <c r="F24" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G24" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45553</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1582,22 +1717,37 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>129343261</v>
+        <v>128129075</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
       </c>
       <c r="E25">
-        <v>601</v>
-      </c>
-      <c r="F25" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G25" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45554</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1620,22 +1770,37 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>129343443</v>
+        <v>128766869</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>601</v>
-      </c>
-      <c r="F26" s="2">
-        <v>45553</v>
-      </c>
-      <c r="G26" s="2">
-        <v>45551</v>
+        <v>1211</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45554</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1658,22 +1823,37 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>129344042</v>
+        <v>128913767</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>601</v>
-      </c>
-      <c r="F27" s="2">
+        <v>1211</v>
+      </c>
+      <c r="F27" s="1">
         <v>45551</v>
       </c>
-      <c r="G27" s="2">
-        <v>45551</v>
+      <c r="G27" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K27" t="s">
+        <v>17</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1696,22 +1876,37 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>129344140</v>
+        <v>129170642</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>601</v>
-      </c>
-      <c r="F28" s="2">
+        <v>1211</v>
+      </c>
+      <c r="F28" s="1">
         <v>45551</v>
       </c>
-      <c r="G28" s="2">
-        <v>45551</v>
+      <c r="G28" s="1">
+        <v>45555</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1734,22 +1929,37 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>129344433</v>
+        <v>129039074</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
       </c>
       <c r="E29">
-        <v>601</v>
-      </c>
-      <c r="F29" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G29" s="2">
-        <v>45551</v>
+        <v>2013</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45530</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45531</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8004</v>
+        <v>8021</v>
+      </c>
+      <c r="K29" t="s">
+        <v>17</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1772,22 +1982,37 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>129344514</v>
+        <v>129110148</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>601</v>
-      </c>
-      <c r="F30" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G30" s="2">
-        <v>45551</v>
+        <v>2013</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45533</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45534</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8004</v>
+        <v>8021</v>
+      </c>
+      <c r="K30" t="s">
+        <v>17</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1810,22 +2035,37 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>129344829</v>
+        <v>129374503</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>601</v>
-      </c>
-      <c r="F31" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G31" s="2">
-        <v>45551</v>
+        <v>2013</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45552</v>
+      </c>
+      <c r="G31" s="1">
+        <v>45553</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8004</v>
+        <v>8021</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1848,22 +2088,37 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>129345113</v>
+        <v>129395147</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
       </c>
       <c r="E32">
         <v>601</v>
       </c>
-      <c r="F32" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G32" s="2">
-        <v>45551</v>
+      <c r="F32" s="1">
+        <v>45553</v>
+      </c>
+      <c r="G32" s="1">
+        <v>45554</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8004</v>
+        <v>8013</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1886,22 +2141,37 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>129345326</v>
+        <v>129350803</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
       </c>
       <c r="E33">
         <v>601</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>45551</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="1">
         <v>45551</v>
       </c>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1924,22 +2194,37 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>129345370</v>
+        <v>129068049</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
       </c>
       <c r="E34">
         <v>601</v>
       </c>
-      <c r="F34" s="2">
-        <v>45553</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45551</v>
+      <c r="F34" s="1">
+        <v>45552</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45552</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1962,16 +2247,28 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>129345469</v>
+        <v>129188062</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
       </c>
       <c r="E35">
         <v>601</v>
       </c>
-      <c r="F35" s="2">
-        <v>45551</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45551</v>
+      <c r="F35" s="1">
+        <v>45552</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45552</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1979,6 +2276,9 @@
       <c r="J35">
         <v>8004</v>
       </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
       <c r="L35">
         <v>0</v>
       </c>
@@ -2000,22 +2300,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>129345881</v>
+        <v>125297725</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G36" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2038,22 +2338,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>129346498</v>
+        <v>125407824</v>
       </c>
       <c r="E37">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G37" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2076,22 +2376,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>129347685</v>
+        <v>125459584</v>
       </c>
       <c r="E38">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45551</v>
+        <v>45554</v>
       </c>
       <c r="G38" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2114,22 +2414,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>129348607</v>
+        <v>125471906</v>
       </c>
       <c r="E39">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G39" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2152,22 +2452,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>129348815</v>
+        <v>125756923</v>
       </c>
       <c r="E40">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G40" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2190,22 +2490,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>129348831</v>
+        <v>126101715</v>
       </c>
       <c r="E41">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G41" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2228,22 +2528,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>129348870</v>
+        <v>126136085</v>
       </c>
       <c r="E42">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G42" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2266,16 +2566,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>129349111</v>
+        <v>126165243</v>
       </c>
       <c r="E43">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G43" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I43">
         <v>42</v>
@@ -2304,22 +2604,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>129349361</v>
+        <v>126182975</v>
       </c>
       <c r="E44">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G44" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2342,22 +2642,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>129349517</v>
+        <v>126184573</v>
       </c>
       <c r="E45">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G45" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2380,16 +2680,16 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>129349873</v>
+        <v>126293827</v>
       </c>
       <c r="E46">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G46" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I46">
         <v>42</v>
@@ -2418,22 +2718,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>129349884</v>
+        <v>126302498</v>
       </c>
       <c r="E47">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G47" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2456,22 +2756,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>129350200</v>
+        <v>126322777</v>
       </c>
       <c r="E48">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G48" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2494,22 +2794,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>129350387</v>
+        <v>126406008</v>
       </c>
       <c r="E49">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G49" s="2">
-        <v>45551</v>
+        <v>45556</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2532,22 +2832,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>129350644</v>
+        <v>126480318</v>
       </c>
       <c r="E50">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F50" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G50" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2570,22 +2870,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>129350688</v>
+        <v>126511339</v>
       </c>
       <c r="E51">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G51" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2608,22 +2908,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>129351094</v>
+        <v>126540346</v>
       </c>
       <c r="E52">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G52" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2646,22 +2946,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>129351207</v>
+        <v>126550198</v>
       </c>
       <c r="E53">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G53" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2684,22 +2984,22 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>129351441</v>
+        <v>126588649</v>
       </c>
       <c r="E54">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G54" s="2">
-        <v>45551</v>
+        <v>45556</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2722,22 +3022,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>129351571</v>
+        <v>126608426</v>
       </c>
       <c r="E55">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F55" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G55" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2760,22 +3060,22 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>129351586</v>
+        <v>126734906</v>
       </c>
       <c r="E56">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G56" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2798,22 +3098,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>129351646</v>
+        <v>126859048</v>
       </c>
       <c r="E57">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G57" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2836,22 +3136,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>129351917</v>
+        <v>126984680</v>
       </c>
       <c r="E58">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G58" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2874,22 +3174,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>129352530</v>
+        <v>127000475</v>
       </c>
       <c r="E59">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G59" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2912,22 +3212,22 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129353039</v>
+        <v>127038986</v>
       </c>
       <c r="E60">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F60" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G60" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2950,22 +3250,22 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>129354415</v>
+        <v>127056320</v>
       </c>
       <c r="E61">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F61" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G61" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -2988,22 +3288,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>129354637</v>
+        <v>127058722</v>
       </c>
       <c r="E62">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G62" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -3026,22 +3326,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>129354946</v>
+        <v>127062394</v>
       </c>
       <c r="E63">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="2">
-        <v>45551</v>
+        <v>45556</v>
       </c>
       <c r="G63" s="2">
-        <v>45551</v>
+        <v>45556</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -3064,16 +3364,16 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>129355000</v>
+        <v>127133185</v>
       </c>
       <c r="E64">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="2">
-        <v>45551</v>
+        <v>45553</v>
       </c>
       <c r="G64" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I64">
         <v>42</v>
@@ -3102,22 +3402,22 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>129355492</v>
+        <v>127168672</v>
       </c>
       <c r="E65">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>45551</v>
+        <v>45548</v>
       </c>
       <c r="G65" s="2">
-        <v>45551</v>
+        <v>45556</v>
       </c>
       <c r="I65">
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3140,16 +3440,16 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>129355523</v>
+        <v>127172160</v>
       </c>
       <c r="E66">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>45551</v>
+        <v>45554</v>
       </c>
       <c r="G66" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I66">
         <v>42</v>
@@ -3178,22 +3478,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>129355721</v>
+        <v>127265224</v>
       </c>
       <c r="E67">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G67" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I67">
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -3216,22 +3516,22 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>129356071</v>
+        <v>127328989</v>
       </c>
       <c r="E68">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G68" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I68">
         <v>42</v>
       </c>
       <c r="J68">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -3254,22 +3554,22 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>129356384</v>
+        <v>127347961</v>
       </c>
       <c r="E69">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="G69" s="2">
-        <v>45551</v>
+        <v>45555</v>
       </c>
       <c r="I69">
         <v>42</v>
       </c>
       <c r="J69">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -3292,22 +3592,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>129361139</v>
+        <v>127356658</v>
       </c>
       <c r="E70">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F70" s="2">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="G70" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I70">
         <v>42</v>
       </c>
       <c r="J70">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -3330,22 +3630,22 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>129361596</v>
+        <v>127481900</v>
       </c>
       <c r="E71">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G71" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I71">
         <v>42</v>
       </c>
       <c r="J71">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -3368,16 +3668,16 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>129361798</v>
+        <v>127507752</v>
       </c>
       <c r="E72">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F72" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G72" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I72">
         <v>42</v>
@@ -3406,22 +3706,22 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>129361845</v>
+        <v>127533760</v>
       </c>
       <c r="E73">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G73" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I73">
         <v>42</v>
       </c>
       <c r="J73">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -3444,22 +3744,22 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>129362008</v>
+        <v>127749536</v>
       </c>
       <c r="E74">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G74" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="I74">
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -3482,22 +3782,22 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>129362897</v>
+        <v>127802053</v>
       </c>
       <c r="E75">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F75" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G75" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I75">
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -3520,22 +3820,22 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>129363422</v>
+        <v>127872524</v>
       </c>
       <c r="E76">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="2">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="G76" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I76">
         <v>42</v>
       </c>
       <c r="J76">
-        <v>1118</v>
+        <v>8001</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -3558,16 +3858,16 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>129363439</v>
+        <v>127951819</v>
       </c>
       <c r="E77">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F77" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G77" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I77">
         <v>42</v>
@@ -3596,16 +3896,16 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>129364104</v>
+        <v>128129075</v>
       </c>
       <c r="E78">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F78" s="2">
-        <v>45552</v>
+        <v>45554</v>
       </c>
       <c r="G78" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I78">
         <v>42</v>
@@ -3634,22 +3934,22 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129364654</v>
+        <v>128213408</v>
       </c>
       <c r="E79">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F79" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G79" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I79">
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -3672,16 +3972,16 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>129364944</v>
+        <v>128216510</v>
       </c>
       <c r="E80">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F80" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G80" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I80">
         <v>42</v>
@@ -3710,22 +4010,22 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>129365281</v>
+        <v>128219997</v>
       </c>
       <c r="E81">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F81" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G81" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I81">
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -3748,16 +4048,16 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>129365543</v>
+        <v>128255482</v>
       </c>
       <c r="E82">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F82" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G82" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I82">
         <v>42</v>
@@ -3786,22 +4086,22 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>129365552</v>
+        <v>128367328</v>
       </c>
       <c r="E83">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F83" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G83" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I83">
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -3824,22 +4124,22 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>129366820</v>
+        <v>128464775</v>
       </c>
       <c r="E84">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F84" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G84" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I84">
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -3862,22 +4162,22 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>129367465</v>
+        <v>128513309</v>
       </c>
       <c r="E85">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F85" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G85" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -3900,22 +4200,22 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>129367591</v>
+        <v>128640884</v>
       </c>
       <c r="E86">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F86" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G86" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -3938,16 +4238,16 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>129367736</v>
+        <v>128649738</v>
       </c>
       <c r="E87">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F87" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G87" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I87">
         <v>42</v>
@@ -3976,22 +4276,22 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>129367764</v>
+        <v>128684423</v>
       </c>
       <c r="E88">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F88" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G88" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I88">
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -4014,22 +4314,22 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>129367807</v>
+        <v>128723743</v>
       </c>
       <c r="E89">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F89" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="G89" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="I89">
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -4052,22 +4352,22 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>129368253</v>
+        <v>128766869</v>
       </c>
       <c r="E90">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F90" s="2">
-        <v>45552</v>
+        <v>45554</v>
       </c>
       <c r="G90" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I90">
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -4090,16 +4390,16 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>129368561</v>
+        <v>128818423</v>
       </c>
       <c r="E91">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F91" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G91" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I91">
         <v>42</v>
@@ -4128,22 +4428,22 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>129368782</v>
+        <v>128909333</v>
       </c>
       <c r="E92">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F92" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G92" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I92">
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -4166,22 +4466,22 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>129368790</v>
+        <v>128913767</v>
       </c>
       <c r="E93">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F93" s="2">
-        <v>45552</v>
+        <v>45551</v>
       </c>
       <c r="G93" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I93">
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -4204,22 +4504,22 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>129369213</v>
+        <v>128918106</v>
       </c>
       <c r="E94">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F94" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G94" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I94">
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -4242,22 +4542,22 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129369368</v>
+        <v>129019585</v>
       </c>
       <c r="E95">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F95" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G95" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I95">
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -4280,22 +4580,22 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>129369735</v>
+        <v>129055370</v>
       </c>
       <c r="E96">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F96" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G96" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I96">
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -4318,22 +4618,22 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>129370001</v>
+        <v>129061482</v>
       </c>
       <c r="E97">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F97" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G97" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I97">
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -4356,22 +4656,22 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>129370006</v>
+        <v>129170642</v>
       </c>
       <c r="E98">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F98" s="2">
-        <v>45552</v>
+        <v>45551</v>
       </c>
       <c r="G98" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I98">
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -4394,22 +4694,22 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>129370143</v>
+        <v>129215510</v>
       </c>
       <c r="E99">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F99" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G99" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I99">
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -4432,22 +4732,22 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>129370181</v>
+        <v>129269566</v>
       </c>
       <c r="E100">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F100" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G100" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I100">
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -4470,22 +4770,22 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>129370185</v>
+        <v>129284112</v>
       </c>
       <c r="E101">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F101" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G101" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I101">
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -4508,22 +4808,22 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>129370191</v>
+        <v>129303329</v>
       </c>
       <c r="E102">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F102" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G102" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I102">
         <v>42</v>
       </c>
       <c r="J102">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -4546,22 +4846,22 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>129370195</v>
+        <v>129318126</v>
       </c>
       <c r="E103">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F103" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G103" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I103">
         <v>42</v>
       </c>
       <c r="J103">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -4584,22 +4884,22 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>129370257</v>
+        <v>129342285</v>
       </c>
       <c r="E104">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F104" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G104" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I104">
         <v>42</v>
       </c>
       <c r="J104">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -4622,22 +4922,22 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>129370665</v>
+        <v>129344559</v>
       </c>
       <c r="E105">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F105" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G105" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I105">
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -4660,22 +4960,22 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>129370755</v>
+        <v>129355101</v>
       </c>
       <c r="E106">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F106" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G106" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I106">
         <v>42</v>
       </c>
       <c r="J106">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -4698,22 +4998,22 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>129371285</v>
+        <v>129363687</v>
       </c>
       <c r="E107">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F107" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="G107" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="I107">
         <v>42</v>
       </c>
       <c r="J107">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -4736,22 +5036,22 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>129371354</v>
+        <v>129365244</v>
       </c>
       <c r="E108">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F108" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G108" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I108">
         <v>42</v>
       </c>
       <c r="J108">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -4774,22 +5074,22 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>129371909</v>
+        <v>129371330</v>
       </c>
       <c r="E109">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F109" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G109" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I109">
         <v>42</v>
       </c>
       <c r="J109">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -4812,22 +5112,22 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>129371986</v>
+        <v>129375682</v>
       </c>
       <c r="E110">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F110" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="G110" s="2">
-        <v>45552</v>
+        <v>45556</v>
       </c>
       <c r="I110">
         <v>42</v>
       </c>
       <c r="J110">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -4850,22 +5150,22 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>129371995</v>
+        <v>129379317</v>
       </c>
       <c r="E111">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F111" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G111" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I111">
         <v>42</v>
       </c>
       <c r="J111">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -4888,22 +5188,22 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>129372004</v>
+        <v>129388623</v>
       </c>
       <c r="E112">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F112" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G112" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I112">
         <v>42</v>
       </c>
       <c r="J112">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -4926,22 +5226,22 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>129372015</v>
+        <v>129396933</v>
       </c>
       <c r="E113">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F113" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G113" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I113">
         <v>42</v>
       </c>
       <c r="J113">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -4964,22 +5264,22 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>129372020</v>
+        <v>129406134</v>
       </c>
       <c r="E114">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F114" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G114" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I114">
         <v>42</v>
       </c>
       <c r="J114">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -5002,22 +5302,22 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>129372121</v>
+        <v>129407372</v>
       </c>
       <c r="E115">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F115" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G115" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I115">
         <v>42</v>
       </c>
       <c r="J115">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L115">
         <v>0</v>
@@ -5040,22 +5340,22 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>129372259</v>
+        <v>129421865</v>
       </c>
       <c r="E116">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F116" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="G116" s="2">
-        <v>45552</v>
+        <v>45555</v>
       </c>
       <c r="I116">
         <v>42</v>
       </c>
       <c r="J116">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -5078,22 +5378,22 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>129372464</v>
+        <v>129437999</v>
       </c>
       <c r="E117">
-        <v>601</v>
+        <v>2024</v>
       </c>
       <c r="F117" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G117" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I117">
         <v>42</v>
       </c>
       <c r="J117">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -5116,22 +5416,22 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>129372657</v>
+        <v>129438010</v>
       </c>
       <c r="E118">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F118" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G118" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I118">
         <v>42</v>
       </c>
       <c r="J118">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L118">
         <v>0</v>
@@ -5154,22 +5454,22 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>129372751</v>
+        <v>129438019</v>
       </c>
       <c r="E119">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F119" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G119" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I119">
         <v>42</v>
       </c>
       <c r="J119">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -5192,22 +5492,22 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>129373471</v>
+        <v>129438021</v>
       </c>
       <c r="E120">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F120" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G120" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I120">
         <v>42</v>
       </c>
       <c r="J120">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L120">
         <v>0</v>
@@ -5230,22 +5530,22 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>129373562</v>
+        <v>129438057</v>
       </c>
       <c r="E121">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F121" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G121" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I121">
         <v>42</v>
       </c>
       <c r="J121">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L121">
         <v>0</v>
@@ -5268,22 +5568,22 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>129374514</v>
+        <v>129438100</v>
       </c>
       <c r="E122">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F122" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G122" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I122">
         <v>42</v>
       </c>
       <c r="J122">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -5306,22 +5606,22 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>129375259</v>
+        <v>129438124</v>
       </c>
       <c r="E123">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F123" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G123" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I123">
         <v>42</v>
       </c>
       <c r="J123">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -5344,22 +5644,22 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>129375445</v>
+        <v>129438155</v>
       </c>
       <c r="E124">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F124" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G124" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I124">
         <v>42</v>
       </c>
       <c r="J124">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L124">
         <v>0</v>
@@ -5382,22 +5682,22 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>129375647</v>
+        <v>129438157</v>
       </c>
       <c r="E125">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F125" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G125" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I125">
         <v>42</v>
       </c>
       <c r="J125">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -5420,22 +5720,22 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>129375874</v>
+        <v>129438161</v>
       </c>
       <c r="E126">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F126" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G126" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I126">
         <v>42</v>
       </c>
       <c r="J126">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -5458,22 +5758,22 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>129376006</v>
+        <v>129438184</v>
       </c>
       <c r="E127">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F127" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="G127" s="2">
-        <v>45552</v>
+        <v>45557</v>
       </c>
       <c r="I127">
         <v>42</v>
       </c>
       <c r="J127">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L127">
         <v>0</v>
@@ -5496,22 +5796,22 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>129378827</v>
+        <v>129438190</v>
       </c>
       <c r="E128">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F128" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G128" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I128">
         <v>42</v>
       </c>
       <c r="J128">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L128">
         <v>0</v>
@@ -5534,22 +5834,22 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>129378841</v>
+        <v>129438199</v>
       </c>
       <c r="E129">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F129" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G129" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I129">
         <v>42</v>
       </c>
       <c r="J129">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -5572,22 +5872,22 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>129379155</v>
+        <v>129438208</v>
       </c>
       <c r="E130">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F130" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G130" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I130">
         <v>42</v>
       </c>
       <c r="J130">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -5610,22 +5910,22 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>129379284</v>
+        <v>129438209</v>
       </c>
       <c r="E131">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F131" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G131" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I131">
         <v>42</v>
       </c>
       <c r="J131">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -5648,22 +5948,22 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>129379591</v>
+        <v>129438217</v>
       </c>
       <c r="E132">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F132" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G132" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I132">
         <v>42</v>
       </c>
       <c r="J132">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L132">
         <v>0</v>
@@ -5686,16 +5986,16 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>129380018</v>
+        <v>129438257</v>
       </c>
       <c r="E133">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F133" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G133" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I133">
         <v>42</v>
@@ -5724,22 +6024,22 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>129380336</v>
+        <v>129438267</v>
       </c>
       <c r="E134">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F134" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G134" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I134">
         <v>42</v>
       </c>
       <c r="J134">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -5762,22 +6062,22 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>129380387</v>
+        <v>129438288</v>
       </c>
       <c r="E135">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F135" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G135" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I135">
         <v>42</v>
       </c>
       <c r="J135">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L135">
         <v>0</v>
@@ -5800,22 +6100,22 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>129380458</v>
+        <v>129438402</v>
       </c>
       <c r="E136">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F136" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G136" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I136">
         <v>42</v>
       </c>
       <c r="J136">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L136">
         <v>0</v>
@@ -5838,22 +6138,22 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>129380684</v>
+        <v>129438424</v>
       </c>
       <c r="E137">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F137" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G137" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I137">
         <v>42</v>
       </c>
       <c r="J137">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -5876,22 +6176,22 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>129381455</v>
+        <v>129438432</v>
       </c>
       <c r="E138">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F138" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G138" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I138">
         <v>42</v>
       </c>
       <c r="J138">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -5914,22 +6214,22 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>129381674</v>
+        <v>129438456</v>
       </c>
       <c r="E139">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F139" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G139" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I139">
         <v>42</v>
       </c>
       <c r="J139">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L139">
         <v>0</v>
@@ -5952,22 +6252,22 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>129381827</v>
+        <v>129438464</v>
       </c>
       <c r="E140">
-        <v>601</v>
+        <v>2024</v>
       </c>
       <c r="F140" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G140" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I140">
         <v>42</v>
       </c>
       <c r="J140">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L140">
         <v>0</v>
@@ -5990,22 +6290,22 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>129383007</v>
+        <v>129438515</v>
       </c>
       <c r="E141">
-        <v>601</v>
+        <v>2002</v>
       </c>
       <c r="F141" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G141" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I141">
         <v>42</v>
       </c>
       <c r="J141">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L141">
         <v>0</v>
@@ -6028,22 +6328,22 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>129383690</v>
+        <v>129438563</v>
       </c>
       <c r="E142">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F142" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G142" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I142">
         <v>42</v>
       </c>
       <c r="J142">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L142">
         <v>0</v>
@@ -6066,22 +6366,22 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>129383884</v>
+        <v>129438575</v>
       </c>
       <c r="E143">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F143" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G143" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I143">
         <v>42</v>
       </c>
       <c r="J143">
-        <v>1118</v>
+        <v>8001</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -6104,22 +6404,22 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>129384559</v>
+        <v>129438599</v>
       </c>
       <c r="E144">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F144" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G144" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I144">
         <v>42</v>
       </c>
       <c r="J144">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L144">
         <v>0</v>
@@ -6142,22 +6442,22 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>129385011</v>
+        <v>129438619</v>
       </c>
       <c r="E145">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F145" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G145" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I145">
         <v>42</v>
       </c>
       <c r="J145">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -6180,22 +6480,22 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>129385116</v>
+        <v>129438638</v>
       </c>
       <c r="E146">
-        <v>601</v>
+        <v>2002</v>
       </c>
       <c r="F146" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G146" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I146">
         <v>42</v>
       </c>
       <c r="J146">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L146">
         <v>0</v>
@@ -6218,22 +6518,22 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>129385282</v>
+        <v>129438675</v>
       </c>
       <c r="E147">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F147" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G147" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I147">
         <v>42</v>
       </c>
       <c r="J147">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L147">
         <v>0</v>
@@ -6256,22 +6556,22 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>129385320</v>
+        <v>129438698</v>
       </c>
       <c r="E148">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F148" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G148" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I148">
         <v>42</v>
       </c>
       <c r="J148">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L148">
         <v>0</v>
@@ -6294,22 +6594,22 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>129385729</v>
+        <v>129438712</v>
       </c>
       <c r="E149">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F149" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G149" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I149">
         <v>42</v>
       </c>
       <c r="J149">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -6332,22 +6632,22 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>129385911</v>
+        <v>129438780</v>
       </c>
       <c r="E150">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F150" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G150" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I150">
         <v>42</v>
       </c>
       <c r="J150">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -6370,22 +6670,22 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>129386015</v>
+        <v>129438787</v>
       </c>
       <c r="E151">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F151" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G151" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I151">
         <v>42</v>
       </c>
       <c r="J151">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L151">
         <v>0</v>
@@ -6408,22 +6708,22 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>129386155</v>
+        <v>129438807</v>
       </c>
       <c r="E152">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F152" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G152" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I152">
         <v>42</v>
       </c>
       <c r="J152">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -6446,22 +6746,22 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>129386244</v>
+        <v>129438808</v>
       </c>
       <c r="E153">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F153" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G153" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I153">
         <v>42</v>
       </c>
       <c r="J153">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -6484,22 +6784,22 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>129386640</v>
+        <v>129438811</v>
       </c>
       <c r="E154">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F154" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G154" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I154">
         <v>42</v>
       </c>
       <c r="J154">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -6522,22 +6822,22 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>129386660</v>
+        <v>129438812</v>
       </c>
       <c r="E155">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F155" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G155" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I155">
         <v>42</v>
       </c>
       <c r="J155">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -6560,22 +6860,22 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>129387345</v>
+        <v>129438841</v>
       </c>
       <c r="E156">
-        <v>601</v>
+        <v>2002</v>
       </c>
       <c r="F156" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G156" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I156">
         <v>42</v>
       </c>
       <c r="J156">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -6598,22 +6898,22 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>129388101</v>
+        <v>129438859</v>
       </c>
       <c r="E157">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F157" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G157" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I157">
         <v>42</v>
       </c>
       <c r="J157">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -6636,22 +6936,22 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>129388505</v>
+        <v>129438870</v>
       </c>
       <c r="E158">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F158" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G158" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I158">
         <v>42</v>
       </c>
       <c r="J158">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -6674,22 +6974,22 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>129388921</v>
+        <v>129438921</v>
       </c>
       <c r="E159">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F159" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G159" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I159">
         <v>42</v>
       </c>
       <c r="J159">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L159">
         <v>0</v>
@@ -6712,22 +7012,22 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>129389289</v>
+        <v>129438949</v>
       </c>
       <c r="E160">
-        <v>601</v>
+        <v>2002</v>
       </c>
       <c r="F160" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G160" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I160">
         <v>42</v>
       </c>
       <c r="J160">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -6750,22 +7050,22 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>129389311</v>
+        <v>129438976</v>
       </c>
       <c r="E161">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F161" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G161" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I161">
         <v>42</v>
       </c>
       <c r="J161">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -6788,16 +7088,16 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>129390706</v>
+        <v>129438999</v>
       </c>
       <c r="E162">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F162" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G162" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I162">
         <v>42</v>
@@ -6826,16 +7126,16 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>129391305</v>
+        <v>129439001</v>
       </c>
       <c r="E163">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F163" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G163" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I163">
         <v>42</v>
@@ -6864,16 +7164,16 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>129392364</v>
+        <v>129439003</v>
       </c>
       <c r="E164">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F164" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G164" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I164">
         <v>42</v>
@@ -6902,22 +7202,22 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>129393945</v>
+        <v>129439012</v>
       </c>
       <c r="E165">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F165" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G165" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I165">
         <v>42</v>
       </c>
       <c r="J165">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -6940,22 +7240,22 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>129394068</v>
+        <v>129439013</v>
       </c>
       <c r="E166">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F166" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G166" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I166">
         <v>42</v>
       </c>
       <c r="J166">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -6978,22 +7278,22 @@
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>129394519</v>
+        <v>129439085</v>
       </c>
       <c r="E167">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F167" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G167" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I167">
         <v>42</v>
       </c>
       <c r="J167">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -7016,22 +7316,22 @@
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>129394586</v>
+        <v>129439138</v>
       </c>
       <c r="E168">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F168" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="G168" s="2">
-        <v>45553</v>
+        <v>45557</v>
       </c>
       <c r="I168">
         <v>42</v>
       </c>
       <c r="J168">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -7054,22 +7354,22 @@
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>129140021</v>
+        <v>129439151</v>
       </c>
       <c r="E169">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F169" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G169" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I169">
         <v>42</v>
       </c>
       <c r="J169">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -7092,22 +7392,22 @@
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>129140105</v>
+        <v>129439159</v>
       </c>
       <c r="E170">
-        <v>609</v>
+        <v>2013</v>
       </c>
       <c r="F170" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G170" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I170">
         <v>42</v>
       </c>
       <c r="J170">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -7130,22 +7430,22 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>129140127</v>
+        <v>129439172</v>
       </c>
       <c r="E171">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F171" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G171" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I171">
         <v>42</v>
       </c>
       <c r="J171">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L171">
         <v>0</v>
@@ -7168,22 +7468,22 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>129140180</v>
+        <v>129439186</v>
       </c>
       <c r="E172">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F172" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G172" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I172">
         <v>42</v>
       </c>
       <c r="J172">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L172">
         <v>0</v>
@@ -7206,22 +7506,22 @@
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>129140188</v>
+        <v>129439223</v>
       </c>
       <c r="E173">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F173" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G173" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I173">
         <v>42</v>
       </c>
       <c r="J173">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L173">
         <v>0</v>
@@ -7244,22 +7544,22 @@
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>129140213</v>
+        <v>129439227</v>
       </c>
       <c r="E174">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F174" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G174" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I174">
         <v>42</v>
       </c>
       <c r="J174">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L174">
         <v>0</v>
@@ -7282,22 +7582,22 @@
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>129140243</v>
+        <v>129439232</v>
       </c>
       <c r="E175">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F175" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G175" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I175">
         <v>42</v>
       </c>
       <c r="J175">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L175">
         <v>0</v>
@@ -7320,22 +7620,22 @@
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>129140285</v>
+        <v>129439243</v>
       </c>
       <c r="E176">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F176" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G176" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I176">
         <v>42</v>
       </c>
       <c r="J176">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L176">
         <v>0</v>
@@ -7358,22 +7658,22 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>129140308</v>
+        <v>129439251</v>
       </c>
       <c r="E177">
-        <v>609</v>
+        <v>2013</v>
       </c>
       <c r="F177" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G177" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I177">
         <v>42</v>
       </c>
       <c r="J177">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L177">
         <v>0</v>
@@ -7396,22 +7696,22 @@
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>129140317</v>
+        <v>129439260</v>
       </c>
       <c r="E178">
-        <v>609</v>
+        <v>2013</v>
       </c>
       <c r="F178" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G178" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I178">
         <v>42</v>
       </c>
       <c r="J178">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L178">
         <v>0</v>
@@ -7434,22 +7734,22 @@
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>129140326</v>
+        <v>129439309</v>
       </c>
       <c r="E179">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F179" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="G179" s="2">
-        <v>45536</v>
+        <v>45557</v>
       </c>
       <c r="I179">
         <v>42</v>
       </c>
       <c r="J179">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -7472,22 +7772,22 @@
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>129336737</v>
+        <v>129439314</v>
       </c>
       <c r="E180">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F180" s="2">
-        <v>45548</v>
+        <v>45557</v>
       </c>
       <c r="G180" s="2">
-        <v>45548</v>
+        <v>45557</v>
       </c>
       <c r="I180">
         <v>42</v>
       </c>
       <c r="J180">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L180">
         <v>0</v>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">Fiel!$A$1:$Q$100</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$Q$154</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
@@ -439,112 +439,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q138"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="17" width="13" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
+      <c r="A1" t="str">
+        <v>NR_PROPOSTA</v>
+      </c>
+      <c r="B1" t="str">
+        <v>CPF_CNPJ</v>
+      </c>
+      <c r="C1" t="str">
+        <v>NOME_SEGURADO</v>
+      </c>
+      <c r="D1" t="str">
+        <v>PREMIO_TOTAL</v>
+      </c>
+      <c r="E1" t="str">
+        <v>RAMO</v>
+      </c>
+      <c r="F1" t="str">
+        <v>DT_PROPOSTA</v>
+      </c>
+      <c r="G1" t="str">
+        <v>DT_ULTIMA_ALTERACAO</v>
+      </c>
+      <c r="H1" t="str">
+        <v>COD_FILIAL</v>
+      </c>
+      <c r="I1" t="str">
+        <v>COD_CORRETOR</v>
+      </c>
+      <c r="J1" t="str">
+        <v>BLOQUEIO_1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>NIVEL_BLOQUEIO_1</v>
+      </c>
+      <c r="L1" t="str">
+        <v>BLOQUEIO_2</v>
+      </c>
+      <c r="M1" t="str">
+        <v>NIVEL_BLOQUEIO_2</v>
+      </c>
+      <c r="N1" t="str">
+        <v>BLOQUEIO_3</v>
+      </c>
+      <c r="O1" t="str">
+        <v>NIVEL_BLOQUEIO_3</v>
+      </c>
+      <c r="P1" t="str">
+        <v>BLOQUEIO_4</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>NR_OPERATIVA</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131417080</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
+        <v>131435385</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2">
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G2" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8004</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
+        <v>1118</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
       </c>
       <c r="L2">
         <v>0</v>
@@ -567,28 +570,28 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131417101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
+        <v>131435542</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3">
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G3" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3">
         <v>42</v>
@@ -596,8 +599,8 @@
       <c r="J3">
         <v>8004</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
+      <c r="K3" t="str">
+        <v/>
       </c>
       <c r="L3">
         <v>0</v>
@@ -620,28 +623,28 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131417539</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
+        <v>131436632</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4">
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G4" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4">
         <v>42</v>
@@ -649,8 +652,8 @@
       <c r="J4">
         <v>8004</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
+      <c r="K4" t="str">
+        <v/>
       </c>
       <c r="L4">
         <v>0</v>
@@ -673,28 +676,28 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131417640</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
+        <v>131440162</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5">
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G5" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5">
         <v>42</v>
@@ -702,8 +705,8 @@
       <c r="J5">
         <v>8004</v>
       </c>
-      <c r="K5" t="s">
-        <v>22</v>
+      <c r="K5" t="str">
+        <v/>
       </c>
       <c r="L5">
         <v>0</v>
@@ -726,37 +729,37 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131418601</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
+        <v>131442746</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6">
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G6" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8004</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
+        <v>8013</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
       </c>
       <c r="L6">
         <v>0</v>
@@ -779,28 +782,28 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131418902</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
+        <v>131444199</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7">
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G7" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7">
         <v>42</v>
@@ -808,8 +811,8 @@
       <c r="J7">
         <v>8013</v>
       </c>
-      <c r="K7" t="s">
-        <v>22</v>
+      <c r="K7" t="str">
+        <v/>
       </c>
       <c r="L7">
         <v>0</v>
@@ -832,37 +835,37 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131418913</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
+        <v>131447868</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8">
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G8" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8013</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
+        <v>1117</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
       </c>
       <c r="L8">
         <v>0</v>
@@ -885,37 +888,37 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131418917</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
+        <v>131448089</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
       </c>
       <c r="E9">
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G9" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8013</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
+        <v>1117</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
       </c>
       <c r="L9">
         <v>0</v>
@@ -938,37 +941,37 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131418923</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
+        <v>131450940</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
       </c>
       <c r="E10">
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G10" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8013</v>
-      </c>
-      <c r="K10" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
       </c>
       <c r="L10">
         <v>0</v>
@@ -991,37 +994,37 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131418929</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
+        <v>131453711</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
       </c>
       <c r="E11">
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G11" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H11" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8013</v>
-      </c>
-      <c r="K11" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1044,37 +1047,37 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131418939</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
+        <v>131454162</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12">
         <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G12" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H12" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8013</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1097,37 +1100,37 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131419070</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>22</v>
+        <v>131454524</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13">
         <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G13" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8013</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1150,37 +1153,37 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131419084</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>22</v>
+        <v>131455232</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
       </c>
       <c r="E14">
         <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G14" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H14" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
       </c>
       <c r="I14">
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8013</v>
-      </c>
-      <c r="K14" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1203,28 +1206,28 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131419415</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
+        <v>131456957</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
       </c>
       <c r="E15">
         <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G15" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1232,8 +1235,8 @@
       <c r="J15">
         <v>8013</v>
       </c>
-      <c r="K15" t="s">
-        <v>22</v>
+      <c r="K15" t="str">
+        <v/>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1256,37 +1259,37 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131419520</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
+        <v>131457106</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16">
         <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G16" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
       <c r="I16">
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8004</v>
-      </c>
-      <c r="K16" t="s">
-        <v>22</v>
+        <v>8013</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1309,28 +1312,28 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131420770</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
+        <v>131464304</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
       </c>
       <c r="E17">
         <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G17" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H17" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1338,8 +1341,8 @@
       <c r="J17">
         <v>8004</v>
       </c>
-      <c r="K17" t="s">
-        <v>22</v>
+      <c r="K17" t="str">
+        <v/>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1362,28 +1365,28 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131420956</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
+        <v>131468830</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
       </c>
       <c r="E18">
         <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G18" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1391,8 +1394,8 @@
       <c r="J18">
         <v>8013</v>
       </c>
-      <c r="K18" t="s">
-        <v>22</v>
+      <c r="K18" t="str">
+        <v/>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1415,28 +1418,28 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131420962</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
+        <v>131469320</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
       </c>
       <c r="E19">
         <v>601</v>
       </c>
       <c r="F19" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G19" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H19" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1444,8 +1447,8 @@
       <c r="J19">
         <v>8013</v>
       </c>
-      <c r="K19" t="s">
-        <v>22</v>
+      <c r="K19" t="str">
+        <v/>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1468,28 +1471,28 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131420971</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
+        <v>131469764</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
       </c>
       <c r="E20">
         <v>601</v>
       </c>
       <c r="F20" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G20" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H20" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1497,8 +1500,8 @@
       <c r="J20">
         <v>8013</v>
       </c>
-      <c r="K20" t="s">
-        <v>22</v>
+      <c r="K20" t="str">
+        <v/>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1521,28 +1524,28 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131421011</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>22</v>
+        <v>131473689</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21">
         <v>601</v>
       </c>
       <c r="F21" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G21" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H21" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1550,8 +1553,8 @@
       <c r="J21">
         <v>8004</v>
       </c>
-      <c r="K21" t="s">
-        <v>22</v>
+      <c r="K21" t="str">
+        <v/>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1574,37 +1577,37 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131422117</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>22</v>
+        <v>131475306</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
       </c>
       <c r="E22">
         <v>601</v>
       </c>
       <c r="F22" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G22" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H22" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8004</v>
-      </c>
-      <c r="K22" t="s">
-        <v>22</v>
+        <v>8013</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1627,37 +1630,37 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131422176</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="s">
-        <v>22</v>
+        <v>131475310</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
       </c>
       <c r="E23">
         <v>601</v>
       </c>
       <c r="F23" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G23" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H23" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8004</v>
-      </c>
-      <c r="K23" t="s">
-        <v>22</v>
+        <v>8013</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1680,37 +1683,37 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>131422738</v>
-      </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>22</v>
+        <v>131476268</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
       </c>
       <c r="E24">
         <v>601</v>
       </c>
       <c r="F24" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G24" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H24" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8013</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1733,28 +1736,28 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131424376</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>22</v>
+        <v>131476834</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
       </c>
       <c r="E25">
         <v>601</v>
       </c>
       <c r="F25" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G25" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H25" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1762,8 +1765,8 @@
       <c r="J25">
         <v>8004</v>
       </c>
-      <c r="K25" t="s">
-        <v>22</v>
+      <c r="K25" t="str">
+        <v/>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1786,37 +1789,37 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>131424498</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" t="s">
-        <v>22</v>
+        <v>131476903</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
       </c>
       <c r="E26">
         <v>601</v>
       </c>
       <c r="F26" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G26" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H26" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8013</v>
-      </c>
-      <c r="K26" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1839,37 +1842,37 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>131424785</v>
-      </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>22</v>
+        <v>131477305</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
       </c>
       <c r="E27">
         <v>601</v>
       </c>
       <c r="F27" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G27" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H27" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8013</v>
-      </c>
-      <c r="K27" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1892,37 +1895,37 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131424788</v>
-      </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
+        <v>131477944</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
       </c>
       <c r="E28">
         <v>601</v>
       </c>
       <c r="F28" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G28" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H28" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8013</v>
-      </c>
-      <c r="K28" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1945,37 +1948,37 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>131424790</v>
-      </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>22</v>
+        <v>131477953</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
       </c>
       <c r="E29">
         <v>601</v>
       </c>
       <c r="F29" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G29" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H29" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8013</v>
-      </c>
-      <c r="K29" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1998,28 +2001,28 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>131424851</v>
-      </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" t="s">
-        <v>22</v>
+        <v>131480394</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
       </c>
       <c r="E30">
         <v>601</v>
       </c>
       <c r="F30" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G30" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H30" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
       <c r="I30">
         <v>42</v>
@@ -2027,8 +2030,8 @@
       <c r="J30">
         <v>8004</v>
       </c>
-      <c r="K30" t="s">
-        <v>22</v>
+      <c r="K30" t="str">
+        <v/>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2051,28 +2054,28 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>131425592</v>
-      </c>
-      <c r="B31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" t="s">
-        <v>22</v>
+        <v>131480416</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
       </c>
       <c r="E31">
         <v>601</v>
       </c>
       <c r="F31" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G31" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H31" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
       </c>
       <c r="I31">
         <v>42</v>
@@ -2080,8 +2083,8 @@
       <c r="J31">
         <v>8004</v>
       </c>
-      <c r="K31" t="s">
-        <v>22</v>
+      <c r="K31" t="str">
+        <v/>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2104,37 +2107,37 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>131425679</v>
-      </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" t="s">
-        <v>22</v>
+        <v>131480913</v>
+      </c>
+      <c r="B32" t="str">
+        <v/>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
       </c>
       <c r="E32">
         <v>601</v>
       </c>
       <c r="F32" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G32" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H32" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8013</v>
-      </c>
-      <c r="K32" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2157,28 +2160,28 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>131425868</v>
-      </c>
-      <c r="B33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" t="s">
-        <v>22</v>
+        <v>131482418</v>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
       </c>
       <c r="E33">
         <v>601</v>
       </c>
       <c r="F33" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G33" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H33" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
       </c>
       <c r="I33">
         <v>42</v>
@@ -2186,8 +2189,8 @@
       <c r="J33">
         <v>8004</v>
       </c>
-      <c r="K33" t="s">
-        <v>22</v>
+      <c r="K33" t="str">
+        <v/>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2210,28 +2213,28 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>131426170</v>
-      </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" t="s">
-        <v>22</v>
+        <v>131483262</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
       </c>
       <c r="E34">
         <v>601</v>
       </c>
       <c r="F34" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G34" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H34" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
       </c>
       <c r="I34">
         <v>42</v>
@@ -2239,8 +2242,8 @@
       <c r="J34">
         <v>8004</v>
       </c>
-      <c r="K34" t="s">
-        <v>22</v>
+      <c r="K34" t="str">
+        <v/>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2263,28 +2266,28 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>131426247</v>
-      </c>
-      <c r="B35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
-        <v>22</v>
+        <v>131483654</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35">
         <v>601</v>
       </c>
       <c r="F35" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G35" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H35" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
       </c>
       <c r="I35">
         <v>42</v>
@@ -2292,8 +2295,8 @@
       <c r="J35">
         <v>8004</v>
       </c>
-      <c r="K35" t="s">
-        <v>22</v>
+      <c r="K35" t="str">
+        <v/>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2316,37 +2319,37 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>131426326</v>
-      </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" t="s">
-        <v>22</v>
+        <v>131483666</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="E36">
         <v>601</v>
       </c>
       <c r="F36" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G36" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H36" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8013</v>
-      </c>
-      <c r="K36" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K36" t="str">
+        <v/>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2369,37 +2372,37 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>131426511</v>
-      </c>
-      <c r="B37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" t="s">
-        <v>22</v>
+        <v>131483911</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
       </c>
       <c r="E37">
         <v>601</v>
       </c>
       <c r="F37" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G37" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H37" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8013</v>
-      </c>
-      <c r="K37" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2422,37 +2425,37 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>131427053</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" t="s">
-        <v>22</v>
+        <v>131484274</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
       </c>
       <c r="E38">
         <v>601</v>
       </c>
       <c r="F38" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G38" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8013</v>
-      </c>
-      <c r="K38" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K38" t="str">
+        <v/>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2475,37 +2478,37 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>131427450</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" t="s">
-        <v>22</v>
+        <v>131484426</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
       </c>
       <c r="E39">
         <v>601</v>
       </c>
       <c r="F39" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G39" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H39" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8013</v>
-      </c>
-      <c r="K39" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2528,37 +2531,37 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>131427500</v>
-      </c>
-      <c r="B40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" t="s">
-        <v>22</v>
+        <v>131484462</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
       </c>
       <c r="E40">
         <v>601</v>
       </c>
       <c r="F40" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G40" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H40" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8013</v>
-      </c>
-      <c r="K40" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K40" t="str">
+        <v/>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2581,37 +2584,37 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>131429415</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" t="s">
-        <v>22</v>
+        <v>131485935</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
       </c>
       <c r="E41">
         <v>601</v>
       </c>
       <c r="F41" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G41" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H41" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8013</v>
-      </c>
-      <c r="K41" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2634,28 +2637,28 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>131429591</v>
-      </c>
-      <c r="B42" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" t="s">
-        <v>22</v>
+        <v>131486296</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
       </c>
       <c r="E42">
         <v>601</v>
       </c>
       <c r="F42" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G42" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H42" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
       </c>
       <c r="I42">
         <v>42</v>
@@ -2663,8 +2666,8 @@
       <c r="J42">
         <v>8004</v>
       </c>
-      <c r="K42" t="s">
-        <v>22</v>
+      <c r="K42" t="str">
+        <v/>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2687,28 +2690,28 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>131429703</v>
-      </c>
-      <c r="B43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" t="s">
-        <v>22</v>
+        <v>131486455</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43">
         <v>601</v>
       </c>
       <c r="F43" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G43" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H43" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
       </c>
       <c r="I43">
         <v>42</v>
@@ -2716,8 +2719,8 @@
       <c r="J43">
         <v>8004</v>
       </c>
-      <c r="K43" t="s">
-        <v>22</v>
+      <c r="K43" t="str">
+        <v/>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2740,28 +2743,28 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>131431258</v>
-      </c>
-      <c r="B44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" t="s">
-        <v>22</v>
+        <v>131486549</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
       </c>
       <c r="E44">
         <v>601</v>
       </c>
       <c r="F44" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G44" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H44" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
       </c>
       <c r="I44">
         <v>42</v>
@@ -2769,8 +2772,8 @@
       <c r="J44">
         <v>8004</v>
       </c>
-      <c r="K44" t="s">
-        <v>22</v>
+      <c r="K44" t="str">
+        <v/>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2793,28 +2796,28 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>131431380</v>
-      </c>
-      <c r="B45" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" t="s">
-        <v>22</v>
+        <v>131486760</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
       </c>
       <c r="E45">
         <v>601</v>
       </c>
       <c r="F45" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G45" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H45" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
       </c>
       <c r="I45">
         <v>42</v>
@@ -2822,8 +2825,8 @@
       <c r="J45">
         <v>8004</v>
       </c>
-      <c r="K45" t="s">
-        <v>22</v>
+      <c r="K45" t="str">
+        <v/>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2846,28 +2849,28 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>131431656</v>
-      </c>
-      <c r="B46" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="s">
-        <v>22</v>
+        <v>131487891</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
       </c>
       <c r="E46">
         <v>601</v>
       </c>
       <c r="F46" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G46" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H46" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
       </c>
       <c r="I46">
         <v>42</v>
@@ -2875,8 +2878,8 @@
       <c r="J46">
         <v>8004</v>
       </c>
-      <c r="K46" t="s">
-        <v>22</v>
+      <c r="K46" t="str">
+        <v/>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2899,37 +2902,37 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>131431772</v>
-      </c>
-      <c r="B47" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" t="s">
-        <v>22</v>
+        <v>131488340</v>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
       </c>
       <c r="E47">
         <v>601</v>
       </c>
       <c r="F47" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G47" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H47" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8013</v>
-      </c>
-      <c r="K47" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K47" t="str">
+        <v/>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2952,28 +2955,28 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>131431903</v>
-      </c>
-      <c r="B48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" t="s">
-        <v>22</v>
+        <v>131488610</v>
+      </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
       </c>
       <c r="E48">
         <v>601</v>
       </c>
       <c r="F48" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G48" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H48" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
       </c>
       <c r="I48">
         <v>42</v>
@@ -2981,8 +2984,8 @@
       <c r="J48">
         <v>8004</v>
       </c>
-      <c r="K48" t="s">
-        <v>22</v>
+      <c r="K48" t="str">
+        <v/>
       </c>
       <c r="L48">
         <v>0</v>
@@ -3005,28 +3008,28 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>131434702</v>
-      </c>
-      <c r="B49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" t="s">
-        <v>22</v>
+        <v>131488681</v>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
       </c>
       <c r="E49">
         <v>601</v>
       </c>
       <c r="F49" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G49" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
       </c>
       <c r="I49">
         <v>42</v>
@@ -3034,8 +3037,8 @@
       <c r="J49">
         <v>8004</v>
       </c>
-      <c r="K49" t="s">
-        <v>22</v>
+      <c r="K49" t="str">
+        <v/>
       </c>
       <c r="L49">
         <v>0</v>
@@ -3058,28 +3061,28 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>131434853</v>
-      </c>
-      <c r="B50" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" t="s">
-        <v>22</v>
+        <v>131488990</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
       </c>
       <c r="E50">
         <v>601</v>
       </c>
       <c r="F50" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G50" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H50" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
       </c>
       <c r="I50">
         <v>42</v>
@@ -3087,8 +3090,8 @@
       <c r="J50">
         <v>8004</v>
       </c>
-      <c r="K50" t="s">
-        <v>22</v>
+      <c r="K50" t="str">
+        <v/>
       </c>
       <c r="L50">
         <v>0</v>
@@ -3111,28 +3114,28 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>131434968</v>
-      </c>
-      <c r="B51" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" t="s">
-        <v>22</v>
+        <v>131489061</v>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
       </c>
       <c r="E51">
         <v>601</v>
       </c>
       <c r="F51" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G51" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H51" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
       </c>
       <c r="I51">
         <v>42</v>
@@ -3140,8 +3143,8 @@
       <c r="J51">
         <v>8004</v>
       </c>
-      <c r="K51" t="s">
-        <v>22</v>
+      <c r="K51" t="str">
+        <v/>
       </c>
       <c r="L51">
         <v>0</v>
@@ -3164,28 +3167,28 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>131434999</v>
-      </c>
-      <c r="B52" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" t="s">
-        <v>22</v>
+        <v>131489266</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
       </c>
       <c r="E52">
         <v>601</v>
       </c>
       <c r="F52" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G52" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H52" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
       </c>
       <c r="I52">
         <v>42</v>
@@ -3193,8 +3196,8 @@
       <c r="J52">
         <v>8004</v>
       </c>
-      <c r="K52" t="s">
-        <v>22</v>
+      <c r="K52" t="str">
+        <v/>
       </c>
       <c r="L52">
         <v>0</v>
@@ -3217,28 +3220,28 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>131435018</v>
-      </c>
-      <c r="B53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" t="s">
-        <v>22</v>
+        <v>131489693</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
       </c>
       <c r="E53">
         <v>601</v>
       </c>
       <c r="F53" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G53" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H53" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
       </c>
       <c r="I53">
         <v>42</v>
@@ -3246,8 +3249,8 @@
       <c r="J53">
         <v>8004</v>
       </c>
-      <c r="K53" t="s">
-        <v>22</v>
+      <c r="K53" t="str">
+        <v/>
       </c>
       <c r="L53">
         <v>0</v>
@@ -3270,28 +3273,28 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>131417292</v>
-      </c>
-      <c r="B54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" t="s">
-        <v>22</v>
+        <v>131489755</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
       </c>
       <c r="E54">
         <v>601</v>
       </c>
       <c r="F54" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G54" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H54" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
       </c>
       <c r="I54">
         <v>42</v>
@@ -3299,8 +3302,8 @@
       <c r="J54">
         <v>8004</v>
       </c>
-      <c r="K54" t="s">
-        <v>22</v>
+      <c r="K54" t="str">
+        <v/>
       </c>
       <c r="L54">
         <v>0</v>
@@ -3323,28 +3326,28 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>131417816</v>
-      </c>
-      <c r="B55" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" t="s">
-        <v>22</v>
+        <v>131490933</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
       </c>
       <c r="E55">
         <v>601</v>
       </c>
       <c r="F55" s="1">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G55" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H55" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
       </c>
       <c r="I55">
         <v>42</v>
@@ -3352,8 +3355,8 @@
       <c r="J55">
         <v>8004</v>
       </c>
-      <c r="K55" t="s">
-        <v>22</v>
+      <c r="K55" t="str">
+        <v/>
       </c>
       <c r="L55">
         <v>0</v>
@@ -3376,37 +3379,37 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>131418296</v>
-      </c>
-      <c r="B56" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" t="s">
-        <v>22</v>
+        <v>131437235</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
       </c>
       <c r="E56">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F56" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G56" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H56" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8004</v>
-      </c>
-      <c r="K56" t="s">
-        <v>22</v>
+        <v>8013</v>
+      </c>
+      <c r="K56" t="str">
+        <v/>
       </c>
       <c r="L56">
         <v>0</v>
@@ -3429,28 +3432,28 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>131419440</v>
-      </c>
-      <c r="B57" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" t="s">
-        <v>22</v>
+        <v>131463605</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
       </c>
       <c r="E57">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F57" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G57" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H57" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
       </c>
       <c r="I57">
         <v>42</v>
@@ -3458,8 +3461,8 @@
       <c r="J57">
         <v>8004</v>
       </c>
-      <c r="K57" t="s">
-        <v>22</v>
+      <c r="K57" t="str">
+        <v/>
       </c>
       <c r="L57">
         <v>0</v>
@@ -3482,28 +3485,28 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>131419895</v>
-      </c>
-      <c r="B58" t="s">
-        <v>22</v>
-      </c>
-      <c r="C58" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" t="s">
-        <v>22</v>
+        <v>131463949</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
       </c>
       <c r="E58">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F58" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G58" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H58" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
       </c>
       <c r="I58">
         <v>42</v>
@@ -3511,8 +3514,8 @@
       <c r="J58">
         <v>8004</v>
       </c>
-      <c r="K58" t="s">
-        <v>22</v>
+      <c r="K58" t="str">
+        <v/>
       </c>
       <c r="L58">
         <v>0</v>
@@ -3535,28 +3538,28 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>131420239</v>
-      </c>
-      <c r="B59" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" t="s">
-        <v>22</v>
+        <v>131464442</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
       </c>
       <c r="E59">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F59" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G59" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H59" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
       </c>
       <c r="I59">
         <v>42</v>
@@ -3564,8 +3567,8 @@
       <c r="J59">
         <v>8004</v>
       </c>
-      <c r="K59" t="s">
-        <v>22</v>
+      <c r="K59" t="str">
+        <v/>
       </c>
       <c r="L59">
         <v>0</v>
@@ -3588,37 +3591,37 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>131420756</v>
-      </c>
-      <c r="B60" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" t="s">
-        <v>22</v>
+        <v>131464823</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
       </c>
       <c r="E60">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F60" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G60" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H60" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8004</v>
-      </c>
-      <c r="K60" t="s">
-        <v>22</v>
+        <v>716</v>
+      </c>
+      <c r="K60" t="str">
+        <v/>
       </c>
       <c r="L60">
         <v>0</v>
@@ -3641,28 +3644,28 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>131421443</v>
-      </c>
-      <c r="B61" t="s">
-        <v>22</v>
-      </c>
-      <c r="C61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D61" t="s">
-        <v>22</v>
+        <v>131465520</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
       </c>
       <c r="E61">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F61" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G61" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H61" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
       </c>
       <c r="I61">
         <v>42</v>
@@ -3670,8 +3673,8 @@
       <c r="J61">
         <v>8004</v>
       </c>
-      <c r="K61" t="s">
-        <v>22</v>
+      <c r="K61" t="str">
+        <v/>
       </c>
       <c r="L61">
         <v>0</v>
@@ -3694,28 +3697,28 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>131422194</v>
-      </c>
-      <c r="B62" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" t="s">
-        <v>22</v>
+        <v>131465920</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
       </c>
       <c r="E62">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F62" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G62" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H62" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
       </c>
       <c r="I62">
         <v>42</v>
@@ -3723,8 +3726,8 @@
       <c r="J62">
         <v>8004</v>
       </c>
-      <c r="K62" t="s">
-        <v>22</v>
+      <c r="K62" t="str">
+        <v/>
       </c>
       <c r="L62">
         <v>0</v>
@@ -3747,28 +3750,28 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>131422492</v>
-      </c>
-      <c r="B63" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" t="s">
-        <v>22</v>
+        <v>131466129</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
       </c>
       <c r="E63">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F63" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G63" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H63" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
       </c>
       <c r="I63">
         <v>42</v>
@@ -3776,8 +3779,8 @@
       <c r="J63">
         <v>8004</v>
       </c>
-      <c r="K63" t="s">
-        <v>22</v>
+      <c r="K63" t="str">
+        <v/>
       </c>
       <c r="L63">
         <v>0</v>
@@ -3800,28 +3803,28 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>131422844</v>
-      </c>
-      <c r="B64" t="s">
-        <v>22</v>
-      </c>
-      <c r="C64" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" t="s">
-        <v>22</v>
+        <v>131466283</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
       </c>
       <c r="E64">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F64" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G64" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H64" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
       </c>
       <c r="I64">
         <v>42</v>
@@ -3829,8 +3832,8 @@
       <c r="J64">
         <v>8004</v>
       </c>
-      <c r="K64" t="s">
-        <v>22</v>
+      <c r="K64" t="str">
+        <v/>
       </c>
       <c r="L64">
         <v>0</v>
@@ -3853,28 +3856,28 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>131427054</v>
-      </c>
-      <c r="B65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C65" t="s">
-        <v>22</v>
-      </c>
-      <c r="D65" t="s">
-        <v>22</v>
+        <v>131466840</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
       </c>
       <c r="E65">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F65" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G65" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H65" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
       </c>
       <c r="I65">
         <v>42</v>
@@ -3882,8 +3885,8 @@
       <c r="J65">
         <v>8004</v>
       </c>
-      <c r="K65" t="s">
-        <v>22</v>
+      <c r="K65" t="str">
+        <v/>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3906,28 +3909,28 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>131428053</v>
-      </c>
-      <c r="B66" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" t="s">
-        <v>22</v>
+        <v>131468874</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
       </c>
       <c r="E66">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F66" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G66" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H66" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
       </c>
       <c r="I66">
         <v>42</v>
@@ -3935,8 +3938,8 @@
       <c r="J66">
         <v>8004</v>
       </c>
-      <c r="K66" t="s">
-        <v>22</v>
+      <c r="K66" t="str">
+        <v/>
       </c>
       <c r="L66">
         <v>0</v>
@@ -3959,37 +3962,37 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>131428989</v>
-      </c>
-      <c r="B67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" t="s">
-        <v>22</v>
+        <v>131468975</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
       </c>
       <c r="E67">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F67" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G67" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H67" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
       </c>
       <c r="I67">
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8004</v>
-      </c>
-      <c r="K67" t="s">
-        <v>22</v>
+        <v>716</v>
+      </c>
+      <c r="K67" t="str">
+        <v/>
       </c>
       <c r="L67">
         <v>0</v>
@@ -4012,28 +4015,28 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>131429021</v>
-      </c>
-      <c r="B68" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" t="s">
-        <v>22</v>
+        <v>131469136</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
       </c>
       <c r="E68">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F68" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G68" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H68" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
       </c>
       <c r="I68">
         <v>42</v>
@@ -4041,8 +4044,8 @@
       <c r="J68">
         <v>8004</v>
       </c>
-      <c r="K68" t="s">
-        <v>22</v>
+      <c r="K68" t="str">
+        <v/>
       </c>
       <c r="L68">
         <v>0</v>
@@ -4065,28 +4068,28 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>131429175</v>
-      </c>
-      <c r="B69" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" t="s">
-        <v>22</v>
+        <v>131469255</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
       </c>
       <c r="E69">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F69" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G69" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H69" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
       </c>
       <c r="I69">
         <v>42</v>
@@ -4094,8 +4097,8 @@
       <c r="J69">
         <v>8004</v>
       </c>
-      <c r="K69" t="s">
-        <v>22</v>
+      <c r="K69" t="str">
+        <v/>
       </c>
       <c r="L69">
         <v>0</v>
@@ -4118,28 +4121,28 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>131429218</v>
-      </c>
-      <c r="B70" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" t="s">
-        <v>22</v>
+        <v>131469361</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
       </c>
       <c r="E70">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F70" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G70" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H70" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
       </c>
       <c r="I70">
         <v>42</v>
@@ -4147,8 +4150,8 @@
       <c r="J70">
         <v>8004</v>
       </c>
-      <c r="K70" t="s">
-        <v>22</v>
+      <c r="K70" t="str">
+        <v/>
       </c>
       <c r="L70">
         <v>0</v>
@@ -4171,28 +4174,28 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>131429564</v>
-      </c>
-      <c r="B71" t="s">
-        <v>22</v>
-      </c>
-      <c r="C71" t="s">
-        <v>22</v>
-      </c>
-      <c r="D71" t="s">
-        <v>22</v>
+        <v>131469457</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v/>
       </c>
       <c r="E71">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F71" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G71" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
       </c>
       <c r="I71">
         <v>42</v>
@@ -4200,8 +4203,8 @@
       <c r="J71">
         <v>8004</v>
       </c>
-      <c r="K71" t="s">
-        <v>22</v>
+      <c r="K71" t="str">
+        <v/>
       </c>
       <c r="L71">
         <v>0</v>
@@ -4224,28 +4227,28 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>131432545</v>
-      </c>
-      <c r="B72" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" t="s">
-        <v>22</v>
+        <v>131469550</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v/>
       </c>
       <c r="E72">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F72" s="1">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="G72" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H72" t="s">
-        <v>22</v>
+        <v>45708</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
       </c>
       <c r="I72">
         <v>42</v>
@@ -4253,8 +4256,8 @@
       <c r="J72">
         <v>8004</v>
       </c>
-      <c r="K72" t="s">
-        <v>22</v>
+      <c r="K72" t="str">
+        <v/>
       </c>
       <c r="L72">
         <v>0</v>
@@ -4277,28 +4280,28 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>131433227</v>
-      </c>
-      <c r="B73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" t="s">
-        <v>22</v>
+        <v>131436567</v>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v/>
       </c>
       <c r="E73">
         <v>601</v>
       </c>
       <c r="F73" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G73" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H73" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
       </c>
       <c r="I73">
         <v>42</v>
@@ -4306,8 +4309,8 @@
       <c r="J73">
         <v>8004</v>
       </c>
-      <c r="K73" t="s">
-        <v>22</v>
+      <c r="K73" t="str">
+        <v/>
       </c>
       <c r="L73">
         <v>0</v>
@@ -4330,37 +4333,37 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>131433751</v>
-      </c>
-      <c r="B74" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" t="s">
-        <v>22</v>
+        <v>131436716</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v/>
       </c>
       <c r="E74">
         <v>601</v>
       </c>
       <c r="F74" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G74" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H74" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
       </c>
       <c r="I74">
         <v>42</v>
       </c>
       <c r="J74">
-        <v>1117</v>
-      </c>
-      <c r="K74" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K74" t="str">
+        <v/>
       </c>
       <c r="L74">
         <v>0</v>
@@ -4383,37 +4386,37 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>131399411</v>
-      </c>
-      <c r="B75" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" t="s">
-        <v>22</v>
-      </c>
-      <c r="D75" t="s">
-        <v>22</v>
+        <v>131437805</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
       </c>
       <c r="E75">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F75" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G75" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H75" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
       </c>
       <c r="I75">
         <v>42</v>
       </c>
       <c r="J75">
-        <v>1735</v>
-      </c>
-      <c r="K75" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K75" t="str">
+        <v/>
       </c>
       <c r="L75">
         <v>0</v>
@@ -4436,37 +4439,37 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>131401791</v>
-      </c>
-      <c r="B76" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" t="s">
-        <v>22</v>
+        <v>131438888</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v/>
       </c>
       <c r="E76">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F76" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G76" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H76" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
       </c>
       <c r="I76">
         <v>42</v>
       </c>
       <c r="J76">
-        <v>1735</v>
-      </c>
-      <c r="K76" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K76" t="str">
+        <v/>
       </c>
       <c r="L76">
         <v>0</v>
@@ -4489,37 +4492,37 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>131408446</v>
-      </c>
-      <c r="B77" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" t="s">
-        <v>22</v>
-      </c>
-      <c r="D77" t="s">
-        <v>22</v>
+        <v>131439327</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
       </c>
       <c r="E77">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F77" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G77" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H77" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
       </c>
       <c r="I77">
         <v>42</v>
       </c>
       <c r="J77">
-        <v>1735</v>
-      </c>
-      <c r="K77" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K77" t="str">
+        <v/>
       </c>
       <c r="L77">
         <v>0</v>
@@ -4542,37 +4545,37 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>123058958</v>
-      </c>
-      <c r="B78" t="s">
-        <v>22</v>
-      </c>
-      <c r="C78" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" t="s">
-        <v>22</v>
+        <v>131441920</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
       </c>
       <c r="E78">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F78" s="1">
-        <v>44993</v>
+        <v>45707</v>
       </c>
       <c r="G78" s="1">
-        <v>44995</v>
-      </c>
-      <c r="H78" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
       </c>
       <c r="I78">
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8001</v>
-      </c>
-      <c r="K78" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K78" t="str">
+        <v/>
       </c>
       <c r="L78">
         <v>0</v>
@@ -4595,37 +4598,37 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>129379286</v>
-      </c>
-      <c r="B79" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" t="s">
-        <v>22</v>
-      </c>
-      <c r="D79" t="s">
-        <v>22</v>
+        <v>131442988</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
       </c>
       <c r="E79">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F79" s="1">
-        <v>45553</v>
+        <v>45707</v>
       </c>
       <c r="G79" s="1">
-        <v>45554</v>
-      </c>
-      <c r="H79" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H79" t="str">
+        <v/>
       </c>
       <c r="I79">
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8021</v>
-      </c>
-      <c r="K79" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K79" t="str">
+        <v/>
       </c>
       <c r="L79">
         <v>0</v>
@@ -4648,37 +4651,37 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>131429178</v>
-      </c>
-      <c r="B80" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" t="s">
-        <v>22</v>
+        <v>131443596</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
       </c>
       <c r="E80">
-        <v>1213</v>
+        <v>601</v>
       </c>
       <c r="F80" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G80" s="1">
         <v>45707</v>
       </c>
-      <c r="H80" t="s">
-        <v>22</v>
+      <c r="H80" t="str">
+        <v/>
       </c>
       <c r="I80">
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8021</v>
-      </c>
-      <c r="K80" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K80" t="str">
+        <v/>
       </c>
       <c r="L80">
         <v>0</v>
@@ -4701,37 +4704,37 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>131434829</v>
-      </c>
-      <c r="B81" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81" t="s">
-        <v>22</v>
+        <v>131444665</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
       </c>
       <c r="E81">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F81" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G81" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H81" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
       </c>
       <c r="I81">
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8001</v>
-      </c>
-      <c r="K81" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K81" t="str">
+        <v/>
       </c>
       <c r="L81">
         <v>0</v>
@@ -4754,37 +4757,37 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>131434829</v>
-      </c>
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" t="s">
-        <v>22</v>
+        <v>131447843</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
       </c>
       <c r="E82">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F82" s="1">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="G82" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H82" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
       </c>
       <c r="I82">
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8001</v>
-      </c>
-      <c r="K82" t="s">
-        <v>22</v>
+        <v>1117</v>
+      </c>
+      <c r="K82" t="str">
+        <v/>
       </c>
       <c r="L82">
         <v>0</v>
@@ -4807,37 +4810,37 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>131454614</v>
-      </c>
-      <c r="B83" t="s">
-        <v>22</v>
-      </c>
-      <c r="C83" t="s">
-        <v>22</v>
-      </c>
-      <c r="D83" t="s">
-        <v>22</v>
+        <v>131449727</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v/>
       </c>
       <c r="E83">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F83" s="1">
-        <v>45708</v>
+        <v>45707</v>
       </c>
       <c r="G83" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H83" t="s">
-        <v>22</v>
+        <v>45707</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
       </c>
       <c r="I83">
         <v>42</v>
       </c>
       <c r="J83">
-        <v>718</v>
-      </c>
-      <c r="K83" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K83" t="str">
+        <v/>
       </c>
       <c r="L83">
         <v>0</v>
@@ -4860,19 +4863,19 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>131454704</v>
-      </c>
-      <c r="B84" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84" t="s">
-        <v>22</v>
-      </c>
-      <c r="D84" t="s">
-        <v>22</v>
+        <v>131453340</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
       </c>
       <c r="E84">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F84" s="1">
         <v>45708</v>
@@ -4880,17 +4883,17 @@
       <c r="G84" s="1">
         <v>45708</v>
       </c>
-      <c r="H84" t="s">
-        <v>22</v>
+      <c r="H84" t="str">
+        <v/>
       </c>
       <c r="I84">
         <v>42</v>
       </c>
       <c r="J84">
-        <v>718</v>
-      </c>
-      <c r="K84" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K84" t="str">
+        <v/>
       </c>
       <c r="L84">
         <v>0</v>
@@ -4913,19 +4916,19 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>131454875</v>
-      </c>
-      <c r="B85" t="s">
-        <v>22</v>
-      </c>
-      <c r="C85" t="s">
-        <v>22</v>
-      </c>
-      <c r="D85" t="s">
-        <v>22</v>
+        <v>131462600</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
       </c>
       <c r="E85">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F85" s="1">
         <v>45708</v>
@@ -4933,17 +4936,17 @@
       <c r="G85" s="1">
         <v>45708</v>
       </c>
-      <c r="H85" t="s">
-        <v>22</v>
+      <c r="H85" t="str">
+        <v/>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>718</v>
-      </c>
-      <c r="K85" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K85" t="str">
+        <v/>
       </c>
       <c r="L85">
         <v>0</v>
@@ -4966,19 +4969,19 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>131455600</v>
-      </c>
-      <c r="B86" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" t="s">
-        <v>22</v>
+        <v>131463243</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
       </c>
       <c r="E86">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F86" s="1">
         <v>45708</v>
@@ -4986,17 +4989,17 @@
       <c r="G86" s="1">
         <v>45708</v>
       </c>
-      <c r="H86" t="s">
-        <v>22</v>
+      <c r="H86" t="str">
+        <v/>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>718</v>
-      </c>
-      <c r="K86" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K86" t="str">
+        <v/>
       </c>
       <c r="L86">
         <v>0</v>
@@ -5019,19 +5022,19 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>131456139</v>
-      </c>
-      <c r="B87" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87" t="s">
-        <v>22</v>
+        <v>131463651</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
       </c>
       <c r="E87">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F87" s="1">
         <v>45708</v>
@@ -5039,17 +5042,17 @@
       <c r="G87" s="1">
         <v>45708</v>
       </c>
-      <c r="H87" t="s">
-        <v>22</v>
+      <c r="H87" t="str">
+        <v/>
       </c>
       <c r="I87">
         <v>42</v>
       </c>
       <c r="J87">
-        <v>718</v>
-      </c>
-      <c r="K87" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K87" t="str">
+        <v/>
       </c>
       <c r="L87">
         <v>0</v>
@@ -5072,19 +5075,19 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>131456730</v>
-      </c>
-      <c r="B88" t="s">
-        <v>22</v>
-      </c>
-      <c r="C88" t="s">
-        <v>22</v>
-      </c>
-      <c r="D88" t="s">
-        <v>22</v>
+        <v>131464050</v>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v/>
       </c>
       <c r="E88">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F88" s="1">
         <v>45708</v>
@@ -5092,17 +5095,17 @@
       <c r="G88" s="1">
         <v>45708</v>
       </c>
-      <c r="H88" t="s">
-        <v>22</v>
+      <c r="H88" t="str">
+        <v/>
       </c>
       <c r="I88">
         <v>42</v>
       </c>
       <c r="J88">
-        <v>718</v>
-      </c>
-      <c r="K88" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K88" t="str">
+        <v/>
       </c>
       <c r="L88">
         <v>0</v>
@@ -5125,19 +5128,19 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>131459358</v>
-      </c>
-      <c r="B89" t="s">
-        <v>22</v>
-      </c>
-      <c r="C89" t="s">
-        <v>22</v>
-      </c>
-      <c r="D89" t="s">
-        <v>22</v>
+        <v>131465251</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
+        <v/>
       </c>
       <c r="E89">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F89" s="1">
         <v>45708</v>
@@ -5145,17 +5148,17 @@
       <c r="G89" s="1">
         <v>45708</v>
       </c>
-      <c r="H89" t="s">
-        <v>22</v>
+      <c r="H89" t="str">
+        <v/>
       </c>
       <c r="I89">
         <v>42</v>
       </c>
       <c r="J89">
-        <v>718</v>
-      </c>
-      <c r="K89" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K89" t="str">
+        <v/>
       </c>
       <c r="L89">
         <v>0</v>
@@ -5178,19 +5181,19 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>131460744</v>
-      </c>
-      <c r="B90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" t="s">
-        <v>22</v>
+        <v>131466265</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v/>
       </c>
       <c r="E90">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F90" s="1">
         <v>45708</v>
@@ -5198,17 +5201,17 @@
       <c r="G90" s="1">
         <v>45708</v>
       </c>
-      <c r="H90" t="s">
-        <v>22</v>
+      <c r="H90" t="str">
+        <v/>
       </c>
       <c r="I90">
         <v>42</v>
       </c>
       <c r="J90">
-        <v>718</v>
-      </c>
-      <c r="K90" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K90" t="str">
+        <v/>
       </c>
       <c r="L90">
         <v>0</v>
@@ -5231,19 +5234,19 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>131460849</v>
-      </c>
-      <c r="B91" t="s">
-        <v>22</v>
-      </c>
-      <c r="C91" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91" t="s">
-        <v>22</v>
+        <v>131467087</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91" t="str">
+        <v/>
       </c>
       <c r="E91">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F91" s="1">
         <v>45708</v>
@@ -5251,17 +5254,17 @@
       <c r="G91" s="1">
         <v>45708</v>
       </c>
-      <c r="H91" t="s">
-        <v>22</v>
+      <c r="H91" t="str">
+        <v/>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>718</v>
-      </c>
-      <c r="K91" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K91" t="str">
+        <v/>
       </c>
       <c r="L91">
         <v>0</v>
@@ -5284,19 +5287,19 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>131462828</v>
-      </c>
-      <c r="B92" t="s">
-        <v>22</v>
-      </c>
-      <c r="C92" t="s">
-        <v>22</v>
-      </c>
-      <c r="D92" t="s">
-        <v>22</v>
+        <v>131467093</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
       </c>
       <c r="E92">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F92" s="1">
         <v>45708</v>
@@ -5304,17 +5307,17 @@
       <c r="G92" s="1">
         <v>45708</v>
       </c>
-      <c r="H92" t="s">
-        <v>22</v>
+      <c r="H92" t="str">
+        <v/>
       </c>
       <c r="I92">
         <v>42</v>
       </c>
       <c r="J92">
-        <v>718</v>
-      </c>
-      <c r="K92" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K92" t="str">
+        <v/>
       </c>
       <c r="L92">
         <v>0</v>
@@ -5337,19 +5340,19 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>131463108</v>
-      </c>
-      <c r="B93" t="s">
-        <v>22</v>
-      </c>
-      <c r="C93" t="s">
-        <v>22</v>
-      </c>
-      <c r="D93" t="s">
-        <v>22</v>
+        <v>131467799</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
       </c>
       <c r="E93">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F93" s="1">
         <v>45708</v>
@@ -5357,17 +5360,17 @@
       <c r="G93" s="1">
         <v>45708</v>
       </c>
-      <c r="H93" t="s">
-        <v>22</v>
+      <c r="H93" t="str">
+        <v/>
       </c>
       <c r="I93">
         <v>42</v>
       </c>
       <c r="J93">
-        <v>718</v>
-      </c>
-      <c r="K93" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K93" t="str">
+        <v/>
       </c>
       <c r="L93">
         <v>0</v>
@@ -5390,19 +5393,19 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>131463722</v>
-      </c>
-      <c r="B94" t="s">
-        <v>22</v>
-      </c>
-      <c r="C94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D94" t="s">
-        <v>22</v>
+        <v>131468805</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
       </c>
       <c r="E94">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F94" s="1">
         <v>45708</v>
@@ -5410,17 +5413,17 @@
       <c r="G94" s="1">
         <v>45708</v>
       </c>
-      <c r="H94" t="s">
-        <v>22</v>
+      <c r="H94" t="str">
+        <v/>
       </c>
       <c r="I94">
         <v>42</v>
       </c>
       <c r="J94">
-        <v>718</v>
-      </c>
-      <c r="K94" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K94" t="str">
+        <v/>
       </c>
       <c r="L94">
         <v>0</v>
@@ -5443,19 +5446,19 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>131465996</v>
-      </c>
-      <c r="B95" t="s">
-        <v>22</v>
-      </c>
-      <c r="C95" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95" t="s">
-        <v>22</v>
+        <v>131469215</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95" t="str">
+        <v/>
       </c>
       <c r="E95">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F95" s="1">
         <v>45708</v>
@@ -5463,17 +5466,17 @@
       <c r="G95" s="1">
         <v>45708</v>
       </c>
-      <c r="H95" t="s">
-        <v>22</v>
+      <c r="H95" t="str">
+        <v/>
       </c>
       <c r="I95">
         <v>42</v>
       </c>
       <c r="J95">
-        <v>718</v>
-      </c>
-      <c r="K95" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K95" t="str">
+        <v/>
       </c>
       <c r="L95">
         <v>0</v>
@@ -5496,19 +5499,19 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>131467196</v>
-      </c>
-      <c r="B96" t="s">
-        <v>22</v>
-      </c>
-      <c r="C96" t="s">
-        <v>22</v>
-      </c>
-      <c r="D96" t="s">
-        <v>22</v>
+        <v>131470189</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
       </c>
       <c r="E96">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F96" s="1">
         <v>45708</v>
@@ -5516,17 +5519,17 @@
       <c r="G96" s="1">
         <v>45708</v>
       </c>
-      <c r="H96" t="s">
-        <v>22</v>
+      <c r="H96" t="str">
+        <v/>
       </c>
       <c r="I96">
         <v>42</v>
       </c>
       <c r="J96">
-        <v>718</v>
-      </c>
-      <c r="K96" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K96" t="str">
+        <v/>
       </c>
       <c r="L96">
         <v>0</v>
@@ -5549,19 +5552,19 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>131469861</v>
-      </c>
-      <c r="B97" t="s">
-        <v>22</v>
-      </c>
-      <c r="C97" t="s">
-        <v>22</v>
-      </c>
-      <c r="D97" t="s">
-        <v>22</v>
+        <v>131471371</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v/>
+      </c>
+      <c r="D97" t="str">
+        <v/>
       </c>
       <c r="E97">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F97" s="1">
         <v>45708</v>
@@ -5569,17 +5572,17 @@
       <c r="G97" s="1">
         <v>45708</v>
       </c>
-      <c r="H97" t="s">
-        <v>22</v>
+      <c r="H97" t="str">
+        <v/>
       </c>
       <c r="I97">
         <v>42</v>
       </c>
       <c r="J97">
-        <v>718</v>
-      </c>
-      <c r="K97" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K97" t="str">
+        <v/>
       </c>
       <c r="L97">
         <v>0</v>
@@ -5602,37 +5605,37 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>131469888</v>
-      </c>
-      <c r="B98" t="s">
-        <v>22</v>
-      </c>
-      <c r="C98" t="s">
-        <v>22</v>
-      </c>
-      <c r="D98" t="s">
-        <v>22</v>
+        <v>131476709</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
       </c>
       <c r="E98">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F98" s="1">
-        <v>45708</v>
+        <v>45709</v>
       </c>
       <c r="G98" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H98" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
       </c>
       <c r="I98">
         <v>42</v>
       </c>
       <c r="J98">
-        <v>718</v>
-      </c>
-      <c r="K98" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K98" t="str">
+        <v/>
       </c>
       <c r="L98">
         <v>0</v>
@@ -5655,37 +5658,37 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>131469916</v>
-      </c>
-      <c r="B99" t="s">
-        <v>22</v>
-      </c>
-      <c r="C99" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" t="s">
-        <v>22</v>
+        <v>131476723</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
       </c>
       <c r="E99">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F99" s="1">
-        <v>45708</v>
+        <v>45709</v>
       </c>
       <c r="G99" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H99" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
       </c>
       <c r="I99">
         <v>42</v>
       </c>
       <c r="J99">
-        <v>718</v>
-      </c>
-      <c r="K99" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K99" t="str">
+        <v/>
       </c>
       <c r="L99">
         <v>0</v>
@@ -5708,37 +5711,37 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>131469944</v>
-      </c>
-      <c r="B100" t="s">
-        <v>22</v>
-      </c>
-      <c r="C100" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" t="s">
-        <v>22</v>
+        <v>131477351</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
       </c>
       <c r="E100">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F100" s="1">
-        <v>45708</v>
+        <v>45709</v>
       </c>
       <c r="G100" s="1">
-        <v>45708</v>
-      </c>
-      <c r="H100" t="s">
-        <v>22</v>
+        <v>45709</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
       </c>
       <c r="I100">
         <v>42</v>
       </c>
       <c r="J100">
-        <v>718</v>
-      </c>
-      <c r="K100" t="s">
-        <v>22</v>
+        <v>8004</v>
+      </c>
+      <c r="K100" t="str">
+        <v/>
       </c>
       <c r="L100">
         <v>0</v>
@@ -5761,37 +5764,37 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>131399277</v>
-      </c>
-      <c r="B101" t="s">
-        <v>21</v>
-      </c>
-      <c r="C101" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" t="s">
-        <v>21</v>
+        <v>131478637</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
       </c>
       <c r="E101">
         <v>601</v>
       </c>
       <c r="F101" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G101" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H101" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
       </c>
       <c r="I101">
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8013</v>
-      </c>
-      <c r="K101" t="s">
-        <v>21</v>
+        <v>8004</v>
+      </c>
+      <c r="K101" t="str">
+        <v/>
       </c>
       <c r="L101">
         <v>0</v>
@@ -5814,28 +5817,28 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>131402489</v>
-      </c>
-      <c r="B102" t="s">
-        <v>21</v>
-      </c>
-      <c r="C102" t="s">
-        <v>21</v>
-      </c>
-      <c r="D102" t="s">
-        <v>21</v>
+        <v>131479028</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
       </c>
       <c r="E102">
         <v>601</v>
       </c>
       <c r="F102" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G102" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H102" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
       </c>
       <c r="I102">
         <v>42</v>
@@ -5843,8 +5846,8 @@
       <c r="J102">
         <v>8004</v>
       </c>
-      <c r="K102" t="s">
-        <v>21</v>
+      <c r="K102" t="str">
+        <v/>
       </c>
       <c r="L102">
         <v>0</v>
@@ -5867,37 +5870,37 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>131405270</v>
-      </c>
-      <c r="B103" t="s">
-        <v>21</v>
-      </c>
-      <c r="C103" t="s">
-        <v>21</v>
-      </c>
-      <c r="D103" t="s">
-        <v>21</v>
+        <v>131481813</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v/>
+      </c>
+      <c r="D103" t="str">
+        <v/>
       </c>
       <c r="E103">
         <v>601</v>
       </c>
       <c r="F103" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G103" s="1">
-        <v>45706</v>
-      </c>
-      <c r="H103" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
       </c>
       <c r="I103">
         <v>42</v>
       </c>
       <c r="J103">
-        <v>8013</v>
-      </c>
-      <c r="K103" t="s">
-        <v>21</v>
+        <v>8004</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
       </c>
       <c r="L103">
         <v>0</v>
@@ -5920,37 +5923,37 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>131406281</v>
-      </c>
-      <c r="B104" t="s">
-        <v>21</v>
-      </c>
-      <c r="C104" t="s">
-        <v>21</v>
-      </c>
-      <c r="D104" t="s">
-        <v>21</v>
+        <v>131482863</v>
+      </c>
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
       </c>
       <c r="E104">
         <v>601</v>
       </c>
       <c r="F104" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G104" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H104" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
       </c>
       <c r="I104">
         <v>42</v>
       </c>
       <c r="J104">
-        <v>8013</v>
-      </c>
-      <c r="K104" t="s">
-        <v>21</v>
+        <v>8003</v>
+      </c>
+      <c r="K104" t="str">
+        <v/>
       </c>
       <c r="L104">
         <v>0</v>
@@ -5973,37 +5976,37 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>131406893</v>
-      </c>
-      <c r="B105" t="s">
-        <v>21</v>
-      </c>
-      <c r="C105" t="s">
-        <v>21</v>
-      </c>
-      <c r="D105" t="s">
-        <v>21</v>
+        <v>131420284</v>
+      </c>
+      <c r="B105" t="str">
+        <v/>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
       </c>
       <c r="E105">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F105" s="1">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="G105" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H105" t="s">
-        <v>21</v>
+        <v>45706</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
       </c>
       <c r="I105">
         <v>42</v>
       </c>
       <c r="J105">
-        <v>8004</v>
-      </c>
-      <c r="K105" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K105" t="str">
+        <v/>
       </c>
       <c r="L105">
         <v>0</v>
@@ -6026,37 +6029,37 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>131407091</v>
-      </c>
-      <c r="B106" t="s">
-        <v>21</v>
-      </c>
-      <c r="C106" t="s">
-        <v>21</v>
-      </c>
-      <c r="D106" t="s">
-        <v>21</v>
+        <v>131424655</v>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
       </c>
       <c r="E106">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F106" s="1">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="G106" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H106" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
       </c>
       <c r="I106">
         <v>42</v>
       </c>
       <c r="J106">
-        <v>8013</v>
-      </c>
-      <c r="K106" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K106" t="str">
+        <v/>
       </c>
       <c r="L106">
         <v>0</v>
@@ -6079,37 +6082,37 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>131408217</v>
-      </c>
-      <c r="B107" t="s">
-        <v>21</v>
-      </c>
-      <c r="C107" t="s">
-        <v>21</v>
-      </c>
-      <c r="D107" t="s">
-        <v>21</v>
+        <v>131436028</v>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
       </c>
       <c r="E107">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F107" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G107" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H107" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
       </c>
       <c r="I107">
         <v>42</v>
       </c>
       <c r="J107">
-        <v>8004</v>
-      </c>
-      <c r="K107" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K107" t="str">
+        <v/>
       </c>
       <c r="L107">
         <v>0</v>
@@ -6132,37 +6135,37 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>131408228</v>
-      </c>
-      <c r="B108" t="s">
-        <v>21</v>
-      </c>
-      <c r="C108" t="s">
-        <v>21</v>
-      </c>
-      <c r="D108" t="s">
-        <v>21</v>
+        <v>131437060</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
       </c>
       <c r="E108">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F108" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G108" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H108" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H108" t="str">
+        <v/>
       </c>
       <c r="I108">
         <v>42</v>
       </c>
       <c r="J108">
-        <v>8004</v>
-      </c>
-      <c r="K108" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K108" t="str">
+        <v/>
       </c>
       <c r="L108">
         <v>0</v>
@@ -6185,37 +6188,37 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>131409641</v>
-      </c>
-      <c r="B109" t="s">
-        <v>21</v>
-      </c>
-      <c r="C109" t="s">
-        <v>21</v>
-      </c>
-      <c r="D109" t="s">
-        <v>21</v>
+        <v>131442389</v>
+      </c>
+      <c r="B109" t="str">
+        <v/>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109" t="str">
+        <v/>
       </c>
       <c r="E109">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F109" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G109" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H109" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H109" t="str">
+        <v/>
       </c>
       <c r="I109">
         <v>42</v>
       </c>
       <c r="J109">
-        <v>8004</v>
-      </c>
-      <c r="K109" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K109" t="str">
+        <v/>
       </c>
       <c r="L109">
         <v>0</v>
@@ -6238,37 +6241,37 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>131410386</v>
-      </c>
-      <c r="B110" t="s">
-        <v>21</v>
-      </c>
-      <c r="C110" t="s">
-        <v>21</v>
-      </c>
-      <c r="D110" t="s">
-        <v>21</v>
+        <v>131446673</v>
+      </c>
+      <c r="B110" t="str">
+        <v/>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+      <c r="D110" t="str">
+        <v/>
       </c>
       <c r="E110">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F110" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G110" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H110" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
       </c>
       <c r="I110">
         <v>42</v>
       </c>
       <c r="J110">
-        <v>8013</v>
-      </c>
-      <c r="K110" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K110" t="str">
+        <v/>
       </c>
       <c r="L110">
         <v>0</v>
@@ -6291,37 +6294,37 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>131413436</v>
-      </c>
-      <c r="B111" t="s">
-        <v>21</v>
-      </c>
-      <c r="C111" t="s">
-        <v>21</v>
-      </c>
-      <c r="D111" t="s">
-        <v>21</v>
+        <v>131446766</v>
+      </c>
+      <c r="B111" t="str">
+        <v/>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111" t="str">
+        <v/>
       </c>
       <c r="E111">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F111" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G111" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H111" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
       </c>
       <c r="I111">
         <v>42</v>
       </c>
       <c r="J111">
-        <v>8004</v>
-      </c>
-      <c r="K111" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K111" t="str">
+        <v/>
       </c>
       <c r="L111">
         <v>0</v>
@@ -6344,37 +6347,37 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>131413560</v>
-      </c>
-      <c r="B112" t="s">
-        <v>21</v>
-      </c>
-      <c r="C112" t="s">
-        <v>21</v>
-      </c>
-      <c r="D112" t="s">
-        <v>21</v>
+        <v>131459831</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112" t="str">
+        <v/>
       </c>
       <c r="E112">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F112" s="1">
-        <v>45705</v>
+        <v>45708</v>
       </c>
       <c r="G112" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H112" t="s">
-        <v>21</v>
+        <v>45708</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
       </c>
       <c r="I112">
         <v>42</v>
       </c>
       <c r="J112">
-        <v>1118</v>
-      </c>
-      <c r="K112" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K112" t="str">
+        <v/>
       </c>
       <c r="L112">
         <v>0</v>
@@ -6397,37 +6400,37 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>131414341</v>
-      </c>
-      <c r="B113" t="s">
-        <v>21</v>
-      </c>
-      <c r="C113" t="s">
-        <v>21</v>
-      </c>
-      <c r="D113" t="s">
-        <v>21</v>
+        <v>131464341</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
+        <v/>
       </c>
       <c r="E113">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F113" s="1">
-        <v>45705</v>
+        <v>45708</v>
       </c>
       <c r="G113" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H113" t="s">
-        <v>21</v>
+        <v>45708</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
       </c>
       <c r="I113">
         <v>42</v>
       </c>
       <c r="J113">
-        <v>8013</v>
-      </c>
-      <c r="K113" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K113" t="str">
+        <v/>
       </c>
       <c r="L113">
         <v>0</v>
@@ -6450,37 +6453,37 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>131414392</v>
-      </c>
-      <c r="B114" t="s">
-        <v>21</v>
-      </c>
-      <c r="C114" t="s">
-        <v>21</v>
-      </c>
-      <c r="D114" t="s">
-        <v>21</v>
+        <v>131469276</v>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114" t="str">
+        <v/>
       </c>
       <c r="E114">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F114" s="1">
-        <v>45705</v>
+        <v>45708</v>
       </c>
       <c r="G114" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H114" t="s">
-        <v>21</v>
+        <v>45708</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
       </c>
       <c r="I114">
         <v>42</v>
       </c>
       <c r="J114">
-        <v>8013</v>
-      </c>
-      <c r="K114" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K114" t="str">
+        <v/>
       </c>
       <c r="L114">
         <v>0</v>
@@ -6503,37 +6506,37 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>131401822</v>
-      </c>
-      <c r="B115" t="s">
-        <v>21</v>
-      </c>
-      <c r="C115" t="s">
-        <v>21</v>
-      </c>
-      <c r="D115" t="s">
-        <v>21</v>
+        <v>131469597</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
       </c>
       <c r="E115">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F115" s="1">
-        <v>45705</v>
+        <v>45708</v>
       </c>
       <c r="G115" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H115" t="s">
-        <v>21</v>
+        <v>45708</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
       </c>
       <c r="I115">
         <v>42</v>
       </c>
       <c r="J115">
-        <v>8004</v>
-      </c>
-      <c r="K115" t="s">
-        <v>21</v>
+        <v>1735</v>
+      </c>
+      <c r="K115" t="str">
+        <v/>
       </c>
       <c r="L115">
         <v>0</v>
@@ -6556,37 +6559,37 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>131402354</v>
-      </c>
-      <c r="B116" t="s">
-        <v>21</v>
-      </c>
-      <c r="C116" t="s">
-        <v>21</v>
-      </c>
-      <c r="D116" t="s">
-        <v>21</v>
+        <v>123058958</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
       </c>
       <c r="E116">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F116" s="1">
-        <v>45705</v>
+        <v>44993</v>
       </c>
       <c r="G116" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H116" t="s">
-        <v>21</v>
+        <v>44995</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
       </c>
       <c r="I116">
         <v>42</v>
       </c>
       <c r="J116">
-        <v>8004</v>
-      </c>
-      <c r="K116" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K116" t="str">
+        <v/>
       </c>
       <c r="L116">
         <v>0</v>
@@ -6609,37 +6612,37 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>131402846</v>
-      </c>
-      <c r="B117" t="s">
-        <v>21</v>
-      </c>
-      <c r="C117" t="s">
-        <v>21</v>
-      </c>
-      <c r="D117" t="s">
-        <v>21</v>
+        <v>129379286</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v/>
       </c>
       <c r="E117">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F117" s="1">
-        <v>45705</v>
+        <v>45553</v>
       </c>
       <c r="G117" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H117" t="s">
-        <v>21</v>
+        <v>45554</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
       </c>
       <c r="I117">
         <v>42</v>
       </c>
       <c r="J117">
-        <v>8004</v>
-      </c>
-      <c r="K117" t="s">
-        <v>21</v>
+        <v>8021</v>
+      </c>
+      <c r="K117" t="str">
+        <v/>
       </c>
       <c r="L117">
         <v>0</v>
@@ -6662,37 +6665,37 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>131404142</v>
-      </c>
-      <c r="B118" t="s">
-        <v>21</v>
-      </c>
-      <c r="C118" t="s">
-        <v>21</v>
-      </c>
-      <c r="D118" t="s">
-        <v>21</v>
+        <v>131429178</v>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v/>
       </c>
       <c r="E118">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F118" s="1">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="G118" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H118" t="s">
-        <v>21</v>
+        <v>45707</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
       </c>
       <c r="I118">
         <v>42</v>
       </c>
       <c r="J118">
-        <v>8004</v>
-      </c>
-      <c r="K118" t="s">
-        <v>21</v>
+        <v>8021</v>
+      </c>
+      <c r="K118" t="str">
+        <v/>
       </c>
       <c r="L118">
         <v>0</v>
@@ -6715,37 +6718,37 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>131404740</v>
-      </c>
-      <c r="B119" t="s">
-        <v>21</v>
-      </c>
-      <c r="C119" t="s">
-        <v>21</v>
-      </c>
-      <c r="D119" t="s">
-        <v>21</v>
+        <v>127351887</v>
+      </c>
+      <c r="B119" t="str">
+        <v/>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119" t="str">
+        <v/>
       </c>
       <c r="E119">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F119" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G119" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H119" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
       </c>
       <c r="I119">
         <v>42</v>
       </c>
       <c r="J119">
-        <v>8004</v>
-      </c>
-      <c r="K119" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K119" t="str">
+        <v/>
       </c>
       <c r="L119">
         <v>0</v>
@@ -6768,37 +6771,37 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>131404984</v>
-      </c>
-      <c r="B120" t="s">
-        <v>21</v>
-      </c>
-      <c r="C120" t="s">
-        <v>21</v>
-      </c>
-      <c r="D120" t="s">
-        <v>21</v>
+        <v>127903138</v>
+      </c>
+      <c r="B120" t="str">
+        <v/>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
       </c>
       <c r="E120">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F120" s="1">
-        <v>45705</v>
+        <v>45707</v>
       </c>
       <c r="G120" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H120" t="s">
-        <v>21</v>
+        <v>45711</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
       </c>
       <c r="I120">
         <v>42</v>
       </c>
       <c r="J120">
-        <v>8004</v>
-      </c>
-      <c r="K120" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K120" t="str">
+        <v/>
       </c>
       <c r="L120">
         <v>0</v>
@@ -6821,37 +6824,37 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>131405002</v>
-      </c>
-      <c r="B121" t="s">
-        <v>21</v>
-      </c>
-      <c r="C121" t="s">
-        <v>21</v>
-      </c>
-      <c r="D121" t="s">
-        <v>21</v>
+        <v>127946597</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
+        <v/>
       </c>
       <c r="E121">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F121" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G121" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H121" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
       </c>
       <c r="I121">
         <v>42</v>
       </c>
       <c r="J121">
-        <v>8004</v>
-      </c>
-      <c r="K121" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K121" t="str">
+        <v/>
       </c>
       <c r="L121">
         <v>0</v>
@@ -6874,37 +6877,37 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>131405237</v>
-      </c>
-      <c r="B122" t="s">
-        <v>21</v>
-      </c>
-      <c r="C122" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122" t="s">
-        <v>21</v>
+        <v>128180811</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
       </c>
       <c r="E122">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F122" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G122" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H122" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
       </c>
       <c r="I122">
         <v>42</v>
       </c>
       <c r="J122">
-        <v>8004</v>
-      </c>
-      <c r="K122" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K122" t="str">
+        <v/>
       </c>
       <c r="L122">
         <v>0</v>
@@ -6927,37 +6930,37 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>131407311</v>
-      </c>
-      <c r="B123" t="s">
-        <v>21</v>
-      </c>
-      <c r="C123" t="s">
-        <v>21</v>
-      </c>
-      <c r="D123" t="s">
-        <v>21</v>
+        <v>128536427</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" t="str">
+        <v/>
       </c>
       <c r="E123">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F123" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G123" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H123" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
       </c>
       <c r="I123">
         <v>42</v>
       </c>
       <c r="J123">
-        <v>8004</v>
-      </c>
-      <c r="K123" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K123" t="str">
+        <v/>
       </c>
       <c r="L123">
         <v>0</v>
@@ -6980,37 +6983,37 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>131413589</v>
-      </c>
-      <c r="B124" t="s">
-        <v>21</v>
-      </c>
-      <c r="C124" t="s">
-        <v>21</v>
-      </c>
-      <c r="D124" t="s">
-        <v>21</v>
+        <v>128618926</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" t="str">
+        <v/>
       </c>
       <c r="E124">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F124" s="1">
-        <v>45705</v>
+        <v>45709</v>
       </c>
       <c r="G124" s="1">
-        <v>45705</v>
-      </c>
-      <c r="H124" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
       </c>
       <c r="I124">
         <v>42</v>
       </c>
       <c r="J124">
-        <v>8004</v>
-      </c>
-      <c r="K124" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K124" t="str">
+        <v/>
       </c>
       <c r="L124">
         <v>0</v>
@@ -7033,28 +7036,28 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>123058958</v>
-      </c>
-      <c r="B125" t="s">
-        <v>21</v>
-      </c>
-      <c r="C125" t="s">
-        <v>21</v>
-      </c>
-      <c r="D125" t="s">
-        <v>21</v>
+        <v>128648042</v>
+      </c>
+      <c r="B125" t="str">
+        <v/>
+      </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" t="str">
+        <v/>
       </c>
       <c r="E125">
         <v>1211</v>
       </c>
       <c r="F125" s="1">
-        <v>44993</v>
+        <v>45709</v>
       </c>
       <c r="G125" s="1">
-        <v>44995</v>
-      </c>
-      <c r="H125" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H125" t="str">
+        <v/>
       </c>
       <c r="I125">
         <v>42</v>
@@ -7062,8 +7065,8 @@
       <c r="J125">
         <v>8001</v>
       </c>
-      <c r="K125" t="s">
-        <v>21</v>
+      <c r="K125" t="str">
+        <v/>
       </c>
       <c r="L125">
         <v>0</v>
@@ -7086,37 +7089,37 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>129379286</v>
-      </c>
-      <c r="B126" t="s">
-        <v>21</v>
-      </c>
-      <c r="C126" t="s">
-        <v>21</v>
-      </c>
-      <c r="D126" t="s">
-        <v>21</v>
+        <v>128792146</v>
+      </c>
+      <c r="B126" t="str">
+        <v/>
+      </c>
+      <c r="C126" t="str">
+        <v/>
+      </c>
+      <c r="D126" t="str">
+        <v/>
       </c>
       <c r="E126">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F126" s="1">
-        <v>45553</v>
+        <v>45709</v>
       </c>
       <c r="G126" s="1">
-        <v>45554</v>
-      </c>
-      <c r="H126" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
       </c>
       <c r="I126">
         <v>42</v>
       </c>
       <c r="J126">
-        <v>8021</v>
-      </c>
-      <c r="K126" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K126" t="str">
+        <v/>
       </c>
       <c r="L126">
         <v>0</v>
@@ -7139,37 +7142,37 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>131435535</v>
-      </c>
-      <c r="B127" t="s">
-        <v>21</v>
-      </c>
-      <c r="C127" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" t="s">
-        <v>21</v>
+        <v>128894976</v>
+      </c>
+      <c r="B127" t="str">
+        <v/>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v/>
       </c>
       <c r="E127">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F127" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G127" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H127" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H127" t="str">
+        <v/>
       </c>
       <c r="I127">
         <v>42</v>
       </c>
       <c r="J127">
-        <v>718</v>
-      </c>
-      <c r="K127" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K127" t="str">
+        <v/>
       </c>
       <c r="L127">
         <v>0</v>
@@ -7192,37 +7195,37 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>131435598</v>
-      </c>
-      <c r="B128" t="s">
-        <v>21</v>
-      </c>
-      <c r="C128" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128" t="s">
-        <v>21</v>
+        <v>129087174</v>
+      </c>
+      <c r="B128" t="str">
+        <v/>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128" t="str">
+        <v/>
       </c>
       <c r="E128">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F128" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G128" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H128" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H128" t="str">
+        <v/>
       </c>
       <c r="I128">
         <v>42</v>
       </c>
       <c r="J128">
-        <v>718</v>
-      </c>
-      <c r="K128" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K128" t="str">
+        <v/>
       </c>
       <c r="L128">
         <v>0</v>
@@ -7245,37 +7248,37 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>131435678</v>
-      </c>
-      <c r="B129" t="s">
-        <v>21</v>
-      </c>
-      <c r="C129" t="s">
-        <v>21</v>
-      </c>
-      <c r="D129" t="s">
-        <v>21</v>
+        <v>129253252</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
+        <v/>
       </c>
       <c r="E129">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F129" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G129" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H129" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H129" t="str">
+        <v/>
       </c>
       <c r="I129">
         <v>42</v>
       </c>
       <c r="J129">
-        <v>718</v>
-      </c>
-      <c r="K129" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K129" t="str">
+        <v/>
       </c>
       <c r="L129">
         <v>0</v>
@@ -7298,37 +7301,37 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>131445044</v>
-      </c>
-      <c r="B130" t="s">
-        <v>21</v>
-      </c>
-      <c r="C130" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" t="s">
-        <v>21</v>
+        <v>129360850</v>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
+        <v/>
       </c>
       <c r="E130">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F130" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G130" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H130" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H130" t="str">
+        <v/>
       </c>
       <c r="I130">
         <v>42</v>
       </c>
       <c r="J130">
-        <v>718</v>
-      </c>
-      <c r="K130" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K130" t="str">
+        <v/>
       </c>
       <c r="L130">
         <v>0</v>
@@ -7351,37 +7354,37 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>131445112</v>
-      </c>
-      <c r="B131" t="s">
-        <v>21</v>
-      </c>
-      <c r="C131" t="s">
-        <v>21</v>
-      </c>
-      <c r="D131" t="s">
-        <v>21</v>
+        <v>130064614</v>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
+        <v/>
       </c>
       <c r="E131">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F131" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G131" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H131" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H131" t="str">
+        <v/>
       </c>
       <c r="I131">
         <v>42</v>
       </c>
       <c r="J131">
-        <v>718</v>
-      </c>
-      <c r="K131" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K131" t="str">
+        <v/>
       </c>
       <c r="L131">
         <v>0</v>
@@ -7404,37 +7407,37 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>131448009</v>
-      </c>
-      <c r="B132" t="s">
-        <v>21</v>
-      </c>
-      <c r="C132" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132" t="s">
-        <v>21</v>
+        <v>130411749</v>
+      </c>
+      <c r="B132" t="str">
+        <v/>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132" t="str">
+        <v/>
       </c>
       <c r="E132">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F132" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G132" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H132" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H132" t="str">
+        <v/>
       </c>
       <c r="I132">
         <v>42</v>
       </c>
       <c r="J132">
-        <v>718</v>
-      </c>
-      <c r="K132" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K132" t="str">
+        <v/>
       </c>
       <c r="L132">
         <v>0</v>
@@ -7457,37 +7460,37 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>131448404</v>
-      </c>
-      <c r="B133" t="s">
-        <v>21</v>
-      </c>
-      <c r="C133" t="s">
-        <v>21</v>
-      </c>
-      <c r="D133" t="s">
-        <v>21</v>
+        <v>130523568</v>
+      </c>
+      <c r="B133" t="str">
+        <v/>
+      </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133" t="str">
+        <v/>
       </c>
       <c r="E133">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F133" s="1">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="G133" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H133" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H133" t="str">
+        <v/>
       </c>
       <c r="I133">
         <v>42</v>
       </c>
       <c r="J133">
-        <v>718</v>
-      </c>
-      <c r="K133" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K133" t="str">
+        <v/>
       </c>
       <c r="L133">
         <v>0</v>
@@ -7510,37 +7513,37 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>131448463</v>
-      </c>
-      <c r="B134" t="s">
-        <v>21</v>
-      </c>
-      <c r="C134" t="s">
-        <v>21</v>
-      </c>
-      <c r="D134" t="s">
-        <v>21</v>
+        <v>130586364</v>
+      </c>
+      <c r="B134" t="str">
+        <v/>
+      </c>
+      <c r="C134" t="str">
+        <v/>
+      </c>
+      <c r="D134" t="str">
+        <v/>
       </c>
       <c r="E134">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F134" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G134" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H134" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H134" t="str">
+        <v/>
       </c>
       <c r="I134">
         <v>42</v>
       </c>
       <c r="J134">
-        <v>718</v>
-      </c>
-      <c r="K134" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K134" t="str">
+        <v/>
       </c>
       <c r="L134">
         <v>0</v>
@@ -7563,37 +7566,37 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>131449123</v>
-      </c>
-      <c r="B135" t="s">
-        <v>21</v>
-      </c>
-      <c r="C135" t="s">
-        <v>21</v>
-      </c>
-      <c r="D135" t="s">
-        <v>21</v>
+        <v>131346678</v>
+      </c>
+      <c r="B135" t="str">
+        <v/>
+      </c>
+      <c r="C135" t="str">
+        <v/>
+      </c>
+      <c r="D135" t="str">
+        <v/>
       </c>
       <c r="E135">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F135" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G135" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H135" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H135" t="str">
+        <v/>
       </c>
       <c r="I135">
         <v>42</v>
       </c>
       <c r="J135">
-        <v>718</v>
-      </c>
-      <c r="K135" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K135" t="str">
+        <v/>
       </c>
       <c r="L135">
         <v>0</v>
@@ -7616,37 +7619,37 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>131450012</v>
-      </c>
-      <c r="B136" t="s">
-        <v>21</v>
-      </c>
-      <c r="C136" t="s">
-        <v>21</v>
-      </c>
-      <c r="D136" t="s">
-        <v>21</v>
+        <v>131412440</v>
+      </c>
+      <c r="B136" t="str">
+        <v/>
+      </c>
+      <c r="C136" t="str">
+        <v/>
+      </c>
+      <c r="D136" t="str">
+        <v/>
       </c>
       <c r="E136">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F136" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G136" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H136" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H136" t="str">
+        <v/>
       </c>
       <c r="I136">
         <v>42</v>
       </c>
       <c r="J136">
-        <v>718</v>
-      </c>
-      <c r="K136" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K136" t="str">
+        <v/>
       </c>
       <c r="L136">
         <v>0</v>
@@ -7669,37 +7672,37 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>131450112</v>
-      </c>
-      <c r="B137" t="s">
-        <v>21</v>
-      </c>
-      <c r="C137" t="s">
-        <v>21</v>
-      </c>
-      <c r="D137" t="s">
-        <v>21</v>
+        <v>131470301</v>
+      </c>
+      <c r="B137" t="str">
+        <v/>
+      </c>
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137" t="str">
+        <v/>
       </c>
       <c r="E137">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F137" s="1">
-        <v>45707</v>
+        <v>45709</v>
       </c>
       <c r="G137" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H137" t="s">
-        <v>21</v>
+        <v>45709</v>
+      </c>
+      <c r="H137" t="str">
+        <v/>
       </c>
       <c r="I137">
         <v>42</v>
       </c>
       <c r="J137">
-        <v>718</v>
-      </c>
-      <c r="K137" t="s">
-        <v>21</v>
+        <v>8001</v>
+      </c>
+      <c r="K137" t="str">
+        <v/>
       </c>
       <c r="L137">
         <v>0</v>
@@ -7722,54 +7725,902 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>131450135</v>
-      </c>
-      <c r="B138" t="s">
-        <v>21</v>
-      </c>
-      <c r="C138" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" t="s">
-        <v>21</v>
+        <v>127946597</v>
+      </c>
+      <c r="B138" t="str">
+        <v/>
+      </c>
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138" t="str">
+        <v/>
       </c>
       <c r="E138">
+        <v>1211</v>
+      </c>
+      <c r="F138" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G138" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8001</v>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>128648042</v>
+      </c>
+      <c r="B139" t="str">
+        <v/>
+      </c>
+      <c r="C139" t="str">
+        <v/>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139">
+        <v>1211</v>
+      </c>
+      <c r="F139" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G139" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8001</v>
+      </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>128792146</v>
+      </c>
+      <c r="B140" t="str">
+        <v/>
+      </c>
+      <c r="C140" t="str">
+        <v/>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+      <c r="E140">
+        <v>1212</v>
+      </c>
+      <c r="F140" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G140" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8001</v>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>128894976</v>
+      </c>
+      <c r="B141" t="str">
+        <v/>
+      </c>
+      <c r="C141" t="str">
+        <v/>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G141" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8001</v>
+      </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>129253252</v>
+      </c>
+      <c r="B142" t="str">
+        <v/>
+      </c>
+      <c r="C142" t="str">
+        <v/>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142">
+        <v>1211</v>
+      </c>
+      <c r="F142" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G142" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8001</v>
+      </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>129360850</v>
+      </c>
+      <c r="B143" t="str">
+        <v/>
+      </c>
+      <c r="C143" t="str">
+        <v/>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+      <c r="E143">
+        <v>1211</v>
+      </c>
+      <c r="F143" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G143" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8001</v>
+      </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>130064614</v>
+      </c>
+      <c r="B144" t="str">
+        <v/>
+      </c>
+      <c r="C144" t="str">
+        <v/>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+      <c r="E144">
+        <v>1211</v>
+      </c>
+      <c r="F144" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G144" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8001</v>
+      </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>130411749</v>
+      </c>
+      <c r="B145" t="str">
+        <v/>
+      </c>
+      <c r="C145" t="str">
+        <v/>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+      <c r="E145">
+        <v>1211</v>
+      </c>
+      <c r="F145" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G145" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8001</v>
+      </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>130523568</v>
+      </c>
+      <c r="B146" t="str">
+        <v/>
+      </c>
+      <c r="C146" t="str">
+        <v/>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+      <c r="E146">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="1">
+        <v>45708</v>
+      </c>
+      <c r="G146" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8001</v>
+      </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>131346678</v>
+      </c>
+      <c r="B147" t="str">
+        <v/>
+      </c>
+      <c r="C147" t="str">
+        <v/>
+      </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
+      <c r="E147">
+        <v>1211</v>
+      </c>
+      <c r="F147" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G147" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>8001</v>
+      </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>131412440</v>
+      </c>
+      <c r="B148" t="str">
+        <v/>
+      </c>
+      <c r="C148" t="str">
+        <v/>
+      </c>
+      <c r="D148" t="str">
+        <v/>
+      </c>
+      <c r="E148">
+        <v>1211</v>
+      </c>
+      <c r="F148" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G148" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>8001</v>
+      </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>131473216</v>
+      </c>
+      <c r="B149" t="str">
+        <v/>
+      </c>
+      <c r="C149" t="str">
+        <v/>
+      </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
+      <c r="E149">
         <v>2013</v>
       </c>
-      <c r="F138" s="1">
-        <v>45707</v>
-      </c>
-      <c r="G138" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H138" t="s">
-        <v>21</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
+      <c r="F149" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G149" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
         <v>718</v>
       </c>
-      <c r="K138" t="s">
-        <v>21</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
+      <c r="K149" t="str">
+        <v/>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>131473297</v>
+      </c>
+      <c r="B150" t="str">
+        <v/>
+      </c>
+      <c r="C150" t="str">
+        <v/>
+      </c>
+      <c r="D150" t="str">
+        <v/>
+      </c>
+      <c r="E150">
+        <v>2013</v>
+      </c>
+      <c r="F150" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G150" s="1">
+        <v>45710</v>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>718</v>
+      </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>131473409</v>
+      </c>
+      <c r="B151" t="str">
+        <v/>
+      </c>
+      <c r="C151" t="str">
+        <v/>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+      <c r="E151">
+        <v>2013</v>
+      </c>
+      <c r="F151" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G151" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151">
+        <v>42</v>
+      </c>
+      <c r="J151">
+        <v>718</v>
+      </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>131477392</v>
+      </c>
+      <c r="B152" t="str">
+        <v/>
+      </c>
+      <c r="C152" t="str">
+        <v/>
+      </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
+      <c r="E152">
+        <v>2013</v>
+      </c>
+      <c r="F152" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G152" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152">
+        <v>42</v>
+      </c>
+      <c r="J152">
+        <v>718</v>
+      </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>131480872</v>
+      </c>
+      <c r="B153" t="str">
+        <v/>
+      </c>
+      <c r="C153" t="str">
+        <v/>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+      <c r="E153">
+        <v>2013</v>
+      </c>
+      <c r="F153" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G153" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153">
+        <v>42</v>
+      </c>
+      <c r="J153">
+        <v>718</v>
+      </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>131485992</v>
+      </c>
+      <c r="B154" t="str">
+        <v/>
+      </c>
+      <c r="C154" t="str">
+        <v/>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+      <c r="E154">
+        <v>2013</v>
+      </c>
+      <c r="F154" s="1">
+        <v>45709</v>
+      </c>
+      <c r="G154" s="1">
+        <v>45709</v>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154">
+        <v>42</v>
+      </c>
+      <c r="J154">
+        <v>718</v>
+      </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$Q$22</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$6</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1048576"/>
+  <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -460,9 +460,11 @@
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="str">
         <v>NR_PROPOSTA</v>
       </c>
@@ -514,10 +516,16 @@
       <c r="Q1" t="str">
         <v>NR_OPERATIVA</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="str">
+        <v>TIPO_SEGURO_TL</v>
+      </c>
+      <c r="S1" t="str">
+        <v>TIPO_SEGURO</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131472523</v>
+        <v>131491951</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -532,10 +540,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="1">
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="G2" s="1">
-        <v>45712</v>
+        <v>45710</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -567,10 +575,13 @@
       <c r="Q2">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131479510</v>
+        <v>123058958</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -585,10 +596,10 @@
         <v>1211</v>
       </c>
       <c r="F3" s="1">
-        <v>45709</v>
+        <v>44993</v>
       </c>
       <c r="G3" s="1">
-        <v>45709</v>
+        <v>44995</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -597,7 +608,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -620,10 +631,13 @@
       <c r="Q3">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131483827</v>
+        <v>129379286</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -638,10 +652,10 @@
         <v>1211</v>
       </c>
       <c r="F4" s="1">
-        <v>45709</v>
+        <v>45553</v>
       </c>
       <c r="G4" s="1">
-        <v>45709</v>
+        <v>45554</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -650,7 +664,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -673,10 +687,13 @@
       <c r="Q4">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131485309</v>
+        <v>131429178</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -688,13 +705,13 @@
         <v/>
       </c>
       <c r="E5">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F5" s="1">
-        <v>45709</v>
+        <v>45706</v>
       </c>
       <c r="G5" s="1">
-        <v>45709</v>
+        <v>45707</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -703,7 +720,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>1735</v>
+        <v>8021</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -726,10 +743,13 @@
       <c r="Q5">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131486391</v>
+        <v>131520154</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -741,13 +761,13 @@
         <v/>
       </c>
       <c r="E6">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F6" s="1">
-        <v>45709</v>
+        <v>45713</v>
       </c>
       <c r="G6" s="1">
-        <v>45709</v>
+        <v>45713</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -756,7 +776,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>718</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -779,853 +799,11 @@
       <c r="Q6">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>131487403</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
-        <v>1212</v>
-      </c>
-      <c r="F7" s="1">
-        <v>45709</v>
-      </c>
-      <c r="G7" s="1">
-        <v>45709</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7">
-        <v>42</v>
-      </c>
-      <c r="J7">
-        <v>1735</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>123058958</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>1211</v>
-      </c>
-      <c r="F8" s="1">
-        <v>44993</v>
-      </c>
-      <c r="G8" s="1">
-        <v>44995</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8">
-        <v>42</v>
-      </c>
-      <c r="J8">
-        <v>8001</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>129379286</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>1211</v>
-      </c>
-      <c r="F9" s="1">
-        <v>45553</v>
-      </c>
-      <c r="G9" s="1">
-        <v>45554</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9">
-        <v>42</v>
-      </c>
-      <c r="J9">
-        <v>8021</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>131429178</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>1213</v>
-      </c>
-      <c r="F10" s="1">
-        <v>45706</v>
-      </c>
-      <c r="G10" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10">
-        <v>42</v>
-      </c>
-      <c r="J10">
-        <v>8021</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>131494490</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
-        <v>2013</v>
-      </c>
-      <c r="F11" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G11" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11">
-        <v>42</v>
-      </c>
-      <c r="J11">
-        <v>718</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>131495307</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>2013</v>
-      </c>
-      <c r="F12" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G12" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12">
-        <v>42</v>
-      </c>
-      <c r="J12">
-        <v>718</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>131495734</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
-        <v>2013</v>
-      </c>
-      <c r="F13" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G13" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13">
-        <v>42</v>
-      </c>
-      <c r="J13">
-        <v>718</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>131496202</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14">
-        <v>2013</v>
-      </c>
-      <c r="F14" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G14" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14">
-        <v>42</v>
-      </c>
-      <c r="J14">
-        <v>718</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>131496781</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15">
-        <v>2013</v>
-      </c>
-      <c r="F15" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G15" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15">
-        <v>42</v>
-      </c>
-      <c r="J15">
-        <v>718</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>131496807</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16">
-        <v>2013</v>
-      </c>
-      <c r="F16" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G16" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16">
-        <v>42</v>
-      </c>
-      <c r="J16">
-        <v>718</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>131496854</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17">
-        <v>2013</v>
-      </c>
-      <c r="F17" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G17" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17">
-        <v>42</v>
-      </c>
-      <c r="J17">
-        <v>718</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>131496932</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18">
-        <v>2013</v>
-      </c>
-      <c r="F18" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G18" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18">
-        <v>42</v>
-      </c>
-      <c r="J18">
-        <v>718</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>131496957</v>
-      </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19">
-        <v>2013</v>
-      </c>
-      <c r="F19" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G19" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19">
-        <v>42</v>
-      </c>
-      <c r="J19">
-        <v>718</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>131497359</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20">
-        <v>2013</v>
-      </c>
-      <c r="F20" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G20" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20">
-        <v>42</v>
-      </c>
-      <c r="J20">
-        <v>718</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>131497678</v>
-      </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21">
-        <v>2013</v>
-      </c>
-      <c r="F21" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G21" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21">
-        <v>42</v>
-      </c>
-      <c r="J21">
-        <v>718</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>131501776</v>
-      </c>
-      <c r="B22" t="str">
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22">
-        <v>2013</v>
-      </c>
-      <c r="F22" s="1">
-        <v>45712</v>
-      </c>
-      <c r="G22" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22">
-        <v>42</v>
-      </c>
-      <c r="J22">
-        <v>718</v>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>61</v>
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Renovação Externa</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD8F8E0-D5F5-4309-B84B-76982ACEF78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D57BF5-EAE6-4F1A-9F13-F4F8B59F464D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,27 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$18</definedName>
+    <definedName name="Fiel">Fiel!$A$1:$S$34</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="24">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -93,7 +106,10 @@
     <t/>
   </si>
   <si>
-    <t/>
+    <t>TIPO_SEGURO_TL</t>
+  </si>
+  <si>
+    <t>TIPO_SEGURO</t>
   </si>
 </sst>
 </file>
@@ -439,123 +455,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1048576"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S147"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="16" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" t="str">
-        <v>NR_PROPOSTA</v>
-      </c>
-      <c r="B1" t="str">
-        <v>CPF_CNPJ</v>
-      </c>
-      <c r="C1" t="str">
-        <v>NOME_SEGURADO</v>
-      </c>
-      <c r="D1" t="str">
-        <v>PREMIO_TOTAL</v>
-      </c>
-      <c r="E1" t="str">
-        <v>RAMO</v>
-      </c>
-      <c r="F1" t="str">
-        <v>DT_PROPOSTA</v>
-      </c>
-      <c r="G1" t="str">
-        <v>DT_ULTIMA_ALTERACAO</v>
-      </c>
-      <c r="H1" t="str">
-        <v>COD_FILIAL</v>
-      </c>
-      <c r="I1" t="str">
-        <v>COD_CORRETOR</v>
-      </c>
-      <c r="J1" t="str">
-        <v>BLOQUEIO_1</v>
-      </c>
-      <c r="K1" t="str">
-        <v>NIVEL_BLOQUEIO_1</v>
-      </c>
-      <c r="L1" t="str">
-        <v>BLOQUEIO_2</v>
-      </c>
-      <c r="M1" t="str">
-        <v>NIVEL_BLOQUEIO_2</v>
-      </c>
-      <c r="N1" t="str">
-        <v>BLOQUEIO_3</v>
-      </c>
-      <c r="O1" t="str">
-        <v>NIVEL_BLOQUEIO_3</v>
-      </c>
-      <c r="P1" t="str">
-        <v>BLOQUEIO_4</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>NR_OPERATIVA</v>
-      </c>
-      <c r="R1" t="str">
-        <v>TIPO_SEGURO_TL</v>
-      </c>
-      <c r="S1" t="str">
-        <v>TIPO_SEGURO</v>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131507612</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
+        <v>131468218</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
       </c>
       <c r="E2">
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G2" s="1">
-        <v>45714</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8013</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
+        <v>8004</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -575,34 +588,34 @@
       <c r="Q2">
         <v>61</v>
       </c>
-      <c r="S2" t="str">
-        <v/>
+      <c r="S2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131495522</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+        <v>131514864</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
       </c>
       <c r="E3">
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G3" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -610,8 +623,8 @@
       <c r="J3">
         <v>8004</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
+      <c r="K3" t="s">
+        <v>21</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -631,43 +644,43 @@
       <c r="Q3">
         <v>61</v>
       </c>
-      <c r="S3" t="str">
-        <v/>
+      <c r="S3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131496459</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
+        <v>131520470</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
       <c r="E4">
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G4" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -687,43 +700,43 @@
       <c r="Q4">
         <v>61</v>
       </c>
-      <c r="S4" t="str">
-        <v/>
+      <c r="S4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131497515</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+        <v>131520474</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
       </c>
       <c r="E5">
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G5" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8004</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -743,43 +756,43 @@
       <c r="Q5">
         <v>61</v>
       </c>
-      <c r="S5" t="str">
-        <v/>
+      <c r="S5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131497917</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+        <v>131520482</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
       </c>
       <c r="E6">
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G6" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8004</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -799,43 +812,43 @@
       <c r="Q6">
         <v>61</v>
       </c>
-      <c r="S6" t="str">
-        <v/>
+      <c r="S6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131498622</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+        <v>131520484</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
       </c>
       <c r="E7">
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G7" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8004</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -855,43 +868,43 @@
       <c r="Q7">
         <v>61</v>
       </c>
-      <c r="S7" t="str">
-        <v/>
+      <c r="S7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131499743</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
+        <v>131520487</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
       </c>
       <c r="E8">
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G8" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8004</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -911,43 +924,43 @@
       <c r="Q8">
         <v>61</v>
       </c>
-      <c r="S8" t="str">
-        <v/>
+      <c r="S8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131500590</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+        <v>131520500</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
       </c>
       <c r="E9">
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G9" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8004</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -967,43 +980,43 @@
       <c r="Q9">
         <v>61</v>
       </c>
-      <c r="S9" t="str">
-        <v/>
+      <c r="S9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131503604</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
+        <v>131520504</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
       </c>
       <c r="E10">
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G10" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8004</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1023,43 +1036,43 @@
       <c r="Q10">
         <v>61</v>
       </c>
-      <c r="S10" t="str">
-        <v/>
+      <c r="S10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131504064</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
+        <v>131520507</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
       </c>
       <c r="E11">
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G11" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8004</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1079,43 +1092,43 @@
       <c r="Q11">
         <v>61</v>
       </c>
-      <c r="S11" t="str">
-        <v/>
+      <c r="S11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131506844</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
+        <v>131520509</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
       </c>
       <c r="E12">
         <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G12" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8004</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1135,43 +1148,43 @@
       <c r="Q12">
         <v>61</v>
       </c>
-      <c r="S12" t="str">
-        <v/>
+      <c r="S12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>123058958</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v/>
+        <v>131520511</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>44993</v>
+        <v>45713</v>
       </c>
       <c r="G13" s="1">
-        <v>44995</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8001</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1191,43 +1204,43 @@
       <c r="Q13">
         <v>61</v>
       </c>
-      <c r="S13" t="str">
-        <v/>
+      <c r="S13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131429178</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
+        <v>131520532</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>1213</v>
+        <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45706</v>
+        <v>45713</v>
       </c>
       <c r="G14" s="1">
-        <v>45707</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
       </c>
       <c r="I14">
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8021</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1247,43 +1260,43 @@
       <c r="Q14">
         <v>61</v>
       </c>
-      <c r="S14" t="str">
-        <v/>
+      <c r="S14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>128179077</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
+        <v>131520535</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G15" s="1">
-        <v>45714</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
       </c>
       <c r="I15">
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8001</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
+        <v>8013</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1303,43 +1316,43 @@
       <c r="Q15">
         <v>61</v>
       </c>
-      <c r="S15" t="str">
-        <v/>
+      <c r="S15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>129963995</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
+        <v>131521418</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
       </c>
       <c r="E16">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G16" s="1">
-        <v>45714</v>
-      </c>
-      <c r="H16" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
       </c>
       <c r="I16">
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8001</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
+        <v>8004</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1359,43 +1372,43 @@
       <c r="Q16">
         <v>61</v>
       </c>
-      <c r="S16" t="str">
-        <v/>
+      <c r="S16" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>129963995</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+        <v>131523349</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="G17" s="1">
-        <v>45714</v>
-      </c>
-      <c r="H17" t="str">
-        <v/>
+        <v>45713</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
       </c>
       <c r="I17">
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8001</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
+        <v>8004</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1415,64 +1428,5254 @@
       <c r="Q17">
         <v>61</v>
       </c>
-      <c r="S17" t="str">
-        <v/>
+      <c r="S17" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131473549</v>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18" t="str">
-        <v/>
+        <v>131527810</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
       </c>
       <c r="E18">
+        <v>601</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>8013</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>61</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>131513940</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19">
+        <v>601</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>42</v>
+      </c>
+      <c r="J19">
+        <v>8004</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>61</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>131517261</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20">
+        <v>601</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20">
+        <v>42</v>
+      </c>
+      <c r="J20">
+        <v>8004</v>
+      </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>61</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>131517327</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21">
+        <v>601</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21">
+        <v>42</v>
+      </c>
+      <c r="J21">
+        <v>8004</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>61</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>131519992</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>601</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22">
+        <v>42</v>
+      </c>
+      <c r="J22">
+        <v>8004</v>
+      </c>
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>61</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>131523757</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23">
+        <v>601</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>8004</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>61</v>
+      </c>
+      <c r="S23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>131525109</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24">
+        <v>601</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24">
+        <v>42</v>
+      </c>
+      <c r="J24">
+        <v>8004</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>61</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>131525490</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25">
+        <v>601</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25">
+        <v>42</v>
+      </c>
+      <c r="J25">
+        <v>8004</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>61</v>
+      </c>
+      <c r="S25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>131527277</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>601</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>8004</v>
+      </c>
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>61</v>
+      </c>
+      <c r="S26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>131527757</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27">
+        <v>601</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G27" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H27" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27">
+        <v>42</v>
+      </c>
+      <c r="J27">
+        <v>8004</v>
+      </c>
+      <c r="K27" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>61</v>
+      </c>
+      <c r="S27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>131501685</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28">
         <v>1211</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F28" s="1">
+        <v>45712</v>
+      </c>
+      <c r="G28" s="1">
+        <v>45712</v>
+      </c>
+      <c r="H28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28">
+        <v>42</v>
+      </c>
+      <c r="J28">
+        <v>1735</v>
+      </c>
+      <c r="K28" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+      <c r="S28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>131503833</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45712</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45712</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29">
+        <v>42</v>
+      </c>
+      <c r="J29">
+        <v>1735</v>
+      </c>
+      <c r="K29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>61</v>
+      </c>
+      <c r="S29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>131507656</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30">
+        <v>1211</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45712</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45712</v>
+      </c>
+      <c r="H30" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>1735</v>
+      </c>
+      <c r="K30" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>61</v>
+      </c>
+      <c r="S30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>131511558</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45712</v>
+      </c>
+      <c r="G31" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H31" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>1735</v>
+      </c>
+      <c r="K31" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>61</v>
+      </c>
+      <c r="S31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>123058958</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="1">
+        <v>44993</v>
+      </c>
+      <c r="G32" s="1">
+        <v>44995</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>8001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+      <c r="S32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>127027149</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G33" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>8001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+      <c r="S33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>127027149</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>8001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+      <c r="S34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>131324718</v>
+      </c>
+      <c r="E35">
+        <v>601</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45699</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45699</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>8013</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>131324724</v>
+      </c>
+      <c r="E36">
+        <v>601</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45699</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45699</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>8013</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>131402354</v>
+      </c>
+      <c r="E37">
+        <v>601</v>
+      </c>
+      <c r="F37" s="2">
         <v>45709</v>
       </c>
-      <c r="G18" s="1">
-        <v>45712</v>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18">
-        <v>42</v>
-      </c>
-      <c r="J18">
-        <v>715</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>61</v>
-      </c>
-      <c r="S18" t="str">
-        <v/>
+      <c r="G37" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>8013</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>131402846</v>
+      </c>
+      <c r="E38">
+        <v>601</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>8013</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>131404142</v>
+      </c>
+      <c r="E39">
+        <v>601</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8013</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>131404740</v>
+      </c>
+      <c r="E40">
+        <v>601</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8013</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>131404984</v>
+      </c>
+      <c r="E41">
+        <v>601</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8013</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>131405002</v>
+      </c>
+      <c r="E42">
+        <v>601</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8013</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>131405237</v>
+      </c>
+      <c r="E43">
+        <v>601</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8013</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>131407311</v>
+      </c>
+      <c r="E44">
+        <v>601</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8013</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>131413436</v>
+      </c>
+      <c r="E45">
+        <v>601</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8013</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>131413589</v>
+      </c>
+      <c r="E46">
+        <v>601</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8013</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>131414333</v>
+      </c>
+      <c r="E47">
+        <v>601</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45705</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8013</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>131414364</v>
+      </c>
+      <c r="E48">
+        <v>601</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45705</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45705</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>1117</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>131417640</v>
+      </c>
+      <c r="E49">
+        <v>601</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8013</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>131417816</v>
+      </c>
+      <c r="E50">
+        <v>601</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8013</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>131419440</v>
+      </c>
+      <c r="E51">
+        <v>601</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8013</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>131419895</v>
+      </c>
+      <c r="E52">
+        <v>601</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8013</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>131420239</v>
+      </c>
+      <c r="E53">
+        <v>601</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8013</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>131420756</v>
+      </c>
+      <c r="E54">
+        <v>601</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8013</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>131421000</v>
+      </c>
+      <c r="E55">
+        <v>601</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45706</v>
+      </c>
+      <c r="G55" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8013</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>131421443</v>
+      </c>
+      <c r="E56">
+        <v>601</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8013</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>131422194</v>
+      </c>
+      <c r="E57">
+        <v>601</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8013</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>131422492</v>
+      </c>
+      <c r="E58">
+        <v>601</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8013</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>131422844</v>
+      </c>
+      <c r="E59">
+        <v>601</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8013</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>131426170</v>
+      </c>
+      <c r="E60">
+        <v>601</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8013</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>131427054</v>
+      </c>
+      <c r="E61">
+        <v>601</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8013</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>131428053</v>
+      </c>
+      <c r="E62">
+        <v>601</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8013</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>131428989</v>
+      </c>
+      <c r="E63">
+        <v>601</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8013</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>131429021</v>
+      </c>
+      <c r="E64">
+        <v>601</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8013</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>131429175</v>
+      </c>
+      <c r="E65">
+        <v>601</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8013</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>131429218</v>
+      </c>
+      <c r="E66">
+        <v>601</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8013</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>131429564</v>
+      </c>
+      <c r="E67">
+        <v>601</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8013</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>131431380</v>
+      </c>
+      <c r="E68">
+        <v>601</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8013</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>131432545</v>
+      </c>
+      <c r="E69">
+        <v>601</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8013</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>131433227</v>
+      </c>
+      <c r="E70">
+        <v>601</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8013</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>131433751</v>
+      </c>
+      <c r="E71">
+        <v>601</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8004</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>131434702</v>
+      </c>
+      <c r="E72">
+        <v>601</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8013</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>131434853</v>
+      </c>
+      <c r="E73">
+        <v>601</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8013</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>131434968</v>
+      </c>
+      <c r="E74">
+        <v>601</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8013</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>131434999</v>
+      </c>
+      <c r="E75">
+        <v>601</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8013</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>131435018</v>
+      </c>
+      <c r="E76">
+        <v>601</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45709</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45706</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8013</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>131513940</v>
+      </c>
+      <c r="E77">
+        <v>601</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8004</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>131514864</v>
+      </c>
+      <c r="E78">
+        <v>601</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8004</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>131517261</v>
+      </c>
+      <c r="E79">
+        <v>601</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8004</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>131517327</v>
+      </c>
+      <c r="E80">
+        <v>601</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8004</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>131519992</v>
+      </c>
+      <c r="E81">
+        <v>601</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8004</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>131520470</v>
+      </c>
+      <c r="E82">
+        <v>601</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8013</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>131520474</v>
+      </c>
+      <c r="E83">
+        <v>601</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8013</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>131520482</v>
+      </c>
+      <c r="E84">
+        <v>601</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8013</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>131520484</v>
+      </c>
+      <c r="E85">
+        <v>601</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8013</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>131520487</v>
+      </c>
+      <c r="E86">
+        <v>601</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8013</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>131520500</v>
+      </c>
+      <c r="E87">
+        <v>601</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8013</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>131520504</v>
+      </c>
+      <c r="E88">
+        <v>601</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8013</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>131520507</v>
+      </c>
+      <c r="E89">
+        <v>601</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8013</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>131520509</v>
+      </c>
+      <c r="E90">
+        <v>601</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8013</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>131520511</v>
+      </c>
+      <c r="E91">
+        <v>601</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8013</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>131520532</v>
+      </c>
+      <c r="E92">
+        <v>601</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8013</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>131520535</v>
+      </c>
+      <c r="E93">
+        <v>601</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8013</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>131521418</v>
+      </c>
+      <c r="E94">
+        <v>601</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8004</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>131523349</v>
+      </c>
+      <c r="E95">
+        <v>601</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8004</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>131523757</v>
+      </c>
+      <c r="E96">
+        <v>601</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8004</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>131525109</v>
+      </c>
+      <c r="E97">
+        <v>601</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8004</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>131525490</v>
+      </c>
+      <c r="E98">
+        <v>601</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8004</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>131527277</v>
+      </c>
+      <c r="E99">
+        <v>601</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8004</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>131527757</v>
+      </c>
+      <c r="E100">
+        <v>601</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8004</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>131527810</v>
+      </c>
+      <c r="E101">
+        <v>601</v>
+      </c>
+      <c r="F101" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G101" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8013</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>131530679</v>
+      </c>
+      <c r="E102">
+        <v>601</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45713</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45713</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8003</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>131532819</v>
+      </c>
+      <c r="E103">
+        <v>601</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G103" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8013</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>131532823</v>
+      </c>
+      <c r="E104">
+        <v>601</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G104" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8013</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>131532961</v>
+      </c>
+      <c r="E105">
+        <v>601</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8004</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>131534847</v>
+      </c>
+      <c r="E106">
+        <v>601</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G106" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8013</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>131535170</v>
+      </c>
+      <c r="E107">
+        <v>601</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G107" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8004</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>131535827</v>
+      </c>
+      <c r="E108">
+        <v>601</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G108" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8004</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>131536507</v>
+      </c>
+      <c r="E109">
+        <v>601</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G109" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8004</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>131540273</v>
+      </c>
+      <c r="E110">
+        <v>601</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G110" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8004</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>131541611</v>
+      </c>
+      <c r="E111">
+        <v>601</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G111" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8004</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>131543517</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G112" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8004</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>131544585</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G113" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8004</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>131545482</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G114" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8004</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>131547800</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G115" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8004</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>131548148</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45714</v>
+      </c>
+      <c r="G116" s="2">
+        <v>45714</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8004</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>131550242</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G117" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8004</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>131550606</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G118" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8004</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>131550732</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G119" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8004</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>131550777</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G120" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8004</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>131550939</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8004</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>131551193</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G122" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8013</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>131552352</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G123" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8004</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>131553617</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8004</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>131553798</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8004</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>131555936</v>
+      </c>
+      <c r="E126">
+        <v>601</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8004</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>131556656</v>
+      </c>
+      <c r="E127">
+        <v>601</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8004</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>131557349</v>
+      </c>
+      <c r="E128">
+        <v>601</v>
+      </c>
+      <c r="F128" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8004</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>131558272</v>
+      </c>
+      <c r="E129">
+        <v>601</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8004</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>131559314</v>
+      </c>
+      <c r="E130">
+        <v>601</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8004</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>131563378</v>
+      </c>
+      <c r="E131">
+        <v>601</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G131" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8004</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131563794</v>
+      </c>
+      <c r="E132">
+        <v>601</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8004</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>131564125</v>
+      </c>
+      <c r="E133">
+        <v>601</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G133" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8004</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>131564816</v>
+      </c>
+      <c r="E134">
+        <v>601</v>
+      </c>
+      <c r="F134" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G134" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8004</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>131565591</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8004</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>131565736</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G136" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8004</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>131565948</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8004</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>131566072</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8004</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>131566769</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>131567550</v>
+      </c>
+      <c r="E140">
+        <v>601</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G140" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8004</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>131567612</v>
+      </c>
+      <c r="E141">
+        <v>601</v>
+      </c>
+      <c r="F141" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8004</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>131567814</v>
+      </c>
+      <c r="E142">
+        <v>601</v>
+      </c>
+      <c r="F142" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G142" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8013</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>131567817</v>
+      </c>
+      <c r="E143">
+        <v>601</v>
+      </c>
+      <c r="F143" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G143" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8013</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>131567880</v>
+      </c>
+      <c r="E144">
+        <v>601</v>
+      </c>
+      <c r="F144" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G144" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8013</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>131568383</v>
+      </c>
+      <c r="E145">
+        <v>601</v>
+      </c>
+      <c r="F145" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G145" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8004</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>131568949</v>
+      </c>
+      <c r="E146">
+        <v>601</v>
+      </c>
+      <c r="F146" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G146" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8004</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>131569857</v>
+      </c>
+      <c r="E147">
+        <v>601</v>
+      </c>
+      <c r="F147" s="2">
+        <v>45715</v>
+      </c>
+      <c r="G147" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>8004</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">Fiel!$A$1:$S$34</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$115</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -110,6 +110,12 @@
   </si>
   <si>
     <t>TIPO_SEGURO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Renovação Externa</t>
   </si>
 </sst>
 </file>
@@ -455,24 +461,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S147"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="17" width="13" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="20" customWidth="1"/>
   </cols>
@@ -538,28 +547,28 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131468218</v>
+        <v>131571772</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G2" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -568,7 +577,7 @@
         <v>8004</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -589,33 +598,33 @@
         <v>61</v>
       </c>
       <c r="S2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131514864</v>
+        <v>131572926</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G3" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -624,7 +633,7 @@
         <v>8004</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -645,42 +654,42 @@
         <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131520470</v>
+        <v>131574582</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G4" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -701,42 +710,42 @@
         <v>61</v>
       </c>
       <c r="S4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131520474</v>
+        <v>131574597</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G5" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -757,42 +766,42 @@
         <v>61</v>
       </c>
       <c r="S5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131520482</v>
+        <v>131575207</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G6" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -813,33 +822,33 @@
         <v>61</v>
       </c>
       <c r="S6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131520484</v>
+        <v>131575486</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G7" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -848,7 +857,7 @@
         <v>8013</v>
       </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -869,33 +878,33 @@
         <v>61</v>
       </c>
       <c r="S7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131520487</v>
+        <v>131575489</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G8" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -904,7 +913,7 @@
         <v>8013</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -925,33 +934,33 @@
         <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131520500</v>
+        <v>131575494</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G9" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -960,7 +969,7 @@
         <v>8013</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -981,33 +990,33 @@
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131520504</v>
+        <v>131575499</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G10" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -1016,7 +1025,7 @@
         <v>8013</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1037,33 +1046,33 @@
         <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131520507</v>
+        <v>131575504</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G11" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -1072,7 +1081,7 @@
         <v>8013</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1093,33 +1102,33 @@
         <v>61</v>
       </c>
       <c r="S11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131520509</v>
+        <v>131576397</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12">
         <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G12" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1128,7 +1137,7 @@
         <v>8013</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1149,42 +1158,42 @@
         <v>61</v>
       </c>
       <c r="S12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131520511</v>
+        <v>131577151</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E13">
         <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G13" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1205,42 +1214,42 @@
         <v>61</v>
       </c>
       <c r="S13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131520532</v>
+        <v>131577469</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G14" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I14">
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1261,42 +1270,42 @@
         <v>61</v>
       </c>
       <c r="S14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131520535</v>
+        <v>131577492</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E15">
         <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G15" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I15">
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1317,33 +1326,33 @@
         <v>61</v>
       </c>
       <c r="S15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131521418</v>
+        <v>131577599</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E16">
         <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G16" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1352,7 +1361,7 @@
         <v>8004</v>
       </c>
       <c r="K16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1373,33 +1382,33 @@
         <v>61</v>
       </c>
       <c r="S16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131523349</v>
+        <v>131578018</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G17" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1408,7 +1417,7 @@
         <v>8004</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1429,42 +1438,42 @@
         <v>61</v>
       </c>
       <c r="S17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131527810</v>
+        <v>131578255</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G18" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I18">
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1485,33 +1494,33 @@
         <v>61</v>
       </c>
       <c r="S18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131513940</v>
+        <v>131580370</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>601</v>
       </c>
       <c r="F19" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G19" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1520,7 +1529,7 @@
         <v>8004</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1541,33 +1550,33 @@
         <v>61</v>
       </c>
       <c r="S19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131517261</v>
+        <v>131580669</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>601</v>
       </c>
       <c r="F20" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G20" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1576,7 +1585,7 @@
         <v>8004</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1597,33 +1606,33 @@
         <v>61</v>
       </c>
       <c r="S20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131517327</v>
+        <v>131581341</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>601</v>
       </c>
       <c r="F21" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G21" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1632,7 +1641,7 @@
         <v>8004</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1653,42 +1662,42 @@
         <v>61</v>
       </c>
       <c r="S21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131519992</v>
+        <v>131581632</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>601</v>
       </c>
       <c r="F22" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G22" s="1">
-        <v>45713</v>
+        <v>45717</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1709,33 +1718,33 @@
         <v>61</v>
       </c>
       <c r="S22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131523757</v>
+        <v>131581830</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>601</v>
       </c>
       <c r="F23" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G23" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1744,7 +1753,7 @@
         <v>8004</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1765,42 +1774,42 @@
         <v>61</v>
       </c>
       <c r="S23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>131525109</v>
+        <v>131582549</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E24">
         <v>601</v>
       </c>
       <c r="F24" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G24" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1821,42 +1830,42 @@
         <v>61</v>
       </c>
       <c r="S24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131525490</v>
+        <v>131582556</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>601</v>
       </c>
       <c r="F25" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G25" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1877,33 +1886,33 @@
         <v>61</v>
       </c>
       <c r="S25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>131527277</v>
+        <v>131582702</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>601</v>
       </c>
       <c r="F26" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G26" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1912,7 +1921,7 @@
         <v>8004</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1933,42 +1942,42 @@
         <v>61</v>
       </c>
       <c r="S26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>131527757</v>
+        <v>131582784</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>601</v>
       </c>
       <c r="F27" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G27" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1989,42 +1998,42 @@
         <v>61</v>
       </c>
       <c r="S27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131501685</v>
+        <v>131583038</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E28">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F28" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="G28" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2045,42 +2054,42 @@
         <v>61</v>
       </c>
       <c r="S28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>131503833</v>
+        <v>131583915</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E29">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F29" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="G29" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2101,42 +2110,42 @@
         <v>61</v>
       </c>
       <c r="S29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>131507656</v>
+        <v>131584442</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F30" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="G30" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2157,42 +2166,42 @@
         <v>61</v>
       </c>
       <c r="S30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>131511558</v>
+        <v>131585986</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E31">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F31" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="G31" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2213,42 +2222,42 @@
         <v>61</v>
       </c>
       <c r="S31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>123058958</v>
+        <v>131587477</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E32">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F32" s="1">
-        <v>44993</v>
+        <v>45716</v>
       </c>
       <c r="G32" s="1">
-        <v>44995</v>
+        <v>45716</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2269,42 +2278,42 @@
         <v>61</v>
       </c>
       <c r="S32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127027149</v>
+        <v>131587680</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E33">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F33" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G33" s="1">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2325,42 +2334,42 @@
         <v>61</v>
       </c>
       <c r="S33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127027149</v>
+        <v>131588318</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E34">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F34" s="1">
-        <v>45713</v>
+        <v>45716</v>
       </c>
       <c r="G34" s="1">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8001</v>
+        <v>1117</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2381,27 +2390,42 @@
         <v>61</v>
       </c>
       <c r="S34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>131324718</v>
+        <v>131592141</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
       </c>
       <c r="E35">
         <v>601</v>
       </c>
-      <c r="F35" s="2">
-        <v>45699</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45699</v>
+      <c r="F35" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2420,26 +2444,44 @@
       </c>
       <c r="Q35">
         <v>61</v>
+      </c>
+      <c r="S35" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>131324724</v>
+        <v>131592382</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
       </c>
       <c r="E36">
         <v>601</v>
       </c>
-      <c r="F36" s="2">
-        <v>45699</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45699</v>
+      <c r="F36" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G36" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K36" t="s">
+        <v>24</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2458,26 +2500,44 @@
       </c>
       <c r="Q36">
         <v>61</v>
+      </c>
+      <c r="S36" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>131402354</v>
+        <v>131592819</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
       </c>
       <c r="E37">
         <v>601</v>
       </c>
-      <c r="F37" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45705</v>
+      <c r="F37" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G37" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2496,26 +2556,44 @@
       </c>
       <c r="Q37">
         <v>61</v>
+      </c>
+      <c r="S37" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>131402846</v>
+        <v>131598370</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
       </c>
       <c r="E38">
         <v>601</v>
       </c>
-      <c r="F38" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45705</v>
+      <c r="F38" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G38" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2534,20 +2612,35 @@
       </c>
       <c r="Q38">
         <v>61</v>
+      </c>
+      <c r="S38" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>131404142</v>
+        <v>131564479</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
       </c>
       <c r="E39">
-        <v>601</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45705</v>
+        <v>609</v>
+      </c>
+      <c r="F39" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G39" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
       </c>
       <c r="I39">
         <v>42</v>
@@ -2555,6 +2648,9 @@
       <c r="J39">
         <v>8013</v>
       </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
       <c r="L39">
         <v>0</v>
       </c>
@@ -2572,20 +2668,35 @@
       </c>
       <c r="Q39">
         <v>61</v>
+      </c>
+      <c r="S39" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>131404740</v>
+        <v>131567420</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
       </c>
       <c r="E40">
-        <v>601</v>
-      </c>
-      <c r="F40" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45705</v>
+        <v>609</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G40" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
       </c>
       <c r="I40">
         <v>42</v>
@@ -2593,6 +2704,9 @@
       <c r="J40">
         <v>8013</v>
       </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
       <c r="L40">
         <v>0</v>
       </c>
@@ -2610,26 +2724,44 @@
       </c>
       <c r="Q40">
         <v>61</v>
+      </c>
+      <c r="S40" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>131404984</v>
+        <v>131302795</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
       </c>
       <c r="E41">
         <v>601</v>
       </c>
-      <c r="F41" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45705</v>
+      <c r="F41" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G41" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2648,26 +2780,44 @@
       </c>
       <c r="Q41">
         <v>61</v>
+      </c>
+      <c r="S41" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>131405002</v>
+        <v>131575500</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>24</v>
       </c>
       <c r="E42">
         <v>601</v>
       </c>
-      <c r="F42" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G42" s="2">
-        <v>45705</v>
+      <c r="F42" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G42" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2686,26 +2836,44 @@
       </c>
       <c r="Q42">
         <v>61</v>
+      </c>
+      <c r="S42" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>131405237</v>
+        <v>131577727</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
       </c>
       <c r="E43">
         <v>601</v>
       </c>
-      <c r="F43" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G43" s="2">
-        <v>45705</v>
+      <c r="F43" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G43" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2724,26 +2892,44 @@
       </c>
       <c r="Q43">
         <v>61</v>
+      </c>
+      <c r="S43" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>131407311</v>
+        <v>131581039</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
       </c>
       <c r="E44">
         <v>601</v>
       </c>
-      <c r="F44" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G44" s="2">
-        <v>45705</v>
+      <c r="F44" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G44" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2762,26 +2948,44 @@
       </c>
       <c r="Q44">
         <v>61</v>
+      </c>
+      <c r="S44" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>131413436</v>
+        <v>131584749</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
       </c>
       <c r="E45">
         <v>601</v>
       </c>
-      <c r="F45" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G45" s="2">
-        <v>45705</v>
+      <c r="F45" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G45" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2800,26 +3004,44 @@
       </c>
       <c r="Q45">
         <v>61</v>
+      </c>
+      <c r="S45" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>131413589</v>
+        <v>131586690</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
       </c>
       <c r="E46">
         <v>601</v>
       </c>
-      <c r="F46" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G46" s="2">
-        <v>45705</v>
+      <c r="F46" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G46" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2838,26 +3060,44 @@
       </c>
       <c r="Q46">
         <v>61</v>
+      </c>
+      <c r="S46" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>131414333</v>
+        <v>131587777</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
       </c>
       <c r="E47">
         <v>601</v>
       </c>
-      <c r="F47" s="2">
-        <v>45705</v>
-      </c>
-      <c r="G47" s="2">
-        <v>45705</v>
+      <c r="F47" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G47" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8013</v>
+        <v>8004</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2876,26 +3116,44 @@
       </c>
       <c r="Q47">
         <v>61</v>
+      </c>
+      <c r="S47" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>131414364</v>
+        <v>131515618</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
       </c>
       <c r="E48">
-        <v>601</v>
-      </c>
-      <c r="F48" s="2">
-        <v>45705</v>
-      </c>
-      <c r="G48" s="2">
-        <v>45705</v>
+        <v>1211</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G48" s="1">
+        <v>45714</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>1117</v>
+        <v>1735</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2915,25 +3173,43 @@
       <c r="Q48">
         <v>61</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>131417640</v>
+        <v>131517089</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
       </c>
       <c r="E49">
-        <v>601</v>
-      </c>
-      <c r="F49" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G49" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G49" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2953,25 +3229,43 @@
       <c r="Q49">
         <v>61</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>131417816</v>
+        <v>131520900</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
       </c>
       <c r="E50">
-        <v>601</v>
-      </c>
-      <c r="F50" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2991,25 +3285,43 @@
       <c r="Q50">
         <v>61</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>131419440</v>
+        <v>131526021</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
       </c>
       <c r="E51">
-        <v>601</v>
-      </c>
-      <c r="F51" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G51" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -3029,25 +3341,43 @@
       <c r="Q51">
         <v>61</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>131419895</v>
+        <v>131527120</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
       </c>
       <c r="E52">
-        <v>601</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G52" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -3067,25 +3397,43 @@
       <c r="Q52">
         <v>61</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>131420239</v>
+        <v>131529283</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
       </c>
       <c r="E53">
-        <v>601</v>
-      </c>
-      <c r="F53" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G53" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F53" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G53" s="1">
+        <v>45713</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -3105,25 +3453,43 @@
       <c r="Q53">
         <v>61</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>131420756</v>
+        <v>131533651</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
       </c>
       <c r="E54">
-        <v>601</v>
-      </c>
-      <c r="F54" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G54" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G54" s="1">
+        <v>45714</v>
+      </c>
+      <c r="H54" t="s">
+        <v>24</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -3143,25 +3509,43 @@
       <c r="Q54">
         <v>61</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>131421000</v>
+        <v>131535137</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
       </c>
       <c r="E55">
-        <v>601</v>
-      </c>
-      <c r="F55" s="2">
-        <v>45706</v>
-      </c>
-      <c r="G55" s="2">
-        <v>45706</v>
+        <v>1212</v>
+      </c>
+      <c r="F55" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G55" s="1">
+        <v>45714</v>
+      </c>
+      <c r="H55" t="s">
+        <v>24</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -3181,25 +3565,43 @@
       <c r="Q55">
         <v>61</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>131421443</v>
+        <v>131535937</v>
+      </c>
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
       </c>
       <c r="E56">
-        <v>601</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G56" s="1">
+        <v>45714</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K56" t="s">
+        <v>24</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -3219,25 +3621,43 @@
       <c r="Q56">
         <v>61</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>131422194</v>
+        <v>131537838</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
       </c>
       <c r="E57">
-        <v>601</v>
-      </c>
-      <c r="F57" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G57" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F57" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G57" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K57" t="s">
+        <v>24</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -3257,25 +3677,43 @@
       <c r="Q57">
         <v>61</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>131422492</v>
+        <v>131550747</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
       </c>
       <c r="E58">
-        <v>601</v>
-      </c>
-      <c r="F58" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F58" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G58" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -3295,25 +3733,43 @@
       <c r="Q58">
         <v>61</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>131422844</v>
+        <v>131554515</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
       </c>
       <c r="E59">
-        <v>601</v>
-      </c>
-      <c r="F59" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G59" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H59" t="s">
+        <v>24</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -3333,25 +3789,43 @@
       <c r="Q59">
         <v>61</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>131426170</v>
+        <v>131559641</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
       </c>
       <c r="E60">
-        <v>601</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45706</v>
+        <v>1212</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G60" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -3371,25 +3845,43 @@
       <c r="Q60">
         <v>61</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>131427054</v>
+        <v>131561795</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
       </c>
       <c r="E61">
-        <v>601</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G61" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
       </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -3409,25 +3901,43 @@
       <c r="Q61">
         <v>61</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>131428053</v>
+        <v>131565115</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
       </c>
       <c r="E62">
-        <v>601</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G62" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -3447,25 +3957,43 @@
       <c r="Q62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>131428989</v>
+        <v>131565739</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
       </c>
       <c r="E63">
-        <v>601</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G63" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -3485,25 +4013,43 @@
       <c r="Q63">
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>131429021</v>
+        <v>131567335</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
       </c>
       <c r="E64">
-        <v>601</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G64" s="1">
+        <v>45715</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
       </c>
       <c r="I64">
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8013</v>
+        <v>1735</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -3523,25 +4069,43 @@
       <c r="Q64">
         <v>61</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>131429175</v>
+        <v>123058958</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
       </c>
       <c r="E65">
-        <v>601</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F65" s="1">
+        <v>44993</v>
+      </c>
+      <c r="G65" s="1">
+        <v>44995</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
       </c>
       <c r="I65">
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3561,25 +4125,43 @@
       <c r="Q65">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>131429218</v>
+        <v>127157776</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
       </c>
       <c r="E66">
-        <v>601</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G66" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
       </c>
       <c r="I66">
         <v>42</v>
       </c>
       <c r="J66">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -3599,25 +4181,43 @@
       <c r="Q66">
         <v>61</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>131429564</v>
+        <v>127308970</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
       </c>
       <c r="E67">
-        <v>601</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
       </c>
       <c r="I67">
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -3637,25 +4237,43 @@
       <c r="Q67">
         <v>61</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>131431380</v>
+        <v>127348439</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
       </c>
       <c r="E68">
-        <v>601</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F68" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G68" s="1">
+        <v>45717</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
       </c>
       <c r="I68">
         <v>42</v>
       </c>
       <c r="J68">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -3675,25 +4293,43 @@
       <c r="Q68">
         <v>61</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>131432545</v>
+        <v>127434503</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
       </c>
       <c r="E69">
-        <v>601</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F69" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
       </c>
       <c r="I69">
         <v>42</v>
       </c>
       <c r="J69">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -3713,25 +4349,43 @@
       <c r="Q69">
         <v>61</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>131433227</v>
+        <v>127570439</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
       </c>
       <c r="E70">
-        <v>601</v>
-      </c>
-      <c r="F70" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G70" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
       </c>
       <c r="I70">
         <v>42</v>
       </c>
       <c r="J70">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -3751,25 +4405,43 @@
       <c r="Q70">
         <v>61</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>131433751</v>
+        <v>127604368</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
       </c>
       <c r="E71">
-        <v>601</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H71" t="s">
+        <v>24</v>
       </c>
       <c r="I71">
         <v>42</v>
       </c>
       <c r="J71">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -3789,25 +4461,43 @@
       <c r="Q71">
         <v>61</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>131434702</v>
+        <v>127841551</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
       </c>
       <c r="E72">
-        <v>601</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
       </c>
       <c r="I72">
         <v>42</v>
       </c>
       <c r="J72">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -3827,25 +4517,43 @@
       <c r="Q72">
         <v>61</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>131434853</v>
+        <v>127918954</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
       </c>
       <c r="E73">
-        <v>601</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G73" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
       </c>
       <c r="I73">
         <v>42</v>
       </c>
       <c r="J73">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -3865,25 +4573,43 @@
       <c r="Q73">
         <v>61</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>131434968</v>
+        <v>128450917</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
       </c>
       <c r="E74">
-        <v>601</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H74" t="s">
+        <v>24</v>
       </c>
       <c r="I74">
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>24</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -3903,25 +4629,43 @@
       <c r="Q74">
         <v>61</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>131434999</v>
+        <v>128616426</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
       </c>
       <c r="E75">
-        <v>601</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
       </c>
       <c r="I75">
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K75" t="s">
+        <v>24</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -3941,25 +4685,43 @@
       <c r="Q75">
         <v>61</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>131435018</v>
+        <v>128727840</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
       </c>
       <c r="E76">
-        <v>601</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45709</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45706</v>
+        <v>1211</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
       </c>
       <c r="I76">
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K76" t="s">
+        <v>24</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -3979,25 +4741,43 @@
       <c r="Q76">
         <v>61</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>131513940</v>
+        <v>129070442</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
       </c>
       <c r="E77">
-        <v>601</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45713</v>
+        <v>1212</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H77" t="s">
+        <v>24</v>
       </c>
       <c r="I77">
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -4017,25 +4797,43 @@
       <c r="Q77">
         <v>61</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>131514864</v>
+        <v>129096996</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
       </c>
       <c r="E78">
-        <v>601</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G78" s="1">
+        <v>45717</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
       </c>
       <c r="I78">
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -4055,25 +4853,43 @@
       <c r="Q78">
         <v>61</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>131517261</v>
+        <v>129238138</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
       </c>
       <c r="E79">
-        <v>601</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45713</v>
+        <v>1212</v>
+      </c>
+      <c r="F79" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G79" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
       </c>
       <c r="I79">
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K79" t="s">
+        <v>24</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -4093,25 +4909,43 @@
       <c r="Q79">
         <v>61</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>131517327</v>
+        <v>129333958</v>
+      </c>
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
       </c>
       <c r="E80">
-        <v>601</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H80" t="s">
+        <v>24</v>
       </c>
       <c r="I80">
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K80" t="s">
+        <v>24</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -4131,25 +4965,43 @@
       <c r="Q80">
         <v>61</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>131519992</v>
+        <v>129407604</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
       </c>
       <c r="E81">
-        <v>601</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G81" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
       </c>
       <c r="I81">
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K81" t="s">
+        <v>24</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -4169,25 +5021,43 @@
       <c r="Q81">
         <v>61</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>131520470</v>
+        <v>129474808</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" t="s">
+        <v>24</v>
       </c>
       <c r="E82">
-        <v>601</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
       </c>
       <c r="I82">
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>24</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -4207,25 +5077,43 @@
       <c r="Q82">
         <v>61</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>131520474</v>
+        <v>129911529</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
       </c>
       <c r="E83">
-        <v>601</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G83" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
       </c>
       <c r="I83">
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K83" t="s">
+        <v>24</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -4245,25 +5133,43 @@
       <c r="Q83">
         <v>61</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>131520482</v>
+        <v>129964054</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" t="s">
+        <v>24</v>
       </c>
       <c r="E84">
-        <v>601</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G84" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H84" t="s">
+        <v>24</v>
       </c>
       <c r="I84">
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K84" t="s">
+        <v>24</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -4283,25 +5189,43 @@
       <c r="Q84">
         <v>61</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>131520484</v>
+        <v>130018442</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
       </c>
       <c r="E85">
-        <v>601</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F85" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H85" t="s">
+        <v>24</v>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K85" t="s">
+        <v>24</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -4321,25 +5245,43 @@
       <c r="Q85">
         <v>61</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>131520487</v>
+        <v>130026181</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
       </c>
       <c r="E86">
-        <v>601</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F86" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G86" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K86" t="s">
+        <v>24</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -4359,25 +5301,43 @@
       <c r="Q86">
         <v>61</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>131520500</v>
+        <v>130046274</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
       </c>
       <c r="E87">
-        <v>601</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F87" s="1">
+        <v>45718</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45718</v>
+      </c>
+      <c r="H87" t="s">
+        <v>24</v>
       </c>
       <c r="I87">
         <v>42</v>
       </c>
       <c r="J87">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K87" t="s">
+        <v>24</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -4397,25 +5357,43 @@
       <c r="Q87">
         <v>61</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>131520504</v>
+        <v>130048648</v>
+      </c>
+      <c r="B88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
       </c>
       <c r="E88">
-        <v>601</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F88" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H88" t="s">
+        <v>24</v>
       </c>
       <c r="I88">
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K88" t="s">
+        <v>24</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -4435,25 +5413,43 @@
       <c r="Q88">
         <v>61</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>131520507</v>
+        <v>130056434</v>
+      </c>
+      <c r="B89" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
       </c>
       <c r="E89">
-        <v>601</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F89" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H89" t="s">
+        <v>24</v>
       </c>
       <c r="I89">
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K89" t="s">
+        <v>24</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -4473,25 +5469,43 @@
       <c r="Q89">
         <v>61</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>131520509</v>
+        <v>130279137</v>
+      </c>
+      <c r="B90" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
       </c>
       <c r="E90">
-        <v>601</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F90" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G90" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H90" t="s">
+        <v>24</v>
       </c>
       <c r="I90">
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K90" t="s">
+        <v>24</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -4511,25 +5525,43 @@
       <c r="Q90">
         <v>61</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>131520511</v>
+        <v>130279484</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
       </c>
       <c r="E91">
-        <v>601</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45713</v>
+        <v>1212</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G91" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H91" t="s">
+        <v>24</v>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K91" t="s">
+        <v>24</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -4549,25 +5581,43 @@
       <c r="Q91">
         <v>61</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>131520532</v>
+        <v>130300036</v>
+      </c>
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
       </c>
       <c r="E92">
-        <v>601</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G92" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
       </c>
       <c r="I92">
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K92" t="s">
+        <v>24</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -4587,25 +5637,43 @@
       <c r="Q92">
         <v>61</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>131520535</v>
+        <v>130373727</v>
+      </c>
+      <c r="B93" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
       </c>
       <c r="E93">
-        <v>601</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F93" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G93" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H93" t="s">
+        <v>24</v>
       </c>
       <c r="I93">
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K93" t="s">
+        <v>24</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -4625,25 +5693,43 @@
       <c r="Q93">
         <v>61</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>131521418</v>
+        <v>130417555</v>
+      </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
       </c>
       <c r="E94">
-        <v>601</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G94" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F94" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G94" s="1">
+        <v>45718</v>
+      </c>
+      <c r="H94" t="s">
+        <v>24</v>
       </c>
       <c r="I94">
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K94" t="s">
+        <v>24</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -4663,25 +5749,43 @@
       <c r="Q94">
         <v>61</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S94" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>131523349</v>
+        <v>130771428</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
       </c>
       <c r="E95">
-        <v>601</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G95" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F95" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G95" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H95" t="s">
+        <v>24</v>
       </c>
       <c r="I95">
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>24</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -4701,25 +5805,43 @@
       <c r="Q95">
         <v>61</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>131523757</v>
+        <v>130877397</v>
+      </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
       </c>
       <c r="E96">
-        <v>601</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G96" s="1">
+        <v>45717</v>
+      </c>
+      <c r="H96" t="s">
+        <v>24</v>
       </c>
       <c r="I96">
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K96" t="s">
+        <v>24</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -4739,25 +5861,43 @@
       <c r="Q96">
         <v>61</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>131525109</v>
+        <v>131159977</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
       </c>
       <c r="E97">
-        <v>601</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G97" s="2">
-        <v>45713</v>
+        <v>1212</v>
+      </c>
+      <c r="F97" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H97" t="s">
+        <v>24</v>
       </c>
       <c r="I97">
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K97" t="s">
+        <v>24</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -4777,25 +5917,43 @@
       <c r="Q97">
         <v>61</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>131525490</v>
+        <v>131176961</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
       </c>
       <c r="E98">
-        <v>601</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G98" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F98" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G98" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H98" t="s">
+        <v>24</v>
       </c>
       <c r="I98">
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K98" t="s">
+        <v>24</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -4815,25 +5973,43 @@
       <c r="Q98">
         <v>61</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S98" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>131527277</v>
+        <v>131247387</v>
+      </c>
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
       </c>
       <c r="E99">
-        <v>601</v>
-      </c>
-      <c r="F99" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G99" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F99" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G99" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H99" t="s">
+        <v>24</v>
       </c>
       <c r="I99">
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K99" t="s">
+        <v>24</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -4853,25 +6029,43 @@
       <c r="Q99">
         <v>61</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>131527757</v>
+        <v>131528916</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>24</v>
       </c>
       <c r="E100">
-        <v>601</v>
-      </c>
-      <c r="F100" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G100" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F100" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G100" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H100" t="s">
+        <v>24</v>
       </c>
       <c r="I100">
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K100" t="s">
+        <v>24</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -4891,25 +6085,43 @@
       <c r="Q100">
         <v>61</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>131527810</v>
+        <v>131552438</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
       </c>
       <c r="E101">
-        <v>601</v>
-      </c>
-      <c r="F101" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G101" s="2">
-        <v>45713</v>
+        <v>1212</v>
+      </c>
+      <c r="F101" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G101" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H101" t="s">
+        <v>24</v>
       </c>
       <c r="I101">
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8013</v>
+        <v>8001</v>
+      </c>
+      <c r="K101" t="s">
+        <v>24</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -4929,25 +6141,43 @@
       <c r="Q101">
         <v>61</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>131530679</v>
+        <v>127157776</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
       </c>
       <c r="E102">
-        <v>601</v>
-      </c>
-      <c r="F102" s="2">
-        <v>45713</v>
-      </c>
-      <c r="G102" s="2">
-        <v>45713</v>
+        <v>1211</v>
+      </c>
+      <c r="F102" s="1">
+        <v>45715</v>
+      </c>
+      <c r="G102" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H102" t="s">
+        <v>24</v>
       </c>
       <c r="I102">
         <v>42</v>
       </c>
       <c r="J102">
-        <v>8003</v>
+        <v>8001</v>
+      </c>
+      <c r="K102" t="s">
+        <v>24</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -4967,367 +6197,547 @@
       <c r="Q102">
         <v>61</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>131532819</v>
+        <v>127308970</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
       </c>
       <c r="E103">
-        <v>601</v>
-      </c>
-      <c r="F103" s="2">
+        <v>1211</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G103" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H103" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8001</v>
+      </c>
+      <c r="K103" t="s">
+        <v>24</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+      <c r="S103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>127434503</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104">
+        <v>1211</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G104" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H104" t="s">
+        <v>24</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8001</v>
+      </c>
+      <c r="K104" t="s">
+        <v>24</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+      <c r="S104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>128616426</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105">
+        <v>1211</v>
+      </c>
+      <c r="F105" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G105" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H105" t="s">
+        <v>24</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8001</v>
+      </c>
+      <c r="K105" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+      <c r="S105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>129474808</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106">
+        <v>1211</v>
+      </c>
+      <c r="F106" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G106" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H106" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8001</v>
+      </c>
+      <c r="K106" t="s">
+        <v>24</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+      <c r="S106" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>130026181</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107">
+        <v>1211</v>
+      </c>
+      <c r="F107" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G107" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H107" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8001</v>
+      </c>
+      <c r="K107" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+      <c r="S107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>130046274</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108">
+        <v>1211</v>
+      </c>
+      <c r="F108" s="1">
+        <v>45718</v>
+      </c>
+      <c r="G108" s="1">
+        <v>45718</v>
+      </c>
+      <c r="H108" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8001</v>
+      </c>
+      <c r="K108" t="s">
+        <v>24</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+      <c r="S108" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>130048648</v>
+      </c>
+      <c r="B109" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s">
+        <v>24</v>
+      </c>
+      <c r="D109" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109">
+        <v>1211</v>
+      </c>
+      <c r="F109" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G109" s="1">
+        <v>45719</v>
+      </c>
+      <c r="H109" t="s">
+        <v>24</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8001</v>
+      </c>
+      <c r="K109" t="s">
+        <v>24</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+      <c r="S109" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>130279484</v>
+      </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110">
+        <v>1212</v>
+      </c>
+      <c r="F110" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G110" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H110" t="s">
+        <v>24</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8001</v>
+      </c>
+      <c r="K110" t="s">
+        <v>24</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+      <c r="S110" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>130300036</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111">
+        <v>1211</v>
+      </c>
+      <c r="F111" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G111" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H111" t="s">
+        <v>24</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8001</v>
+      </c>
+      <c r="K111" t="s">
+        <v>24</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+      <c r="S111" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>130417555</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112">
+        <v>1211</v>
+      </c>
+      <c r="F112" s="1">
         <v>45714</v>
       </c>
-      <c r="G103" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I103">
-        <v>42</v>
-      </c>
-      <c r="J103">
-        <v>8013</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>131532823</v>
-      </c>
-      <c r="E104">
-        <v>601</v>
-      </c>
-      <c r="F104" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G104" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-      <c r="J104">
-        <v>8013</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>131532961</v>
-      </c>
-      <c r="E105">
-        <v>601</v>
-      </c>
-      <c r="F105" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G105" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I105">
-        <v>42</v>
-      </c>
-      <c r="J105">
-        <v>8004</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>131534847</v>
-      </c>
-      <c r="E106">
-        <v>601</v>
-      </c>
-      <c r="F106" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G106" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I106">
-        <v>42</v>
-      </c>
-      <c r="J106">
-        <v>8013</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>131535170</v>
-      </c>
-      <c r="E107">
-        <v>601</v>
-      </c>
-      <c r="F107" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G107" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I107">
-        <v>42</v>
-      </c>
-      <c r="J107">
-        <v>8004</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>131535827</v>
-      </c>
-      <c r="E108">
-        <v>601</v>
-      </c>
-      <c r="F108" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G108" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I108">
-        <v>42</v>
-      </c>
-      <c r="J108">
-        <v>8004</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>131536507</v>
-      </c>
-      <c r="E109">
-        <v>601</v>
-      </c>
-      <c r="F109" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G109" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I109">
-        <v>42</v>
-      </c>
-      <c r="J109">
-        <v>8004</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>131540273</v>
-      </c>
-      <c r="E110">
-        <v>601</v>
-      </c>
-      <c r="F110" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G110" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I110">
-        <v>42</v>
-      </c>
-      <c r="J110">
-        <v>8004</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>131541611</v>
-      </c>
-      <c r="E111">
-        <v>601</v>
-      </c>
-      <c r="F111" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G111" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I111">
-        <v>42</v>
-      </c>
-      <c r="J111">
-        <v>8004</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>131543517</v>
-      </c>
-      <c r="E112">
-        <v>601</v>
-      </c>
-      <c r="F112" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G112" s="2">
-        <v>45714</v>
+      <c r="G112" s="1">
+        <v>45718</v>
+      </c>
+      <c r="H112" t="s">
+        <v>24</v>
       </c>
       <c r="I112">
         <v>42</v>
       </c>
       <c r="J112">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K112" t="s">
+        <v>24</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -5347,25 +6757,43 @@
       <c r="Q112">
         <v>61</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S112" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>131544585</v>
+        <v>131176961</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" t="s">
+        <v>24</v>
       </c>
       <c r="E113">
-        <v>601</v>
-      </c>
-      <c r="F113" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G113" s="2">
-        <v>45714</v>
+        <v>1211</v>
+      </c>
+      <c r="F113" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G113" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H113" t="s">
+        <v>24</v>
       </c>
       <c r="I113">
         <v>42</v>
       </c>
       <c r="J113">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K113" t="s">
+        <v>24</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -5385,25 +6813,43 @@
       <c r="Q113">
         <v>61</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>131545482</v>
+        <v>131528916</v>
+      </c>
+      <c r="B114" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" t="s">
+        <v>24</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
       </c>
       <c r="E114">
-        <v>601</v>
-      </c>
-      <c r="F114" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G114" s="2">
-        <v>45714</v>
+        <v>1211</v>
+      </c>
+      <c r="F114" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G114" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H114" t="s">
+        <v>24</v>
       </c>
       <c r="I114">
         <v>42</v>
       </c>
       <c r="J114">
-        <v>8004</v>
+        <v>8001</v>
+      </c>
+      <c r="K114" t="s">
+        <v>24</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -5423,25 +6869,43 @@
       <c r="Q114">
         <v>61</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>131547800</v>
+        <v>131588707</v>
+      </c>
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
       </c>
       <c r="E115">
-        <v>601</v>
-      </c>
-      <c r="F115" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G115" s="2">
-        <v>45714</v>
+        <v>2013</v>
+      </c>
+      <c r="F115" s="1">
+        <v>45716</v>
+      </c>
+      <c r="G115" s="1">
+        <v>45716</v>
+      </c>
+      <c r="H115" t="s">
+        <v>24</v>
       </c>
       <c r="I115">
         <v>42</v>
       </c>
       <c r="J115">
-        <v>8004</v>
+        <v>718</v>
+      </c>
+      <c r="K115" t="s">
+        <v>24</v>
       </c>
       <c r="L115">
         <v>0</v>
@@ -5461,1221 +6925,11 @@
       <c r="Q115">
         <v>61</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>131548148</v>
-      </c>
-      <c r="E116">
-        <v>601</v>
-      </c>
-      <c r="F116" s="2">
-        <v>45714</v>
-      </c>
-      <c r="G116" s="2">
-        <v>45714</v>
-      </c>
-      <c r="I116">
-        <v>42</v>
-      </c>
-      <c r="J116">
-        <v>8004</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>131550242</v>
-      </c>
-      <c r="E117">
-        <v>601</v>
-      </c>
-      <c r="F117" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G117" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I117">
-        <v>42</v>
-      </c>
-      <c r="J117">
-        <v>8004</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>131550606</v>
-      </c>
-      <c r="E118">
-        <v>601</v>
-      </c>
-      <c r="F118" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G118" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I118">
-        <v>42</v>
-      </c>
-      <c r="J118">
-        <v>8004</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>131550732</v>
-      </c>
-      <c r="E119">
-        <v>601</v>
-      </c>
-      <c r="F119" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G119" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I119">
-        <v>42</v>
-      </c>
-      <c r="J119">
-        <v>8004</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>131550777</v>
-      </c>
-      <c r="E120">
-        <v>601</v>
-      </c>
-      <c r="F120" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G120" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I120">
-        <v>42</v>
-      </c>
-      <c r="J120">
-        <v>8004</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>131550939</v>
-      </c>
-      <c r="E121">
-        <v>601</v>
-      </c>
-      <c r="F121" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G121" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I121">
-        <v>42</v>
-      </c>
-      <c r="J121">
-        <v>8004</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>131551193</v>
-      </c>
-      <c r="E122">
-        <v>601</v>
-      </c>
-      <c r="F122" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G122" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I122">
-        <v>42</v>
-      </c>
-      <c r="J122">
-        <v>8013</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>131552352</v>
-      </c>
-      <c r="E123">
-        <v>601</v>
-      </c>
-      <c r="F123" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G123" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I123">
-        <v>42</v>
-      </c>
-      <c r="J123">
-        <v>8004</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>131553617</v>
-      </c>
-      <c r="E124">
-        <v>601</v>
-      </c>
-      <c r="F124" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G124" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I124">
-        <v>42</v>
-      </c>
-      <c r="J124">
-        <v>8004</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>131553798</v>
-      </c>
-      <c r="E125">
-        <v>601</v>
-      </c>
-      <c r="F125" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G125" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I125">
-        <v>42</v>
-      </c>
-      <c r="J125">
-        <v>8004</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>131555936</v>
-      </c>
-      <c r="E126">
-        <v>601</v>
-      </c>
-      <c r="F126" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G126" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I126">
-        <v>42</v>
-      </c>
-      <c r="J126">
-        <v>8004</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>131556656</v>
-      </c>
-      <c r="E127">
-        <v>601</v>
-      </c>
-      <c r="F127" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G127" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I127">
-        <v>42</v>
-      </c>
-      <c r="J127">
-        <v>8004</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
-        <v>0</v>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>131557349</v>
-      </c>
-      <c r="E128">
-        <v>601</v>
-      </c>
-      <c r="F128" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G128" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I128">
-        <v>42</v>
-      </c>
-      <c r="J128">
-        <v>8004</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
-        <v>0</v>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>131558272</v>
-      </c>
-      <c r="E129">
-        <v>601</v>
-      </c>
-      <c r="F129" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G129" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I129">
-        <v>42</v>
-      </c>
-      <c r="J129">
-        <v>8004</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
-        <v>0</v>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>131559314</v>
-      </c>
-      <c r="E130">
-        <v>601</v>
-      </c>
-      <c r="F130" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G130" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I130">
-        <v>42</v>
-      </c>
-      <c r="J130">
-        <v>8004</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>131563378</v>
-      </c>
-      <c r="E131">
-        <v>601</v>
-      </c>
-      <c r="F131" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G131" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I131">
-        <v>42</v>
-      </c>
-      <c r="J131">
-        <v>8004</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>131563794</v>
-      </c>
-      <c r="E132">
-        <v>601</v>
-      </c>
-      <c r="F132" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G132" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I132">
-        <v>42</v>
-      </c>
-      <c r="J132">
-        <v>8004</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>131564125</v>
-      </c>
-      <c r="E133">
-        <v>601</v>
-      </c>
-      <c r="F133" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G133" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I133">
-        <v>42</v>
-      </c>
-      <c r="J133">
-        <v>8004</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>131564816</v>
-      </c>
-      <c r="E134">
-        <v>601</v>
-      </c>
-      <c r="F134" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G134" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I134">
-        <v>42</v>
-      </c>
-      <c r="J134">
-        <v>8004</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>0</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>131565591</v>
-      </c>
-      <c r="E135">
-        <v>601</v>
-      </c>
-      <c r="F135" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G135" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I135">
-        <v>42</v>
-      </c>
-      <c r="J135">
-        <v>8004</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>131565736</v>
-      </c>
-      <c r="E136">
-        <v>601</v>
-      </c>
-      <c r="F136" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G136" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I136">
-        <v>42</v>
-      </c>
-      <c r="J136">
-        <v>8004</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>131565948</v>
-      </c>
-      <c r="E137">
-        <v>601</v>
-      </c>
-      <c r="F137" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G137" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I137">
-        <v>42</v>
-      </c>
-      <c r="J137">
-        <v>8004</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>131566072</v>
-      </c>
-      <c r="E138">
-        <v>601</v>
-      </c>
-      <c r="F138" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G138" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
-        <v>8004</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>131566769</v>
-      </c>
-      <c r="E139">
-        <v>601</v>
-      </c>
-      <c r="F139" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G139" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I139">
-        <v>42</v>
-      </c>
-      <c r="J139">
-        <v>8004</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>131567550</v>
-      </c>
-      <c r="E140">
-        <v>601</v>
-      </c>
-      <c r="F140" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G140" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I140">
-        <v>42</v>
-      </c>
-      <c r="J140">
-        <v>8004</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>131567612</v>
-      </c>
-      <c r="E141">
-        <v>601</v>
-      </c>
-      <c r="F141" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G141" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I141">
-        <v>42</v>
-      </c>
-      <c r="J141">
-        <v>8004</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>131567814</v>
-      </c>
-      <c r="E142">
-        <v>601</v>
-      </c>
-      <c r="F142" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G142" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I142">
-        <v>42</v>
-      </c>
-      <c r="J142">
-        <v>8013</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>131567817</v>
-      </c>
-      <c r="E143">
-        <v>601</v>
-      </c>
-      <c r="F143" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G143" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I143">
-        <v>42</v>
-      </c>
-      <c r="J143">
-        <v>8013</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>131567880</v>
-      </c>
-      <c r="E144">
-        <v>601</v>
-      </c>
-      <c r="F144" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G144" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I144">
-        <v>42</v>
-      </c>
-      <c r="J144">
-        <v>8013</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>131568383</v>
-      </c>
-      <c r="E145">
-        <v>601</v>
-      </c>
-      <c r="F145" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G145" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I145">
-        <v>42</v>
-      </c>
-      <c r="J145">
-        <v>8004</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>131568949</v>
-      </c>
-      <c r="E146">
-        <v>601</v>
-      </c>
-      <c r="F146" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G146" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I146">
-        <v>42</v>
-      </c>
-      <c r="J146">
-        <v>8004</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>131569857</v>
-      </c>
-      <c r="E147">
-        <v>601</v>
-      </c>
-      <c r="F147" s="2">
-        <v>45715</v>
-      </c>
-      <c r="G147" s="2">
-        <v>45715</v>
-      </c>
-      <c r="I147">
-        <v>42</v>
-      </c>
-      <c r="J147">
-        <v>8004</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>61</v>
+      <c r="R115">
+        <v>3</v>
+      </c>
+      <c r="S115" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$8</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$78</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>123058958</v>
+        <v>131602941</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -559,13 +559,13 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>44993</v>
+        <v>45721</v>
       </c>
       <c r="G2" s="1">
-        <v>44995</v>
+        <v>45721</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -574,7 +574,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131617633</v>
+        <v>131602947</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -615,13 +615,13 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="G3" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -653,16 +653,13 @@
       <c r="Q3">
         <v>61</v>
       </c>
-      <c r="R3">
-        <v>3</v>
-      </c>
       <c r="S3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131625746</v>
+        <v>131602949</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,13 +671,13 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="G4" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -689,7 +686,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -712,16 +709,13 @@
       <c r="Q4">
         <v>61</v>
       </c>
-      <c r="R4">
-        <v>3</v>
-      </c>
       <c r="S4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131626337</v>
+        <v>131602951</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -733,13 +727,13 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="G5" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -748,7 +742,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
@@ -771,16 +765,13 @@
       <c r="Q5">
         <v>61</v>
       </c>
-      <c r="R5">
-        <v>3</v>
-      </c>
       <c r="S5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131627600</v>
+        <v>131602952</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -792,13 +783,13 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="G6" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -807,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -830,16 +821,13 @@
       <c r="Q6">
         <v>61</v>
       </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
       <c r="S6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131628133</v>
+        <v>131602953</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -851,13 +839,13 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="G7" s="1">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -866,7 +854,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>718</v>
+        <v>8013</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
@@ -889,16 +877,13 @@
       <c r="Q7">
         <v>61</v>
       </c>
-      <c r="R7">
-        <v>3</v>
-      </c>
       <c r="S7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131631077</v>
+        <v>131602954</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -910,48 +895,3998 @@
         <v>24</v>
       </c>
       <c r="E8">
+        <v>601</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>42</v>
+      </c>
+      <c r="J8">
+        <v>8013</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>61</v>
+      </c>
+      <c r="S8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>131602956</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>601</v>
+      </c>
+      <c r="F9" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>42</v>
+      </c>
+      <c r="J9">
+        <v>8013</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>61</v>
+      </c>
+      <c r="S9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>131602957</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10">
+        <v>601</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G10" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>8013</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>131603408</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>601</v>
+      </c>
+      <c r="F11" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G11" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>8013</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>61</v>
+      </c>
+      <c r="S11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>131603409</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>601</v>
+      </c>
+      <c r="F12" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G12" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>42</v>
+      </c>
+      <c r="J12">
+        <v>8013</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>61</v>
+      </c>
+      <c r="S12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>131603422</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13">
+        <v>601</v>
+      </c>
+      <c r="F13" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G13" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>8013</v>
+      </c>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>61</v>
+      </c>
+      <c r="S13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>131603456</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>601</v>
+      </c>
+      <c r="F14" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G14" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>42</v>
+      </c>
+      <c r="J14">
+        <v>1117</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>61</v>
+      </c>
+      <c r="S14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>131605032</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>601</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>8004</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>61</v>
+      </c>
+      <c r="S15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>131610969</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>601</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>42</v>
+      </c>
+      <c r="J16">
+        <v>8004</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>61</v>
+      </c>
+      <c r="S16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>131613335</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17">
+        <v>601</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>42</v>
+      </c>
+      <c r="J17">
+        <v>8013</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>61</v>
+      </c>
+      <c r="S17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>131613342</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>601</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>8013</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>61</v>
+      </c>
+      <c r="S18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>131613346</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>601</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>42</v>
+      </c>
+      <c r="J19">
+        <v>8013</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>61</v>
+      </c>
+      <c r="S19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>131613351</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>601</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>42</v>
+      </c>
+      <c r="J20">
+        <v>8013</v>
+      </c>
+      <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>61</v>
+      </c>
+      <c r="S20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>131606031</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21">
+        <v>601</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>42</v>
+      </c>
+      <c r="J21">
+        <v>8004</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>61</v>
+      </c>
+      <c r="S21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>131611304</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>601</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>42</v>
+      </c>
+      <c r="J22">
+        <v>8004</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>61</v>
+      </c>
+      <c r="S22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>131611794</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>601</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>8004</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>61</v>
+      </c>
+      <c r="S23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>123058958</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>1211</v>
+      </c>
+      <c r="F24" s="1">
+        <v>44993</v>
+      </c>
+      <c r="G24" s="1">
+        <v>44995</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24">
+        <v>42</v>
+      </c>
+      <c r="J24">
+        <v>8001</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>61</v>
+      </c>
+      <c r="S24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>131606653</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>1211</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45721</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25">
+        <v>42</v>
+      </c>
+      <c r="J25">
+        <v>8021</v>
+      </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>61</v>
+      </c>
+      <c r="S25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>127365872</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>1211</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>8001</v>
+      </c>
+      <c r="K26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>61</v>
+      </c>
+      <c r="S26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>127498766</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27">
+        <v>1211</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G27" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27">
+        <v>42</v>
+      </c>
+      <c r="J27">
+        <v>8001</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>61</v>
+      </c>
+      <c r="S27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>127519020</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28">
+        <v>1211</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G28" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28">
+        <v>42</v>
+      </c>
+      <c r="J28">
+        <v>8001</v>
+      </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+      <c r="S28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>128078774</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29">
+        <v>42</v>
+      </c>
+      <c r="J29">
+        <v>8001</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>61</v>
+      </c>
+      <c r="S29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>128154004</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>1211</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>8001</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>61</v>
+      </c>
+      <c r="S30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>128396108</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G31" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>8001</v>
+      </c>
+      <c r="K31" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>61</v>
+      </c>
+      <c r="S31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>128606382</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G32" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>8001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+      <c r="S32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>128693951</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33">
+        <v>1211</v>
+      </c>
+      <c r="F33" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G33" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>8001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+      <c r="S33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>128947714</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>8001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+      <c r="S34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>129153933</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>8001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+      <c r="S35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>129266542</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G36" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>8001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+      <c r="S36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>129476085</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G37" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>8001</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+      <c r="S37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>129613979</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G38" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>8001</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+      <c r="S38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>129925947</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G39" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8001</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+      <c r="S39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>130251940</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G40" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8001</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+      <c r="S40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>130315294</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41">
+        <v>1212</v>
+      </c>
+      <c r="F41" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G41" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8001</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+      <c r="S41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>130385149</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>1212</v>
+      </c>
+      <c r="F42" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G42" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8001</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+      <c r="S42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>130528966</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G43" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8001</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+      <c r="S43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>130529951</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G44" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8001</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+      <c r="S44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>130762152</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G45" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8001</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+      <c r="S45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>130800804</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46">
+        <v>1212</v>
+      </c>
+      <c r="F46" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G46" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8001</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+      <c r="S46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>131136073</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G47" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8001</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+      <c r="S47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>131555746</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G48" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>8001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+      <c r="S48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>131589897</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G49" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8001</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+      <c r="S49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>131625240</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+      <c r="S50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>127365872</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G51" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+      <c r="S51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>127498766</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G52" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+      <c r="S52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>127519020</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G53" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+      <c r="S53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>128396108</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G54" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H54" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8001</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+      <c r="S54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>128606382</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G55" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+      <c r="S55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>128947714</v>
+      </c>
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G56" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8001</v>
+      </c>
+      <c r="K56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+      <c r="S56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>129153933</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G57" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8001</v>
+      </c>
+      <c r="K57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+      <c r="S57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>129266542</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G58" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+      <c r="S58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>129476085</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H59" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8001</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+      <c r="S59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>129925947</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G60" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+      <c r="S60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>130251940</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45721</v>
+      </c>
+      <c r="G61" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+      <c r="S61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>130315294</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62">
+        <v>1212</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G62" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+      <c r="S62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>130762152</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G63" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+      <c r="S63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>130800804</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64">
+        <v>1212</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G64" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+      <c r="S64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>131136073</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G65" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+      <c r="S65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>131555746</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G66" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+      <c r="S66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>131625240</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+      <c r="S67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>131635297</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68">
         <v>2013</v>
       </c>
-      <c r="F8" s="1">
-        <v>45722</v>
-      </c>
-      <c r="G8" s="1">
-        <v>45722</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8">
-        <v>42</v>
-      </c>
-      <c r="J8">
+      <c r="F68" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G68" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
         <v>718</v>
       </c>
-      <c r="K8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>61</v>
-      </c>
-      <c r="R8">
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+      <c r="R68">
         <v>3</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>131638378</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69">
+        <v>2013</v>
+      </c>
+      <c r="F69" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>718</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+      <c r="R69">
+        <v>3</v>
+      </c>
+      <c r="S69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>131638610</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70">
+        <v>2013</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G70" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>718</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+      <c r="R70">
+        <v>3</v>
+      </c>
+      <c r="S70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>131638662</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71">
+        <v>2013</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45724</v>
+      </c>
+      <c r="H71" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>718</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+      <c r="R71">
+        <v>3</v>
+      </c>
+      <c r="S71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>131640367</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72">
+        <v>2013</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>718</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+      <c r="R72">
+        <v>3</v>
+      </c>
+      <c r="S72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>131646895</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73">
+        <v>2013</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G73" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>718</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+      <c r="R73">
+        <v>3</v>
+      </c>
+      <c r="S73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>131647834</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74">
+        <v>2013</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H74" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>718</v>
+      </c>
+      <c r="K74" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+      <c r="R74">
+        <v>3</v>
+      </c>
+      <c r="S74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>131648283</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75">
+        <v>2013</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>718</v>
+      </c>
+      <c r="K75" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+      <c r="R75">
+        <v>3</v>
+      </c>
+      <c r="S75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>131648495</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76">
+        <v>2013</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45723</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>718</v>
+      </c>
+      <c r="K76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+      <c r="R76">
+        <v>3</v>
+      </c>
+      <c r="S76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>131648657</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77">
+        <v>2013</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45724</v>
+      </c>
+      <c r="H77" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>718</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>131650579</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78">
+        <v>2013</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45723</v>
+      </c>
+      <c r="G78" s="1">
+        <v>45724</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>718</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+      <c r="R78">
+        <v>3</v>
+      </c>
+      <c r="S78" t="s">
         <v>25</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$78</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$85</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131602941</v>
+        <v>131616069</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -562,10 +562,10 @@
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G2" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131602947</v>
+        <v>131616623</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -618,10 +618,10 @@
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G3" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131602949</v>
+        <v>131617327</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,10 +674,10 @@
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G4" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131602951</v>
+        <v>131617332</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -730,10 +730,10 @@
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G5" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131602952</v>
+        <v>131617336</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -786,10 +786,10 @@
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G6" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131602953</v>
+        <v>131617356</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -842,10 +842,10 @@
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G7" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131602954</v>
+        <v>131617383</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -898,10 +898,10 @@
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G8" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131602956</v>
+        <v>131617796</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -954,10 +954,10 @@
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G9" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131602957</v>
+        <v>131619644</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1010,10 +1010,10 @@
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G10" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1022,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131603408</v>
+        <v>131621315</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1066,10 +1066,10 @@
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G11" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
@@ -1078,7 +1078,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131603409</v>
+        <v>131623775</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1122,10 +1122,10 @@
         <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G12" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131603422</v>
+        <v>131623778</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1178,10 +1178,10 @@
         <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G13" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131603456</v>
+        <v>131623784</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1234,10 +1234,10 @@
         <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G14" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
@@ -1246,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>1117</v>
+        <v>8013</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131605032</v>
+        <v>131623789</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1290,10 +1290,10 @@
         <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G15" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1302,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131610969</v>
+        <v>131623790</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1346,10 +1346,10 @@
         <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G16" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1358,7 +1358,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K16" t="s">
         <v>24</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131613335</v>
+        <v>131623808</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -1402,10 +1402,10 @@
         <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G17" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H17" t="s">
         <v>24</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131613342</v>
+        <v>131624452</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1458,10 +1458,10 @@
         <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G18" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131613346</v>
+        <v>131624460</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -1514,10 +1514,10 @@
         <v>601</v>
       </c>
       <c r="F19" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G19" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H19" t="s">
         <v>24</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131613351</v>
+        <v>131625483</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1570,10 +1570,10 @@
         <v>601</v>
       </c>
       <c r="F20" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G20" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131606031</v>
+        <v>131625487</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1626,10 +1626,10 @@
         <v>601</v>
       </c>
       <c r="F21" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G21" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
@@ -1638,7 +1638,7 @@
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K21" t="s">
         <v>24</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131611304</v>
+        <v>131626221</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -1682,10 +1682,10 @@
         <v>601</v>
       </c>
       <c r="F22" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G22" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1694,7 +1694,7 @@
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131611794</v>
+        <v>131626226</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -1738,10 +1738,10 @@
         <v>601</v>
       </c>
       <c r="F23" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G23" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H23" t="s">
         <v>24</v>
@@ -1750,7 +1750,7 @@
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>123058958</v>
+        <v>131626229</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -1791,13 +1791,13 @@
         <v>24</v>
       </c>
       <c r="E24">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F24" s="1">
-        <v>44993</v>
+        <v>45722</v>
       </c>
       <c r="G24" s="1">
-        <v>44995</v>
+        <v>45722</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
@@ -1806,7 +1806,7 @@
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131606653</v>
+        <v>131626233</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -1847,13 +1847,13 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F25" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G25" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
@@ -1862,7 +1862,7 @@
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8021</v>
+        <v>8013</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>127365872</v>
+        <v>131626239</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -1903,13 +1903,13 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F26" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G26" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
@@ -1918,7 +1918,7 @@
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K26" t="s">
         <v>24</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>127498766</v>
+        <v>131626243</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -1959,13 +1959,13 @@
         <v>24</v>
       </c>
       <c r="E27">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F27" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G27" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
@@ -1974,7 +1974,7 @@
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K27" t="s">
         <v>24</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>127519020</v>
+        <v>131626244</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2015,13 +2015,13 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F28" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G28" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H28" t="s">
         <v>24</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>128078774</v>
+        <v>131626251</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2071,13 +2071,13 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F29" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G29" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
@@ -2086,7 +2086,7 @@
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>128154004</v>
+        <v>131626258</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2127,13 +2127,13 @@
         <v>24</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F30" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G30" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H30" t="s">
         <v>24</v>
@@ -2142,7 +2142,7 @@
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K30" t="s">
         <v>24</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>128396108</v>
+        <v>131626261</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -2183,13 +2183,13 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F31" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G31" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H31" t="s">
         <v>24</v>
@@ -2198,7 +2198,7 @@
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>128606382</v>
+        <v>131626266</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -2239,13 +2239,13 @@
         <v>24</v>
       </c>
       <c r="E32">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F32" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G32" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H32" t="s">
         <v>24</v>
@@ -2254,7 +2254,7 @@
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K32" t="s">
         <v>24</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>128693951</v>
+        <v>131626269</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -2295,13 +2295,13 @@
         <v>24</v>
       </c>
       <c r="E33">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F33" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G33" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H33" t="s">
         <v>24</v>
@@ -2310,7 +2310,7 @@
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K33" t="s">
         <v>24</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>128947714</v>
+        <v>131626276</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -2351,13 +2351,13 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F34" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G34" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2366,7 +2366,7 @@
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>129153933</v>
+        <v>131626319</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -2407,13 +2407,13 @@
         <v>24</v>
       </c>
       <c r="E35">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F35" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G35" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -2422,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K35" t="s">
         <v>24</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>129266542</v>
+        <v>131627023</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2463,13 +2463,13 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F36" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G36" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H36" t="s">
         <v>24</v>
@@ -2478,7 +2478,7 @@
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K36" t="s">
         <v>24</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>129476085</v>
+        <v>131627041</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -2519,13 +2519,13 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F37" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G37" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H37" t="s">
         <v>24</v>
@@ -2534,7 +2534,7 @@
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K37" t="s">
         <v>24</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>129613979</v>
+        <v>131627047</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -2575,13 +2575,13 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F38" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G38" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H38" t="s">
         <v>24</v>
@@ -2590,7 +2590,7 @@
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K38" t="s">
         <v>24</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>129925947</v>
+        <v>131627050</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -2631,13 +2631,13 @@
         <v>24</v>
       </c>
       <c r="E39">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F39" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G39" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H39" t="s">
         <v>24</v>
@@ -2646,7 +2646,7 @@
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K39" t="s">
         <v>24</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>130251940</v>
+        <v>131627053</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -2687,13 +2687,13 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F40" s="1">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="G40" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H40" t="s">
         <v>24</v>
@@ -2702,7 +2702,7 @@
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K40" t="s">
         <v>24</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>130315294</v>
+        <v>131627058</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
@@ -2743,13 +2743,13 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F41" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G41" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H41" t="s">
         <v>24</v>
@@ -2758,7 +2758,7 @@
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K41" t="s">
         <v>24</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>130385149</v>
+        <v>131627063</v>
       </c>
       <c r="B42" t="s">
         <v>24</v>
@@ -2799,13 +2799,13 @@
         <v>24</v>
       </c>
       <c r="E42">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F42" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G42" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H42" t="s">
         <v>24</v>
@@ -2814,7 +2814,7 @@
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K42" t="s">
         <v>24</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>130528966</v>
+        <v>131627070</v>
       </c>
       <c r="B43" t="s">
         <v>24</v>
@@ -2855,13 +2855,13 @@
         <v>24</v>
       </c>
       <c r="E43">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F43" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G43" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H43" t="s">
         <v>24</v>
@@ -2870,7 +2870,7 @@
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K43" t="s">
         <v>24</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>130529951</v>
+        <v>131627075</v>
       </c>
       <c r="B44" t="s">
         <v>24</v>
@@ -2911,13 +2911,13 @@
         <v>24</v>
       </c>
       <c r="E44">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F44" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G44" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H44" t="s">
         <v>24</v>
@@ -2926,7 +2926,7 @@
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K44" t="s">
         <v>24</v>
@@ -2955,7 +2955,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>130762152</v>
+        <v>131627175</v>
       </c>
       <c r="B45" t="s">
         <v>24</v>
@@ -2967,13 +2967,13 @@
         <v>24</v>
       </c>
       <c r="E45">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F45" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G45" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H45" t="s">
         <v>24</v>
@@ -2982,7 +2982,7 @@
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K45" t="s">
         <v>24</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>130800804</v>
+        <v>131627191</v>
       </c>
       <c r="B46" t="s">
         <v>24</v>
@@ -3023,13 +3023,13 @@
         <v>24</v>
       </c>
       <c r="E46">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F46" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G46" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H46" t="s">
         <v>24</v>
@@ -3038,7 +3038,7 @@
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K46" t="s">
         <v>24</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>131136073</v>
+        <v>131627196</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
@@ -3079,13 +3079,13 @@
         <v>24</v>
       </c>
       <c r="E47">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F47" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G47" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H47" t="s">
         <v>24</v>
@@ -3094,7 +3094,7 @@
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="K47" t="s">
         <v>24</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>131555746</v>
+        <v>131628503</v>
       </c>
       <c r="B48" t="s">
         <v>24</v>
@@ -3135,13 +3135,13 @@
         <v>24</v>
       </c>
       <c r="E48">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F48" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G48" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H48" t="s">
         <v>24</v>
@@ -3150,7 +3150,7 @@
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K48" t="s">
         <v>24</v>
@@ -3179,7 +3179,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>131589897</v>
+        <v>131620228</v>
       </c>
       <c r="B49" t="s">
         <v>24</v>
@@ -3191,13 +3191,13 @@
         <v>24</v>
       </c>
       <c r="E49">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F49" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G49" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H49" t="s">
         <v>24</v>
@@ -3206,7 +3206,7 @@
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K49" t="s">
         <v>24</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>131625240</v>
+        <v>131626369</v>
       </c>
       <c r="B50" t="s">
         <v>24</v>
@@ -3247,13 +3247,13 @@
         <v>24</v>
       </c>
       <c r="E50">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F50" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G50" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H50" t="s">
         <v>24</v>
@@ -3262,7 +3262,7 @@
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K50" t="s">
         <v>24</v>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>127365872</v>
+        <v>131628068</v>
       </c>
       <c r="B51" t="s">
         <v>24</v>
@@ -3303,13 +3303,13 @@
         <v>24</v>
       </c>
       <c r="E51">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F51" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G51" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H51" t="s">
         <v>24</v>
@@ -3318,7 +3318,7 @@
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K51" t="s">
         <v>24</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>127498766</v>
+        <v>131629082</v>
       </c>
       <c r="B52" t="s">
         <v>24</v>
@@ -3359,13 +3359,13 @@
         <v>24</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F52" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G52" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H52" t="s">
         <v>24</v>
@@ -3374,7 +3374,7 @@
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K52" t="s">
         <v>24</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>127519020</v>
+        <v>131629337</v>
       </c>
       <c r="B53" t="s">
         <v>24</v>
@@ -3415,13 +3415,13 @@
         <v>24</v>
       </c>
       <c r="E53">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F53" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G53" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H53" t="s">
         <v>24</v>
@@ -3430,7 +3430,7 @@
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K53" t="s">
         <v>24</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>128396108</v>
+        <v>131629804</v>
       </c>
       <c r="B54" t="s">
         <v>24</v>
@@ -3471,13 +3471,13 @@
         <v>24</v>
       </c>
       <c r="E54">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F54" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G54" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H54" t="s">
         <v>24</v>
@@ -3486,7 +3486,7 @@
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K54" t="s">
         <v>24</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>128606382</v>
+        <v>131630723</v>
       </c>
       <c r="B55" t="s">
         <v>24</v>
@@ -3527,13 +3527,13 @@
         <v>24</v>
       </c>
       <c r="E55">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F55" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G55" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H55" t="s">
         <v>24</v>
@@ -3542,7 +3542,7 @@
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K55" t="s">
         <v>24</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>128947714</v>
+        <v>131631301</v>
       </c>
       <c r="B56" t="s">
         <v>24</v>
@@ -3583,13 +3583,13 @@
         <v>24</v>
       </c>
       <c r="E56">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F56" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G56" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H56" t="s">
         <v>24</v>
@@ -3598,7 +3598,7 @@
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K56" t="s">
         <v>24</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>129153933</v>
+        <v>131631389</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
@@ -3639,13 +3639,13 @@
         <v>24</v>
       </c>
       <c r="E57">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F57" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G57" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H57" t="s">
         <v>24</v>
@@ -3654,7 +3654,7 @@
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K57" t="s">
         <v>24</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>129266542</v>
+        <v>131631691</v>
       </c>
       <c r="B58" t="s">
         <v>24</v>
@@ -3695,13 +3695,13 @@
         <v>24</v>
       </c>
       <c r="E58">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F58" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G58" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H58" t="s">
         <v>24</v>
@@ -3710,7 +3710,7 @@
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K58" t="s">
         <v>24</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>129476085</v>
+        <v>131607669</v>
       </c>
       <c r="B59" t="s">
         <v>24</v>
@@ -3754,10 +3754,10 @@
         <v>1211</v>
       </c>
       <c r="F59" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="G59" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="H59" t="s">
         <v>24</v>
@@ -3766,7 +3766,7 @@
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K59" t="s">
         <v>24</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>129925947</v>
+        <v>131608038</v>
       </c>
       <c r="B60" t="s">
         <v>24</v>
@@ -3810,10 +3810,10 @@
         <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="G60" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="H60" t="s">
         <v>24</v>
@@ -3822,7 +3822,7 @@
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K60" t="s">
         <v>24</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>130251940</v>
+        <v>131615600</v>
       </c>
       <c r="B61" t="s">
         <v>24</v>
@@ -3869,7 +3869,7 @@
         <v>45721</v>
       </c>
       <c r="G61" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="H61" t="s">
         <v>24</v>
@@ -3878,7 +3878,7 @@
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K61" t="s">
         <v>24</v>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>130315294</v>
+        <v>131618027</v>
       </c>
       <c r="B62" t="s">
         <v>24</v>
@@ -3919,13 +3919,13 @@
         <v>24</v>
       </c>
       <c r="E62">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G62" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H62" t="s">
         <v>24</v>
@@ -3934,7 +3934,7 @@
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K62" t="s">
         <v>24</v>
@@ -3963,7 +3963,7 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>130762152</v>
+        <v>131619055</v>
       </c>
       <c r="B63" t="s">
         <v>24</v>
@@ -3978,7 +3978,7 @@
         <v>1211</v>
       </c>
       <c r="F63" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G63" s="1">
         <v>45723</v>
@@ -3990,7 +3990,7 @@
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K63" t="s">
         <v>24</v>
@@ -4019,7 +4019,7 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>130800804</v>
+        <v>131622196</v>
       </c>
       <c r="B64" t="s">
         <v>24</v>
@@ -4031,13 +4031,13 @@
         <v>24</v>
       </c>
       <c r="E64">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G64" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H64" t="s">
         <v>24</v>
@@ -4046,7 +4046,7 @@
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K64" t="s">
         <v>24</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>131136073</v>
+        <v>131627426</v>
       </c>
       <c r="B65" t="s">
         <v>24</v>
@@ -4090,10 +4090,10 @@
         <v>1211</v>
       </c>
       <c r="F65" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G65" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H65" t="s">
         <v>24</v>
@@ -4102,7 +4102,7 @@
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K65" t="s">
         <v>24</v>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>131555746</v>
+        <v>131631377</v>
       </c>
       <c r="B66" t="s">
         <v>24</v>
@@ -4146,7 +4146,7 @@
         <v>1211</v>
       </c>
       <c r="F66" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G66" s="1">
         <v>45723</v>
@@ -4158,7 +4158,7 @@
         <v>42</v>
       </c>
       <c r="J66">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K66" t="s">
         <v>24</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>131625240</v>
+        <v>131632187</v>
       </c>
       <c r="B67" t="s">
         <v>24</v>
@@ -4202,10 +4202,10 @@
         <v>1211</v>
       </c>
       <c r="F67" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="G67" s="1">
-        <v>45723</v>
+        <v>45722</v>
       </c>
       <c r="H67" t="s">
         <v>24</v>
@@ -4214,7 +4214,7 @@
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K67" t="s">
         <v>24</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>131635297</v>
+        <v>131636417</v>
       </c>
       <c r="B68" t="s">
         <v>24</v>
@@ -4255,7 +4255,7 @@
         <v>24</v>
       </c>
       <c r="E68">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="1">
         <v>45723</v>
@@ -4270,7 +4270,7 @@
         <v>42</v>
       </c>
       <c r="J68">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K68" t="s">
         <v>24</v>
@@ -4293,16 +4293,13 @@
       <c r="Q68">
         <v>61</v>
       </c>
-      <c r="R68">
-        <v>3</v>
-      </c>
       <c r="S68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>131638378</v>
+        <v>131639769</v>
       </c>
       <c r="B69" t="s">
         <v>24</v>
@@ -4314,7 +4311,7 @@
         <v>24</v>
       </c>
       <c r="E69">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F69" s="1">
         <v>45723</v>
@@ -4329,7 +4326,7 @@
         <v>42</v>
       </c>
       <c r="J69">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K69" t="s">
         <v>24</v>
@@ -4352,16 +4349,13 @@
       <c r="Q69">
         <v>61</v>
       </c>
-      <c r="R69">
-        <v>3</v>
-      </c>
       <c r="S69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>131638610</v>
+        <v>131642819</v>
       </c>
       <c r="B70" t="s">
         <v>24</v>
@@ -4373,7 +4367,7 @@
         <v>24</v>
       </c>
       <c r="E70">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F70" s="1">
         <v>45723</v>
@@ -4388,7 +4382,7 @@
         <v>42</v>
       </c>
       <c r="J70">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K70" t="s">
         <v>24</v>
@@ -4411,16 +4405,13 @@
       <c r="Q70">
         <v>61</v>
       </c>
-      <c r="R70">
-        <v>3</v>
-      </c>
       <c r="S70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>131638662</v>
+        <v>131646787</v>
       </c>
       <c r="B71" t="s">
         <v>24</v>
@@ -4432,13 +4423,13 @@
         <v>24</v>
       </c>
       <c r="E71">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="1">
         <v>45723</v>
       </c>
       <c r="G71" s="1">
-        <v>45724</v>
+        <v>45723</v>
       </c>
       <c r="H71" t="s">
         <v>24</v>
@@ -4447,7 +4438,7 @@
         <v>42</v>
       </c>
       <c r="J71">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K71" t="s">
         <v>24</v>
@@ -4470,16 +4461,13 @@
       <c r="Q71">
         <v>61</v>
       </c>
-      <c r="R71">
-        <v>3</v>
-      </c>
       <c r="S71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>131640367</v>
+        <v>131649136</v>
       </c>
       <c r="B72" t="s">
         <v>24</v>
@@ -4491,13 +4479,13 @@
         <v>24</v>
       </c>
       <c r="E72">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F72" s="1">
         <v>45723</v>
       </c>
       <c r="G72" s="1">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="H72" t="s">
         <v>24</v>
@@ -4506,7 +4494,7 @@
         <v>42</v>
       </c>
       <c r="J72">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K72" t="s">
         <v>24</v>
@@ -4529,16 +4517,13 @@
       <c r="Q72">
         <v>61</v>
       </c>
-      <c r="R72">
-        <v>3</v>
-      </c>
       <c r="S72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>131646895</v>
+        <v>131650207</v>
       </c>
       <c r="B73" t="s">
         <v>24</v>
@@ -4550,13 +4535,13 @@
         <v>24</v>
       </c>
       <c r="E73">
-        <v>2013</v>
+        <v>1212</v>
       </c>
       <c r="F73" s="1">
         <v>45723</v>
       </c>
       <c r="G73" s="1">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="H73" t="s">
         <v>24</v>
@@ -4565,7 +4550,7 @@
         <v>42</v>
       </c>
       <c r="J73">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K73" t="s">
         <v>24</v>
@@ -4588,16 +4573,13 @@
       <c r="Q73">
         <v>61</v>
       </c>
-      <c r="R73">
-        <v>3</v>
-      </c>
       <c r="S73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>131647834</v>
+        <v>131656353</v>
       </c>
       <c r="B74" t="s">
         <v>24</v>
@@ -4609,7 +4591,7 @@
         <v>24</v>
       </c>
       <c r="E74">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="1">
         <v>45723</v>
@@ -4624,7 +4606,7 @@
         <v>42</v>
       </c>
       <c r="J74">
-        <v>718</v>
+        <v>1735</v>
       </c>
       <c r="K74" t="s">
         <v>24</v>
@@ -4647,16 +4629,13 @@
       <c r="Q74">
         <v>61</v>
       </c>
-      <c r="R74">
-        <v>3</v>
-      </c>
       <c r="S74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>131648283</v>
+        <v>123058958</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
@@ -4668,13 +4647,13 @@
         <v>24</v>
       </c>
       <c r="E75">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F75" s="1">
-        <v>45723</v>
+        <v>44993</v>
       </c>
       <c r="G75" s="1">
-        <v>45723</v>
+        <v>44995</v>
       </c>
       <c r="H75" t="s">
         <v>24</v>
@@ -4683,7 +4662,7 @@
         <v>42</v>
       </c>
       <c r="J75">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K75" t="s">
         <v>24</v>
@@ -4706,16 +4685,13 @@
       <c r="Q75">
         <v>61</v>
       </c>
-      <c r="R75">
-        <v>3</v>
-      </c>
       <c r="S75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>131648495</v>
+        <v>131606653</v>
       </c>
       <c r="B76" t="s">
         <v>24</v>
@@ -4727,13 +4703,13 @@
         <v>24</v>
       </c>
       <c r="E76">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="G76" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="H76" t="s">
         <v>24</v>
@@ -4742,7 +4718,7 @@
         <v>42</v>
       </c>
       <c r="J76">
-        <v>718</v>
+        <v>8021</v>
       </c>
       <c r="K76" t="s">
         <v>24</v>
@@ -4765,16 +4741,13 @@
       <c r="Q76">
         <v>61</v>
       </c>
-      <c r="R76">
-        <v>3</v>
-      </c>
       <c r="S76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>131648657</v>
+        <v>131661097</v>
       </c>
       <c r="B77" t="s">
         <v>24</v>
@@ -4789,10 +4762,10 @@
         <v>2013</v>
       </c>
       <c r="F77" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G77" s="1">
-        <v>45724</v>
+        <v>45726</v>
       </c>
       <c r="H77" t="s">
         <v>24</v>
@@ -4833,7 +4806,7 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>131650579</v>
+        <v>131664045</v>
       </c>
       <c r="B78" t="s">
         <v>24</v>
@@ -4848,10 +4821,10 @@
         <v>2013</v>
       </c>
       <c r="F78" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G78" s="1">
-        <v>45724</v>
+        <v>45726</v>
       </c>
       <c r="H78" t="s">
         <v>24</v>
@@ -4887,6 +4860,419 @@
         <v>3</v>
       </c>
       <c r="S78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>131667454</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79">
+        <v>2013</v>
+      </c>
+      <c r="F79" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G79" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>718</v>
+      </c>
+      <c r="K79" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+      <c r="R79">
+        <v>3</v>
+      </c>
+      <c r="S79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>131667509</v>
+      </c>
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80">
+        <v>2013</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H80" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>718</v>
+      </c>
+      <c r="K80" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+      <c r="R80">
+        <v>3</v>
+      </c>
+      <c r="S80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>131667549</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81">
+        <v>2013</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G81" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>718</v>
+      </c>
+      <c r="K81" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+      <c r="R81">
+        <v>3</v>
+      </c>
+      <c r="S81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>131667705</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82">
+        <v>2013</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>718</v>
+      </c>
+      <c r="K82" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+      <c r="R82">
+        <v>3</v>
+      </c>
+      <c r="S82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>131667825</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83">
+        <v>2013</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G83" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>718</v>
+      </c>
+      <c r="K83" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+      <c r="R83">
+        <v>3</v>
+      </c>
+      <c r="S83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>131669382</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84">
+        <v>2013</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G84" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H84" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>718</v>
+      </c>
+      <c r="K84" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+      <c r="R84">
+        <v>3</v>
+      </c>
+      <c r="S84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>131677505</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85">
+        <v>2013</v>
+      </c>
+      <c r="F85" s="1">
+        <v>45726</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45726</v>
+      </c>
+      <c r="H85" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>718</v>
+      </c>
+      <c r="K85" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+      <c r="R85">
+        <v>3</v>
+      </c>
+      <c r="S85" t="s">
         <v>25</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$50</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$36</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131635161</v>
+        <v>131660406</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -562,10 +562,10 @@
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G2" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131635164</v>
+        <v>131662383</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -618,10 +618,10 @@
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G3" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131635165</v>
+        <v>131662388</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,10 +674,10 @@
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G4" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -686,7 +686,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131635168</v>
+        <v>131662830</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -730,10 +730,10 @@
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G5" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -742,7 +742,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131635173</v>
+        <v>131664970</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -786,10 +786,10 @@
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G6" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131635175</v>
+        <v>131667968</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -842,10 +842,10 @@
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G7" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131636256</v>
+        <v>131668985</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -898,10 +898,10 @@
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G8" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131636257</v>
+        <v>131670178</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -954,10 +954,10 @@
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G9" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131636261</v>
+        <v>131670186</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1010,10 +1010,10 @@
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G10" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1022,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131636265</v>
+        <v>131670193</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1066,10 +1066,10 @@
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G11" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
@@ -1078,7 +1078,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131636409</v>
+        <v>131670199</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1122,10 +1122,10 @@
         <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G12" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -1134,7 +1134,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131643656</v>
+        <v>131670203</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1178,10 +1178,10 @@
         <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G13" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
@@ -1190,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131645251</v>
+        <v>131670253</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1234,10 +1234,10 @@
         <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G14" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
@@ -1246,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131645697</v>
+        <v>131670264</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1290,10 +1290,10 @@
         <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G15" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131645710</v>
+        <v>131673780</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1346,10 +1346,10 @@
         <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G16" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131645802</v>
+        <v>131673832</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -1402,10 +1402,10 @@
         <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G17" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H17" t="s">
         <v>24</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131646679</v>
+        <v>131676549</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1458,10 +1458,10 @@
         <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G18" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131647442</v>
+        <v>131677587</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -1514,10 +1514,10 @@
         <v>601</v>
       </c>
       <c r="F19" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G19" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H19" t="s">
         <v>24</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131648631</v>
+        <v>131677589</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1570,10 +1570,10 @@
         <v>601</v>
       </c>
       <c r="F20" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G20" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131649286</v>
+        <v>131544383</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1626,10 +1626,10 @@
         <v>601</v>
       </c>
       <c r="F21" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G21" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131651706</v>
+        <v>131656603</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -1682,10 +1682,10 @@
         <v>601</v>
       </c>
       <c r="F22" s="1">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="G22" s="1">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1694,7 +1694,7 @@
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131651717</v>
+        <v>131656672</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -1738,10 +1738,10 @@
         <v>601</v>
       </c>
       <c r="F23" s="1">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="G23" s="1">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="H23" t="s">
         <v>24</v>
@@ -1750,7 +1750,7 @@
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>131651721</v>
+        <v>131667072</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -1794,10 +1794,10 @@
         <v>601</v>
       </c>
       <c r="F24" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G24" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
@@ -1806,7 +1806,7 @@
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131651728</v>
+        <v>131669307</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -1850,10 +1850,10 @@
         <v>601</v>
       </c>
       <c r="F25" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G25" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
@@ -1862,7 +1862,7 @@
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>131651731</v>
+        <v>131674526</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -1906,10 +1906,10 @@
         <v>601</v>
       </c>
       <c r="F26" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G26" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
@@ -1918,7 +1918,7 @@
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K26" t="s">
         <v>24</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>131651736</v>
+        <v>131675085</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -1962,10 +1962,10 @@
         <v>601</v>
       </c>
       <c r="F27" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G27" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
@@ -1974,7 +1974,7 @@
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K27" t="s">
         <v>24</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131651779</v>
+        <v>131675846</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2018,10 +2018,10 @@
         <v>601</v>
       </c>
       <c r="F28" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G28" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H28" t="s">
         <v>24</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>131652707</v>
+        <v>131676181</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2074,10 +2074,10 @@
         <v>601</v>
       </c>
       <c r="F29" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G29" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
@@ -2086,7 +2086,7 @@
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>131652879</v>
+        <v>131676699</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2130,10 +2130,10 @@
         <v>601</v>
       </c>
       <c r="F30" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G30" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H30" t="s">
         <v>24</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>131653316</v>
+        <v>123058958</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -2183,13 +2183,13 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45723</v>
+        <v>44993</v>
       </c>
       <c r="G31" s="1">
-        <v>45723</v>
+        <v>44995</v>
       </c>
       <c r="H31" t="s">
         <v>24</v>
@@ -2198,7 +2198,7 @@
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>131640495</v>
+        <v>131606653</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -2239,13 +2239,13 @@
         <v>24</v>
       </c>
       <c r="E32">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="G32" s="1">
-        <v>45723</v>
+        <v>45721</v>
       </c>
       <c r="H32" t="s">
         <v>24</v>
@@ -2254,7 +2254,7 @@
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K32" t="s">
         <v>24</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>131641063</v>
+        <v>131660184</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -2295,13 +2295,13 @@
         <v>24</v>
       </c>
       <c r="E33">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G33" s="1">
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="H33" t="s">
         <v>24</v>
@@ -2310,7 +2310,7 @@
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K33" t="s">
         <v>24</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>131642049</v>
+        <v>130647855</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -2351,13 +2351,13 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G34" s="1">
-        <v>45723</v>
+        <v>45728</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2366,7 +2366,7 @@
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>131650142</v>
+        <v>130759449</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -2407,13 +2407,13 @@
         <v>24</v>
       </c>
       <c r="E35">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G35" s="1">
-        <v>45723</v>
+        <v>45728</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -2422,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K35" t="s">
         <v>24</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>131652448</v>
+        <v>130647855</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2463,13 +2463,13 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="G36" s="1">
-        <v>45723</v>
+        <v>45728</v>
       </c>
       <c r="H36" t="s">
         <v>24</v>
@@ -2478,7 +2478,7 @@
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K36" t="s">
         <v>24</v>
@@ -2503,817 +2503,6 @@
       </c>
       <c r="S36" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>131654628</v>
-      </c>
-      <c r="B37" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37">
-        <v>601</v>
-      </c>
-      <c r="F37" s="1">
-        <v>45723</v>
-      </c>
-      <c r="G37" s="1">
-        <v>45723</v>
-      </c>
-      <c r="H37" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8004</v>
-      </c>
-      <c r="K37" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-      <c r="S37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>123058958</v>
-      </c>
-      <c r="B38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38">
-        <v>1211</v>
-      </c>
-      <c r="F38" s="1">
-        <v>44993</v>
-      </c>
-      <c r="G38" s="1">
-        <v>44995</v>
-      </c>
-      <c r="H38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8001</v>
-      </c>
-      <c r="K38" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-      <c r="S38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>131606653</v>
-      </c>
-      <c r="B39" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39">
-        <v>1211</v>
-      </c>
-      <c r="F39" s="1">
-        <v>45721</v>
-      </c>
-      <c r="G39" s="1">
-        <v>45721</v>
-      </c>
-      <c r="H39" t="s">
-        <v>24</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8021</v>
-      </c>
-      <c r="K39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>61</v>
-      </c>
-      <c r="S39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>131630077</v>
-      </c>
-      <c r="B40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="1">
-        <v>45722</v>
-      </c>
-      <c r="G40" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H40" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40">
-        <v>42</v>
-      </c>
-      <c r="J40">
-        <v>8001</v>
-      </c>
-      <c r="K40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>61</v>
-      </c>
-      <c r="S40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>131621595</v>
-      </c>
-      <c r="B41" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" t="s">
-        <v>24</v>
-      </c>
-      <c r="E41">
-        <v>1212</v>
-      </c>
-      <c r="F41" s="1">
-        <v>45722</v>
-      </c>
-      <c r="G41" s="1">
-        <v>45723</v>
-      </c>
-      <c r="H41" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>715</v>
-      </c>
-      <c r="K41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-      <c r="S41" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>131679949</v>
-      </c>
-      <c r="B42" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42">
-        <v>2013</v>
-      </c>
-      <c r="F42" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G42" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H42" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>718</v>
-      </c>
-      <c r="K42" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-      <c r="R42">
-        <v>3</v>
-      </c>
-      <c r="S42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>131680182</v>
-      </c>
-      <c r="B43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43">
-        <v>2013</v>
-      </c>
-      <c r="F43" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G43" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H43" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>718</v>
-      </c>
-      <c r="K43" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>61</v>
-      </c>
-      <c r="R43">
-        <v>3</v>
-      </c>
-      <c r="S43" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>131680576</v>
-      </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" t="s">
-        <v>24</v>
-      </c>
-      <c r="E44">
-        <v>2013</v>
-      </c>
-      <c r="F44" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G44" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H44" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44">
-        <v>42</v>
-      </c>
-      <c r="J44">
-        <v>718</v>
-      </c>
-      <c r="K44" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>61</v>
-      </c>
-      <c r="R44">
-        <v>3</v>
-      </c>
-      <c r="S44" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>131681083</v>
-      </c>
-      <c r="B45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45">
-        <v>2013</v>
-      </c>
-      <c r="F45" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G45" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H45" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45">
-        <v>42</v>
-      </c>
-      <c r="J45">
-        <v>718</v>
-      </c>
-      <c r="K45" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>61</v>
-      </c>
-      <c r="R45">
-        <v>3</v>
-      </c>
-      <c r="S45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>131685163</v>
-      </c>
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46">
-        <v>2013</v>
-      </c>
-      <c r="F46" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G46" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H46" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46">
-        <v>42</v>
-      </c>
-      <c r="J46">
-        <v>718</v>
-      </c>
-      <c r="K46" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>61</v>
-      </c>
-      <c r="R46">
-        <v>3</v>
-      </c>
-      <c r="S46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>131686158</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47">
-        <v>2013</v>
-      </c>
-      <c r="F47" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G47" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H47" t="s">
-        <v>24</v>
-      </c>
-      <c r="I47">
-        <v>42</v>
-      </c>
-      <c r="J47">
-        <v>718</v>
-      </c>
-      <c r="K47" t="s">
-        <v>24</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>61</v>
-      </c>
-      <c r="R47">
-        <v>3</v>
-      </c>
-      <c r="S47" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>131688800</v>
-      </c>
-      <c r="B48" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48">
-        <v>2013</v>
-      </c>
-      <c r="F48" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G48" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I48">
-        <v>42</v>
-      </c>
-      <c r="J48">
-        <v>718</v>
-      </c>
-      <c r="K48" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>61</v>
-      </c>
-      <c r="R48">
-        <v>3</v>
-      </c>
-      <c r="S48" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>131688829</v>
-      </c>
-      <c r="B49" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49">
-        <v>2013</v>
-      </c>
-      <c r="F49" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G49" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H49" t="s">
-        <v>24</v>
-      </c>
-      <c r="I49">
-        <v>42</v>
-      </c>
-      <c r="J49">
-        <v>718</v>
-      </c>
-      <c r="K49" t="s">
-        <v>24</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>61</v>
-      </c>
-      <c r="R49">
-        <v>3</v>
-      </c>
-      <c r="S49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>131691541</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50">
-        <v>2013</v>
-      </c>
-      <c r="F50" s="1">
-        <v>45727</v>
-      </c>
-      <c r="G50" s="1">
-        <v>45727</v>
-      </c>
-      <c r="H50" t="s">
-        <v>24</v>
-      </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>718</v>
-      </c>
-      <c r="K50" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>61</v>
-      </c>
-      <c r="R50">
-        <v>3</v>
-      </c>
-      <c r="S50" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$36</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$35</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131660406</v>
+        <v>131685214</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -562,10 +562,10 @@
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G2" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -574,7 +574,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131662383</v>
+        <v>131685390</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -618,10 +618,10 @@
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G3" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131662388</v>
+        <v>131688325</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,10 +674,10 @@
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G4" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131662830</v>
+        <v>131688515</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -730,10 +730,10 @@
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G5" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131664970</v>
+        <v>131688997</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -786,10 +786,10 @@
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G6" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -798,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131667968</v>
+        <v>131689209</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -842,10 +842,10 @@
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G7" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -854,7 +854,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131668985</v>
+        <v>131689249</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -898,10 +898,10 @@
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G8" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131670178</v>
+        <v>131689788</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -954,10 +954,10 @@
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G9" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131670186</v>
+        <v>131692330</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1010,10 +1010,10 @@
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G10" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1022,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131670193</v>
+        <v>131692334</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1066,10 +1066,10 @@
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G11" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
@@ -1078,7 +1078,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131670199</v>
+        <v>131692521</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1122,10 +1122,10 @@
         <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G12" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -1134,7 +1134,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131670203</v>
+        <v>131693104</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1178,10 +1178,10 @@
         <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G13" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
@@ -1190,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131670253</v>
+        <v>131695306</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1234,10 +1234,10 @@
         <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G14" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
@@ -1246,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131670264</v>
+        <v>131695805</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1290,10 +1290,10 @@
         <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G15" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1302,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131673780</v>
+        <v>131695812</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1346,10 +1346,10 @@
         <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G16" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1358,7 +1358,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K16" t="s">
         <v>24</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131673832</v>
+        <v>131695814</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -1402,10 +1402,10 @@
         <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G17" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H17" t="s">
         <v>24</v>
@@ -1414,7 +1414,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K17" t="s">
         <v>24</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131676549</v>
+        <v>131695827</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1458,10 +1458,10 @@
         <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G18" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
@@ -1470,7 +1470,7 @@
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K18" t="s">
         <v>24</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131677587</v>
+        <v>131695833</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -1514,10 +1514,10 @@
         <v>601</v>
       </c>
       <c r="F19" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G19" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H19" t="s">
         <v>24</v>
@@ -1526,7 +1526,7 @@
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K19" t="s">
         <v>24</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131677589</v>
+        <v>131695839</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1570,10 +1570,10 @@
         <v>601</v>
       </c>
       <c r="F20" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G20" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
@@ -1582,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K20" t="s">
         <v>24</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131544383</v>
+        <v>131696667</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1626,10 +1626,10 @@
         <v>601</v>
       </c>
       <c r="F21" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G21" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
@@ -1638,7 +1638,7 @@
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K21" t="s">
         <v>24</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131656603</v>
+        <v>131683544</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -1682,10 +1682,10 @@
         <v>601</v>
       </c>
       <c r="F22" s="1">
-        <v>45724</v>
+        <v>45727</v>
       </c>
       <c r="G22" s="1">
-        <v>45724</v>
+        <v>45727</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131656672</v>
+        <v>131685898</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -1738,10 +1738,10 @@
         <v>601</v>
       </c>
       <c r="F23" s="1">
-        <v>45724</v>
+        <v>45727</v>
       </c>
       <c r="G23" s="1">
-        <v>45724</v>
+        <v>45727</v>
       </c>
       <c r="H23" t="s">
         <v>24</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>131667072</v>
+        <v>131686004</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -1794,10 +1794,10 @@
         <v>601</v>
       </c>
       <c r="F24" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G24" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131669307</v>
+        <v>131691485</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -1850,10 +1850,10 @@
         <v>601</v>
       </c>
       <c r="F25" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G25" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>131674526</v>
+        <v>131694871</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -1906,10 +1906,10 @@
         <v>601</v>
       </c>
       <c r="F26" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G26" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>131675085</v>
+        <v>131696550</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -1962,10 +1962,10 @@
         <v>601</v>
       </c>
       <c r="F27" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="G27" s="1">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131675846</v>
+        <v>123058958</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2015,13 +2015,13 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="1">
-        <v>45726</v>
+        <v>44993</v>
       </c>
       <c r="G28" s="1">
-        <v>45726</v>
+        <v>44995</v>
       </c>
       <c r="H28" t="s">
         <v>24</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>131676181</v>
+        <v>131606653</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2071,13 +2071,13 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="1">
-        <v>45726</v>
+        <v>45721</v>
       </c>
       <c r="G29" s="1">
-        <v>45726</v>
+        <v>45721</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
@@ -2086,7 +2086,7 @@
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>131676699</v>
+        <v>131719434</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2127,13 +2127,13 @@
         <v>24</v>
       </c>
       <c r="E30">
-        <v>601</v>
+        <v>2013</v>
       </c>
       <c r="F30" s="1">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="G30" s="1">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="H30" t="s">
         <v>24</v>
@@ -2142,7 +2142,7 @@
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8004</v>
+        <v>718</v>
       </c>
       <c r="K30" t="s">
         <v>24</v>
@@ -2165,13 +2165,16 @@
       <c r="Q30">
         <v>61</v>
       </c>
+      <c r="R30">
+        <v>3</v>
+      </c>
       <c r="S30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>123058958</v>
+        <v>131729239</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -2183,13 +2186,13 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F31" s="1">
-        <v>44993</v>
+        <v>45729</v>
       </c>
       <c r="G31" s="1">
-        <v>44995</v>
+        <v>45729</v>
       </c>
       <c r="H31" t="s">
         <v>24</v>
@@ -2198,7 +2201,7 @@
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2221,13 +2224,16 @@
       <c r="Q31">
         <v>61</v>
       </c>
+      <c r="R31">
+        <v>3</v>
+      </c>
       <c r="S31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>131606653</v>
+        <v>131730310</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -2239,13 +2245,13 @@
         <v>24</v>
       </c>
       <c r="E32">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F32" s="1">
-        <v>45721</v>
+        <v>45729</v>
       </c>
       <c r="G32" s="1">
-        <v>45721</v>
+        <v>45729</v>
       </c>
       <c r="H32" t="s">
         <v>24</v>
@@ -2254,7 +2260,7 @@
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8021</v>
+        <v>718</v>
       </c>
       <c r="K32" t="s">
         <v>24</v>
@@ -2277,13 +2283,16 @@
       <c r="Q32">
         <v>61</v>
       </c>
+      <c r="R32">
+        <v>3</v>
+      </c>
       <c r="S32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>131660184</v>
+        <v>131730773</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -2295,13 +2304,13 @@
         <v>24</v>
       </c>
       <c r="E33">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F33" s="1">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="G33" s="1">
-        <v>45727</v>
+        <v>45729</v>
       </c>
       <c r="H33" t="s">
         <v>24</v>
@@ -2310,7 +2319,7 @@
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8021</v>
+        <v>718</v>
       </c>
       <c r="K33" t="s">
         <v>24</v>
@@ -2333,13 +2342,16 @@
       <c r="Q33">
         <v>61</v>
       </c>
+      <c r="R33">
+        <v>3</v>
+      </c>
       <c r="S33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>130647855</v>
+        <v>131733916</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -2351,13 +2363,13 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F34" s="1">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="G34" s="1">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2366,7 +2378,7 @@
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2389,13 +2401,16 @@
       <c r="Q34">
         <v>61</v>
       </c>
+      <c r="R34">
+        <v>3</v>
+      </c>
       <c r="S34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>130759449</v>
+        <v>131734218</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -2407,13 +2422,13 @@
         <v>24</v>
       </c>
       <c r="E35">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F35" s="1">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="G35" s="1">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -2422,7 +2437,7 @@
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8001</v>
+        <v>718</v>
       </c>
       <c r="K35" t="s">
         <v>24</v>
@@ -2445,64 +2460,11 @@
       <c r="Q35">
         <v>61</v>
       </c>
+      <c r="R35">
+        <v>3</v>
+      </c>
       <c r="S35" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>130647855</v>
-      </c>
-      <c r="B36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36">
-        <v>1211</v>
-      </c>
-      <c r="F36" s="1">
-        <v>45726</v>
-      </c>
-      <c r="G36" s="1">
-        <v>45728</v>
-      </c>
-      <c r="H36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8001</v>
-      </c>
-      <c r="K36" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-      <c r="S36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$3</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$23</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131761706</v>
+        <v>131765099</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -559,13 +559,13 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45731</v>
+        <v>45733</v>
       </c>
       <c r="G2" s="1">
-        <v>45732</v>
+        <v>45733</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -574,7 +574,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>123058958</v>
+        <v>131765390</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -615,13 +615,13 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>44993</v>
+        <v>45733</v>
       </c>
       <c r="G3" s="1">
-        <v>44995</v>
+        <v>45733</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -655,6 +655,1159 @@
       </c>
       <c r="S3" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>131779877</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>601</v>
+      </c>
+      <c r="F4" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>42</v>
+      </c>
+      <c r="J4">
+        <v>8004</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>61</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>131780556</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>601</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5">
+        <v>42</v>
+      </c>
+      <c r="J5">
+        <v>8013</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>61</v>
+      </c>
+      <c r="S5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>131766060</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>601</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>42</v>
+      </c>
+      <c r="J6">
+        <v>8013</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>61</v>
+      </c>
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>131766242</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>601</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>42</v>
+      </c>
+      <c r="J7">
+        <v>8004</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>61</v>
+      </c>
+      <c r="S7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>131767452</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8">
+        <v>601</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>42</v>
+      </c>
+      <c r="J8">
+        <v>8004</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>61</v>
+      </c>
+      <c r="S8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>131767569</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>601</v>
+      </c>
+      <c r="F9" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>42</v>
+      </c>
+      <c r="J9">
+        <v>8004</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>61</v>
+      </c>
+      <c r="S9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>131768249</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10">
+        <v>601</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G10" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>8004</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>131780034</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>601</v>
+      </c>
+      <c r="F11" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G11" s="1">
+        <v>45733</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>8004</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>61</v>
+      </c>
+      <c r="S11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>123058958</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12">
+        <v>1211</v>
+      </c>
+      <c r="F12" s="1">
+        <v>44993</v>
+      </c>
+      <c r="G12" s="1">
+        <v>44995</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>42</v>
+      </c>
+      <c r="J12">
+        <v>8001</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>61</v>
+      </c>
+      <c r="S12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>131803273</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13">
+        <v>2013</v>
+      </c>
+      <c r="F13" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G13" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>718</v>
+      </c>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>61</v>
+      </c>
+      <c r="R13">
+        <v>3</v>
+      </c>
+      <c r="S13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>131803645</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>2013</v>
+      </c>
+      <c r="F14" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G14" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14">
+        <v>42</v>
+      </c>
+      <c r="J14">
+        <v>718</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>61</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>131803980</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>2013</v>
+      </c>
+      <c r="F15" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G15" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>718</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>61</v>
+      </c>
+      <c r="R15">
+        <v>3</v>
+      </c>
+      <c r="S15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>131804186</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>2013</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>42</v>
+      </c>
+      <c r="J16">
+        <v>718</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>61</v>
+      </c>
+      <c r="R16">
+        <v>3</v>
+      </c>
+      <c r="S16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>131804252</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17">
+        <v>2013</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G17" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17">
+        <v>42</v>
+      </c>
+      <c r="J17">
+        <v>718</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>61</v>
+      </c>
+      <c r="R17">
+        <v>3</v>
+      </c>
+      <c r="S17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>131808011</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>2013</v>
+      </c>
+      <c r="F18" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G18" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>718</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>61</v>
+      </c>
+      <c r="R18">
+        <v>3</v>
+      </c>
+      <c r="S18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>131810176</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>2013</v>
+      </c>
+      <c r="F19" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G19" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>42</v>
+      </c>
+      <c r="J19">
+        <v>718</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>61</v>
+      </c>
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>131813561</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>2013</v>
+      </c>
+      <c r="F20" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G20" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20">
+        <v>42</v>
+      </c>
+      <c r="J20">
+        <v>718</v>
+      </c>
+      <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>61</v>
+      </c>
+      <c r="R20">
+        <v>3</v>
+      </c>
+      <c r="S20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>131815132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21">
+        <v>2013</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>42</v>
+      </c>
+      <c r="J21">
+        <v>718</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>61</v>
+      </c>
+      <c r="R21">
+        <v>3</v>
+      </c>
+      <c r="S21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>131815330</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>2013</v>
+      </c>
+      <c r="F22" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G22" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>42</v>
+      </c>
+      <c r="J22">
+        <v>718</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>61</v>
+      </c>
+      <c r="R22">
+        <v>3</v>
+      </c>
+      <c r="S22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>131815546</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>2013</v>
+      </c>
+      <c r="F23" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>718</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>61</v>
+      </c>
+      <c r="R23">
+        <v>3</v>
+      </c>
+      <c r="S23" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$23</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$77</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131765099</v>
+        <v>131813111</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -562,10 +562,10 @@
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="G2" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -574,7 +574,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131765390</v>
+        <v>131813112</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -618,10 +618,10 @@
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="G3" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131779877</v>
+        <v>131838196</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,10 +674,10 @@
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45733</v>
+        <v>45736</v>
       </c>
       <c r="G4" s="1">
-        <v>45733</v>
+        <v>45736</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -686,7 +686,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131780556</v>
+        <v>131857211</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -730,10 +730,10 @@
         <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45733</v>
+        <v>45737</v>
       </c>
       <c r="G5" s="1">
-        <v>45733</v>
+        <v>45737</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131766060</v>
+        <v>131804744</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -786,10 +786,10 @@
         <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="G6" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -798,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131766242</v>
+        <v>131806168</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -842,10 +842,10 @@
         <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="G7" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131767452</v>
+        <v>131807508</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -898,10 +898,10 @@
         <v>601</v>
       </c>
       <c r="F8" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="G8" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131767569</v>
+        <v>131808640</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -954,10 +954,10 @@
         <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="G9" s="1">
-        <v>45733</v>
+        <v>45735</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131768249</v>
+        <v>131826146</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1010,10 +1010,10 @@
         <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45733</v>
+        <v>45736</v>
       </c>
       <c r="G10" s="1">
-        <v>45733</v>
+        <v>45736</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131780034</v>
+        <v>131841586</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1066,10 +1066,10 @@
         <v>601</v>
       </c>
       <c r="F11" s="1">
-        <v>45733</v>
+        <v>45737</v>
       </c>
       <c r="G11" s="1">
-        <v>45733</v>
+        <v>45737</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>123058958</v>
+        <v>131843133</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1119,13 +1119,13 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F12" s="1">
-        <v>44993</v>
+        <v>45737</v>
       </c>
       <c r="G12" s="1">
-        <v>44995</v>
+        <v>45737</v>
       </c>
       <c r="H12" t="s">
         <v>24</v>
@@ -1134,7 +1134,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131803273</v>
+        <v>131843963</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1175,13 +1175,13 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F13" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G13" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H13" t="s">
         <v>24</v>
@@ -1190,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1213,16 +1213,13 @@
       <c r="Q13">
         <v>61</v>
       </c>
-      <c r="R13">
-        <v>3</v>
-      </c>
       <c r="S13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131803645</v>
+        <v>131844111</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1234,13 +1231,13 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G14" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
@@ -1249,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1272,16 +1269,13 @@
       <c r="Q14">
         <v>61</v>
       </c>
-      <c r="R14">
-        <v>3</v>
-      </c>
       <c r="S14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131803980</v>
+        <v>131845574</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1293,13 +1287,13 @@
         <v>24</v>
       </c>
       <c r="E15">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G15" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1308,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -1331,16 +1325,13 @@
       <c r="Q15">
         <v>61</v>
       </c>
-      <c r="R15">
-        <v>3</v>
-      </c>
       <c r="S15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131804186</v>
+        <v>131845834</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1352,13 +1343,13 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G16" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1367,7 +1358,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K16" t="s">
         <v>24</v>
@@ -1390,16 +1381,13 @@
       <c r="Q16">
         <v>61</v>
       </c>
-      <c r="R16">
-        <v>3</v>
-      </c>
       <c r="S16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131804252</v>
+        <v>131850100</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -1411,13 +1399,13 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G17" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H17" t="s">
         <v>24</v>
@@ -1426,7 +1414,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K17" t="s">
         <v>24</v>
@@ -1449,16 +1437,13 @@
       <c r="Q17">
         <v>61</v>
       </c>
-      <c r="R17">
-        <v>3</v>
-      </c>
       <c r="S17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131808011</v>
+        <v>131855882</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1470,13 +1455,13 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G18" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
@@ -1485,7 +1470,7 @@
         <v>42</v>
       </c>
       <c r="J18">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K18" t="s">
         <v>24</v>
@@ -1508,16 +1493,13 @@
       <c r="Q18">
         <v>61</v>
       </c>
-      <c r="R18">
-        <v>3</v>
-      </c>
       <c r="S18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131810176</v>
+        <v>131857562</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -1529,13 +1511,13 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F19" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G19" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H19" t="s">
         <v>24</v>
@@ -1544,7 +1526,7 @@
         <v>42</v>
       </c>
       <c r="J19">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K19" t="s">
         <v>24</v>
@@ -1567,16 +1549,13 @@
       <c r="Q19">
         <v>61</v>
       </c>
-      <c r="R19">
-        <v>3</v>
-      </c>
       <c r="S19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131813561</v>
+        <v>131831723</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1588,13 +1567,13 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F20" s="1">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="G20" s="1">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
@@ -1603,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="J20">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K20" t="s">
         <v>24</v>
@@ -1626,16 +1605,13 @@
       <c r="Q20">
         <v>61</v>
       </c>
-      <c r="R20">
-        <v>3</v>
-      </c>
       <c r="S20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131815132</v>
+        <v>131834493</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1647,13 +1623,13 @@
         <v>24</v>
       </c>
       <c r="E21">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F21" s="1">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="G21" s="1">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
@@ -1662,7 +1638,7 @@
         <v>42</v>
       </c>
       <c r="J21">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K21" t="s">
         <v>24</v>
@@ -1685,16 +1661,13 @@
       <c r="Q21">
         <v>61</v>
       </c>
-      <c r="R21">
-        <v>3</v>
-      </c>
       <c r="S21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131815330</v>
+        <v>131842141</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -1706,13 +1679,13 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F22" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="G22" s="1">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1721,7 +1694,7 @@
         <v>42</v>
       </c>
       <c r="J22">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -1744,16 +1717,13 @@
       <c r="Q22">
         <v>61</v>
       </c>
-      <c r="R22">
-        <v>3</v>
-      </c>
       <c r="S22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131815546</v>
+        <v>131846839</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -1765,49 +1735,3070 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F23" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G23" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>8004</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>61</v>
+      </c>
+      <c r="S23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>131847633</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>609</v>
+      </c>
+      <c r="F24" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G24" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24">
+        <v>42</v>
+      </c>
+      <c r="J24">
+        <v>8004</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>61</v>
+      </c>
+      <c r="S24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>131848520</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>609</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G25" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25">
+        <v>42</v>
+      </c>
+      <c r="J25">
+        <v>8004</v>
+      </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>61</v>
+      </c>
+      <c r="S25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>131849385</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>609</v>
+      </c>
+      <c r="F26" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G26" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>8004</v>
+      </c>
+      <c r="K26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>61</v>
+      </c>
+      <c r="S26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>131784868</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27">
+        <v>1211</v>
+      </c>
+      <c r="F27" s="1">
+        <v>45734</v>
+      </c>
+      <c r="G27" s="1">
         <v>45735</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27">
+        <v>42</v>
+      </c>
+      <c r="J27">
+        <v>1735</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>61</v>
+      </c>
+      <c r="S27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>131788622</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28">
+        <v>1213</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45734</v>
+      </c>
+      <c r="G28" s="1">
+        <v>45734</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28">
+        <v>42</v>
+      </c>
+      <c r="J28">
+        <v>1735</v>
+      </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+      <c r="S28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>131790676</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29">
+        <v>1211</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45734</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45734</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29">
+        <v>42</v>
+      </c>
+      <c r="J29">
+        <v>1735</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>61</v>
+      </c>
+      <c r="S29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>131800590</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>1212</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45734</v>
+      </c>
+      <c r="G30" s="1">
+        <v>45734</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>1735</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>61</v>
+      </c>
+      <c r="S30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>131802165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31">
+        <v>1211</v>
+      </c>
+      <c r="F31" s="1">
+        <v>45734</v>
+      </c>
+      <c r="G31" s="1">
+        <v>45734</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>1735</v>
+      </c>
+      <c r="K31" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>61</v>
+      </c>
+      <c r="S31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>131802199</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="1">
+        <v>45734</v>
+      </c>
+      <c r="G32" s="1">
+        <v>45734</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>1735</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+      <c r="S32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>131808833</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33">
+        <v>1212</v>
+      </c>
+      <c r="F33" s="1">
         <v>45735</v>
       </c>
-      <c r="H23" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23">
-        <v>42</v>
-      </c>
-      <c r="J23">
-        <v>718</v>
-      </c>
-      <c r="K23" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>61</v>
-      </c>
-      <c r="R23">
-        <v>3</v>
-      </c>
-      <c r="S23" t="s">
-        <v>25</v>
+      <c r="G33" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>1735</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+      <c r="S33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>131811596</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34">
+        <v>1211</v>
+      </c>
+      <c r="F34" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G34" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>1735</v>
+      </c>
+      <c r="K34" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+      <c r="S34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>131815545</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G35" s="1">
+        <v>45735</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>1735</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+      <c r="S35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>131817863</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G36" s="1">
+        <v>45736</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>1735</v>
+      </c>
+      <c r="K36" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+      <c r="S36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>131821942</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G37" s="1">
+        <v>45736</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>1735</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+      <c r="S37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>131822087</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G38" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>1735</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+      <c r="S38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>131835699</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G39" s="1">
+        <v>45736</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>1735</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+      <c r="S39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>131837872</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G40" s="1">
+        <v>45736</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>1735</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+      <c r="S40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>131838151</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G41" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>1735</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+      <c r="S41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>123058958</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="1">
+        <v>44993</v>
+      </c>
+      <c r="G42" s="1">
+        <v>44995</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8001</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+      <c r="S42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>131821059</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G43" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8021</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+      <c r="S43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>128247602</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G44" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8001</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+      <c r="S44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>128344483</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G45" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8001</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+      <c r="S45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>128382395</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G46" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8001</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+      <c r="S46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>128762462</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G47" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8001</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+      <c r="S47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>128783447</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G48" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>8001</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+      <c r="S48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>129969131</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G49" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8001</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+      <c r="S49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>130016478</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50">
+        <v>2002</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+      <c r="S50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>130410543</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G51" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+      <c r="S51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>130495588</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G52" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8001</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+      <c r="S52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>130629472</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53">
+        <v>1213</v>
+      </c>
+      <c r="F53" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G53" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+      <c r="S53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>130872228</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G54" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H54" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8001</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+      <c r="S54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>130891387</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G55" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+      <c r="S55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>131189555</v>
+      </c>
+      <c r="B56" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G56" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8001</v>
+      </c>
+      <c r="K56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+      <c r="S56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>131362867</v>
+      </c>
+      <c r="B57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G57" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8001</v>
+      </c>
+      <c r="K57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+      <c r="S57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>131477144</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G58" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+      <c r="S58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>131568519</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H59" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8001</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+      <c r="S59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>131593065</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G60" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+      <c r="S60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>131622448</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G61" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+      <c r="S61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>131735489</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G62" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+      <c r="S62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>131790822</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G63" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+      <c r="S63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>128247602</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G64" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+      <c r="S64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>128344483</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G65" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+      <c r="S65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>128382395</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G66" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+      <c r="S66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>129969131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+      <c r="S67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>130016478</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68">
+        <v>2002</v>
+      </c>
+      <c r="F68" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G68" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8001</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+      <c r="S68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>130891387</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+      <c r="S69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>131189555</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G70" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8001</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+      <c r="S70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>131362867</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H71" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+      <c r="S71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>131477144</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+      <c r="S72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>131568519</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G73" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+      <c r="S73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>131593065</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H74" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+      <c r="S74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>131622448</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8001</v>
+      </c>
+      <c r="K75" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+      <c r="S75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>131735489</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8001</v>
+      </c>
+      <c r="K76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+      <c r="S76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>131790822</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45737</v>
+      </c>
+      <c r="H77" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8001</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+      <c r="S77" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$97</definedName>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$60</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$147</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
   <extLst>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>131886159</v>
+        <v>131904570</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -562,10 +562,10 @@
         <v>601</v>
       </c>
       <c r="F2" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="G2" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H2" t="s">
         <v>24</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131893152</v>
+        <v>131904573</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -618,10 +618,10 @@
         <v>601</v>
       </c>
       <c r="F3" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="G3" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -630,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>131884504</v>
+        <v>131904575</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -674,10 +674,10 @@
         <v>601</v>
       </c>
       <c r="F4" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="G4" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -686,7 +686,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>131894378</v>
+        <v>131904577</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -727,13 +727,13 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F5" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="G5" s="1">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -742,7 +742,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131913706</v>
+        <v>131909702</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -783,13 +783,13 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F6" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G6" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
@@ -798,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131913708</v>
+        <v>131909959</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -839,13 +839,13 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F7" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G7" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
@@ -854,7 +854,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131913959</v>
+        <v>131910291</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -895,7 +895,7 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F8" s="1">
         <v>45743</v>
@@ -910,7 +910,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131914171</v>
+        <v>131918117</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -951,13 +951,13 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F9" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G9" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>131914225</v>
+        <v>131918666</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -1007,13 +1007,13 @@
         <v>24</v>
       </c>
       <c r="E10">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F10" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G10" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H10" t="s">
         <v>24</v>
@@ -1022,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>131914276</v>
+        <v>131919366</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F11" s="1">
         <v>45743</v>
@@ -1078,7 +1078,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8021</v>
+        <v>8013</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>131914331</v>
+        <v>131919437</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -1119,7 +1119,7 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F12" s="1">
         <v>45743</v>
@@ -1134,7 +1134,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8021</v>
+        <v>8013</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>131914366</v>
+        <v>131919438</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1175,7 +1175,7 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F13" s="1">
         <v>45743</v>
@@ -1190,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8021</v>
+        <v>8013</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>131915796</v>
+        <v>131919505</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1231,7 +1231,7 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F14" s="1">
         <v>45743</v>
@@ -1246,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8021</v>
+        <v>8013</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>131915889</v>
+        <v>131941267</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -1287,13 +1287,13 @@
         <v>24</v>
       </c>
       <c r="E15">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F15" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G15" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H15" t="s">
         <v>24</v>
@@ -1302,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K15" t="s">
         <v>24</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>131915952</v>
+        <v>131942169</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -1343,13 +1343,13 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F16" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G16" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -1358,7 +1358,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8021</v>
+        <v>8013</v>
       </c>
       <c r="K16" t="s">
         <v>24</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>131915959</v>
+        <v>131943603</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -1399,13 +1399,13 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F17" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G17" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H17" t="s">
         <v>24</v>
@@ -1414,7 +1414,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K17" t="s">
         <v>24</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>131915982</v>
+        <v>131946438</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -1455,13 +1455,13 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F18" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G18" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H18" t="s">
         <v>24</v>
@@ -1470,7 +1470,7 @@
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K18" t="s">
         <v>24</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>131916001</v>
+        <v>131917759</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -1511,7 +1511,7 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F19" s="1">
         <v>45743</v>
@@ -1526,7 +1526,7 @@
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K19" t="s">
         <v>24</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>131917578</v>
+        <v>131921537</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1567,7 +1567,7 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F20" s="1">
         <v>45743</v>
@@ -1582,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K20" t="s">
         <v>24</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>131917647</v>
+        <v>131937561</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1623,13 +1623,13 @@
         <v>24</v>
       </c>
       <c r="E21">
-        <v>2013</v>
+        <v>609</v>
       </c>
       <c r="F21" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G21" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
@@ -1638,7 +1638,7 @@
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K21" t="s">
         <v>24</v>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>131918124</v>
+        <v>131898877</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -1679,13 +1679,13 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F22" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G22" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
@@ -1694,7 +1694,7 @@
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K22" t="s">
         <v>24</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>131919535</v>
+        <v>131903652</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>2024</v>
+        <v>601</v>
       </c>
       <c r="F23" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G23" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H23" t="s">
         <v>24</v>
@@ -1750,7 +1750,7 @@
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K23" t="s">
         <v>24</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>131919806</v>
+        <v>131908411</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -1791,13 +1791,13 @@
         <v>24</v>
       </c>
       <c r="E24">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F24" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G24" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
@@ -1806,7 +1806,7 @@
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>131920153</v>
+        <v>131909573</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -1847,13 +1847,13 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F25" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G25" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H25" t="s">
         <v>24</v>
@@ -1862,7 +1862,7 @@
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>131920216</v>
+        <v>131926535</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -1903,7 +1903,7 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F26" s="1">
         <v>45743</v>
@@ -1918,7 +1918,7 @@
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K26" t="s">
         <v>24</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>131921823</v>
+        <v>131927527</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
@@ -1959,7 +1959,7 @@
         <v>24</v>
       </c>
       <c r="E27">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F27" s="1">
         <v>45743</v>
@@ -1974,7 +1974,7 @@
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K27" t="s">
         <v>24</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131921985</v>
+        <v>131927973</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
@@ -2015,7 +2015,7 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F28" s="1">
         <v>45743</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K28" t="s">
         <v>24</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>131922114</v>
+        <v>131937712</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
@@ -2071,13 +2071,13 @@
         <v>24</v>
       </c>
       <c r="E29">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F29" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="G29" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
@@ -2086,7 +2086,7 @@
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="K29" t="s">
         <v>24</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>131923765</v>
+        <v>131885620</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -2127,13 +2127,13 @@
         <v>24</v>
       </c>
       <c r="E30">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="1">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="G30" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H30" t="s">
         <v>24</v>
@@ -2142,7 +2142,7 @@
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K30" t="s">
         <v>24</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>131923865</v>
+        <v>131887121</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -2183,13 +2183,13 @@
         <v>24</v>
       </c>
       <c r="E31">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="1">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="G31" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H31" t="s">
         <v>24</v>
@@ -2198,7 +2198,7 @@
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K31" t="s">
         <v>24</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>131923914</v>
+        <v>131888204</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -2239,13 +2239,13 @@
         <v>24</v>
       </c>
       <c r="E32">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="1">
-        <v>45743</v>
+        <v>45741</v>
       </c>
       <c r="G32" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H32" t="s">
         <v>24</v>
@@ -2254,7 +2254,7 @@
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K32" t="s">
         <v>24</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>131924034</v>
+        <v>131900236</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -2295,13 +2295,13 @@
         <v>24</v>
       </c>
       <c r="E33">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G33" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H33" t="s">
         <v>24</v>
@@ -2310,7 +2310,7 @@
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K33" t="s">
         <v>24</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>131924179</v>
+        <v>131902732</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -2351,13 +2351,13 @@
         <v>24</v>
       </c>
       <c r="E34">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G34" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2366,7 +2366,7 @@
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>131924194</v>
+        <v>131903854</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -2407,13 +2407,13 @@
         <v>24</v>
       </c>
       <c r="E35">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G35" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -2422,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K35" t="s">
         <v>24</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>131925362</v>
+        <v>131904591</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2463,10 +2463,10 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G36" s="1">
         <v>45743</v>
@@ -2478,7 +2478,7 @@
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K36" t="s">
         <v>24</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>131925591</v>
+        <v>131905881</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -2519,13 +2519,13 @@
         <v>24</v>
       </c>
       <c r="E37">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="G37" s="1">
-        <v>45743</v>
+        <v>45742</v>
       </c>
       <c r="H37" t="s">
         <v>24</v>
@@ -2534,7 +2534,7 @@
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K37" t="s">
         <v>24</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>131925817</v>
+        <v>131915499</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -2575,7 +2575,7 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>2013</v>
+        <v>1213</v>
       </c>
       <c r="F38" s="1">
         <v>45743</v>
@@ -2590,7 +2590,7 @@
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K38" t="s">
         <v>24</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>131925825</v>
+        <v>131917678</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -2631,7 +2631,7 @@
         <v>24</v>
       </c>
       <c r="E39">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="1">
         <v>45743</v>
@@ -2646,7 +2646,7 @@
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K39" t="s">
         <v>24</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>131925866</v>
+        <v>131919432</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -2687,13 +2687,13 @@
         <v>24</v>
       </c>
       <c r="E40">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="1">
         <v>45743</v>
       </c>
       <c r="G40" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H40" t="s">
         <v>24</v>
@@ -2702,7 +2702,7 @@
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K40" t="s">
         <v>24</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>131926013</v>
+        <v>131924008</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
@@ -2743,7 +2743,7 @@
         <v>24</v>
       </c>
       <c r="E41">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="1">
         <v>45743</v>
@@ -2758,7 +2758,7 @@
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K41" t="s">
         <v>24</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>131927655</v>
+        <v>131931004</v>
       </c>
       <c r="B42" t="s">
         <v>24</v>
@@ -2799,7 +2799,7 @@
         <v>24</v>
       </c>
       <c r="E42">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="1">
         <v>45743</v>
@@ -2814,7 +2814,7 @@
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K42" t="s">
         <v>24</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>131927731</v>
+        <v>131931230</v>
       </c>
       <c r="B43" t="s">
         <v>24</v>
@@ -2855,13 +2855,13 @@
         <v>24</v>
       </c>
       <c r="E43">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="1">
         <v>45743</v>
       </c>
       <c r="G43" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H43" t="s">
         <v>24</v>
@@ -2870,7 +2870,7 @@
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="K43" t="s">
         <v>24</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>131927776</v>
+        <v>123058958</v>
       </c>
       <c r="B44" t="s">
         <v>24</v>
@@ -2911,13 +2911,13 @@
         <v>24</v>
       </c>
       <c r="E44">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="1">
-        <v>45743</v>
+        <v>44993</v>
       </c>
       <c r="G44" s="1">
-        <v>45743</v>
+        <v>44995</v>
       </c>
       <c r="H44" t="s">
         <v>24</v>
@@ -2926,7 +2926,7 @@
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K44" t="s">
         <v>24</v>
@@ -2955,7 +2955,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>131927841</v>
+        <v>128004544</v>
       </c>
       <c r="B45" t="s">
         <v>24</v>
@@ -2967,13 +2967,13 @@
         <v>24</v>
       </c>
       <c r="E45">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="1">
         <v>45743</v>
       </c>
       <c r="G45" s="1">
-        <v>45743</v>
+        <v>45745</v>
       </c>
       <c r="H45" t="s">
         <v>24</v>
@@ -2982,7 +2982,7 @@
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K45" t="s">
         <v>24</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>131927943</v>
+        <v>128545834</v>
       </c>
       <c r="B46" t="s">
         <v>24</v>
@@ -3023,7 +3023,7 @@
         <v>24</v>
       </c>
       <c r="E46">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="1">
         <v>45743</v>
@@ -3038,7 +3038,7 @@
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K46" t="s">
         <v>24</v>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>131929116</v>
+        <v>129350308</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
@@ -3079,13 +3079,13 @@
         <v>24</v>
       </c>
       <c r="E47">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="1">
         <v>45743</v>
       </c>
       <c r="G47" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H47" t="s">
         <v>24</v>
@@ -3094,7 +3094,7 @@
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K47" t="s">
         <v>24</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>131929154</v>
+        <v>130154461</v>
       </c>
       <c r="B48" t="s">
         <v>24</v>
@@ -3135,13 +3135,13 @@
         <v>24</v>
       </c>
       <c r="E48">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="1">
         <v>45743</v>
       </c>
       <c r="G48" s="1">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H48" t="s">
         <v>24</v>
@@ -3150,7 +3150,7 @@
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K48" t="s">
         <v>24</v>
@@ -3179,7 +3179,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>131929343</v>
+        <v>131750513</v>
       </c>
       <c r="B49" t="s">
         <v>24</v>
@@ -3191,13 +3191,13 @@
         <v>24</v>
       </c>
       <c r="E49">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="G49" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="H49" t="s">
         <v>24</v>
@@ -3206,7 +3206,7 @@
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K49" t="s">
         <v>24</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>131929411</v>
+        <v>131923044</v>
       </c>
       <c r="B50" t="s">
         <v>24</v>
@@ -3262,7 +3262,7 @@
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K50" t="s">
         <v>24</v>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>131929475</v>
+        <v>131953158</v>
       </c>
       <c r="B51" t="s">
         <v>24</v>
@@ -3303,13 +3303,13 @@
         <v>24</v>
       </c>
       <c r="E51">
-        <v>2024</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="G51" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="H51" t="s">
         <v>24</v>
@@ -3318,7 +3318,7 @@
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K51" t="s">
         <v>24</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>131929512</v>
+        <v>131953161</v>
       </c>
       <c r="B52" t="s">
         <v>24</v>
@@ -3359,13 +3359,13 @@
         <v>24</v>
       </c>
       <c r="E52">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="G52" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="H52" t="s">
         <v>24</v>
@@ -3374,7 +3374,7 @@
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K52" t="s">
         <v>24</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>131929522</v>
+        <v>131953191</v>
       </c>
       <c r="B53" t="s">
         <v>24</v>
@@ -3415,13 +3415,13 @@
         <v>24</v>
       </c>
       <c r="E53">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="G53" s="1">
-        <v>45743</v>
+        <v>45746</v>
       </c>
       <c r="H53" t="s">
         <v>24</v>
@@ -3430,7 +3430,7 @@
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K53" t="s">
         <v>24</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>131871035</v>
+        <v>131953278</v>
       </c>
       <c r="B54" t="s">
         <v>24</v>
@@ -3474,10 +3474,10 @@
         <v>1211</v>
       </c>
       <c r="F54" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="G54" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="H54" t="s">
         <v>24</v>
@@ -3486,7 +3486,7 @@
         <v>42</v>
       </c>
       <c r="J54">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K54" t="s">
         <v>24</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>131872573</v>
+        <v>131953286</v>
       </c>
       <c r="B55" t="s">
         <v>24</v>
@@ -3530,10 +3530,10 @@
         <v>1211</v>
       </c>
       <c r="F55" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="G55" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="H55" t="s">
         <v>24</v>
@@ -3542,7 +3542,7 @@
         <v>42</v>
       </c>
       <c r="J55">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K55" t="s">
         <v>24</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>131876211</v>
+        <v>131953289</v>
       </c>
       <c r="B56" t="s">
         <v>24</v>
@@ -3586,10 +3586,10 @@
         <v>1211</v>
       </c>
       <c r="F56" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="G56" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="H56" t="s">
         <v>24</v>
@@ -3598,7 +3598,7 @@
         <v>42</v>
       </c>
       <c r="J56">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K56" t="s">
         <v>24</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>131878891</v>
+        <v>131953292</v>
       </c>
       <c r="B57" t="s">
         <v>24</v>
@@ -3639,13 +3639,13 @@
         <v>24</v>
       </c>
       <c r="E57">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="G57" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="H57" t="s">
         <v>24</v>
@@ -3654,7 +3654,7 @@
         <v>42</v>
       </c>
       <c r="J57">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K57" t="s">
         <v>24</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>131880227</v>
+        <v>131953297</v>
       </c>
       <c r="B58" t="s">
         <v>24</v>
@@ -3698,10 +3698,10 @@
         <v>1211</v>
       </c>
       <c r="F58" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="G58" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="H58" t="s">
         <v>24</v>
@@ -3710,7 +3710,7 @@
         <v>42</v>
       </c>
       <c r="J58">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K58" t="s">
         <v>24</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>131881149</v>
+        <v>131953307</v>
       </c>
       <c r="B59" t="s">
         <v>24</v>
@@ -3751,13 +3751,13 @@
         <v>24</v>
       </c>
       <c r="E59">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F59" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="G59" s="1">
-        <v>45740</v>
+        <v>45746</v>
       </c>
       <c r="H59" t="s">
         <v>24</v>
@@ -3766,7 +3766,7 @@
         <v>42</v>
       </c>
       <c r="J59">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="K59" t="s">
         <v>24</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>123058958</v>
+        <v>131953314</v>
       </c>
       <c r="B60" t="s">
         <v>24</v>
@@ -3810,10 +3810,10 @@
         <v>1211</v>
       </c>
       <c r="F60" s="1">
-        <v>44993</v>
+        <v>45746</v>
       </c>
       <c r="G60" s="1">
-        <v>44995</v>
+        <v>45746</v>
       </c>
       <c r="H60" t="s">
         <v>24</v>
@@ -3846,6 +3846,4878 @@
         <v>61</v>
       </c>
       <c r="S60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>131953317</v>
+      </c>
+      <c r="B61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G61" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+      <c r="S61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>131953341</v>
+      </c>
+      <c r="B62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G62" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+      <c r="S62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>131953388</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G63" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+      <c r="S63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>131953413</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G64" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+      <c r="S64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>131953418</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G65" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+      <c r="S65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>131953419</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G66" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+      <c r="S66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>131953431</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+      <c r="S67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>131953438</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68">
+        <v>1213</v>
+      </c>
+      <c r="F68" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G68" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8001</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+      <c r="S68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>131953440</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G69" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+      <c r="S69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>131953456</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70">
+        <v>1212</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G70" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8001</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+      <c r="S70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>131953484</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G71" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H71" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+      <c r="S71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>131953497</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G72" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+      <c r="S72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>131953518</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G73" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+      <c r="S73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>131953594</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74">
+        <v>2024</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G74" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H74" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+      <c r="S74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>131953603</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G75" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8001</v>
+      </c>
+      <c r="K75" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+      <c r="S75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>131953686</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G76" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8001</v>
+      </c>
+      <c r="K76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+      <c r="S76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>131953699</v>
+      </c>
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H77" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8001</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+      <c r="S77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>131953708</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78">
+        <v>1212</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G78" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+      <c r="S78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>131953711</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79">
+        <v>2013</v>
+      </c>
+      <c r="F79" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G79" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8001</v>
+      </c>
+      <c r="K79" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+      <c r="S79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>131953736</v>
+      </c>
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80">
+        <v>1211</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G80" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H80" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8001</v>
+      </c>
+      <c r="K80" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+      <c r="S80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>131953764</v>
+      </c>
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81">
+        <v>2013</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G81" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8001</v>
+      </c>
+      <c r="K81" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+      <c r="S81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>131953992</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G82" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8001</v>
+      </c>
+      <c r="K82" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+      <c r="S82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>131954034</v>
+      </c>
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83">
+        <v>1211</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G83" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8001</v>
+      </c>
+      <c r="K83" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+      <c r="S83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>131954041</v>
+      </c>
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G84" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H84" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8001</v>
+      </c>
+      <c r="K84" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+      <c r="S84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>131954042</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85">
+        <v>1211</v>
+      </c>
+      <c r="F85" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G85" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H85" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8001</v>
+      </c>
+      <c r="K85" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+      <c r="S85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>131954057</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86">
+        <v>2013</v>
+      </c>
+      <c r="F86" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G86" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8001</v>
+      </c>
+      <c r="K86" t="s">
+        <v>24</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+      <c r="S86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>131954084</v>
+      </c>
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87">
+        <v>2013</v>
+      </c>
+      <c r="F87" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H87" t="s">
+        <v>24</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8001</v>
+      </c>
+      <c r="K87" t="s">
+        <v>24</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+      <c r="S87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>131954095</v>
+      </c>
+      <c r="B88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H88" t="s">
+        <v>24</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8001</v>
+      </c>
+      <c r="K88" t="s">
+        <v>24</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+      <c r="S88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>131954108</v>
+      </c>
+      <c r="B89" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G89" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H89" t="s">
+        <v>24</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8001</v>
+      </c>
+      <c r="K89" t="s">
+        <v>24</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+      <c r="S89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>131954110</v>
+      </c>
+      <c r="B90" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G90" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H90" t="s">
+        <v>24</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8001</v>
+      </c>
+      <c r="K90" t="s">
+        <v>24</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+      <c r="S90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>131954122</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G91" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H91" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8001</v>
+      </c>
+      <c r="K91" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+      <c r="S91" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>131954141</v>
+      </c>
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G92" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8001</v>
+      </c>
+      <c r="K92" t="s">
+        <v>24</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+      <c r="S92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>131954163</v>
+      </c>
+      <c r="B93" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G93" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H93" t="s">
+        <v>24</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8001</v>
+      </c>
+      <c r="K93" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+      <c r="S93" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>131954171</v>
+      </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G94" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H94" t="s">
+        <v>24</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8001</v>
+      </c>
+      <c r="K94" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+      <c r="S94" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>131954190</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G95" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H95" t="s">
+        <v>24</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8001</v>
+      </c>
+      <c r="K95" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+      <c r="S95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>131954192</v>
+      </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96">
+        <v>2013</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G96" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H96" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8001</v>
+      </c>
+      <c r="K96" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+      <c r="S96" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>131954237</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97">
+        <v>2013</v>
+      </c>
+      <c r="F97" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H97" t="s">
+        <v>24</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8001</v>
+      </c>
+      <c r="K97" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+      <c r="S97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>131954249</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98">
+        <v>1211</v>
+      </c>
+      <c r="F98" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G98" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H98" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8001</v>
+      </c>
+      <c r="K98" t="s">
+        <v>24</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+      <c r="S98" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>131954251</v>
+      </c>
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99">
+        <v>1211</v>
+      </c>
+      <c r="F99" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G99" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H99" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8001</v>
+      </c>
+      <c r="K99" t="s">
+        <v>24</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+      <c r="S99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>131954254</v>
+      </c>
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100">
+        <v>2013</v>
+      </c>
+      <c r="F100" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G100" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H100" t="s">
+        <v>24</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8001</v>
+      </c>
+      <c r="K100" t="s">
+        <v>24</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+      <c r="S100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>131954255</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101">
+        <v>1211</v>
+      </c>
+      <c r="F101" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G101" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H101" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8001</v>
+      </c>
+      <c r="K101" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+      <c r="S101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>131954261</v>
+      </c>
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102">
+        <v>1211</v>
+      </c>
+      <c r="F102" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G102" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H102" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8001</v>
+      </c>
+      <c r="K102" t="s">
+        <v>24</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+      <c r="S102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>131954273</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103">
+        <v>1211</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G103" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H103" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8001</v>
+      </c>
+      <c r="K103" t="s">
+        <v>24</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+      <c r="S103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>131954282</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104">
+        <v>1211</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G104" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H104" t="s">
+        <v>24</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8001</v>
+      </c>
+      <c r="K104" t="s">
+        <v>24</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+      <c r="S104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>131954285</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105">
+        <v>1211</v>
+      </c>
+      <c r="F105" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G105" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H105" t="s">
+        <v>24</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8001</v>
+      </c>
+      <c r="K105" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+      <c r="S105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>131954302</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106">
+        <v>2013</v>
+      </c>
+      <c r="F106" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G106" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H106" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8001</v>
+      </c>
+      <c r="K106" t="s">
+        <v>24</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+      <c r="S106" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>131954304</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107">
+        <v>1211</v>
+      </c>
+      <c r="F107" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G107" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H107" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8001</v>
+      </c>
+      <c r="K107" t="s">
+        <v>24</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+      <c r="S107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>131954323</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108">
+        <v>1211</v>
+      </c>
+      <c r="F108" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G108" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H108" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8001</v>
+      </c>
+      <c r="K108" t="s">
+        <v>24</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+      <c r="S108" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>131954327</v>
+      </c>
+      <c r="B109" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s">
+        <v>24</v>
+      </c>
+      <c r="D109" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109">
+        <v>1211</v>
+      </c>
+      <c r="F109" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G109" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H109" t="s">
+        <v>24</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8001</v>
+      </c>
+      <c r="K109" t="s">
+        <v>24</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+      <c r="S109" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>131954329</v>
+      </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110">
+        <v>1211</v>
+      </c>
+      <c r="F110" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G110" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H110" t="s">
+        <v>24</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8001</v>
+      </c>
+      <c r="K110" t="s">
+        <v>24</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+      <c r="S110" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>131954340</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111">
+        <v>1211</v>
+      </c>
+      <c r="F111" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G111" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H111" t="s">
+        <v>24</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8001</v>
+      </c>
+      <c r="K111" t="s">
+        <v>24</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+      <c r="S111" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>131954341</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112">
+        <v>1211</v>
+      </c>
+      <c r="F112" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G112" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H112" t="s">
+        <v>24</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8001</v>
+      </c>
+      <c r="K112" t="s">
+        <v>24</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+      <c r="S112" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>131954346</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113">
+        <v>2013</v>
+      </c>
+      <c r="F113" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G113" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H113" t="s">
+        <v>24</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8001</v>
+      </c>
+      <c r="K113" t="s">
+        <v>24</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+      <c r="S113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>131954357</v>
+      </c>
+      <c r="B114" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" t="s">
+        <v>24</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114">
+        <v>2013</v>
+      </c>
+      <c r="F114" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G114" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H114" t="s">
+        <v>24</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8001</v>
+      </c>
+      <c r="K114" t="s">
+        <v>24</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+      <c r="S114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>131954362</v>
+      </c>
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115">
+        <v>1211</v>
+      </c>
+      <c r="F115" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G115" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H115" t="s">
+        <v>24</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8001</v>
+      </c>
+      <c r="K115" t="s">
+        <v>24</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+      <c r="S115" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>131954363</v>
+      </c>
+      <c r="B116" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116">
+        <v>2013</v>
+      </c>
+      <c r="F116" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G116" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H116" t="s">
+        <v>24</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8001</v>
+      </c>
+      <c r="K116" t="s">
+        <v>24</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+      <c r="S116" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>131954387</v>
+      </c>
+      <c r="B117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
+        <v>24</v>
+      </c>
+      <c r="D117" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117">
+        <v>1211</v>
+      </c>
+      <c r="F117" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G117" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H117" t="s">
+        <v>24</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8001</v>
+      </c>
+      <c r="K117" t="s">
+        <v>24</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+      <c r="S117" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>131954395</v>
+      </c>
+      <c r="B118" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118">
+        <v>1211</v>
+      </c>
+      <c r="F118" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G118" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H118" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8001</v>
+      </c>
+      <c r="K118" t="s">
+        <v>24</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+      <c r="S118" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>131954428</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119">
+        <v>1211</v>
+      </c>
+      <c r="F119" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G119" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H119" t="s">
+        <v>24</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8001</v>
+      </c>
+      <c r="K119" t="s">
+        <v>24</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+      <c r="S119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>131954437</v>
+      </c>
+      <c r="B120" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" t="s">
+        <v>24</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120">
+        <v>1211</v>
+      </c>
+      <c r="F120" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G120" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H120" t="s">
+        <v>24</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8001</v>
+      </c>
+      <c r="K120" t="s">
+        <v>24</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+      <c r="S120" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>131954439</v>
+      </c>
+      <c r="B121" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" t="s">
+        <v>24</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121">
+        <v>1211</v>
+      </c>
+      <c r="F121" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G121" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H121" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8001</v>
+      </c>
+      <c r="K121" t="s">
+        <v>24</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+      <c r="S121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>131954452</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122">
+        <v>1211</v>
+      </c>
+      <c r="F122" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G122" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H122" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8001</v>
+      </c>
+      <c r="K122" t="s">
+        <v>24</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+      <c r="S122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>131954472</v>
+      </c>
+      <c r="B123" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123">
+        <v>1211</v>
+      </c>
+      <c r="F123" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G123" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H123" t="s">
+        <v>24</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8001</v>
+      </c>
+      <c r="K123" t="s">
+        <v>24</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+      <c r="S123" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>131923044</v>
+      </c>
+      <c r="B124" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124">
+        <v>2013</v>
+      </c>
+      <c r="F124" s="1">
+        <v>45743</v>
+      </c>
+      <c r="G124" s="1">
+        <v>45743</v>
+      </c>
+      <c r="H124" t="s">
+        <v>24</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8001</v>
+      </c>
+      <c r="K124" t="s">
+        <v>24</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+      <c r="S124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>131953158</v>
+      </c>
+      <c r="B125" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" t="s">
+        <v>24</v>
+      </c>
+      <c r="D125" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125">
+        <v>1211</v>
+      </c>
+      <c r="F125" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G125" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H125" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8001</v>
+      </c>
+      <c r="K125" t="s">
+        <v>24</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+      <c r="S125" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>131953418</v>
+      </c>
+      <c r="B126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" t="s">
+        <v>24</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126">
+        <v>1211</v>
+      </c>
+      <c r="F126" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G126" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H126" t="s">
+        <v>24</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8001</v>
+      </c>
+      <c r="K126" t="s">
+        <v>24</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+      <c r="S126" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>131953419</v>
+      </c>
+      <c r="B127" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" t="s">
+        <v>24</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127">
+        <v>1211</v>
+      </c>
+      <c r="F127" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G127" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H127" t="s">
+        <v>24</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8001</v>
+      </c>
+      <c r="K127" t="s">
+        <v>24</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+      <c r="S127" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>131953594</v>
+      </c>
+      <c r="B128" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" t="s">
+        <v>24</v>
+      </c>
+      <c r="D128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128">
+        <v>2024</v>
+      </c>
+      <c r="F128" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G128" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H128" t="s">
+        <v>24</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8001</v>
+      </c>
+      <c r="K128" t="s">
+        <v>24</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+      <c r="S128" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>131953603</v>
+      </c>
+      <c r="B129" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" t="s">
+        <v>24</v>
+      </c>
+      <c r="D129" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129">
+        <v>1211</v>
+      </c>
+      <c r="F129" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G129" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H129" t="s">
+        <v>24</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8001</v>
+      </c>
+      <c r="K129" t="s">
+        <v>24</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+      <c r="S129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>131953699</v>
+      </c>
+      <c r="B130" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" t="s">
+        <v>24</v>
+      </c>
+      <c r="D130" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130">
+        <v>1211</v>
+      </c>
+      <c r="F130" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G130" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H130" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8001</v>
+      </c>
+      <c r="K130" t="s">
+        <v>24</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+      <c r="S130" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>131953708</v>
+      </c>
+      <c r="B131" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" t="s">
+        <v>24</v>
+      </c>
+      <c r="D131" t="s">
+        <v>24</v>
+      </c>
+      <c r="E131">
+        <v>1212</v>
+      </c>
+      <c r="F131" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G131" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H131" t="s">
+        <v>24</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8001</v>
+      </c>
+      <c r="K131" t="s">
+        <v>24</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+      <c r="S131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131953711</v>
+      </c>
+      <c r="B132" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" t="s">
+        <v>24</v>
+      </c>
+      <c r="D132" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132">
+        <v>2013</v>
+      </c>
+      <c r="F132" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G132" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H132" t="s">
+        <v>24</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8001</v>
+      </c>
+      <c r="K132" t="s">
+        <v>24</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+      <c r="S132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>131954057</v>
+      </c>
+      <c r="B133" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133" t="s">
+        <v>24</v>
+      </c>
+      <c r="E133">
+        <v>2013</v>
+      </c>
+      <c r="F133" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G133" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H133" t="s">
+        <v>24</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8001</v>
+      </c>
+      <c r="K133" t="s">
+        <v>24</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+      <c r="S133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>131954084</v>
+      </c>
+      <c r="B134" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" t="s">
+        <v>24</v>
+      </c>
+      <c r="D134" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134">
+        <v>2013</v>
+      </c>
+      <c r="F134" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G134" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H134" t="s">
+        <v>24</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8001</v>
+      </c>
+      <c r="K134" t="s">
+        <v>24</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+      <c r="S134" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>131954110</v>
+      </c>
+      <c r="B135" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" t="s">
+        <v>24</v>
+      </c>
+      <c r="D135" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135">
+        <v>1211</v>
+      </c>
+      <c r="F135" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G135" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H135" t="s">
+        <v>24</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8001</v>
+      </c>
+      <c r="K135" t="s">
+        <v>24</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+      <c r="S135" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>131954141</v>
+      </c>
+      <c r="B136" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" t="s">
+        <v>24</v>
+      </c>
+      <c r="D136" t="s">
+        <v>24</v>
+      </c>
+      <c r="E136">
+        <v>1211</v>
+      </c>
+      <c r="F136" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G136" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H136" t="s">
+        <v>24</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8001</v>
+      </c>
+      <c r="K136" t="s">
+        <v>24</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+      <c r="S136" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>131954171</v>
+      </c>
+      <c r="B137" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" t="s">
+        <v>24</v>
+      </c>
+      <c r="D137" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137">
+        <v>1211</v>
+      </c>
+      <c r="F137" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G137" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H137" t="s">
+        <v>24</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8001</v>
+      </c>
+      <c r="K137" t="s">
+        <v>24</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+      <c r="S137" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>131954192</v>
+      </c>
+      <c r="B138" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" t="s">
+        <v>24</v>
+      </c>
+      <c r="D138" t="s">
+        <v>24</v>
+      </c>
+      <c r="E138">
+        <v>2013</v>
+      </c>
+      <c r="F138" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G138" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H138" t="s">
+        <v>24</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8001</v>
+      </c>
+      <c r="K138" t="s">
+        <v>24</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+      <c r="S138" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>131954254</v>
+      </c>
+      <c r="B139" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" t="s">
+        <v>24</v>
+      </c>
+      <c r="D139" t="s">
+        <v>24</v>
+      </c>
+      <c r="E139">
+        <v>2013</v>
+      </c>
+      <c r="F139" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G139" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H139" t="s">
+        <v>24</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8001</v>
+      </c>
+      <c r="K139" t="s">
+        <v>24</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+      <c r="S139" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>131954302</v>
+      </c>
+      <c r="B140" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" t="s">
+        <v>24</v>
+      </c>
+      <c r="D140" t="s">
+        <v>24</v>
+      </c>
+      <c r="E140">
+        <v>2013</v>
+      </c>
+      <c r="F140" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G140" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H140" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8001</v>
+      </c>
+      <c r="K140" t="s">
+        <v>24</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+      <c r="S140" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>131954340</v>
+      </c>
+      <c r="B141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" t="s">
+        <v>24</v>
+      </c>
+      <c r="D141" t="s">
+        <v>24</v>
+      </c>
+      <c r="E141">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G141" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H141" t="s">
+        <v>24</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8001</v>
+      </c>
+      <c r="K141" t="s">
+        <v>24</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+      <c r="S141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>131954346</v>
+      </c>
+      <c r="B142" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" t="s">
+        <v>24</v>
+      </c>
+      <c r="D142" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142">
+        <v>2013</v>
+      </c>
+      <c r="F142" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G142" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H142" t="s">
+        <v>24</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8001</v>
+      </c>
+      <c r="K142" t="s">
+        <v>24</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+      <c r="S142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>131954363</v>
+      </c>
+      <c r="B143" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" t="s">
+        <v>24</v>
+      </c>
+      <c r="D143" t="s">
+        <v>24</v>
+      </c>
+      <c r="E143">
+        <v>2013</v>
+      </c>
+      <c r="F143" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G143" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H143" t="s">
+        <v>24</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8001</v>
+      </c>
+      <c r="K143" t="s">
+        <v>24</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+      <c r="S143" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>131954387</v>
+      </c>
+      <c r="B144" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" t="s">
+        <v>24</v>
+      </c>
+      <c r="E144">
+        <v>1211</v>
+      </c>
+      <c r="F144" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G144" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H144" t="s">
+        <v>24</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8001</v>
+      </c>
+      <c r="K144" t="s">
+        <v>24</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+      <c r="S144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>131954437</v>
+      </c>
+      <c r="B145" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" t="s">
+        <v>24</v>
+      </c>
+      <c r="D145" t="s">
+        <v>24</v>
+      </c>
+      <c r="E145">
+        <v>1211</v>
+      </c>
+      <c r="F145" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G145" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H145" t="s">
+        <v>24</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8001</v>
+      </c>
+      <c r="K145" t="s">
+        <v>24</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+      <c r="S145" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>131954472</v>
+      </c>
+      <c r="B146" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" t="s">
+        <v>24</v>
+      </c>
+      <c r="D146" t="s">
+        <v>24</v>
+      </c>
+      <c r="E146">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="1">
+        <v>45746</v>
+      </c>
+      <c r="G146" s="1">
+        <v>45746</v>
+      </c>
+      <c r="H146" t="s">
+        <v>24</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8001</v>
+      </c>
+      <c r="K146" t="s">
+        <v>24</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+      <c r="S146" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>131884092</v>
+      </c>
+      <c r="B147" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147" t="s">
+        <v>24</v>
+      </c>
+      <c r="E147">
+        <v>1211</v>
+      </c>
+      <c r="F147" s="1">
+        <v>45741</v>
+      </c>
+      <c r="G147" s="1">
+        <v>45741</v>
+      </c>
+      <c r="H147" t="s">
+        <v>24</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>715</v>
+      </c>
+      <c r="K147" t="s">
+        <v>24</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+      <c r="S147" t="s">
         <v>24</v>
       </c>
     </row>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -10,14 +10,14 @@
     <sheet name="Fiel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$4</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$20</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Renovação Externa</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>123058958</v>
+        <v>132228684</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -506,10 +509,10 @@
         <v>1211</v>
       </c>
       <c r="F2" s="12">
-        <v>44993</v>
+        <v>45767</v>
       </c>
       <c r="G2" s="12">
-        <v>44995</v>
+        <v>45767</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -518,7 +521,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
@@ -547,7 +550,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>132128714</v>
+        <v>123058958</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -559,13 +562,13 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="12">
-        <v>45764</v>
+        <v>44993</v>
       </c>
       <c r="G3" s="12">
-        <v>45764</v>
+        <v>44995</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -574,7 +577,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="K3" t="s">
         <v>19</v>
@@ -603,7 +606,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>128661660</v>
+        <v>132247566</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -615,13 +618,13 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="12">
-        <v>45764</v>
+        <v>45770</v>
       </c>
       <c r="G4" s="12">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -630,7 +633,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
@@ -653,8 +656,955 @@
       <c r="Q4">
         <v>61</v>
       </c>
+      <c r="R4">
+        <v>3</v>
+      </c>
       <c r="S4" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>132247655</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>2013</v>
+      </c>
+      <c r="F5" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G5" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>42</v>
+      </c>
+      <c r="J5">
+        <v>718</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>61</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="S5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>132247741</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>2013</v>
+      </c>
+      <c r="F6" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G6" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>42</v>
+      </c>
+      <c r="J6">
+        <v>718</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>61</v>
+      </c>
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>132248446</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>2013</v>
+      </c>
+      <c r="F7" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G7" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7">
+        <v>42</v>
+      </c>
+      <c r="J7">
+        <v>718</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>61</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>132248508</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>2013</v>
+      </c>
+      <c r="F8" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G8" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>42</v>
+      </c>
+      <c r="J8">
+        <v>718</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>61</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
+      <c r="S8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>132249845</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>2013</v>
+      </c>
+      <c r="F9" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G9" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9">
+        <v>42</v>
+      </c>
+      <c r="J9">
+        <v>718</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>61</v>
+      </c>
+      <c r="R9">
+        <v>3</v>
+      </c>
+      <c r="S9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>132250516</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>2013</v>
+      </c>
+      <c r="F10" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G10" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>718</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>61</v>
+      </c>
+      <c r="R10">
+        <v>3</v>
+      </c>
+      <c r="S10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>132250568</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>2013</v>
+      </c>
+      <c r="F11" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G11" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>718</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>61</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>132250668</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12">
+        <v>2013</v>
+      </c>
+      <c r="F12" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G12" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12">
+        <v>42</v>
+      </c>
+      <c r="J12">
+        <v>718</v>
+      </c>
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>61</v>
+      </c>
+      <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="S12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>132250925</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13">
+        <v>2013</v>
+      </c>
+      <c r="F13" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G13" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>718</v>
+      </c>
+      <c r="K13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>61</v>
+      </c>
+      <c r="R13">
+        <v>3</v>
+      </c>
+      <c r="S13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>132251780</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14">
+        <v>2013</v>
+      </c>
+      <c r="F14" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G14" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14">
+        <v>42</v>
+      </c>
+      <c r="J14">
+        <v>718</v>
+      </c>
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>61</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>132254914</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15">
+        <v>2013</v>
+      </c>
+      <c r="F15" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G15" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>718</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>61</v>
+      </c>
+      <c r="R15">
+        <v>3</v>
+      </c>
+      <c r="S15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>132255446</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16">
+        <v>2013</v>
+      </c>
+      <c r="F16" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G16" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16">
+        <v>42</v>
+      </c>
+      <c r="J16">
+        <v>718</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>61</v>
+      </c>
+      <c r="R16">
+        <v>3</v>
+      </c>
+      <c r="S16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>132257741</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17">
+        <v>2013</v>
+      </c>
+      <c r="F17" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G17" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17">
+        <v>42</v>
+      </c>
+      <c r="J17">
+        <v>718</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>61</v>
+      </c>
+      <c r="R17">
+        <v>3</v>
+      </c>
+      <c r="S17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>132258376</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18">
+        <v>2013</v>
+      </c>
+      <c r="F18" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G18" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>718</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>61</v>
+      </c>
+      <c r="R18">
+        <v>3</v>
+      </c>
+      <c r="S18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>132259581</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19">
+        <v>2013</v>
+      </c>
+      <c r="F19" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G19" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19">
+        <v>42</v>
+      </c>
+      <c r="J19">
+        <v>718</v>
+      </c>
+      <c r="K19" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>61</v>
+      </c>
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>132260149</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20">
+        <v>2013</v>
+      </c>
+      <c r="F20" s="12">
+        <v>45770</v>
+      </c>
+      <c r="G20" s="12">
+        <v>45770</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20">
+        <v>42</v>
+      </c>
+      <c r="J20">
+        <v>718</v>
+      </c>
+      <c r="K20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>61</v>
+      </c>
+      <c r="R20">
+        <v>3</v>
+      </c>
+      <c r="S20" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Fiel.XLSX
+++ b/Treinamento/Fiel.XLSX
@@ -10,14 +10,14 @@
     <sheet name="Fiel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fiel">'Fiel'!$A$1:$S$20</definedName>
+    <definedName name="Fiel">'Fiel'!$A$1:$S$19</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>NR_PROPOSTA</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>Renovação Externa</t>
   </si>
 </sst>
 </file>
@@ -494,7 +491,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>132228684</v>
+        <v>132239318</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -506,13 +503,13 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F2" s="12">
-        <v>45767</v>
+        <v>45769</v>
       </c>
       <c r="G2" s="12">
-        <v>45767</v>
+        <v>45770</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -521,7 +518,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>1735</v>
+        <v>8013</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
@@ -550,7 +547,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>123058958</v>
+        <v>132240900</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -562,13 +559,13 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F3" s="12">
-        <v>44993</v>
+        <v>45769</v>
       </c>
       <c r="G3" s="12">
-        <v>44995</v>
+        <v>45769</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -577,7 +574,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="K3" t="s">
         <v>19</v>
@@ -606,7 +603,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>132247566</v>
+        <v>132242504</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -618,13 +615,13 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F4" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G4" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -633,7 +630,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
@@ -656,16 +653,13 @@
       <c r="Q4">
         <v>61</v>
       </c>
-      <c r="R4">
-        <v>3</v>
-      </c>
       <c r="S4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>132247655</v>
+        <v>132244800</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -677,13 +671,13 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F5" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G5" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -692,7 +686,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K5" t="s">
         <v>19</v>
@@ -715,16 +709,13 @@
       <c r="Q5">
         <v>61</v>
       </c>
-      <c r="R5">
-        <v>3</v>
-      </c>
       <c r="S5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>132247741</v>
+        <v>132231382</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -736,13 +727,13 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F6" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G6" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -751,7 +742,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K6" t="s">
         <v>19</v>
@@ -774,16 +765,13 @@
       <c r="Q6">
         <v>61</v>
       </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
       <c r="S6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>132248446</v>
+        <v>132233062</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -795,13 +783,13 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F7" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G7" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -810,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K7" t="s">
         <v>19</v>
@@ -833,16 +821,13 @@
       <c r="Q7">
         <v>61</v>
       </c>
-      <c r="R7">
-        <v>3</v>
-      </c>
       <c r="S7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>132248508</v>
+        <v>132234617</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -854,13 +839,13 @@
         <v>19</v>
       </c>
       <c r="E8">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F8" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G8" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -869,7 +854,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K8" t="s">
         <v>19</v>
@@ -892,16 +877,13 @@
       <c r="Q8">
         <v>61</v>
       </c>
-      <c r="R8">
-        <v>3</v>
-      </c>
       <c r="S8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>132249845</v>
+        <v>132238339</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -913,13 +895,13 @@
         <v>19</v>
       </c>
       <c r="E9">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F9" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G9" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -928,7 +910,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K9" t="s">
         <v>19</v>
@@ -951,16 +933,13 @@
       <c r="Q9">
         <v>61</v>
       </c>
-      <c r="R9">
-        <v>3</v>
-      </c>
       <c r="S9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>132250516</v>
+        <v>132240838</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -972,13 +951,13 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>2013</v>
+        <v>601</v>
       </c>
       <c r="F10" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G10" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -987,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>718</v>
+        <v>8004</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
@@ -1010,16 +989,13 @@
       <c r="Q10">
         <v>61</v>
       </c>
-      <c r="R10">
-        <v>3</v>
-      </c>
       <c r="S10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>132250568</v>
+        <v>123058958</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1031,13 +1007,13 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="12">
-        <v>45770</v>
+        <v>44993</v>
       </c>
       <c r="G11" s="12">
-        <v>45770</v>
+        <v>44995</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -1046,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
@@ -1069,16 +1045,13 @@
       <c r="Q11">
         <v>61</v>
       </c>
-      <c r="R11">
-        <v>3</v>
-      </c>
       <c r="S11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>132250668</v>
+        <v>132230568</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -1090,13 +1063,13 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F12" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G12" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -1105,7 +1078,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K12" t="s">
         <v>19</v>
@@ -1128,16 +1101,13 @@
       <c r="Q12">
         <v>61</v>
       </c>
-      <c r="R12">
-        <v>3</v>
-      </c>
       <c r="S12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>132250925</v>
+        <v>132240598</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -1149,13 +1119,13 @@
         <v>19</v>
       </c>
       <c r="E13">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F13" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G13" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -1164,7 +1134,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K13" t="s">
         <v>19</v>
@@ -1187,16 +1157,13 @@
       <c r="Q13">
         <v>61</v>
       </c>
-      <c r="R13">
-        <v>3</v>
-      </c>
       <c r="S13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>132251780</v>
+        <v>132242423</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -1208,13 +1175,13 @@
         <v>19</v>
       </c>
       <c r="E14">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F14" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G14" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -1223,7 +1190,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K14" t="s">
         <v>19</v>
@@ -1246,16 +1213,13 @@
       <c r="Q14">
         <v>61</v>
       </c>
-      <c r="R14">
-        <v>3</v>
-      </c>
       <c r="S14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>132254914</v>
+        <v>132244917</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -1267,13 +1231,13 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F15" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G15" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -1282,7 +1246,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K15" t="s">
         <v>19</v>
@@ -1305,16 +1269,13 @@
       <c r="Q15">
         <v>61</v>
       </c>
-      <c r="R15">
-        <v>3</v>
-      </c>
       <c r="S15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>132255446</v>
+        <v>132230568</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -1326,13 +1287,13 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F16" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G16" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -1341,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K16" t="s">
         <v>19</v>
@@ -1364,16 +1325,13 @@
       <c r="Q16">
         <v>61</v>
       </c>
-      <c r="R16">
-        <v>3</v>
-      </c>
       <c r="S16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>132257741</v>
+        <v>132240598</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -1385,13 +1343,13 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F17" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G17" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -1400,7 +1358,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K17" t="s">
         <v>19</v>
@@ -1423,16 +1381,13 @@
       <c r="Q17">
         <v>61</v>
       </c>
-      <c r="R17">
-        <v>3</v>
-      </c>
       <c r="S17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>132258376</v>
+        <v>132242423</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
@@ -1444,13 +1399,13 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F18" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G18" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -1459,7 +1414,7 @@
         <v>42</v>
       </c>
       <c r="J18">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K18" t="s">
         <v>19</v>
@@ -1482,16 +1437,13 @@
       <c r="Q18">
         <v>61</v>
       </c>
-      <c r="R18">
-        <v>3</v>
-      </c>
       <c r="S18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>132259581</v>
+        <v>132244917</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
@@ -1503,13 +1455,13 @@
         <v>19</v>
       </c>
       <c r="E19">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F19" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G19" s="12">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -1518,7 +1470,7 @@
         <v>42</v>
       </c>
       <c r="J19">
-        <v>718</v>
+        <v>8001</v>
       </c>
       <c r="K19" t="s">
         <v>19</v>
@@ -1541,70 +1493,8 @@
       <c r="Q19">
         <v>61</v>
       </c>
-      <c r="R19">
-        <v>3</v>
-      </c>
       <c r="S19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>132260149</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20">
-        <v>2013</v>
-      </c>
-      <c r="F20" s="12">
-        <v>45770</v>
-      </c>
-      <c r="G20" s="12">
-        <v>45770</v>
-      </c>
-      <c r="H20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20">
-        <v>42</v>
-      </c>
-      <c r="J20">
-        <v>718</v>
-      </c>
-      <c r="K20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>61</v>
-      </c>
-      <c r="R20">
-        <v>3</v>
-      </c>
-      <c r="S20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
